--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -735,10 +735,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -771,10 +771,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -807,10 +807,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -843,10 +843,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -879,10 +879,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -915,10 +915,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -951,10 +951,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -987,10 +987,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1023,10 +1023,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1059,10 +1059,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD62"/>
+  <dimension ref="A1:AD124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1577,45 +1577,65 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="D5" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C5)</f>
+        <v/>
+      </c>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="G5" s="7">
+        <f>ROUND(MAX(0,MIN(100,(1-E5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>MIN(1,(G5-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
+      <c r="K5" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M5" s="7">
+        <f>MAX(0,(L5-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N5" s="7">
+        <f>$B$2+H5+M5</f>
+        <v/>
+      </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr"/>
       <c r="V5" s="7" t="n">
-        <v>5519</v>
+        <v>1</v>
       </c>
       <c r="X5" s="7" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="Y5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z5" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1642,41 +1662,61 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="D6" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C6)</f>
+        <v/>
+      </c>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="G6" s="4">
+        <f>ROUND(MAX(0,MIN(100,(1-E6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>MIN(1,(G6-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="K6" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>MAX(0,(L6-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>$B$2+H6+M6</f>
+        <v/>
+      </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr"/>
       <c r="V6" s="4" t="n">
-        <v>5569</v>
+        <v>1</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB6" s="4" t="n">
@@ -1707,41 +1747,61 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
+      <c r="D7" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C7)</f>
+        <v/>
+      </c>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="G7" s="7">
+        <f>ROUND(MAX(0,MIN(100,(1-E7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>MIN(1,(G7-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
+      <c r="K7" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7">
+        <f>MAX(0,(L7-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N7" s="7">
+        <f>$B$2+H7+M7</f>
+        <v/>
+      </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr"/>
       <c r="V7" s="7" t="n">
-        <v>5621</v>
+        <v>1</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="Y7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z7" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB7" s="7" t="n">
@@ -1790,23 +1850,23 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V8" s="4" t="n">
-        <v>15184</v>
+        <v>5519</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB8" s="4" t="n">
@@ -1849,23 +1909,23 @@
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>5569</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>15708</v>
-      </c>
-      <c r="X9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB9" s="7" t="n">
@@ -1916,27 +1976,27 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>5621</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V10" s="4" t="n">
-        <v>15056</v>
-      </c>
-      <c r="X10" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -1970,19 +2030,19 @@
       <c r="N11" s="7" t="n"/>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V11" s="7" t="n">
-        <v>87207</v>
+        <v>5557</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -1991,11 +2051,11 @@
       </c>
       <c r="Z11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2029,32 +2089,32 @@
       <c r="N12" s="4" t="n"/>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>86030</v>
+        <v>5196</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2088,32 +2148,32 @@
       <c r="N13" s="7" t="n"/>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V13" s="7" t="n">
-        <v>82667</v>
+        <v>5203</v>
       </c>
       <c r="X13" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z13" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2152,27 +2212,27 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>721</v>
+        <v>15184</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2211,27 +2271,27 @@
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V15" s="7" t="n">
-        <v>729</v>
+        <v>15708</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z15" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2270,23 +2330,23 @@
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>717</v>
+        <v>15056</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB16" s="4" t="n">
@@ -2324,28 +2384,28 @@
       <c r="N17" s="7" t="n"/>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V17" s="7" t="n">
-        <v>50559</v>
+        <v>15493</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB17" s="7" t="n">
@@ -2383,28 +2443,28 @@
       <c r="N18" s="4" t="n"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>51501</v>
+        <v>14553</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB18" s="4" t="n">
@@ -2442,28 +2502,28 @@
       <c r="N19" s="7" t="n"/>
       <c r="T19" s="7" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="n">
+        <v>14491</v>
+      </c>
+      <c r="X19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>51715</v>
-      </c>
-      <c r="X19" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="Z19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB19" s="7" t="n">
@@ -2506,27 +2566,27 @@
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>11599</v>
+        <v>87207</v>
       </c>
       <c r="X20" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB20" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB20" s="4" t="n">
-        <v>327</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2565,23 +2625,23 @@
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V21" s="7" t="n">
-        <v>11522</v>
+        <v>86030</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB21" s="7" t="n">
@@ -2624,27 +2684,27 @@
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>11614</v>
+        <v>82667</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2678,28 +2738,28 @@
       <c r="N23" s="7" t="n"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V23" s="7" t="n">
-        <v>26509</v>
+        <v>82796</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB23" s="7" t="n">
@@ -2737,28 +2797,28 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>26876</v>
+        <v>80792</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB24" s="4" t="n">
@@ -2796,32 +2856,32 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>27154</v>
+        <v>80181</v>
       </c>
       <c r="X25" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB25" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB25" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2860,27 +2920,27 @@
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>721</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V26" s="4" t="n">
-        <v>17949</v>
-      </c>
-      <c r="X26" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
       <c r="AB26" s="4" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2919,27 +2979,27 @@
       </c>
       <c r="U27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>17549</v>
+        <v>729</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -2978,23 +3038,23 @@
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>17646</v>
+        <v>717</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB28" s="4" t="n">
@@ -3032,28 +3092,28 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB29" s="7" t="n">
@@ -3091,19 +3151,19 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>763</v>
+        <v>696</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -3112,7 +3172,7 @@
       </c>
       <c r="Z30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB30" s="4" t="n">
@@ -3150,32 +3210,32 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="n">
+        <v>723</v>
+      </c>
+      <c r="X31" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y31" s="7" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X31" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="Z31" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3223,27 +3283,27 @@
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2142</v>
+        <v>50559</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3258,7 +3318,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D4)</f>
+        <f>AVERAGE(D2:D7)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3268,7 +3328,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H4)</f>
+        <f>AVERAGE(H2:H7)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3296,23 +3356,23 @@
       </c>
       <c r="U33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>2408</v>
+        <v>51501</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB33" s="7" t="n">
@@ -3337,108 +3397,148 @@
       </c>
       <c r="U34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2141</v>
+        <v>51715</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB34" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="T35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="n">
+        <v>50240</v>
+      </c>
+      <c r="X35" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>48948</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z36" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB36" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AD36" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="T35" s="7" t="n"/>
-      <c r="U35" s="7" t="n"/>
-      <c r="V35" s="7" t="n"/>
-      <c r="X35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB35" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AC35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AD35" s="7" t="inlineStr">
+    <row r="37">
+      <c r="T37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U37" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="T36" s="4" t="n"/>
-      <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n"/>
-      <c r="X36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AD36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" s="7" t="n"/>
-      <c r="U37" s="7" t="n"/>
-      <c r="V37" s="7" t="n"/>
-      <c r="X37" s="7" t="n"/>
-      <c r="Y37" s="7" t="n"/>
-      <c r="Z37" s="7" t="n"/>
+      <c r="V37" s="7" t="n">
+        <v>48922</v>
+      </c>
+      <c r="X37" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z37" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
       <c r="AB37" s="7" t="n">
         <v>10</v>
       </c>
@@ -3454,12 +3554,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="n"/>
-      <c r="U38" s="4" t="n"/>
-      <c r="V38" s="4" t="n"/>
-      <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="4" t="n"/>
-      <c r="Z38" s="4" t="n"/>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB38" s="4" t="n">
         <v>1</v>
       </c>
@@ -3475,12 +3595,32 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="n"/>
-      <c r="U39" s="7" t="n"/>
-      <c r="V39" s="7" t="n"/>
-      <c r="X39" s="7" t="n"/>
-      <c r="Y39" s="7" t="n"/>
-      <c r="Z39" s="7" t="n"/>
+      <c r="T39" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U39" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+        </is>
+      </c>
+      <c r="V39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y39" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z39" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB39" s="7" t="n">
         <v>1</v>
       </c>
@@ -3496,12 +3636,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="n"/>
-      <c r="U40" s="4" t="n"/>
-      <c r="V40" s="4" t="n"/>
-      <c r="X40" s="4" t="n"/>
-      <c r="Y40" s="4" t="n"/>
-      <c r="Z40" s="4" t="n"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>11599</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z40" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB40" s="4" t="n">
         <v>15</v>
       </c>
@@ -3517,12 +3677,32 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="n"/>
-      <c r="U41" s="7" t="n"/>
-      <c r="V41" s="7" t="n"/>
-      <c r="X41" s="7" t="n"/>
-      <c r="Y41" s="7" t="n"/>
-      <c r="Z41" s="7" t="n"/>
+      <c r="T41" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U41" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V41" s="7" t="n">
+        <v>11522</v>
+      </c>
+      <c r="X41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z41" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB41" s="7" t="n">
         <v>4</v>
       </c>
@@ -3538,75 +3718,155 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="n"/>
-      <c r="U42" s="4" t="n"/>
-      <c r="V42" s="4" t="n"/>
-      <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="4" t="n"/>
-      <c r="Z42" s="4" t="n"/>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>11614</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z42" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB42" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD42" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="T43" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U43" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V43" s="7" t="n">
+        <v>11098</v>
+      </c>
+      <c r="X43" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y43" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z43" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB43" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr">
+      <c r="AC43" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AD43" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="T43" s="7" t="n"/>
-      <c r="U43" s="7" t="n"/>
-      <c r="V43" s="7" t="n"/>
-      <c r="X43" s="7" t="n"/>
-      <c r="Y43" s="7" t="n"/>
-      <c r="Z43" s="7" t="n"/>
-      <c r="AB43" s="7" t="n">
+    <row r="44">
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>11097</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z44" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AC43" s="7" t="inlineStr">
+      <c r="AC44" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD43" s="7" t="inlineStr">
+      <c r="AD44" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="T44" s="4" t="n"/>
-      <c r="U44" s="4" t="n"/>
-      <c r="V44" s="4" t="n"/>
-      <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="4" t="n"/>
-      <c r="Z44" s="4" t="n"/>
-      <c r="AB44" s="4" t="n">
-        <v>276</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="T45" s="7" t="n"/>
-      <c r="U45" s="7" t="n"/>
-      <c r="V45" s="7" t="n"/>
-      <c r="X45" s="7" t="n"/>
-      <c r="Y45" s="7" t="n"/>
-      <c r="Z45" s="7" t="n"/>
+      <c r="T45" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U45" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="n">
+        <v>11410</v>
+      </c>
+      <c r="X45" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y45" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z45" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB45" s="7" t="n">
         <v>21</v>
       </c>
@@ -3622,12 +3882,32 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="n"/>
-      <c r="U46" s="4" t="n"/>
-      <c r="V46" s="4" t="n"/>
-      <c r="X46" s="4" t="n"/>
-      <c r="Y46" s="4" t="n"/>
-      <c r="Z46" s="4" t="n"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>26509</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z46" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB46" s="4" t="n">
         <v>175</v>
       </c>
@@ -3643,62 +3923,122 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="n"/>
-      <c r="U47" s="7" t="n"/>
-      <c r="V47" s="7" t="n"/>
-      <c r="X47" s="7" t="n"/>
-      <c r="Y47" s="7" t="n"/>
-      <c r="Z47" s="7" t="n"/>
+      <c r="T47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U47" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V47" s="7" t="n">
+        <v>26876</v>
+      </c>
+      <c r="X47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z47" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD47" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>27154</v>
+      </c>
+      <c r="X48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z48" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB48" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC47" s="7" t="inlineStr">
+      <c r="AC48" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD47" s="7" t="inlineStr">
+      <c r="AD48" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="T48" s="4" t="n"/>
-      <c r="U48" s="4" t="n"/>
-      <c r="V48" s="4" t="n"/>
-      <c r="X48" s="4" t="n"/>
-      <c r="Y48" s="4" t="n"/>
-      <c r="Z48" s="4" t="n"/>
-      <c r="AB48" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="T49" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U49" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V49" s="7" t="n">
+        <v>26655</v>
+      </c>
+      <c r="X49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z49" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB49" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC49" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="T49" s="7" t="n"/>
-      <c r="U49" s="7" t="n"/>
-      <c r="V49" s="7" t="n"/>
-      <c r="X49" s="7" t="n"/>
-      <c r="Y49" s="7" t="n"/>
-      <c r="Z49" s="7" t="n"/>
-      <c r="AB49" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="AD49" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
@@ -3706,12 +4046,32 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="n"/>
-      <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n"/>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n"/>
-      <c r="Z50" s="4" t="n"/>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>25267</v>
+      </c>
+      <c r="X50" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z50" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB50" s="4" t="n">
         <v>5</v>
       </c>
@@ -3727,12 +4087,32 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="n"/>
-      <c r="U51" s="7" t="n"/>
-      <c r="V51" s="7" t="n"/>
-      <c r="X51" s="7" t="n"/>
-      <c r="Y51" s="7" t="n"/>
-      <c r="Z51" s="7" t="n"/>
+      <c r="T51" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U51" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V51" s="7" t="n">
+        <v>24712</v>
+      </c>
+      <c r="X51" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y51" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z51" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB51" s="7" t="n">
         <v>5</v>
       </c>
@@ -3748,54 +4128,114 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="n"/>
-      <c r="U52" s="4" t="n"/>
-      <c r="V52" s="4" t="n"/>
-      <c r="X52" s="4" t="n"/>
-      <c r="Y52" s="4" t="n"/>
-      <c r="Z52" s="4" t="n"/>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>17949</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z52" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD52" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="T53" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U53" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V53" s="7" t="n">
+        <v>17549</v>
+      </c>
+      <c r="X53" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y53" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z53" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr">
+      <c r="AC53" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD52" s="4" t="inlineStr">
+      <c r="AD53" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="T53" s="7" t="n"/>
-      <c r="U53" s="7" t="n"/>
-      <c r="V53" s="7" t="n"/>
-      <c r="X53" s="7" t="n"/>
-      <c r="Y53" s="7" t="n"/>
-      <c r="Z53" s="7" t="n"/>
-      <c r="AB53" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC53" s="7" t="inlineStr">
+    <row r="54">
+      <c r="T54" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="T54" s="4" t="n"/>
-      <c r="U54" s="4" t="n"/>
-      <c r="V54" s="4" t="n"/>
-      <c r="X54" s="4" t="n"/>
-      <c r="Y54" s="4" t="n"/>
-      <c r="Z54" s="4" t="n"/>
+      <c r="U54" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>17646</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z54" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB54" s="4" t="n">
         <v>59</v>
       </c>
@@ -3811,14 +4251,34 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="n"/>
-      <c r="U55" s="7" t="n"/>
-      <c r="V55" s="7" t="n"/>
-      <c r="X55" s="7" t="n"/>
-      <c r="Y55" s="7" t="n"/>
-      <c r="Z55" s="7" t="n"/>
+      <c r="T55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U55" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="n">
+        <v>17131</v>
+      </c>
+      <c r="X55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z55" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB55" s="7" t="n">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -3832,12 +4292,32 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="n"/>
-      <c r="U56" s="4" t="n"/>
-      <c r="V56" s="4" t="n"/>
-      <c r="X56" s="4" t="n"/>
-      <c r="Y56" s="4" t="n"/>
-      <c r="Z56" s="4" t="n"/>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U56" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>17470</v>
+      </c>
+      <c r="X56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z56" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB56" s="4" t="n">
         <v>7</v>
       </c>
@@ -3853,14 +4333,34 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="n"/>
-      <c r="U57" s="7" t="n"/>
-      <c r="V57" s="7" t="n"/>
-      <c r="X57" s="7" t="n"/>
-      <c r="Y57" s="7" t="n"/>
-      <c r="Z57" s="7" t="n"/>
+      <c r="T57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U57" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V57" s="7" t="n">
+        <v>17485</v>
+      </c>
+      <c r="X57" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z57" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB57" s="7" t="n">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -3874,12 +4374,32 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="n"/>
-      <c r="U58" s="4" t="n"/>
-      <c r="V58" s="4" t="n"/>
-      <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="4" t="n"/>
-      <c r="Z58" s="4" t="n"/>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>745</v>
+      </c>
+      <c r="X58" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z58" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB58" s="4" t="n">
         <v>1</v>
       </c>
@@ -3895,12 +4415,32 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="n"/>
-      <c r="U59" s="7" t="n"/>
-      <c r="V59" s="7" t="n"/>
-      <c r="X59" s="7" t="n"/>
-      <c r="Y59" s="7" t="n"/>
-      <c r="Z59" s="7" t="n"/>
+      <c r="T59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U59" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V59" s="7" t="n">
+        <v>763</v>
+      </c>
+      <c r="X59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z59" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB59" s="7" t="n">
         <v>1</v>
       </c>
@@ -3916,12 +4456,32 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="n"/>
-      <c r="U60" s="4" t="n"/>
-      <c r="V60" s="4" t="n"/>
-      <c r="X60" s="4" t="n"/>
-      <c r="Y60" s="4" t="n"/>
-      <c r="Z60" s="4" t="n"/>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U60" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>740</v>
+      </c>
+      <c r="X60" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z60" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB60" s="4" t="n">
         <v>1</v>
       </c>
@@ -3937,12 +4497,32 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="n"/>
-      <c r="U61" s="7" t="n"/>
-      <c r="V61" s="7" t="n"/>
-      <c r="X61" s="7" t="n"/>
-      <c r="Y61" s="7" t="n"/>
-      <c r="Z61" s="7" t="n"/>
+      <c r="T61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U61" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V61" s="7" t="n">
+        <v>783</v>
+      </c>
+      <c r="X61" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z61" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB61" s="7" t="n">
         <v>6</v>
       </c>
@@ -3958,12 +4538,32 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="n"/>
-      <c r="U62" s="4" t="n"/>
-      <c r="V62" s="4" t="n"/>
-      <c r="X62" s="4" t="n"/>
-      <c r="Y62" s="4" t="n"/>
-      <c r="Z62" s="4" t="n"/>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>763</v>
+      </c>
+      <c r="X62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z62" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB62" s="4" t="n">
         <v>6</v>
       </c>
@@ -3973,6 +4573,1488 @@
         </is>
       </c>
       <c r="AD62" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U63" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V63" s="7" t="n">
+        <v>735</v>
+      </c>
+      <c r="X63" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z63" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB63" s="7" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>2142</v>
+      </c>
+      <c r="X64" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="T65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U65" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V65" s="7" t="n">
+        <v>2408</v>
+      </c>
+      <c r="X65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z65" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD65" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U66" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>2141</v>
+      </c>
+      <c r="X66" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z66" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD66" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="T67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U67" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V67" s="7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="X67" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z67" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB67" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD67" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="X68" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="T69" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U69" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V69" s="7" t="n">
+        <v>2043</v>
+      </c>
+      <c r="X69" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y69" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z69" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB69" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC69" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD69" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
+      <c r="X70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
+      <c r="X71" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB71" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB72" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
+      <c r="X73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z73" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB73" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD73" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
+      <c r="X74" s="4" t="n"/>
+      <c r="Y74" s="4" t="n"/>
+      <c r="Z74" s="4" t="n"/>
+      <c r="AB74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
+      <c r="X75" s="7" t="n"/>
+      <c r="Y75" s="7" t="n"/>
+      <c r="Z75" s="7" t="n"/>
+      <c r="AB75" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC75" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD75" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
+      <c r="X76" s="4" t="n"/>
+      <c r="Y76" s="4" t="n"/>
+      <c r="Z76" s="4" t="n"/>
+      <c r="AB76" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
+      <c r="X77" s="7" t="n"/>
+      <c r="Y77" s="7" t="n"/>
+      <c r="Z77" s="7" t="n"/>
+      <c r="AB77" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
+      <c r="X78" s="4" t="n"/>
+      <c r="Y78" s="4" t="n"/>
+      <c r="Z78" s="4" t="n"/>
+      <c r="AB78" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD78" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
+      <c r="X79" s="7" t="n"/>
+      <c r="Y79" s="7" t="n"/>
+      <c r="Z79" s="7" t="n"/>
+      <c r="AB79" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC79" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD79" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
+      <c r="X80" s="4" t="n"/>
+      <c r="Y80" s="4" t="n"/>
+      <c r="Z80" s="4" t="n"/>
+      <c r="AB80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD80" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
+      <c r="X81" s="7" t="n"/>
+      <c r="Y81" s="7" t="n"/>
+      <c r="Z81" s="7" t="n"/>
+      <c r="AB81" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC81" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD81" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
+      <c r="X82" s="4" t="n"/>
+      <c r="Y82" s="4" t="n"/>
+      <c r="Z82" s="4" t="n"/>
+      <c r="AB82" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD82" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
+      <c r="X83" s="7" t="n"/>
+      <c r="Y83" s="7" t="n"/>
+      <c r="Z83" s="7" t="n"/>
+      <c r="AB83" s="7" t="n">
+        <v>327</v>
+      </c>
+      <c r="AC83" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD83" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
+      <c r="X84" s="4" t="n"/>
+      <c r="Y84" s="4" t="n"/>
+      <c r="Z84" s="4" t="n"/>
+      <c r="AB84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
+      <c r="X85" s="7" t="n"/>
+      <c r="Y85" s="7" t="n"/>
+      <c r="Z85" s="7" t="n"/>
+      <c r="AB85" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
+      <c r="X86" s="4" t="n"/>
+      <c r="Y86" s="4" t="n"/>
+      <c r="Z86" s="4" t="n"/>
+      <c r="AB86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
+      <c r="X87" s="7" t="n"/>
+      <c r="Y87" s="7" t="n"/>
+      <c r="Z87" s="7" t="n"/>
+      <c r="AB87" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
+      <c r="X88" s="4" t="n"/>
+      <c r="Y88" s="4" t="n"/>
+      <c r="Z88" s="4" t="n"/>
+      <c r="AB88" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
+      <c r="X89" s="7" t="n"/>
+      <c r="Y89" s="7" t="n"/>
+      <c r="Z89" s="7" t="n"/>
+      <c r="AB89" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC89" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD89" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
+      <c r="X90" s="4" t="n"/>
+      <c r="Y90" s="4" t="n"/>
+      <c r="Z90" s="4" t="n"/>
+      <c r="AB90" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD90" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
+      <c r="X91" s="7" t="n"/>
+      <c r="Y91" s="7" t="n"/>
+      <c r="Z91" s="7" t="n"/>
+      <c r="AB91" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD91" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
+      <c r="X92" s="4" t="n"/>
+      <c r="Y92" s="4" t="n"/>
+      <c r="Z92" s="4" t="n"/>
+      <c r="AB92" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD92" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
+      <c r="X93" s="7" t="n"/>
+      <c r="Y93" s="7" t="n"/>
+      <c r="Z93" s="7" t="n"/>
+      <c r="AB93" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC93" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD93" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
+      <c r="X94" s="4" t="n"/>
+      <c r="Y94" s="4" t="n"/>
+      <c r="Z94" s="4" t="n"/>
+      <c r="AB94" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD94" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
+      <c r="X95" s="7" t="n"/>
+      <c r="Y95" s="7" t="n"/>
+      <c r="Z95" s="7" t="n"/>
+      <c r="AB95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD95" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
+      <c r="X96" s="4" t="n"/>
+      <c r="Y96" s="4" t="n"/>
+      <c r="Z96" s="4" t="n"/>
+      <c r="AB96" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD96" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
+      <c r="X97" s="7" t="n"/>
+      <c r="Y97" s="7" t="n"/>
+      <c r="Z97" s="7" t="n"/>
+      <c r="AB97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD97" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
+      <c r="X98" s="4" t="n"/>
+      <c r="Y98" s="4" t="n"/>
+      <c r="Z98" s="4" t="n"/>
+      <c r="AB98" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
+      <c r="X99" s="7" t="n"/>
+      <c r="Y99" s="7" t="n"/>
+      <c r="Z99" s="7" t="n"/>
+      <c r="AB99" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD99" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
+      <c r="X100" s="4" t="n"/>
+      <c r="Y100" s="4" t="n"/>
+      <c r="Z100" s="4" t="n"/>
+      <c r="AB100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD100" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
+      <c r="X101" s="7" t="n"/>
+      <c r="Y101" s="7" t="n"/>
+      <c r="Z101" s="7" t="n"/>
+      <c r="AB101" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC101" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD101" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
+      <c r="X102" s="4" t="n"/>
+      <c r="Y102" s="4" t="n"/>
+      <c r="Z102" s="4" t="n"/>
+      <c r="AB102" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD102" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
+      <c r="X103" s="7" t="n"/>
+      <c r="Y103" s="7" t="n"/>
+      <c r="Z103" s="7" t="n"/>
+      <c r="AB103" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD103" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
+      <c r="X104" s="4" t="n"/>
+      <c r="Y104" s="4" t="n"/>
+      <c r="Z104" s="4" t="n"/>
+      <c r="AB104" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD104" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
+      <c r="X105" s="7" t="n"/>
+      <c r="Y105" s="7" t="n"/>
+      <c r="Z105" s="7" t="n"/>
+      <c r="AB105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC105" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD105" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
+      <c r="X106" s="4" t="n"/>
+      <c r="Y106" s="4" t="n"/>
+      <c r="Z106" s="4" t="n"/>
+      <c r="AB106" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD106" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
+      <c r="X107" s="7" t="n"/>
+      <c r="Y107" s="7" t="n"/>
+      <c r="Z107" s="7" t="n"/>
+      <c r="AB107" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC107" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD107" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
+      <c r="X108" s="4" t="n"/>
+      <c r="Y108" s="4" t="n"/>
+      <c r="Z108" s="4" t="n"/>
+      <c r="AB108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD108" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
+      <c r="X109" s="7" t="n"/>
+      <c r="Y109" s="7" t="n"/>
+      <c r="Z109" s="7" t="n"/>
+      <c r="AB109" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="AC109" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD109" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
+      <c r="X110" s="4" t="n"/>
+      <c r="Y110" s="4" t="n"/>
+      <c r="Z110" s="4" t="n"/>
+      <c r="AB110" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD110" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
+      <c r="X111" s="7" t="n"/>
+      <c r="Y111" s="7" t="n"/>
+      <c r="Z111" s="7" t="n"/>
+      <c r="AB111" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC111" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD111" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
+      <c r="X112" s="4" t="n"/>
+      <c r="Y112" s="4" t="n"/>
+      <c r="Z112" s="4" t="n"/>
+      <c r="AB112" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD112" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
+      <c r="X113" s="7" t="n"/>
+      <c r="Y113" s="7" t="n"/>
+      <c r="Z113" s="7" t="n"/>
+      <c r="AB113" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC113" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD113" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
+      <c r="X114" s="4" t="n"/>
+      <c r="Y114" s="4" t="n"/>
+      <c r="Z114" s="4" t="n"/>
+      <c r="AB114" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD114" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="T115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
+      <c r="X115" s="7" t="n"/>
+      <c r="Y115" s="7" t="n"/>
+      <c r="Z115" s="7" t="n"/>
+      <c r="AB115" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC115" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD115" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="n"/>
+      <c r="X116" s="4" t="n"/>
+      <c r="Y116" s="4" t="n"/>
+      <c r="Z116" s="4" t="n"/>
+      <c r="AB116" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD116" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="T117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
+      <c r="X117" s="7" t="n"/>
+      <c r="Y117" s="7" t="n"/>
+      <c r="Z117" s="7" t="n"/>
+      <c r="AB117" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="AC117" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD117" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="n"/>
+      <c r="X118" s="4" t="n"/>
+      <c r="Y118" s="4" t="n"/>
+      <c r="Z118" s="4" t="n"/>
+      <c r="AB118" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC118" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD118" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="T119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
+      <c r="X119" s="7" t="n"/>
+      <c r="Y119" s="7" t="n"/>
+      <c r="Z119" s="7" t="n"/>
+      <c r="AB119" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC119" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD119" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="4" t="n"/>
+      <c r="V120" s="4" t="n"/>
+      <c r="X120" s="4" t="n"/>
+      <c r="Y120" s="4" t="n"/>
+      <c r="Z120" s="4" t="n"/>
+      <c r="AB120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD120" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="T121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
+      <c r="X121" s="7" t="n"/>
+      <c r="Y121" s="7" t="n"/>
+      <c r="Z121" s="7" t="n"/>
+      <c r="AB121" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC121" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD121" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="n"/>
+      <c r="X122" s="4" t="n"/>
+      <c r="Y122" s="4" t="n"/>
+      <c r="Z122" s="4" t="n"/>
+      <c r="AB122" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD122" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="T123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
+      <c r="X123" s="7" t="n"/>
+      <c r="Y123" s="7" t="n"/>
+      <c r="Z123" s="7" t="n"/>
+      <c r="AB123" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC123" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD123" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="4" t="n"/>
+      <c r="V124" s="4" t="n"/>
+      <c r="X124" s="4" t="n"/>
+      <c r="Y124" s="4" t="n"/>
+      <c r="Z124" s="4" t="n"/>
+      <c r="AB124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD124" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -3994,7 +6076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD49"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4354,7 +6436,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -4373,34 +6455,66 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="D5">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C5)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C5)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>ROUND(MAX(0,MIN(100,(1-E5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>MIN(1,(G5-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C5)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>MAX(0,(L5-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>$B$2+H5+M5</f>
+        <v/>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1530</v>
+        <v>19486</v>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -4427,30 +6541,62 @@
           <t>2026-09-05</t>
         </is>
       </c>
+      <c r="D6">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C6)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C6)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>ROUND(MAX(0,MIN(100,(1-E6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>MIN(1,(G6-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C6)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>MAX(0,(L6-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>$B$2+H6+M6</f>
+        <v/>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>2311</v>
+        <v>25421</v>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -4481,30 +6627,62 @@
           <t>2026-09-06</t>
         </is>
       </c>
+      <c r="D7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C7)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C7)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>ROUND(MAX(0,MIN(100,(1-E7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>MIN(1,(G7-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C7)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>MAX(0,(L7-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>$B$2+H7+M7</f>
+        <v/>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>2868</v>
+        <v>36128</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -4542,23 +6720,23 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1815</v>
+        <v>1530</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -4588,23 +6766,23 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2333</v>
+        <v>2311</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -4644,23 +6822,23 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>3182</v>
+        <v>2868</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -4685,28 +6863,28 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2322</v>
+        <v>4059</v>
       </c>
       <c r="X11" t="n">
         <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -4731,32 +6909,32 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3533</v>
+        <v>5092</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -4777,28 +6955,28 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>4891</v>
+        <v>6962</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -4828,27 +7006,27 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1827</v>
+        <v>1815</v>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -4874,23 +7052,23 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2275</v>
+        <v>2333</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -4920,14 +7098,14 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2882</v>
+        <v>3182</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -4936,7 +7114,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -4961,28 +7139,28 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>250</v>
+        <v>4129</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -5007,28 +7185,28 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>428</v>
+        <v>5644</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -5053,32 +7231,32 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>365</v>
+        <v>7963</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -5104,27 +7282,27 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>6249</v>
+        <v>2322</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -5150,27 +7328,27 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>8329</v>
+        <v>3533</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -5196,14 +7374,14 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>10619</v>
+        <v>4891</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -5212,11 +7390,11 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -5237,32 +7415,32 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>30</v>
+        <v>6461</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -5283,32 +7461,32 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>81</v>
+        <v>8274</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -5329,28 +7507,28 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>103</v>
+        <v>12174</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -5380,27 +7558,27 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>603</v>
+        <v>1827</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -5426,27 +7604,27 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>820</v>
+        <v>2275</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5472,11 +7650,24 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>1204</v>
+        <v>2882</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
       </c>
       <c r="AB28" t="n">
         <v>5</v>
@@ -5500,19 +7691,32 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>3280</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>90</v>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5533,19 +7737,32 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>3951</v>
+      </c>
+      <c r="X30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>119</v>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
       <c r="AB30" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5566,16 +7783,29 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>157</v>
+        <v>5096</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
       <c r="AB31" t="n">
         <v>1</v>
@@ -5612,6 +7842,32 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>250</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB32" t="n">
         <v>5</v>
       </c>
@@ -5628,7 +7884,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D4)</f>
+        <f>AVERAGE(D2:D7)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -5636,7 +7892,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H4)</f>
+        <f>AVERAGE(H2:H7)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -5655,36 +7911,114 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>428</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB33" t="n">
+        <v>63</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>365</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
         <v>7</v>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="AB34" t="n">
-        <v>63</v>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>471</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB35" t="n">
         <v>3</v>
       </c>
@@ -5700,6 +8034,32 @@
       </c>
     </row>
     <row r="36">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>554</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB36" t="n">
         <v>43</v>
       </c>
@@ -5715,36 +8075,114 @@
       </c>
     </row>
     <row r="37">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>902</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>6249</v>
+      </c>
+      <c r="X38" t="n">
         <v>1</v>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="AB38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>8329</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB39" t="n">
         <v>5</v>
       </c>
@@ -5760,6 +8198,32 @@
       </c>
     </row>
     <row r="40">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>10619</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB40" t="n">
         <v>2</v>
       </c>
@@ -5775,6 +8239,32 @@
       </c>
     </row>
     <row r="41">
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>13894</v>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB41" t="n">
         <v>10</v>
       </c>
@@ -5790,6 +8280,32 @@
       </c>
     </row>
     <row r="42">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>17235</v>
+      </c>
+      <c r="X42" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB42" t="n">
         <v>2</v>
       </c>
@@ -5805,81 +8321,237 @@
       </c>
     </row>
     <row r="43">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>23145</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>30</v>
+      </c>
+      <c r="X44" t="n">
         <v>1</v>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="AB44" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC44" t="inlineStr">
+    <row r="45">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>81</v>
+      </c>
+      <c r="X45" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="AB45" t="n">
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>103</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>154</v>
+      </c>
+      <c r="X47" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
         <v>7</v>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="AB46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
+    <row r="48">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>183</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="AB47" t="n">
-        <v>47</v>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
       <c r="AB48" t="n">
         <v>1</v>
       </c>
@@ -5895,6 +8567,32 @@
       </c>
     </row>
     <row r="49">
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>238</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB49" t="n">
         <v>1</v>
       </c>
@@ -5904,6 +8602,1104 @@
         </is>
       </c>
       <c r="AD49" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>603</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>820</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>92</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>1204</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>1689</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>2042</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>2581</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>90</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>119</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>157</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>244</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>341</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="AB62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="AB63" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="AB64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="AB65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="AB66" t="n">
+        <v>140</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="AB67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="AB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="AB69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="AB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="AB71" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="AB72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="AB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="AB74" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="AB75" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="AB76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="AB78" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="AB79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="AB80" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="AB81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="AB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="AB83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="AB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="AB85" t="n">
+        <v>179</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="AB86" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="AB87" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="AB89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="AB90" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="AB91" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="AB92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="AB93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="AB94" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="AB95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="AB96" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="AB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="AB98" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="AB99" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="AB100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="AB101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="AB102" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="AB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="AB104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -735,10 +735,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -771,10 +771,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -807,10 +807,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -843,10 +843,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -879,10 +879,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -915,10 +915,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -951,10 +951,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -987,10 +987,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1023,10 +1023,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1059,10 +1059,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1363,15 +1363,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>68</v>
       </c>
@@ -1386,7 +1380,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1448,15 +1442,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>68</v>
       </c>
@@ -1471,7 +1459,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1533,15 +1521,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>91</v>
       </c>
@@ -1612,15 +1594,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>75</v>
       </c>
@@ -1697,15 +1673,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>1</v>
       </c>
@@ -1720,7 +1690,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1782,15 +1752,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>88</v>
       </c>
@@ -1805,7 +1769,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1843,21 +1807,11 @@
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>5519</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
@@ -1870,7 +1824,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1902,19 +1856,9 @@
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>5569</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>14</v>
       </c>
@@ -1929,7 +1873,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -1969,19 +1913,9 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>5621</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>12</v>
       </c>
@@ -1996,7 +1930,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2028,19 +1962,9 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>14</v>
       </c>
@@ -2055,7 +1979,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2087,19 +2011,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>5196</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>16</v>
       </c>
@@ -2114,7 +2028,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2146,19 +2060,9 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>5203</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>12</v>
       </c>
@@ -2173,7 +2077,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2205,19 +2109,9 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>15184</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>10</v>
       </c>
@@ -2232,7 +2126,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2264,19 +2158,9 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>15708</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>2</v>
       </c>
@@ -2291,7 +2175,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2323,19 +2207,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>15056</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>37</v>
       </c>
@@ -2350,7 +2224,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>188</v>
+        <v>3</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2382,19 +2256,9 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>15493</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>36</v>
       </c>
@@ -2441,21 +2305,11 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>14553</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
@@ -2500,21 +2354,11 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>14491</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
@@ -2559,19 +2403,9 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>87207</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>34</v>
       </c>
@@ -2618,19 +2452,9 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>86030</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>1</v>
       </c>
@@ -2677,19 +2501,9 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>82667</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>1</v>
       </c>
@@ -2736,21 +2550,11 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>82796</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
@@ -2795,21 +2599,11 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>80792</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
@@ -2854,21 +2648,11 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>80181</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
@@ -2913,21 +2697,11 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
@@ -2940,7 +2714,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2972,21 +2746,11 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>729</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
@@ -2999,7 +2763,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3031,21 +2795,11 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
@@ -3058,7 +2812,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -3090,19 +2844,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>753</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>8</v>
       </c>
@@ -3149,19 +2893,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>3</v>
       </c>
@@ -3176,7 +2910,7 @@
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3208,19 +2942,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>723</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>15</v>
       </c>
@@ -3235,7 +2959,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3276,19 +3000,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>50559</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>27</v>
       </c>
@@ -3303,7 +3017,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3349,19 +3063,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>51501</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3390,19 +3094,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>51715</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>1</v>
       </c>
@@ -3417,7 +3111,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3431,19 +3125,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>50240</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>18</v>
       </c>
@@ -3458,7 +3142,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3472,19 +3156,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>48948</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>3</v>
       </c>
@@ -3499,7 +3173,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3513,19 +3187,9 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>48922</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
         <v>25</v>
       </c>
@@ -3540,7 +3204,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3554,19 +3218,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
         <v>19</v>
       </c>
@@ -3595,21 +3249,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
+      <c r="X39" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="X39" s="7" t="n">
-        <v>21</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
@@ -3636,21 +3280,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>11599</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
@@ -3677,19 +3311,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>11522</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>3</v>
       </c>
@@ -3718,19 +3342,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>11614</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>19</v>
       </c>
@@ -3759,19 +3373,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>11098</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>21</v>
       </c>
@@ -3786,7 +3390,7 @@
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
@@ -3800,19 +3404,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>11097</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>15</v>
       </c>
@@ -3827,7 +3421,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3841,19 +3435,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>11410</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>14</v>
       </c>
@@ -3882,103 +3466,73 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
+      <c r="X46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>26509</v>
-      </c>
-      <c r="X46" s="4" t="n">
+      <c r="Z46" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD46" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
+      <c r="X47" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="Y46" s="4" t="inlineStr">
+      <c r="Y47" s="7" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z46" s="4" t="inlineStr">
+      <c r="Z47" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB46" s="4" t="n">
+      <c r="AB47" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr">
+      <c r="AC47" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD46" s="4" t="inlineStr">
+      <c r="AD47" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>26876</v>
-      </c>
-      <c r="X47" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB47" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>27154</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
@@ -4005,19 +3559,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>26655</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>1</v>
       </c>
@@ -4032,7 +3576,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4046,21 +3590,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>25267</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
@@ -4087,19 +3621,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>24712</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>7</v>
       </c>
@@ -4114,7 +3638,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4128,21 +3652,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>17949</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
@@ -4169,21 +3683,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>17549</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
@@ -4210,21 +3714,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>17646</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
@@ -4251,101 +3745,71 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
+      <c r="X55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y55" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>17131</v>
-      </c>
-      <c r="X55" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y55" s="7" t="inlineStr">
+      <c r="Z55" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB55" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD55" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
+      <c r="X56" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y56" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="Z55" s="7" t="inlineStr">
+      <c r="Z56" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB55" s="7" t="n">
+      <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="7" t="inlineStr">
+      <c r="AC56" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD55" s="7" t="inlineStr">
+      <c r="AD56" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>17470</v>
-      </c>
-      <c r="X56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>17485</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>3</v>
       </c>
@@ -4374,19 +3838,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>58</v>
       </c>
@@ -4415,21 +3869,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>763</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
@@ -4456,101 +3900,71 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
+      <c r="X60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z60" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>740</v>
-      </c>
-      <c r="X60" s="4" t="n">
+      <c r="AD60" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
+      <c r="X61" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="Y60" s="4" t="inlineStr">
+      <c r="Y61" s="7" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="Z60" s="4" t="inlineStr">
+      <c r="Z61" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB60" s="4" t="n">
+      <c r="AB61" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr">
+      <c r="AC61" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD60" s="4" t="inlineStr">
+      <c r="AD61" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>783</v>
-      </c>
-      <c r="X61" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB61" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-    </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>763</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>1</v>
       </c>
@@ -4579,19 +3993,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>735</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>9</v>
       </c>
@@ -4606,7 +4010,7 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4620,19 +4024,9 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>2142</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
         <v>6</v>
       </c>
@@ -4647,7 +4041,7 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4661,19 +4055,9 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>2408</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
         <v>1</v>
       </c>
@@ -4688,7 +4072,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4702,19 +4086,9 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>2141</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>4</v>
       </c>
@@ -4729,7 +4103,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4743,19 +4117,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>2082</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>4</v>
       </c>
@@ -4770,7 +4134,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4784,19 +4148,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>1990</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>5</v>
       </c>
@@ -4811,7 +4165,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4825,19 +4179,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>2043</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>6</v>
       </c>
@@ -4852,7 +4196,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4914,7 +4258,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -4945,7 +4289,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -4976,7 +4320,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -4997,7 +4341,7 @@
       <c r="Y74" s="4" t="n"/>
       <c r="Z74" s="4" t="n"/>
       <c r="AB74" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5018,7 +4362,7 @@
       <c r="Y75" s="7" t="n"/>
       <c r="Z75" s="7" t="n"/>
       <c r="AB75" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5249,7 +4593,7 @@
       <c r="Y86" s="4" t="n"/>
       <c r="Z86" s="4" t="n"/>
       <c r="AB86" s="4" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5291,7 +4635,7 @@
       <c r="Y88" s="4" t="n"/>
       <c r="Z88" s="4" t="n"/>
       <c r="AB88" s="4" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -5312,7 +4656,7 @@
       <c r="Y89" s="7" t="n"/>
       <c r="Z89" s="7" t="n"/>
       <c r="AB89" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -5396,7 +4740,7 @@
       <c r="Y93" s="7" t="n"/>
       <c r="Z93" s="7" t="n"/>
       <c r="AB93" s="7" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5438,7 +4782,7 @@
       <c r="Y95" s="7" t="n"/>
       <c r="Z95" s="7" t="n"/>
       <c r="AB95" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -5606,7 +4950,7 @@
       <c r="Y103" s="7" t="n"/>
       <c r="Z103" s="7" t="n"/>
       <c r="AB103" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -5648,7 +4992,7 @@
       <c r="Y105" s="7" t="n"/>
       <c r="Z105" s="7" t="n"/>
       <c r="AB105" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
@@ -5669,7 +5013,7 @@
       <c r="Y106" s="4" t="n"/>
       <c r="Z106" s="4" t="n"/>
       <c r="AB106" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -5690,7 +5034,7 @@
       <c r="Y107" s="7" t="n"/>
       <c r="Z107" s="7" t="n"/>
       <c r="AB107" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -5711,7 +5055,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -5732,7 +5076,7 @@
       <c r="Y109" s="7" t="n"/>
       <c r="Z109" s="7" t="n"/>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -5795,7 +5139,7 @@
       <c r="Y112" s="4" t="n"/>
       <c r="Z112" s="4" t="n"/>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -5816,7 +5160,7 @@
       <c r="Y113" s="7" t="n"/>
       <c r="Z113" s="7" t="n"/>
       <c r="AB113" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -5837,7 +5181,7 @@
       <c r="Y114" s="4" t="n"/>
       <c r="Z114" s="4" t="n"/>
       <c r="AB114" s="4" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -5858,7 +5202,7 @@
       <c r="Y115" s="7" t="n"/>
       <c r="Z115" s="7" t="n"/>
       <c r="AB115" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -5879,7 +5223,7 @@
       <c r="Y116" s="4" t="n"/>
       <c r="Z116" s="4" t="n"/>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5244,7 @@
       <c r="Y117" s="7" t="n"/>
       <c r="Z117" s="7" t="n"/>
       <c r="AB117" s="7" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -5921,7 +5265,7 @@
       <c r="Y118" s="4" t="n"/>
       <c r="Z118" s="4" t="n"/>
       <c r="AB118" s="4" t="n">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -6005,7 +5349,7 @@
       <c r="Y122" s="4" t="n"/>
       <c r="Z122" s="4" t="n"/>
       <c r="AB122" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
@@ -6026,7 +5370,7 @@
       <c r="Y123" s="7" t="n"/>
       <c r="Z123" s="7" t="n"/>
       <c r="AB123" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
@@ -6237,19 +5581,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>7773</v>
-      </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
@@ -6264,7 +5595,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -6323,19 +5654,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10781</v>
-      </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
@@ -6350,7 +5668,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -6409,19 +5727,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>14077</v>
-      </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
@@ -6436,7 +5741,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -6487,19 +5792,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>19486</v>
-      </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
@@ -6514,7 +5806,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -6573,21 +5865,8 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>25421</v>
-      </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -6659,21 +5938,8 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>36128</v>
-      </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -6713,21 +5979,8 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1530</v>
-      </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -6759,19 +6012,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>2311</v>
-      </c>
       <c r="X9" t="n">
         <v>6</v>
       </c>
@@ -6815,19 +6055,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>2868</v>
-      </c>
       <c r="X10" t="n">
         <v>4</v>
       </c>
@@ -6842,7 +6069,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -6861,19 +6088,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>4059</v>
-      </c>
       <c r="X11" t="n">
         <v>5</v>
       </c>
@@ -6888,7 +6102,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -6907,19 +6121,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>5092</v>
-      </c>
       <c r="X12" t="n">
         <v>5</v>
       </c>
@@ -6953,19 +6154,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>6962</v>
-      </c>
       <c r="X13" t="n">
         <v>5</v>
       </c>
@@ -6980,7 +6168,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -6999,19 +6187,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>1815</v>
-      </c>
       <c r="X14" t="n">
         <v>2</v>
       </c>
@@ -7026,7 +6201,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -7045,19 +6220,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>2333</v>
-      </c>
       <c r="X15" t="n">
         <v>6</v>
       </c>
@@ -7091,19 +6253,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>3182</v>
-      </c>
       <c r="X16" t="n">
         <v>20</v>
       </c>
@@ -7137,19 +6286,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>4129</v>
-      </c>
       <c r="X17" t="n">
         <v>9</v>
       </c>
@@ -7183,21 +6319,8 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>5644</v>
-      </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -7229,34 +6352,21 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V19" t="n">
-        <v>7963</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -7275,21 +6385,8 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>2322</v>
-      </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -7302,7 +6399,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -7321,21 +6418,8 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>3533</v>
-      </c>
       <c r="X21" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -7348,7 +6432,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -7367,19 +6451,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>4891</v>
-      </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
@@ -7394,7 +6465,7 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -7413,19 +6484,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>6461</v>
-      </c>
       <c r="X23" t="n">
         <v>5</v>
       </c>
@@ -7440,7 +6498,7 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -7459,34 +6517,21 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V24" t="n">
-        <v>8274</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AB24" t="n">
         <v>1</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB24" t="n">
-        <v>4</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -7505,34 +6550,21 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V25" t="n">
-        <v>12174</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -7551,19 +6583,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>1827</v>
-      </c>
       <c r="X26" t="n">
         <v>5</v>
       </c>
@@ -7597,19 +6616,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>2275</v>
-      </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
@@ -7643,19 +6649,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>2882</v>
-      </c>
       <c r="X28" t="n">
         <v>9</v>
       </c>
@@ -7670,7 +6663,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -7689,19 +6682,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>3280</v>
-      </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
@@ -7716,7 +6696,7 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -7735,34 +6715,21 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V30" t="n">
-        <v>3951</v>
-      </c>
-      <c r="X30" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -7781,21 +6748,8 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>5096</v>
-      </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -7841,19 +6795,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>250</v>
       </c>
       <c r="X32" t="n">
         <v>3</v>
@@ -7911,19 +6852,6 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>428</v>
-      </c>
       <c r="X33" t="n">
         <v>3</v>
       </c>
@@ -7952,19 +6880,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>365</v>
-      </c>
       <c r="X34" t="n">
         <v>8</v>
       </c>
@@ -7993,19 +6908,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>471</v>
-      </c>
       <c r="X35" t="n">
         <v>7</v>
       </c>
@@ -8034,19 +6936,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>554</v>
-      </c>
       <c r="X36" t="n">
         <v>8</v>
       </c>
@@ -8061,7 +6950,7 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -8075,19 +6964,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>902</v>
-      </c>
       <c r="X37" t="n">
         <v>5</v>
       </c>
@@ -8102,7 +6978,7 @@
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -8116,21 +6992,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>6249</v>
-      </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -8157,144 +7020,92 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" t="inlineStr">
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="V39" t="n">
-        <v>8329</v>
-      </c>
-      <c r="X39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AB39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB39" t="n">
+      <c r="AB40" t="n">
         <v>5</v>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="T40" t="inlineStr">
+    <row r="41">
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="V40" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="inlineStr">
+      <c r="AB41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="X42" t="n">
         <v>2</v>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>13894</v>
-      </c>
-      <c r="X41" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>17235</v>
-      </c>
-      <c r="X42" t="n">
-        <v>18</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -8321,21 +7132,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>23145</v>
-      </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -8362,19 +7160,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>30</v>
-      </c>
       <c r="X44" t="n">
         <v>1</v>
       </c>
@@ -8403,19 +7188,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>81</v>
-      </c>
       <c r="X45" t="n">
         <v>31</v>
       </c>
@@ -8430,7 +7202,7 @@
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8444,19 +7216,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>103</v>
-      </c>
       <c r="X46" t="n">
         <v>1</v>
       </c>
@@ -8485,62 +7244,36 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>154</v>
-      </c>
       <c r="X47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="X48" t="n">
         <v>33</v>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>183</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -8567,19 +7300,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>238</v>
-      </c>
       <c r="X49" t="n">
         <v>3</v>
       </c>
@@ -8608,19 +7328,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>603</v>
-      </c>
       <c r="X50" t="n">
         <v>1</v>
       </c>
@@ -8635,7 +7342,7 @@
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -8649,19 +7356,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>820</v>
-      </c>
       <c r="X51" t="n">
         <v>1</v>
       </c>
@@ -8676,7 +7370,7 @@
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -8690,19 +7384,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>1204</v>
-      </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
@@ -8717,7 +7398,7 @@
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -8731,19 +7412,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>1689</v>
-      </c>
       <c r="X53" t="n">
         <v>1</v>
       </c>
@@ -8758,7 +7426,7 @@
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -8772,19 +7440,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V54" t="n">
-        <v>2042</v>
-      </c>
       <c r="X54" t="n">
         <v>1</v>
       </c>
@@ -8799,7 +7454,7 @@
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -8813,19 +7468,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>2581</v>
-      </c>
       <c r="X55" t="n">
         <v>5</v>
       </c>
@@ -8840,7 +7482,7 @@
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -8854,19 +7496,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>90</v>
-      </c>
       <c r="X56" t="n">
         <v>1</v>
       </c>
@@ -8895,19 +7524,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>119</v>
-      </c>
       <c r="X57" t="n">
         <v>1</v>
       </c>
@@ -8936,19 +7552,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>157</v>
-      </c>
       <c r="X58" t="n">
         <v>2</v>
       </c>
@@ -8963,61 +7566,35 @@
         </is>
       </c>
       <c r="AB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="AB59" t="n">
         <v>17</v>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>244</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>270</v>
-      </c>
       <c r="AB60" t="n">
         <v>2</v>
       </c>
@@ -9033,21 +7610,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>341</v>
-      </c>
       <c r="AB61" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -9062,7 +7626,7 @@
     </row>
     <row r="62">
       <c r="AB62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9077,7 +7641,7 @@
     </row>
     <row r="63">
       <c r="AB63" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -9122,7 +7686,7 @@
     </row>
     <row r="66">
       <c r="AB66" t="n">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
@@ -9137,7 +7701,7 @@
     </row>
     <row r="67">
       <c r="AB67" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
@@ -9152,7 +7716,7 @@
     </row>
     <row r="68">
       <c r="AB68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -9167,7 +7731,7 @@
     </row>
     <row r="69">
       <c r="AB69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -9182,7 +7746,7 @@
     </row>
     <row r="70">
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -9197,7 +7761,7 @@
     </row>
     <row r="71">
       <c r="AB71" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -9212,7 +7776,7 @@
     </row>
     <row r="72">
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -9227,7 +7791,7 @@
     </row>
     <row r="73">
       <c r="AB73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -9242,7 +7806,7 @@
     </row>
     <row r="74">
       <c r="AB74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -9317,7 +7881,7 @@
     </row>
     <row r="79">
       <c r="AB79" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -9332,7 +7896,7 @@
     </row>
     <row r="80">
       <c r="AB80" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -9467,7 +8031,7 @@
     </row>
     <row r="89">
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -9497,7 +8061,7 @@
     </row>
     <row r="91">
       <c r="AB91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -9527,7 +8091,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -9542,7 +8106,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -9557,7 +8121,7 @@
     </row>
     <row r="95">
       <c r="AB95" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -9572,7 +8136,7 @@
     </row>
     <row r="96">
       <c r="AB96" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -9587,7 +8151,7 @@
     </row>
     <row r="97">
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -9662,7 +8226,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -9677,7 +8241,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -735,7 +735,7 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.19</v>
@@ -771,7 +771,7 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.19</v>
@@ -807,7 +807,7 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>1.19</v>
@@ -843,7 +843,7 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1.19</v>
@@ -879,7 +879,7 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1.19</v>
@@ -915,7 +915,7 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>1.19</v>
@@ -951,7 +951,7 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>1.19</v>
@@ -987,7 +987,7 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1.19</v>
@@ -1023,7 +1023,7 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1.19</v>
@@ -1059,7 +1059,7 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1.19</v>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD124"/>
+  <dimension ref="A1:AD147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1707,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="7" t="inlineStr">
         <is>
@@ -1832,32 +1832,52 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
+      <c r="D8" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C8)</f>
+        <v/>
+      </c>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="G8" s="4">
+        <f>ROUND(MAX(0,MIN(100,(1-E8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>MIN(1,(G8-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="K8" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>MAX(0,(L8-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>$B$2+H8+M8</f>
+        <v/>
+      </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="n">
-        <v>5519</v>
+        <v>1</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
@@ -1870,7 +1890,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1904,7 +1924,7 @@
       <c r="N9" s="7" t="n"/>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
@@ -1913,19 +1933,19 @@
         </is>
       </c>
       <c r="V9" s="7" t="n">
-        <v>5569</v>
+        <v>5519</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="Y9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z9" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB9" s="7" t="n">
@@ -1971,7 +1991,7 @@
       <c r="N10" s="4" t="n"/>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
@@ -1980,23 +2000,23 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>5621</v>
+        <v>5569</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2030,7 +2050,7 @@
       <c r="N11" s="7" t="n"/>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -2039,23 +2059,23 @@
         </is>
       </c>
       <c r="V11" s="7" t="n">
-        <v>5557</v>
+        <v>5621</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2089,7 +2109,7 @@
       <c r="N12" s="4" t="n"/>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -2098,14 +2118,14 @@
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5196</v>
+        <v>5557</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
@@ -2148,7 +2168,7 @@
       <c r="N13" s="7" t="n"/>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
@@ -2157,14 +2177,14 @@
         </is>
       </c>
       <c r="V13" s="7" t="n">
-        <v>5203</v>
+        <v>5196</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>12</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z13" s="7" t="inlineStr">
@@ -2207,32 +2227,32 @@
       <c r="N14" s="4" t="n"/>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>5203</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V14" s="4" t="n">
-        <v>15184</v>
-      </c>
-      <c r="X14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
       <c r="AB14" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2266,32 +2286,32 @@
       <c r="N15" s="7" t="n"/>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="n">
+        <v>5687</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V15" s="7" t="n">
-        <v>15708</v>
-      </c>
-      <c r="X15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB15" s="7" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2325,7 +2345,7 @@
       <c r="N16" s="4" t="n"/>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
@@ -2334,23 +2354,23 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>15056</v>
+        <v>15184</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2384,7 +2404,7 @@
       <c r="N17" s="7" t="n"/>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -2393,19 +2413,19 @@
         </is>
       </c>
       <c r="V17" s="7" t="n">
-        <v>15493</v>
+        <v>15708</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB17" s="7" t="n">
@@ -2443,7 +2463,7 @@
       <c r="N18" s="4" t="n"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
@@ -2452,19 +2472,19 @@
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>14553</v>
+        <v>15056</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB18" s="4" t="n">
@@ -2502,7 +2522,7 @@
       <c r="N19" s="7" t="n"/>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -2511,14 +2531,14 @@
         </is>
       </c>
       <c r="V19" s="7" t="n">
-        <v>14491</v>
+        <v>15493</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z19" s="7" t="inlineStr">
@@ -2561,23 +2581,23 @@
       <c r="N20" s="4" t="n"/>
       <c r="T20" s="4" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>14553</v>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>87207</v>
-      </c>
-      <c r="X20" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
@@ -2620,23 +2640,23 @@
       <c r="N21" s="7" t="n"/>
       <c r="T21" s="7" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="n">
+        <v>14491</v>
+      </c>
+      <c r="X21" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>86030</v>
-      </c>
-      <c r="X21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
@@ -2679,23 +2699,23 @@
       <c r="N22" s="4" t="n"/>
       <c r="T22" s="4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>15132</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>82667</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
@@ -2738,7 +2758,7 @@
       <c r="N23" s="7" t="n"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -2747,14 +2767,14 @@
         </is>
       </c>
       <c r="V23" s="7" t="n">
-        <v>82796</v>
+        <v>87207</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
@@ -2797,7 +2817,7 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -2806,14 +2826,14 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>80792</v>
+        <v>86030</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
@@ -2856,7 +2876,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -2865,14 +2885,14 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>80181</v>
+        <v>82667</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z25" s="7" t="inlineStr">
@@ -2881,7 +2901,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2915,32 +2935,32 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>721</v>
+        <v>82796</v>
       </c>
       <c r="X26" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB26" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2974,28 +2994,28 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>729</v>
+        <v>80792</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB27" s="7" t="n">
@@ -3033,28 +3053,28 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>717</v>
+        <v>80181</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB28" s="4" t="n">
@@ -3092,32 +3112,32 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>753</v>
+        <v>82769</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
@@ -3151,7 +3171,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3160,23 +3180,23 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3210,7 +3230,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3219,19 +3239,19 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z31" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB31" s="7" t="n">
@@ -3278,28 +3298,28 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>50559</v>
+        <v>717</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB32" s="4" t="n">
@@ -3318,7 +3338,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D7)</f>
+        <f>AVERAGE(D2:D8)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3328,7 +3348,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H7)</f>
+        <f>AVERAGE(H2:H8)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3351,28 +3371,28 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>51501</v>
+        <v>753</v>
       </c>
       <c r="X33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB33" s="7" t="n">
@@ -3392,23 +3412,23 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>51715</v>
+        <v>696</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
@@ -3417,7 +3437,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3433,23 +3453,23 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>50240</v>
+        <v>723</v>
       </c>
       <c r="X35" s="7" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z35" s="7" t="inlineStr">
@@ -3458,7 +3478,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3474,23 +3494,23 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>48948</v>
+        <v>743</v>
       </c>
       <c r="X36" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
@@ -3499,7 +3519,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3515,7 +3535,7 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
@@ -3524,14 +3544,14 @@
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>48922</v>
+        <v>50559</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z37" s="7" t="inlineStr">
@@ -3540,7 +3560,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3556,28 +3576,28 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>1</v>
+        <v>51501</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB38" s="4" t="n">
@@ -3597,28 +3617,28 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V39" s="7" t="n">
+        <v>51715</v>
+      </c>
+      <c r="X39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="X39" s="7" t="n">
-        <v>21</v>
-      </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB39" s="7" t="n">
@@ -3638,28 +3658,28 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>11599</v>
+        <v>50240</v>
       </c>
       <c r="X40" s="4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB40" s="4" t="n">
@@ -3679,28 +3699,28 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>11522</v>
+        <v>48948</v>
       </c>
       <c r="X41" s="7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB41" s="7" t="n">
@@ -3720,32 +3740,32 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>11614</v>
+        <v>48922</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3761,32 +3781,32 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>11098</v>
+        <v>51004</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
@@ -3807,23 +3827,23 @@
       </c>
       <c r="U44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>11097</v>
+        <v>1</v>
       </c>
       <c r="X44" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB44" s="4" t="n">
@@ -3848,23 +3868,23 @@
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>11410</v>
+        <v>1</v>
       </c>
       <c r="X45" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB45" s="7" t="n">
@@ -3889,27 +3909,27 @@
       </c>
       <c r="U46" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>11599</v>
+      </c>
+      <c r="X46" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z46" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V46" s="4" t="n">
-        <v>26509</v>
-      </c>
-      <c r="X46" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
       <c r="AB46" s="4" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3930,14 +3950,14 @@
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>26876</v>
+        <v>11522</v>
       </c>
       <c r="X47" s="7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
@@ -3946,11 +3966,11 @@
       </c>
       <c r="Z47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -3971,14 +3991,14 @@
       </c>
       <c r="U48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>27154</v>
+        <v>11614</v>
       </c>
       <c r="X48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
@@ -3987,11 +4007,11 @@
       </c>
       <c r="Z48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4012,14 +4032,14 @@
       </c>
       <c r="U49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>26655</v>
+        <v>11098</v>
       </c>
       <c r="X49" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
@@ -4028,11 +4048,11 @@
       </c>
       <c r="Z49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4053,23 +4073,23 @@
       </c>
       <c r="U50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>25267</v>
+        <v>11097</v>
       </c>
       <c r="X50" s="4" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB50" s="4" t="n">
@@ -4094,14 +4114,14 @@
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>24712</v>
+        <v>11410</v>
       </c>
       <c r="X51" s="7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Y51" s="7" t="inlineStr">
         <is>
@@ -4110,11 +4130,11 @@
       </c>
       <c r="Z51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4130,28 +4150,28 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>17949</v>
+        <v>11482</v>
       </c>
       <c r="X52" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB52" s="4" t="n">
@@ -4171,32 +4191,32 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>17549</v>
+        <v>26509</v>
       </c>
       <c r="X53" s="7" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4212,32 +4232,32 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>17646</v>
+        <v>26876</v>
       </c>
       <c r="X54" s="4" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
@@ -4253,32 +4273,32 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>17131</v>
+        <v>27154</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Y55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4294,32 +4314,32 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>17470</v>
+        <v>26655</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4335,23 +4355,23 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>17485</v>
+        <v>25267</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z57" s="7" t="inlineStr">
@@ -4360,7 +4380,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>198</v>
+        <v>10</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4376,23 +4396,23 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>24712</v>
+      </c>
+      <c r="X58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y58" s="4" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>745</v>
-      </c>
-      <c r="X58" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z58" s="4" t="inlineStr">
@@ -4417,23 +4437,23 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U59" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V59" s="7" t="n">
+        <v>26356</v>
+      </c>
+      <c r="X59" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y59" s="7" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>763</v>
-      </c>
-      <c r="X59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z59" s="7" t="inlineStr">
@@ -4458,23 +4478,23 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>740</v>
+        <v>17949</v>
       </c>
       <c r="X60" s="4" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z60" s="4" t="inlineStr">
@@ -4483,7 +4503,7 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4499,23 +4519,23 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>783</v>
+        <v>17549</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z61" s="7" t="inlineStr">
@@ -4524,7 +4544,7 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4540,28 +4560,28 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>763</v>
+        <v>17646</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB62" s="4" t="n">
@@ -4581,32 +4601,32 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>735</v>
+        <v>17131</v>
       </c>
       <c r="X63" s="7" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Y63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4622,28 +4642,28 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>2142</v>
+        <v>17470</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB64" s="4" t="n">
@@ -4663,32 +4683,32 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>2408</v>
+        <v>17485</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4704,28 +4724,28 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>2141</v>
+        <v>17825</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB66" s="4" t="n">
@@ -4745,28 +4765,28 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U67" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V67" s="7" t="n">
+        <v>745</v>
+      </c>
+      <c r="X67" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y67" s="7" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>2082</v>
-      </c>
-      <c r="X67" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="Z67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB67" s="7" t="n">
@@ -4786,32 +4806,32 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>763</v>
+      </c>
+      <c r="X68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y68" s="4" t="inlineStr">
+        <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="X68" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="Z68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4827,32 +4847,32 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>2043</v>
+        <v>740</v>
       </c>
       <c r="X69" s="7" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4866,199 +4886,319 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="n"/>
-      <c r="U70" s="4" t="n"/>
-      <c r="V70" s="4" t="n"/>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>783</v>
+      </c>
       <c r="X70" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Y70" s="4" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="T71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V71" s="7" t="n">
+        <v>763</v>
+      </c>
+      <c r="X71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB71" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>735</v>
+      </c>
+      <c r="X72" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB72" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="T73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U73" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V73" s="7" t="n">
+        <v>841</v>
+      </c>
+      <c r="X73" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z73" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD73" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>2142</v>
+      </c>
+      <c r="X74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="T75" s="7" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="Z70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr">
+      <c r="U75" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V75" s="7" t="n">
+        <v>2408</v>
+      </c>
+      <c r="X75" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y75" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z75" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB75" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC75" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="T71" s="7" t="n"/>
-      <c r="U71" s="7" t="n"/>
-      <c r="V71" s="7" t="n"/>
-      <c r="X71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y71" s="7" t="inlineStr">
+      <c r="AD75" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="T76" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB71" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC71" s="7" t="inlineStr">
+      <c r="U76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V76" s="4" t="n">
+        <v>2141</v>
+      </c>
+      <c r="X76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="T72" s="4" t="n"/>
-      <c r="U72" s="4" t="n"/>
-      <c r="V72" s="4" t="n"/>
-      <c r="X72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="AB76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="T73" s="7" t="n"/>
-      <c r="U73" s="7" t="n"/>
-      <c r="V73" s="7" t="n"/>
-      <c r="X73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y73" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB73" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="AC73" s="7" t="inlineStr">
+      <c r="AD76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="T77" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="T74" s="4" t="n"/>
-      <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n"/>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n"/>
-      <c r="Z74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="T75" s="7" t="n"/>
-      <c r="U75" s="7" t="n"/>
-      <c r="V75" s="7" t="n"/>
-      <c r="X75" s="7" t="n"/>
-      <c r="Y75" s="7" t="n"/>
-      <c r="Z75" s="7" t="n"/>
-      <c r="AB75" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="T76" s="4" t="n"/>
-      <c r="U76" s="4" t="n"/>
-      <c r="V76" s="4" t="n"/>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="4" t="n"/>
-      <c r="Z76" s="4" t="n"/>
-      <c r="AB76" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="T77" s="7" t="n"/>
-      <c r="U77" s="7" t="n"/>
-      <c r="V77" s="7" t="n"/>
-      <c r="X77" s="7" t="n"/>
-      <c r="Y77" s="7" t="n"/>
-      <c r="Z77" s="7" t="n"/>
+      <c r="U77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V77" s="7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="X77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB77" s="7" t="n">
         <v>157</v>
       </c>
@@ -5074,54 +5214,114 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="n"/>
-      <c r="U78" s="4" t="n"/>
-      <c r="V78" s="4" t="n"/>
-      <c r="X78" s="4" t="n"/>
-      <c r="Y78" s="4" t="n"/>
-      <c r="Z78" s="4" t="n"/>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U78" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="X78" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z78" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB78" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD78" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U79" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V79" s="7" t="n">
+        <v>2043</v>
+      </c>
+      <c r="X79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z79" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB79" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr">
+      <c r="AC79" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD78" s="4" t="inlineStr">
+      <c r="AD79" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="T79" s="7" t="n"/>
-      <c r="U79" s="7" t="n"/>
-      <c r="V79" s="7" t="n"/>
-      <c r="X79" s="7" t="n"/>
-      <c r="Y79" s="7" t="n"/>
-      <c r="Z79" s="7" t="n"/>
-      <c r="AB79" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC79" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
-      <c r="T80" s="4" t="n"/>
-      <c r="U80" s="4" t="n"/>
-      <c r="V80" s="4" t="n"/>
-      <c r="X80" s="4" t="n"/>
-      <c r="Y80" s="4" t="n"/>
-      <c r="Z80" s="4" t="n"/>
+      <c r="T80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U80" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>2148</v>
+      </c>
+      <c r="X80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z80" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB80" s="4" t="n">
         <v>3</v>
       </c>
@@ -5140,9 +5340,19 @@
       <c r="T81" s="7" t="n"/>
       <c r="U81" s="7" t="n"/>
       <c r="V81" s="7" t="n"/>
-      <c r="X81" s="7" t="n"/>
-      <c r="Y81" s="7" t="n"/>
-      <c r="Z81" s="7" t="n"/>
+      <c r="X81" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y81" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z81" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB81" s="7" t="n">
         <v>9</v>
       </c>
@@ -5161,9 +5371,19 @@
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
-      <c r="X82" s="4" t="n"/>
-      <c r="Y82" s="4" t="n"/>
-      <c r="Z82" s="4" t="n"/>
+      <c r="X82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z82" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB82" s="4" t="n">
         <v>3</v>
       </c>
@@ -5182,9 +5402,19 @@
       <c r="T83" s="7" t="n"/>
       <c r="U83" s="7" t="n"/>
       <c r="V83" s="7" t="n"/>
-      <c r="X83" s="7" t="n"/>
-      <c r="Y83" s="7" t="n"/>
-      <c r="Z83" s="7" t="n"/>
+      <c r="X83" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y83" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z83" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB83" s="7" t="n">
         <v>327</v>
       </c>
@@ -5203,11 +5433,21 @@
       <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
-      <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
-      <c r="Z84" s="4" t="n"/>
+      <c r="X84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -5224,11 +5464,21 @@
       <c r="T85" s="7" t="n"/>
       <c r="U85" s="7" t="n"/>
       <c r="V85" s="7" t="n"/>
-      <c r="X85" s="7" t="n"/>
-      <c r="Y85" s="7" t="n"/>
-      <c r="Z85" s="7" t="n"/>
+      <c r="X85" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB85" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -5245,9 +5495,19 @@
       <c r="T86" s="4" t="n"/>
       <c r="U86" s="4" t="n"/>
       <c r="V86" s="4" t="n"/>
-      <c r="X86" s="4" t="n"/>
-      <c r="Y86" s="4" t="n"/>
-      <c r="Z86" s="4" t="n"/>
+      <c r="X86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB86" s="4" t="n">
         <v>1</v>
       </c>
@@ -5266,11 +5526,21 @@
       <c r="T87" s="7" t="n"/>
       <c r="U87" s="7" t="n"/>
       <c r="V87" s="7" t="n"/>
-      <c r="X87" s="7" t="n"/>
-      <c r="Y87" s="7" t="n"/>
-      <c r="Z87" s="7" t="n"/>
+      <c r="X87" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB87" s="7" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
@@ -5287,11 +5557,21 @@
       <c r="T88" s="4" t="n"/>
       <c r="U88" s="4" t="n"/>
       <c r="V88" s="4" t="n"/>
-      <c r="X88" s="4" t="n"/>
-      <c r="Y88" s="4" t="n"/>
-      <c r="Z88" s="4" t="n"/>
+      <c r="X88" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB88" s="4" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -5308,9 +5588,19 @@
       <c r="T89" s="7" t="n"/>
       <c r="U89" s="7" t="n"/>
       <c r="V89" s="7" t="n"/>
-      <c r="X89" s="7" t="n"/>
-      <c r="Y89" s="7" t="n"/>
-      <c r="Z89" s="7" t="n"/>
+      <c r="X89" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y89" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z89" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB89" s="7" t="n">
         <v>7</v>
       </c>
@@ -5606,7 +5896,7 @@
       <c r="Y103" s="7" t="n"/>
       <c r="Z103" s="7" t="n"/>
       <c r="AB103" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -5648,7 +5938,7 @@
       <c r="Y105" s="7" t="n"/>
       <c r="Z105" s="7" t="n"/>
       <c r="AB105" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
@@ -5795,7 +6085,7 @@
       <c r="Y112" s="4" t="n"/>
       <c r="Z112" s="4" t="n"/>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -5816,7 +6106,7 @@
       <c r="Y113" s="7" t="n"/>
       <c r="Z113" s="7" t="n"/>
       <c r="AB113" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -5858,7 +6148,7 @@
       <c r="Y115" s="7" t="n"/>
       <c r="Z115" s="7" t="n"/>
       <c r="AB115" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -5879,7 +6169,7 @@
       <c r="Y116" s="4" t="n"/>
       <c r="Z116" s="4" t="n"/>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -5900,7 +6190,7 @@
       <c r="Y117" s="7" t="n"/>
       <c r="Z117" s="7" t="n"/>
       <c r="AB117" s="7" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -5921,7 +6211,7 @@
       <c r="Y118" s="4" t="n"/>
       <c r="Z118" s="4" t="n"/>
       <c r="AB118" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -5942,7 +6232,7 @@
       <c r="Y119" s="7" t="n"/>
       <c r="Z119" s="7" t="n"/>
       <c r="AB119" s="7" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -5963,7 +6253,7 @@
       <c r="Y120" s="4" t="n"/>
       <c r="Z120" s="4" t="n"/>
       <c r="AB120" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -6005,7 +6295,7 @@
       <c r="Y122" s="4" t="n"/>
       <c r="Z122" s="4" t="n"/>
       <c r="AB122" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
@@ -6026,7 +6316,7 @@
       <c r="Y123" s="7" t="n"/>
       <c r="Z123" s="7" t="n"/>
       <c r="AB123" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
@@ -6055,6 +6345,489 @@
         </is>
       </c>
       <c r="AD124" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="T125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
+      <c r="X125" s="7" t="n"/>
+      <c r="Y125" s="7" t="n"/>
+      <c r="Z125" s="7" t="n"/>
+      <c r="AB125" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC125" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD125" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="n"/>
+      <c r="X126" s="4" t="n"/>
+      <c r="Y126" s="4" t="n"/>
+      <c r="Z126" s="4" t="n"/>
+      <c r="AB126" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD126" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="T127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
+      <c r="X127" s="7" t="n"/>
+      <c r="Y127" s="7" t="n"/>
+      <c r="Z127" s="7" t="n"/>
+      <c r="AB127" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC127" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD127" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="4" t="n"/>
+      <c r="V128" s="4" t="n"/>
+      <c r="X128" s="4" t="n"/>
+      <c r="Y128" s="4" t="n"/>
+      <c r="Z128" s="4" t="n"/>
+      <c r="AB128" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD128" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="T129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
+      <c r="X129" s="7" t="n"/>
+      <c r="Y129" s="7" t="n"/>
+      <c r="Z129" s="7" t="n"/>
+      <c r="AB129" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC129" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD129" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="4" t="n"/>
+      <c r="V130" s="4" t="n"/>
+      <c r="X130" s="4" t="n"/>
+      <c r="Y130" s="4" t="n"/>
+      <c r="Z130" s="4" t="n"/>
+      <c r="AB130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD130" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="T131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
+      <c r="X131" s="7" t="n"/>
+      <c r="Y131" s="7" t="n"/>
+      <c r="Z131" s="7" t="n"/>
+      <c r="AB131" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC131" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD131" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="4" t="n"/>
+      <c r="V132" s="4" t="n"/>
+      <c r="X132" s="4" t="n"/>
+      <c r="Y132" s="4" t="n"/>
+      <c r="Z132" s="4" t="n"/>
+      <c r="AB132" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD132" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="T133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
+      <c r="X133" s="7" t="n"/>
+      <c r="Y133" s="7" t="n"/>
+      <c r="Z133" s="7" t="n"/>
+      <c r="AB133" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC133" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD133" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="4" t="n"/>
+      <c r="V134" s="4" t="n"/>
+      <c r="X134" s="4" t="n"/>
+      <c r="Y134" s="4" t="n"/>
+      <c r="Z134" s="4" t="n"/>
+      <c r="AB134" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD134" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="T135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
+      <c r="X135" s="7" t="n"/>
+      <c r="Y135" s="7" t="n"/>
+      <c r="Z135" s="7" t="n"/>
+      <c r="AB135" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC135" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD135" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="n"/>
+      <c r="X136" s="4" t="n"/>
+      <c r="Y136" s="4" t="n"/>
+      <c r="Z136" s="4" t="n"/>
+      <c r="AB136" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD136" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="T137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
+      <c r="X137" s="7" t="n"/>
+      <c r="Y137" s="7" t="n"/>
+      <c r="Z137" s="7" t="n"/>
+      <c r="AB137" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC137" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD137" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="4" t="n"/>
+      <c r="V138" s="4" t="n"/>
+      <c r="X138" s="4" t="n"/>
+      <c r="Y138" s="4" t="n"/>
+      <c r="Z138" s="4" t="n"/>
+      <c r="AB138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD138" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="T139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
+      <c r="X139" s="7" t="n"/>
+      <c r="Y139" s="7" t="n"/>
+      <c r="Z139" s="7" t="n"/>
+      <c r="AB139" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC139" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD139" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="n"/>
+      <c r="X140" s="4" t="n"/>
+      <c r="Y140" s="4" t="n"/>
+      <c r="Z140" s="4" t="n"/>
+      <c r="AB140" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD140" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="T141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
+      <c r="X141" s="7" t="n"/>
+      <c r="Y141" s="7" t="n"/>
+      <c r="Z141" s="7" t="n"/>
+      <c r="AB141" s="7" t="n">
+        <v>161</v>
+      </c>
+      <c r="AC141" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD141" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="n"/>
+      <c r="X142" s="4" t="n"/>
+      <c r="Y142" s="4" t="n"/>
+      <c r="Z142" s="4" t="n"/>
+      <c r="AB142" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD142" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="T143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
+      <c r="X143" s="7" t="n"/>
+      <c r="Y143" s="7" t="n"/>
+      <c r="Z143" s="7" t="n"/>
+      <c r="AB143" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC143" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD143" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="4" t="n"/>
+      <c r="V144" s="4" t="n"/>
+      <c r="X144" s="4" t="n"/>
+      <c r="Y144" s="4" t="n"/>
+      <c r="Z144" s="4" t="n"/>
+      <c r="AB144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD144" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="T145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
+      <c r="X145" s="7" t="n"/>
+      <c r="Y145" s="7" t="n"/>
+      <c r="Z145" s="7" t="n"/>
+      <c r="AB145" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC145" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD145" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
+      <c r="X146" s="4" t="n"/>
+      <c r="Y146" s="4" t="n"/>
+      <c r="Z146" s="4" t="n"/>
+      <c r="AB146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD146" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="T147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
+      <c r="X147" s="7" t="n"/>
+      <c r="Y147" s="7" t="n"/>
+      <c r="Z147" s="7" t="n"/>
+      <c r="AB147" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC147" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD147" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -6076,7 +6849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6264,7 +7037,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -6350,7 +7123,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -6436,7 +7209,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -6514,7 +7287,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -6587,7 +7360,7 @@
         <v>25421</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -6600,7 +7373,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -6673,7 +7446,7 @@
         <v>36128</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -6686,7 +7459,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -6713,21 +7486,53 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="D8">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C8)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C8)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>ROUND(MAX(0,MIN(100,(1-E8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>MIN(1,(G8-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C8)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>MAX(0,(L8-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>$B$2+H8+M8</f>
+        <v/>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1530</v>
+        <v>51111</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -6761,7 +7566,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -6770,19 +7575,19 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2311</v>
+        <v>1530</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -6817,7 +7622,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -6826,19 +7631,19 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2868</v>
+        <v>2311</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -6863,7 +7668,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -6872,14 +7677,14 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>4059</v>
+        <v>2868</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -6909,7 +7714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -6918,14 +7723,14 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>5092</v>
+        <v>4059</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -6955,7 +7760,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -6964,14 +7769,14 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>6962</v>
+        <v>5092</v>
       </c>
       <c r="X13" t="n">
         <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -7001,28 +7806,28 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1815</v>
+        <v>6962</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -7047,28 +7852,28 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2333</v>
+        <v>9959</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -7093,7 +7898,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -7102,19 +7907,19 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>3182</v>
+        <v>1815</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -7139,7 +7944,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -7148,14 +7953,14 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>4129</v>
+        <v>2333</v>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -7185,7 +7990,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -7194,14 +7999,14 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>5644</v>
+        <v>3182</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -7231,7 +8036,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -7240,14 +8045,14 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>7963</v>
+        <v>4129</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -7277,23 +8082,23 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>2322</v>
+        <v>5644</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -7323,23 +8128,23 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>3533</v>
+        <v>7963</v>
       </c>
       <c r="X21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -7369,28 +8174,28 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>4891</v>
+        <v>11169</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -7415,7 +8220,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -7424,23 +8229,23 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>6461</v>
+        <v>2322</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -7461,7 +8266,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -7470,19 +8275,19 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>8274</v>
+        <v>3533</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -7507,7 +8312,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -7516,23 +8321,23 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>12174</v>
+        <v>4891</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -7553,32 +8358,32 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>1827</v>
+        <v>6461</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -7599,23 +8404,23 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>2275</v>
+        <v>8274</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -7624,7 +8429,7 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -7645,32 +8450,32 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>12174</v>
+      </c>
+      <c r="X28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>2882</v>
-      </c>
-      <c r="X28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -7691,32 +8496,32 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>19723</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>3280</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
         <v>1</v>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB29" t="n">
-        <v>21</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -7737,7 +8542,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -7746,23 +8551,23 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>3951</v>
+        <v>1827</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -7783,7 +8588,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -7792,19 +8597,19 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>5096</v>
+        <v>2275</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -7844,28 +8649,28 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>250</v>
+        <v>2882</v>
       </c>
       <c r="X32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -7884,7 +8689,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D7)</f>
+        <f>AVERAGE(D2:D8)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -7892,7 +8697,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H7)</f>
+        <f>AVERAGE(H2:H8)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -7913,32 +8718,32 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>428</v>
+        <v>3280</v>
       </c>
       <c r="X33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -7954,32 +8759,32 @@
     <row r="34">
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>365</v>
+        <v>3951</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -7995,28 +8800,28 @@
     <row r="35">
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>471</v>
+        <v>5096</v>
       </c>
       <c r="X35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -8036,23 +8841,23 @@
     <row r="36">
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>554</v>
+        <v>6277</v>
       </c>
       <c r="X36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -8061,7 +8866,7 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -8077,7 +8882,7 @@
     <row r="37">
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8086,23 +8891,23 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>902</v>
+        <v>250</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -8118,19 +8923,19 @@
     <row r="38">
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>6249</v>
+        <v>428</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -8139,7 +8944,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -8159,28 +8964,28 @@
     <row r="39">
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>8329</v>
+        <v>365</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -8200,32 +9005,32 @@
     <row r="40">
       <c r="T40" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>471</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -8241,32 +9046,32 @@
     <row r="41">
       <c r="T41" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>554</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>13894</v>
-      </c>
-      <c r="X41" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -8282,28 +9087,28 @@
     <row r="42">
       <c r="T42" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>902</v>
+      </c>
+      <c r="X42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>17235</v>
-      </c>
-      <c r="X42" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -8323,32 +9128,32 @@
     <row r="43">
       <c r="T43" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>1420</v>
+      </c>
+      <c r="X43" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>23145</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -8369,27 +9174,27 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>30</v>
+        <v>6249</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -8410,18 +9215,18 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>81</v>
+        <v>8329</v>
       </c>
       <c r="X45" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -8430,7 +9235,7 @@
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8451,18 +9256,18 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>103</v>
+        <v>10619</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -8492,18 +9297,18 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>154</v>
+        <v>13894</v>
       </c>
       <c r="X47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -8512,7 +9317,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -8533,18 +9338,18 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>183</v>
+        <v>17235</v>
       </c>
       <c r="X48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -8574,23 +9379,23 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>238</v>
+        <v>23145</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -8610,32 +9415,32 @@
     <row r="50">
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>603</v>
+        <v>32675</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -8651,32 +9456,32 @@
     <row r="51">
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>820</v>
+        <v>30</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -8692,32 +9497,32 @@
     <row r="52">
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>1204</v>
+        <v>81</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -8733,32 +9538,32 @@
     <row r="53">
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>1689</v>
+        <v>103</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -8774,28 +9579,28 @@
     <row r="54">
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>2042</v>
+        <v>154</v>
       </c>
       <c r="X54" t="n">
         <v>1</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8815,28 +9620,28 @@
     <row r="55">
       <c r="T55" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>183</v>
+      </c>
+      <c r="X55" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>2581</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8856,32 +9661,32 @@
     <row r="56">
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>90</v>
+        <v>238</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -8897,32 +9702,32 @@
     <row r="57">
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -8938,32 +9743,32 @@
     <row r="58">
       <c r="T58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>157</v>
+        <v>603</v>
       </c>
       <c r="X58" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
         <v>2</v>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB58" t="n">
-        <v>17</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -8979,16 +9784,29 @@
     <row r="59">
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>244</v>
+        <v>820</v>
+      </c>
+      <c r="X59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB59" t="n">
         <v>1</v>
@@ -9007,19 +9825,32 @@
     <row r="60">
       <c r="T60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>270</v>
+        <v>1204</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -9035,62 +9866,153 @@
     <row r="61">
       <c r="T61" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>1689</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>2042</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="T63" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>341</v>
-      </c>
-      <c r="AB61" t="n">
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>2581</v>
+      </c>
+      <c r="X63" t="n">
         <v>1</v>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD61" t="inlineStr">
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="AB62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="AB63" t="n">
-        <v>49</v>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>3880</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB64" t="n">
         <v>2</v>
       </c>
@@ -9106,6 +10028,32 @@
       </c>
     </row>
     <row r="65">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>90</v>
+      </c>
+      <c r="X65" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB65" t="n">
         <v>3</v>
       </c>
@@ -9121,83 +10069,213 @@
       </c>
     </row>
     <row r="66">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>119</v>
+      </c>
+      <c r="X66" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>157</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
         <v>140</v>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="AB67" t="n">
+    <row r="68">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>244</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>270</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>341</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>409</v>
+      </c>
+      <c r="AB71" t="n">
         <v>3</v>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="AB68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="AB69" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="AB70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="AB71" t="n">
-        <v>58</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -9212,7 +10290,7 @@
     </row>
     <row r="72">
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -9272,7 +10350,7 @@
     </row>
     <row r="76">
       <c r="AB76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
@@ -9287,7 +10365,7 @@
     </row>
     <row r="77">
       <c r="AB77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -9467,7 +10545,7 @@
     </row>
     <row r="89">
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -9482,7 +10560,7 @@
     </row>
     <row r="90">
       <c r="AB90" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -9512,7 +10590,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -9527,7 +10605,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -9602,7 +10680,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -9632,7 +10710,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -9662,7 +10740,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -9677,7 +10755,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -9700,6 +10778,246 @@
         </is>
       </c>
       <c r="AD104" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="AB105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="AB106" t="n">
+        <v>196</v>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="AB107" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="AB108" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="AB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="AB110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="AB111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="AB112" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="AB113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="AB114" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="AB115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="AB116" t="n">
+        <v>111</v>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="AB117" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="AB119" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="AB120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1386,7 +1388,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1471,7 +1473,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1556,7 +1558,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1635,7 +1637,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1707,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
@@ -1720,7 +1722,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1792,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="Y7" s="7" t="inlineStr">
         <is>
@@ -1805,7 +1807,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1890,7 +1892,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1949,7 +1951,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2075,7 +2077,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2901,7 +2903,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2960,7 +2962,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3019,7 +3021,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3078,7 +3080,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -3137,7 +3139,7 @@
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
@@ -3255,7 +3257,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3323,7 +3325,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3547,7 +3549,7 @@
         <v>50559</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
@@ -3588,7 +3590,7 @@
         <v>51501</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3629,7 +3631,7 @@
         <v>51715</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
@@ -3670,7 +3672,7 @@
         <v>50240</v>
       </c>
       <c r="X40" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
@@ -3765,7 +3767,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3793,7 +3795,7 @@
         <v>51004</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
@@ -3806,7 +3808,7 @@
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>276</v>
+        <v>2</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
@@ -3834,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="X44" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
@@ -3847,7 +3849,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3970,7 +3972,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -3998,7 +4000,7 @@
         <v>11614</v>
       </c>
       <c r="X48" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
@@ -4011,7 +4013,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4039,7 +4041,7 @@
         <v>11098</v>
       </c>
       <c r="X49" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
@@ -4367,7 +4369,7 @@
         <v>25267</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
@@ -4408,7 +4410,7 @@
         <v>24712</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4449,7 +4451,7 @@
         <v>26356</v>
       </c>
       <c r="X59" s="7" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
@@ -4490,7 +4492,7 @@
         <v>17949</v>
       </c>
       <c r="X60" s="4" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
@@ -4572,7 +4574,7 @@
         <v>17646</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -4654,7 +4656,7 @@
         <v>17470</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
@@ -4667,7 +4669,7 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4695,7 +4697,7 @@
         <v>17485</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
@@ -4708,7 +4710,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4738,7 @@
         <v>17825</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
@@ -4749,7 +4751,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4790,7 +4792,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4818,7 +4820,7 @@
         <v>763</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Y68" s="4" t="inlineStr">
         <is>
@@ -4831,7 +4833,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4859,7 +4861,7 @@
         <v>740</v>
       </c>
       <c r="X69" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
@@ -4872,7 +4874,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4913,7 +4915,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4941,7 +4943,7 @@
         <v>763</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
@@ -4982,7 +4984,7 @@
         <v>735</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
@@ -5023,7 +5025,7 @@
         <v>841</v>
       </c>
       <c r="X73" s="7" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
@@ -5077,7 +5079,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5105,7 +5107,7 @@
         <v>2408</v>
       </c>
       <c r="X75" s="7" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
@@ -5159,7 +5161,7 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -5571,7 +5573,7 @@
         </is>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -5602,7 +5604,7 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -5686,7 +5688,7 @@
       <c r="Y93" s="7" t="n"/>
       <c r="Z93" s="7" t="n"/>
       <c r="AB93" s="7" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5707,7 +5709,7 @@
       <c r="Y94" s="4" t="n"/>
       <c r="Z94" s="4" t="n"/>
       <c r="AB94" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -5728,7 +5730,7 @@
       <c r="Y95" s="7" t="n"/>
       <c r="Z95" s="7" t="n"/>
       <c r="AB95" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -6001,7 +6003,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6043,7 +6045,7 @@
       <c r="Y110" s="4" t="n"/>
       <c r="Z110" s="4" t="n"/>
       <c r="AB110" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6148,7 +6150,7 @@
       <c r="Y115" s="7" t="n"/>
       <c r="Z115" s="7" t="n"/>
       <c r="AB115" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6169,7 +6171,7 @@
       <c r="Y116" s="4" t="n"/>
       <c r="Z116" s="4" t="n"/>
       <c r="AB116" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -6358,7 +6360,7 @@
       <c r="Y125" s="7" t="n"/>
       <c r="Z125" s="7" t="n"/>
       <c r="AB125" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
@@ -6379,7 +6381,7 @@
       <c r="Y126" s="4" t="n"/>
       <c r="Z126" s="4" t="n"/>
       <c r="AB126" s="4" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -6400,7 +6402,7 @@
       <c r="Y127" s="7" t="n"/>
       <c r="Z127" s="7" t="n"/>
       <c r="AB127" s="7" t="n">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
@@ -6421,7 +6423,7 @@
       <c r="Y128" s="4" t="n"/>
       <c r="Z128" s="4" t="n"/>
       <c r="AB128" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6442,7 +6444,7 @@
       <c r="Y129" s="7" t="n"/>
       <c r="Z129" s="7" t="n"/>
       <c r="AB129" s="7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6463,7 +6465,7 @@
       <c r="Y130" s="4" t="n"/>
       <c r="Z130" s="4" t="n"/>
       <c r="AB130" s="4" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -6484,7 +6486,7 @@
       <c r="Y131" s="7" t="n"/>
       <c r="Z131" s="7" t="n"/>
       <c r="AB131" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -6505,7 +6507,7 @@
       <c r="Y132" s="4" t="n"/>
       <c r="Z132" s="4" t="n"/>
       <c r="AB132" s="4" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -6526,7 +6528,7 @@
       <c r="Y133" s="7" t="n"/>
       <c r="Z133" s="7" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6547,7 +6549,7 @@
       <c r="Y134" s="4" t="n"/>
       <c r="Z134" s="4" t="n"/>
       <c r="AB134" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -6568,7 +6570,7 @@
       <c r="Y135" s="7" t="n"/>
       <c r="Z135" s="7" t="n"/>
       <c r="AB135" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -6589,7 +6591,7 @@
       <c r="Y136" s="4" t="n"/>
       <c r="Z136" s="4" t="n"/>
       <c r="AB136" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -6631,7 +6633,7 @@
       <c r="Y138" s="4" t="n"/>
       <c r="Z138" s="4" t="n"/>
       <c r="AB138" s="4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -6652,7 +6654,7 @@
       <c r="Y139" s="7" t="n"/>
       <c r="Z139" s="7" t="n"/>
       <c r="AB139" s="7" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -6778,7 +6780,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -6799,7 +6801,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -7360,7 +7362,7 @@
         <v>25421</v>
       </c>
       <c r="X6" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -7446,7 +7448,7 @@
         <v>36128</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -7545,7 +7547,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -7591,7 +7593,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -7785,7 +7787,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -7831,7 +7833,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -8140,7 +8142,7 @@
         <v>7963</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -8186,7 +8188,7 @@
         <v>11169</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -8291,7 +8293,7 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -8324,7 +8326,7 @@
         <v>4891</v>
       </c>
       <c r="X25" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -8337,7 +8339,7 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -8370,7 +8372,7 @@
         <v>6461</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -8508,7 +8510,7 @@
         <v>19723</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -8554,7 +8556,7 @@
         <v>1827</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -8661,7 +8663,7 @@
         <v>2882</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -8730,7 +8732,7 @@
         <v>3280</v>
       </c>
       <c r="X33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -8866,7 +8868,7 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -8894,20 +8896,20 @@
         <v>250</v>
       </c>
       <c r="X37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
         <v>1</v>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v>43</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -8935,7 +8937,7 @@
         <v>428</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -8948,7 +8950,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -8989,7 +8991,7 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9030,7 +9032,7 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9891,7 +9893,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -9932,7 +9934,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9973,7 +9975,7 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -10247,7 +10249,7 @@
         <v>341</v>
       </c>
       <c r="AB70" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -10275,7 +10277,7 @@
         <v>409</v>
       </c>
       <c r="AB71" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -10290,7 +10292,7 @@
     </row>
     <row r="72">
       <c r="AB72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -10305,7 +10307,7 @@
     </row>
     <row r="73">
       <c r="AB73" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -10335,7 +10337,7 @@
     </row>
     <row r="75">
       <c r="AB75" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -10395,7 +10397,7 @@
     </row>
     <row r="79">
       <c r="AB79" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -10410,7 +10412,7 @@
     </row>
     <row r="80">
       <c r="AB80" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -10545,7 +10547,7 @@
     </row>
     <row r="89">
       <c r="AB89" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -10560,7 +10562,7 @@
     </row>
     <row r="90">
       <c r="AB90" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -10575,7 +10577,7 @@
     </row>
     <row r="91">
       <c r="AB91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -10590,7 +10592,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -10605,7 +10607,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -10680,7 +10682,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -10710,7 +10712,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -10740,7 +10742,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -10755,7 +10757,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -10830,7 +10832,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -10845,7 +10847,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -10860,7 +10862,7 @@
     </row>
     <row r="110">
       <c r="AB110" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -10890,7 +10892,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -10950,7 +10952,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -10965,7 +10967,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -11554,4 +11556,1618 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>CFU part in AQS</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="C1" s="32" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>Total users count (ios_User_Count)</t>
+        </is>
+      </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>Crashed users count (Query)</t>
+        </is>
+      </c>
+      <c r="G1" s="32" t="inlineStr">
+        <is>
+          <t>CFU %</t>
+        </is>
+      </c>
+      <c r="K1" s="32" t="inlineStr">
+        <is>
+          <t>Hang user count (Query)</t>
+        </is>
+      </c>
+      <c r="L1" s="32" t="inlineStr">
+        <is>
+          <t>Hang free %</t>
+        </is>
+      </c>
+      <c r="N1" s="32" t="inlineStr">
+        <is>
+          <t>Projected AQS including hangs</t>
+        </is>
+      </c>
+      <c r="T1" s="33" t="inlineStr">
+        <is>
+          <t>dt</t>
+        </is>
+      </c>
+      <c r="U1" s="33" t="inlineStr">
+        <is>
+          <t>appId</t>
+        </is>
+      </c>
+      <c r="V1" s="33" t="inlineStr">
+        <is>
+          <t>user_count</t>
+        </is>
+      </c>
+      <c r="X1" s="34" t="inlineStr">
+        <is>
+          <t>CRASH_USERS</t>
+        </is>
+      </c>
+      <c r="Y1" s="34" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="Z1" s="34" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="AB1" s="35" t="inlineStr">
+        <is>
+          <t>HANG_USERS</t>
+        </is>
+      </c>
+      <c r="AC1" s="35" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="AD1" s="35" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>base AQS score</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D2">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C2)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C2)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>ROUND(MAX(0,MIN(100,(1-E2/IF(D2&gt;0,D2,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>MIN(1,(G2-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C2)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K2/IF(D2&gt;0,D2,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>MAX(0,(L2-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>$B$2+H2+M2</f>
+        <v/>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>CFU minimum</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D3">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C3)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C3)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>ROUND(MAX(0,MIN(100,(1-E3/IF(D3&gt;0,D3,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>MIN(1,(G3-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C3)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K3/IF(D3&gt;0,D3,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>MAX(0,(L3-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>$B$2+H3+M3</f>
+        <v/>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>3208</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>CFU maximum</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C4)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C4)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>ROUND(MAX(0,MIN(100,(1-E4/IF(D4&gt;0,D4,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>MIN(1,(G4-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C4)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K4/IF(D4&gt;0,D4,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>MAX(0,(L4-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>$B$2+H4+M4</f>
+        <v/>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D5">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C5)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C5)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>ROUND(MAX(0,MIN(100,(1-E5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>MIN(1,(G5-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C5)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K5/IF(D5&gt;0,D5,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>MAX(0,(L5-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>$B$2+H5+M5</f>
+        <v/>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>705</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Hang minimum</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D6">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C6)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C6)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>ROUND(MAX(0,MIN(100,(1-E6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>MIN(1,(G6-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C6)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K6/IF(D6&gt;0,D6,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>MAX(0,(L6-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>$B$2+H6+M6</f>
+        <v/>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Hang maximum</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C7)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C7)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>ROUND(MAX(0,MIN(100,(1-E7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>MIN(1,(G7-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C7)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K7/IF(D7&gt;0,D7,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>MAX(0,(L7-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>$B$2+H7+M7</f>
+        <v/>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>969</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Hang part in AQS</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D8">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C8)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C8)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>ROUND(MAX(0,MIN(100,(1-E8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>MIN(1,(G8-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C8)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K8/IF(D8&gt;0,D8,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>MAX(0,(L8-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>$B$2+H8+M8</f>
+        <v/>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>woowa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="G32" s="36" t="inlineStr">
+        <is>
+          <t>AVG CFU</t>
+        </is>
+      </c>
+      <c r="I32" s="36" t="inlineStr">
+        <is>
+          <t>September AQS score</t>
+        </is>
+      </c>
+      <c r="L32" s="36" t="inlineStr">
+        <is>
+          <t>AVG Hang-free</t>
+        </is>
+      </c>
+      <c r="N32" s="36" t="inlineStr">
+        <is>
+          <t>Projected AQS including hangs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33">
+        <f>AVERAGE(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="G33" s="37">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*")/IF(SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*")&gt;0,SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"),SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>AVERAGE(H2:H8)</f>
+        <v/>
+      </c>
+      <c r="I33" s="38">
+        <f>$B$2+H33</f>
+        <v/>
+      </c>
+      <c r="L33" s="37">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*")/IF(SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*")&gt;0,SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*"),SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>MAX(0,(L33-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N33" s="38">
+        <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"foodora,woowa,foodpanda,talabat,efood,glovo,hungerstation,yemek,foody,pedidosya"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Crash free users</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>App Hangs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>App size</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ASTI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>STTI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Frozen Frames</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Skipped Frames</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Riders count</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Weight Rider ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Foodpanda</t>
+        </is>
+      </c>
+      <c r="B2" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A2&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A2&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A2&amp;"*"),I2*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A2&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A2&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A2&amp;"*"),I2*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>78203</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0.3966</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Foodora</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A3&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A3&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A3&amp;"*"),I3*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A3&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A3&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A3&amp;"*"),I3*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>14946</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Talabat</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A4&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A4&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A4&amp;"*"),I4*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C4" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A4&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A4&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A4&amp;"*"),I4*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>16988</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.0861</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>pedidosya</t>
+        </is>
+      </c>
+      <c r="B5" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A5&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A5&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A5&amp;"*"),I5*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A5&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A5&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A5&amp;"*"),I5*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>20641</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.1047</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>HungerStation</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A6&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A6&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A6&amp;"*"),I6*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A6&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A6&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A6&amp;"*"),I6*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>10630</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.0539</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Yemeksepeti</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A7&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A7&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A7&amp;"*"),I7*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A7&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A7&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A7&amp;"*"),I7*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2186</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0.0111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A8&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A8&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A8&amp;"*"),I8*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C8" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A8&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A8&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A8&amp;"*"),I8*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>46896</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.2378</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Woowa</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A9&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A9&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A9&amp;"*"),I9*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A9&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A9&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A9&amp;"*"),I9*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>731</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>efood</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A10&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A10&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A10&amp;"*"),I10*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A10&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A10&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A10&amp;"*"),I10*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>5258</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.0267</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Foody</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$X:$X,'v4.2637.1'!$Z:$Z,"*"&amp;$A11&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A11&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A11&amp;"*"),I11*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>TRUNC(MAX(0,MIN(100,(1-SUMIFS('v4.2637.1'!$AB:$AB,'v4.2637.1'!$AD:$AD,"*"&amp;$A11&amp;"*")/IF(SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A11&amp;"*")&gt;0,SUMIFS('v4.2637.1'!$V:$V,'v4.2637.1'!$U:$U,"*"&amp;$A11&amp;"*"),I11*30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>729</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>TRUNC(SUMPRODUCT(B2:B11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>TRUNC(SUMPRODUCT(C2:C11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>TRUNC(SUMPRODUCT(D2:D11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="E12" s="10">
+        <f>TRUNC(SUMPRODUCT(E2:E11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="10">
+        <f>TRUNC(SUMPRODUCT(F2:F11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>TRUNC(SUMPRODUCT(G2:G11,J2:J11),2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>TRUNC(SUMPRODUCT(H2:H11,J2:J11),2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>AQS</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>MIN(100,MAX(0,(((B12-99.7)/(99.9-99.7))*50)+50))*35%</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>MIN(100,MAX(0,(((C12-99.7)/(99.9-99.7))*50)+50))*25%</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>MIN(100,MAX(0,(((D12-75)/(60-75))*50)+50))*2%</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>MIN(100,MAX(0,(((E12-4)/(2-4))*50)+50))*10%</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>MIN(100,MAX(0,(((F12-1.5)/(0.5-1.5))*50)+50))*10%</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>MIN(100,MAX(0,(((G12-3)/(1-3))*50)+50))*13%</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
+        <f>MIN(100,MAX(0,(((H12-2)/(1-2))*50)+50))*5%</f>
+        <v/>
+      </c>
+      <c r="J13" s="13">
+        <f>SUM(J2:J11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>FINAL AQS =</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <f>ROUND(SUM(B13:H13),2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -737,10 +737,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -773,10 +773,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -809,10 +809,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -845,10 +845,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -881,10 +881,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -917,10 +917,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -953,10 +953,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -989,10 +989,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1025,10 +1025,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1061,10 +1061,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1365,15 +1365,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>68</v>
       </c>
@@ -1450,15 +1444,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>68</v>
       </c>
@@ -1535,15 +1523,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>91</v>
       </c>
@@ -1558,7 +1540,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1614,15 +1596,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>75</v>
       </c>
@@ -1637,7 +1613,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1699,15 +1675,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>1</v>
       </c>
@@ -1784,15 +1754,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>88</v>
       </c>
@@ -1807,7 +1771,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1869,15 +1833,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>115</v>
       </c>
@@ -1892,7 +1850,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1924,19 +1882,9 @@
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>5519</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>72</v>
       </c>
@@ -1951,7 +1899,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -1991,19 +1939,9 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>5569</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>1</v>
       </c>
@@ -2018,7 +1956,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2050,19 +1988,9 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>5621</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>3</v>
       </c>
@@ -2109,19 +2037,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>14</v>
       </c>
@@ -2136,7 +2054,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2168,19 +2086,9 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>5196</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>12</v>
       </c>
@@ -2195,7 +2103,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2227,19 +2135,9 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>5203</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>14</v>
       </c>
@@ -2286,19 +2184,9 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>5687</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>16</v>
       </c>
@@ -2345,19 +2233,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>15184</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>12</v>
       </c>
@@ -2404,19 +2282,9 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>15708</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>10</v>
       </c>
@@ -2463,19 +2331,9 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>15056</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>13</v>
       </c>
@@ -2522,21 +2380,11 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>15493</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
@@ -2581,21 +2429,11 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>14553</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
@@ -2640,19 +2478,9 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>14491</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>36</v>
       </c>
@@ -2699,21 +2527,11 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>15132</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
@@ -2758,21 +2576,11 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>87207</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
@@ -2785,7 +2593,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2817,21 +2625,11 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>86030</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
@@ -2844,7 +2642,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -2876,21 +2674,11 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>82667</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
@@ -2903,7 +2691,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2935,21 +2723,11 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>82796</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
@@ -2962,7 +2740,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2994,19 +2772,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>80792</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>1</v>
       </c>
@@ -3021,7 +2789,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3053,21 +2821,11 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>80181</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
@@ -3112,19 +2870,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>82769</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>41</v>
       </c>
@@ -3171,19 +2919,9 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
         <v>2</v>
       </c>
@@ -3230,19 +2968,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>729</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3298,21 +3026,11 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
@@ -3371,21 +3089,11 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>753</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
@@ -3412,19 +3120,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>15</v>
       </c>
@@ -3453,19 +3151,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>723</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>2</v>
       </c>
@@ -3494,19 +3182,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>8</v>
       </c>
@@ -3535,21 +3213,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>50559</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
@@ -3576,21 +3244,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>51501</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3617,19 +3275,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>51715</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>27</v>
       </c>
@@ -3658,19 +3306,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>50240</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>1</v>
       </c>
@@ -3699,21 +3337,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>48948</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
@@ -3740,21 +3368,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>48922</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
@@ -3767,7 +3385,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3781,19 +3399,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>51004</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>3</v>
       </c>
@@ -3822,19 +3430,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>25</v>
       </c>
@@ -3849,7 +3447,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3863,19 +3461,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>13</v>
       </c>
@@ -3904,19 +3492,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>11599</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>2</v>
       </c>
@@ -3945,19 +3523,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>11522</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>19</v>
       </c>
@@ -3986,19 +3554,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>11614</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>21</v>
       </c>
@@ -4027,19 +3585,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>11098</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>1</v>
       </c>
@@ -4054,7 +3602,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4068,19 +3616,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>11097</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>3</v>
       </c>
@@ -4109,19 +3647,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>11410</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>19</v>
       </c>
@@ -4136,7 +3664,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4150,19 +3678,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>11482</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>21</v>
       </c>
@@ -4191,19 +3709,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>26509</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>15</v>
       </c>
@@ -4218,7 +3726,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4232,19 +3740,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>26876</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>14</v>
       </c>
@@ -4259,7 +3757,7 @@
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
@@ -4273,19 +3771,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>27154</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>2</v>
       </c>
@@ -4314,19 +3802,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>26655</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>13</v>
       </c>
@@ -4355,21 +3833,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>25267</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
@@ -4396,21 +3864,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>24712</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4437,21 +3895,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>26356</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
@@ -4478,19 +3926,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>17949</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>2</v>
       </c>
@@ -4519,21 +3957,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>17549</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
@@ -4560,21 +3988,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>17646</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -4601,19 +4019,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>17131</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>49</v>
       </c>
@@ -4628,136 +4036,106 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
+      <c r="X64" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AC63" s="7" t="inlineStr">
+      <c r="Y64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD63" s="7" t="inlineStr">
+      <c r="AD64" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>17470</v>
-      </c>
-      <c r="X64" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z64" s="4" t="inlineStr">
+    <row r="65">
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
+      <c r="X65" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z65" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB64" s="4" t="n">
-        <v>316</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr">
+      <c r="AB65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD64" s="4" t="inlineStr">
+      <c r="AD65" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>17485</v>
-      </c>
-      <c r="X65" s="7" t="n">
+    <row r="66">
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
+      <c r="X66" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Y65" s="7" t="inlineStr">
+      <c r="Y66" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="Z65" s="7" t="inlineStr">
+      <c r="Z66" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB65" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC65" s="7" t="inlineStr">
+      <c r="AB66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>17825</v>
-      </c>
-      <c r="X66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB66" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="AD66" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
@@ -4765,19 +4143,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>745</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>58</v>
       </c>
@@ -4792,7 +4160,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4806,62 +4174,42 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>763</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD68" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
+      <c r="X69" s="7" t="n">
         <v>58</v>
-      </c>
-      <c r="Y68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB68" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="AC68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>740</v>
-      </c>
-      <c r="X69" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
@@ -4888,103 +4236,73 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
+      <c r="X70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>783</v>
-      </c>
-      <c r="X70" s="4" t="n">
+      <c r="AD70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
+      <c r="X71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB71" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>763</v>
-      </c>
-      <c r="X71" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y71" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB71" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC71" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>735</v>
-      </c>
-      <c r="X72" s="4" t="n">
-        <v>70</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
@@ -5011,34 +4329,24 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
+      <c r="X73" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y73" s="7" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>841</v>
-      </c>
-      <c r="X73" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y73" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z73" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5052,19 +4360,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>2142</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>6</v>
       </c>
@@ -5079,74 +4377,54 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
+      <c r="X75" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y75" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z75" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB75" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr">
+      <c r="AC75" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD74" s="4" t="inlineStr">
+      <c r="AD75" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>2408</v>
-      </c>
-      <c r="X75" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB75" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="AC75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>2141</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>1</v>
       </c>
@@ -5161,7 +4439,7 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -5175,19 +4453,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>2082</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>9</v>
       </c>
@@ -5216,19 +4484,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>1990</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>6</v>
       </c>
@@ -5257,19 +4515,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>2043</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>1</v>
       </c>
@@ -5298,19 +4546,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>2148</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>4</v>
       </c>
@@ -5511,7 +4749,7 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5542,7 +4780,7 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
@@ -5625,7 +4863,7 @@
       <c r="Y90" s="4" t="n"/>
       <c r="Z90" s="4" t="n"/>
       <c r="AB90" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5646,7 +4884,7 @@
       <c r="Y91" s="7" t="n"/>
       <c r="Z91" s="7" t="n"/>
       <c r="AB91" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -5688,7 +4926,7 @@
       <c r="Y93" s="7" t="n"/>
       <c r="Z93" s="7" t="n"/>
       <c r="AB93" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5709,7 +4947,7 @@
       <c r="Y94" s="4" t="n"/>
       <c r="Z94" s="4" t="n"/>
       <c r="AB94" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -5898,7 +5136,7 @@
       <c r="Y103" s="7" t="n"/>
       <c r="Z103" s="7" t="n"/>
       <c r="AB103" s="7" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -5919,7 +5157,7 @@
       <c r="Y104" s="4" t="n"/>
       <c r="Z104" s="4" t="n"/>
       <c r="AB104" s="4" t="n">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
@@ -6003,7 +5241,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6024,7 +5262,7 @@
       <c r="Y109" s="7" t="n"/>
       <c r="Z109" s="7" t="n"/>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6045,7 +5283,7 @@
       <c r="Y110" s="4" t="n"/>
       <c r="Z110" s="4" t="n"/>
       <c r="AB110" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6066,7 +5304,7 @@
       <c r="Y111" s="7" t="n"/>
       <c r="Z111" s="7" t="n"/>
       <c r="AB111" s="7" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6087,7 +5325,7 @@
       <c r="Y112" s="4" t="n"/>
       <c r="Z112" s="4" t="n"/>
       <c r="AB112" s="4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6129,7 +5367,7 @@
       <c r="Y114" s="4" t="n"/>
       <c r="Z114" s="4" t="n"/>
       <c r="AB114" s="4" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6150,7 +5388,7 @@
       <c r="Y115" s="7" t="n"/>
       <c r="Z115" s="7" t="n"/>
       <c r="AB115" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6171,7 +5409,7 @@
       <c r="Y116" s="4" t="n"/>
       <c r="Z116" s="4" t="n"/>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -6423,7 +5661,7 @@
       <c r="Y128" s="4" t="n"/>
       <c r="Z128" s="4" t="n"/>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6444,7 +5682,7 @@
       <c r="Y129" s="7" t="n"/>
       <c r="Z129" s="7" t="n"/>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6570,7 +5808,7 @@
       <c r="Y135" s="7" t="n"/>
       <c r="Z135" s="7" t="n"/>
       <c r="AB135" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -6591,7 +5829,7 @@
       <c r="Y136" s="4" t="n"/>
       <c r="Z136" s="4" t="n"/>
       <c r="AB136" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -6612,7 +5850,7 @@
       <c r="Y137" s="7" t="n"/>
       <c r="Z137" s="7" t="n"/>
       <c r="AB137" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -6654,7 +5892,7 @@
       <c r="Y139" s="7" t="n"/>
       <c r="Z139" s="7" t="n"/>
       <c r="AB139" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -6780,7 +6018,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -6801,7 +6039,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -7012,19 +6250,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>7773</v>
-      </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
@@ -7039,7 +6264,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -7098,19 +6323,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10781</v>
-      </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
@@ -7125,7 +6337,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -7184,19 +6396,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>14077</v>
-      </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
@@ -7262,19 +6461,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>19486</v>
-      </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
@@ -7348,19 +6534,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>25421</v>
-      </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -7434,19 +6607,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>36128</v>
-      </c>
       <c r="X7" t="n">
         <v>35</v>
       </c>
@@ -7520,19 +6680,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>51111</v>
-      </c>
       <c r="X8" t="n">
         <v>55</v>
       </c>
@@ -7547,7 +6694,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -7566,19 +6713,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>1530</v>
-      </c>
       <c r="X9" t="n">
         <v>41</v>
       </c>
@@ -7593,7 +6727,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -7622,19 +6756,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>2311</v>
-      </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
@@ -7668,19 +6789,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2868</v>
-      </c>
       <c r="X11" t="n">
         <v>6</v>
       </c>
@@ -7714,19 +6822,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>4059</v>
-      </c>
       <c r="X12" t="n">
         <v>4</v>
       </c>
@@ -7760,19 +6855,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>5092</v>
-      </c>
       <c r="X13" t="n">
         <v>5</v>
       </c>
@@ -7806,19 +6888,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>6962</v>
-      </c>
       <c r="X14" t="n">
         <v>5</v>
       </c>
@@ -7852,19 +6921,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>9959</v>
-      </c>
       <c r="X15" t="n">
         <v>5</v>
       </c>
@@ -7898,19 +6954,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>1815</v>
-      </c>
       <c r="X16" t="n">
         <v>10</v>
       </c>
@@ -7944,19 +6987,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>2333</v>
-      </c>
       <c r="X17" t="n">
         <v>2</v>
       </c>
@@ -7990,19 +7020,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>3182</v>
-      </c>
       <c r="X18" t="n">
         <v>6</v>
       </c>
@@ -8036,19 +7053,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>4129</v>
-      </c>
       <c r="X19" t="n">
         <v>20</v>
       </c>
@@ -8082,19 +7086,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>5644</v>
-      </c>
       <c r="X20" t="n">
         <v>9</v>
       </c>
@@ -8128,19 +7119,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>7963</v>
-      </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
@@ -8174,19 +7152,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>11169</v>
-      </c>
       <c r="X22" t="n">
         <v>22</v>
       </c>
@@ -8220,19 +7185,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>2322</v>
-      </c>
       <c r="X23" t="n">
         <v>27</v>
       </c>
@@ -8247,7 +7199,7 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -8266,19 +7218,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>3533</v>
-      </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
@@ -8312,19 +7251,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>4891</v>
-      </c>
       <c r="X25" t="n">
         <v>2</v>
       </c>
@@ -8339,7 +7265,7 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -8358,19 +7284,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>6461</v>
-      </c>
       <c r="X26" t="n">
         <v>44</v>
       </c>
@@ -8385,7 +7298,7 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -8404,19 +7317,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>8274</v>
-      </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
@@ -8431,7 +7331,7 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -8450,19 +7350,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>12174</v>
-      </c>
       <c r="X28" t="n">
         <v>5</v>
       </c>
@@ -8496,21 +7383,8 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>19723</v>
-      </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -8542,21 +7416,8 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>1827</v>
-      </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -8588,19 +7449,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>2275</v>
-      </c>
       <c r="X31" t="n">
         <v>5</v>
       </c>
@@ -8649,21 +7497,8 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>2882</v>
-      </c>
       <c r="X32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -8718,21 +7553,8 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>3280</v>
-      </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -8759,21 +7581,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>3951</v>
-      </c>
       <c r="X34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -8800,21 +7609,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>5096</v>
-      </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -8841,19 +7637,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>6277</v>
-      </c>
       <c r="X36" t="n">
         <v>1</v>
       </c>
@@ -8882,21 +7665,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>250</v>
-      </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -8923,21 +7693,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>428</v>
-      </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -8964,19 +7721,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>365</v>
-      </c>
       <c r="X39" t="n">
         <v>3</v>
       </c>
@@ -8991,7 +7735,7 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9005,19 +7749,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>471</v>
-      </c>
       <c r="X40" t="n">
         <v>3</v>
       </c>
@@ -9032,7 +7763,7 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9046,19 +7777,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>554</v>
-      </c>
       <c r="X41" t="n">
         <v>8</v>
       </c>
@@ -9073,7 +7791,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9087,19 +7805,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>902</v>
-      </c>
       <c r="X42" t="n">
         <v>7</v>
       </c>
@@ -9128,19 +7833,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>1420</v>
-      </c>
       <c r="X43" t="n">
         <v>8</v>
       </c>
@@ -9169,19 +7861,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>6249</v>
-      </c>
       <c r="X44" t="n">
         <v>7</v>
       </c>
@@ -9210,19 +7889,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>8329</v>
-      </c>
       <c r="X45" t="n">
         <v>5</v>
       </c>
@@ -9237,115 +7903,76 @@
         </is>
       </c>
       <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
         <v>7</v>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="T46" t="inlineStr">
+    <row r="47">
+      <c r="X47" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="V46" t="n">
-        <v>10619</v>
-      </c>
-      <c r="X46" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>13894</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
     </row>
     <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>17235</v>
-      </c>
       <c r="X48" t="n">
         <v>1</v>
       </c>
@@ -9374,19 +8001,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>23145</v>
-      </c>
       <c r="X49" t="n">
         <v>17</v>
       </c>
@@ -9415,21 +8029,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>32675</v>
-      </c>
       <c r="X50" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -9456,21 +8057,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>30</v>
-      </c>
       <c r="X51" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -9497,19 +8085,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>81</v>
-      </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
@@ -9538,19 +8113,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>103</v>
-      </c>
       <c r="X53" t="n">
         <v>31</v>
       </c>
@@ -9579,19 +8141,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V54" t="n">
-        <v>154</v>
-      </c>
       <c r="X54" t="n">
         <v>1</v>
       </c>
@@ -9620,19 +8169,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>183</v>
-      </c>
       <c r="X55" t="n">
         <v>33</v>
       </c>
@@ -9661,19 +8197,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>238</v>
-      </c>
       <c r="X56" t="n">
         <v>2</v>
       </c>
@@ -9688,7 +8211,7 @@
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -9702,19 +8225,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>354</v>
-      </c>
       <c r="X57" t="n">
         <v>4</v>
       </c>
@@ -9729,7 +8239,7 @@
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -9743,19 +8253,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>603</v>
-      </c>
       <c r="X58" t="n">
         <v>43</v>
       </c>
@@ -9770,7 +8267,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -9784,19 +8281,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>820</v>
-      </c>
       <c r="X59" t="n">
         <v>3</v>
       </c>
@@ -9811,7 +8295,7 @@
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -9825,19 +8309,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>1204</v>
-      </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
@@ -9852,7 +8323,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -9866,19 +8337,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>1689</v>
-      </c>
       <c r="X61" t="n">
         <v>1</v>
       </c>
@@ -9893,7 +8351,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -9907,19 +8365,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>2042</v>
-      </c>
       <c r="X62" t="n">
         <v>1</v>
       </c>
@@ -9934,7 +8379,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9948,19 +8393,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V63" t="n">
-        <v>2581</v>
-      </c>
       <c r="X63" t="n">
         <v>1</v>
       </c>
@@ -9989,19 +8421,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>3880</v>
-      </c>
       <c r="X64" t="n">
         <v>1</v>
       </c>
@@ -10030,19 +8449,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>90</v>
-      </c>
       <c r="X65" t="n">
         <v>5</v>
       </c>
@@ -10071,19 +8477,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>119</v>
-      </c>
       <c r="X66" t="n">
         <v>6</v>
       </c>
@@ -10112,19 +8505,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>157</v>
-      </c>
       <c r="X67" t="n">
         <v>1</v>
       </c>
@@ -10153,19 +8533,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V68" t="n">
-        <v>244</v>
-      </c>
       <c r="X68" t="n">
         <v>1</v>
       </c>
@@ -10194,19 +8561,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V69" t="n">
-        <v>270</v>
-      </c>
       <c r="X69" t="n">
         <v>2</v>
       </c>
@@ -10235,19 +8589,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V70" t="n">
-        <v>341</v>
-      </c>
       <c r="AB70" t="n">
         <v>1</v>
       </c>
@@ -10263,19 +8604,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V71" t="n">
-        <v>409</v>
-      </c>
       <c r="AB71" t="n">
         <v>58</v>
       </c>
@@ -10307,7 +8635,7 @@
     </row>
     <row r="73">
       <c r="AB73" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -10337,7 +8665,7 @@
     </row>
     <row r="75">
       <c r="AB75" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -10397,7 +8725,7 @@
     </row>
     <row r="79">
       <c r="AB79" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -10412,7 +8740,7 @@
     </row>
     <row r="80">
       <c r="AB80" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -10592,7 +8920,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -10622,7 +8950,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -10637,7 +8965,7 @@
     </row>
     <row r="95">
       <c r="AB95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -10652,7 +8980,7 @@
     </row>
     <row r="96">
       <c r="AB96" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -10667,7 +8995,7 @@
     </row>
     <row r="97">
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -10682,7 +9010,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -10697,7 +9025,7 @@
     </row>
     <row r="99">
       <c r="AB99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -10712,7 +9040,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -10877,7 +9205,7 @@
     </row>
     <row r="111">
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
@@ -10892,7 +9220,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -10907,7 +9235,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -10922,7 +9250,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -10937,7 +9265,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -10952,7 +9280,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -11725,19 +10053,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="X2" t="n">
         <v>3</v>
       </c>
@@ -11811,19 +10126,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3208</v>
-      </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
@@ -11897,19 +10199,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
       <c r="X4" t="n">
         <v>2</v>
       </c>
@@ -11975,19 +10264,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>705</v>
-      </c>
       <c r="X5" t="n">
         <v>6</v>
       </c>
@@ -12061,19 +10337,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -12147,19 +10410,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>969</v>
-      </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
@@ -12233,19 +10483,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
       <c r="AB8" t="n">
         <v>1</v>
       </c>
@@ -12266,19 +10503,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>1063</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -12296,19 +10520,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
@@ -12316,19 +10527,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>904</v>
-      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -12336,19 +10534,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
@@ -12356,19 +10541,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>113</v>
-      </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
@@ -12376,19 +10548,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
@@ -12396,19 +10555,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>3024</v>
-      </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
@@ -12416,19 +10562,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>34</v>
-      </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
@@ -12436,19 +10569,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="C18" t="inlineStr">
@@ -12456,19 +10576,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>354</v>
-      </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
@@ -12476,38 +10583,12 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="21">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD147"/>
+  <dimension ref="A1:AD167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1913,29 +1913,49 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="D9" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C9)</f>
+        <v/>
+      </c>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="G9" s="7">
+        <f>ROUND(MAX(0,MIN(100,(1-E9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H9" s="7">
+        <f>MIN(1,(G9-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
+      <c r="K9" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M9" s="7">
+        <f>MAX(0,(L9-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="7">
+        <f>$B$2+H9+M9</f>
+        <v/>
+      </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr"/>
       <c r="V9" s="7" t="n">
-        <v>5519</v>
+        <v>1</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>72</v>
@@ -1951,7 +1971,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -1993,7 +2013,7 @@
       <c r="N10" s="4" t="n"/>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
@@ -2002,7 +2022,7 @@
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>5569</v>
+        <v>5519</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>1</v>
@@ -2052,7 +2072,7 @@
       <c r="N11" s="7" t="n"/>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
@@ -2061,7 +2081,7 @@
         </is>
       </c>
       <c r="V11" s="7" t="n">
-        <v>5621</v>
+        <v>5569</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>3</v>
@@ -2077,7 +2097,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2111,7 +2131,7 @@
       <c r="N12" s="4" t="n"/>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -2120,19 +2140,19 @@
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5557</v>
+        <v>5621</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB12" s="4" t="n">
@@ -2170,7 +2190,7 @@
       <c r="N13" s="7" t="n"/>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
@@ -2179,19 +2199,19 @@
         </is>
       </c>
       <c r="V13" s="7" t="n">
-        <v>5196</v>
+        <v>5557</v>
       </c>
       <c r="X13" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z13" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB13" s="7" t="n">
@@ -2229,7 +2249,7 @@
       <c r="N14" s="4" t="n"/>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
@@ -2238,14 +2258,14 @@
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5203</v>
+        <v>5196</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>14</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
@@ -2254,7 +2274,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2288,7 +2308,7 @@
       <c r="N15" s="7" t="n"/>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
@@ -2297,14 +2317,14 @@
         </is>
       </c>
       <c r="V15" s="7" t="n">
-        <v>5687</v>
+        <v>5203</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z15" s="7" t="inlineStr">
@@ -2347,32 +2367,32 @@
       <c r="N16" s="4" t="n"/>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>5687</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V16" s="4" t="n">
-        <v>15184</v>
-      </c>
-      <c r="X16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
       <c r="AB16" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2406,23 +2426,23 @@
       <c r="N17" s="7" t="n"/>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V17" s="7" t="n">
-        <v>15708</v>
+        <v>5395</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z17" s="7" t="inlineStr">
@@ -2465,7 +2485,7 @@
       <c r="N18" s="4" t="n"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
@@ -2474,14 +2494,14 @@
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>15056</v>
+        <v>15184</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
@@ -2524,7 +2544,7 @@
       <c r="N19" s="7" t="n"/>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -2533,19 +2553,19 @@
         </is>
       </c>
       <c r="V19" s="7" t="n">
-        <v>15493</v>
+        <v>15708</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB19" s="7" t="n">
@@ -2583,7 +2603,7 @@
       <c r="N20" s="4" t="n"/>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
@@ -2592,19 +2612,19 @@
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>14553</v>
+        <v>15056</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB20" s="4" t="n">
@@ -2642,7 +2662,7 @@
       <c r="N21" s="7" t="n"/>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -2651,19 +2671,19 @@
         </is>
       </c>
       <c r="V21" s="7" t="n">
-        <v>14491</v>
+        <v>15493</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB21" s="7" t="n">
@@ -2701,7 +2721,7 @@
       <c r="N22" s="4" t="n"/>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
@@ -2710,19 +2730,19 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>15132</v>
+        <v>14553</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB22" s="4" t="n">
@@ -2760,23 +2780,23 @@
       <c r="N23" s="7" t="n"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="n">
+        <v>14491</v>
+      </c>
+      <c r="X23" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>87207</v>
-      </c>
-      <c r="X23" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
@@ -2819,23 +2839,23 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>86030</v>
+        <v>15132</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
@@ -2878,23 +2898,23 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>82667</v>
+        <v>15616</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z25" s="7" t="inlineStr">
@@ -2937,7 +2957,7 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -2946,14 +2966,14 @@
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>82796</v>
+        <v>87207</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z26" s="4" t="inlineStr">
@@ -2962,7 +2982,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2996,7 +3016,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3005,14 +3025,14 @@
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>80792</v>
+        <v>86030</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
@@ -3021,7 +3041,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3055,7 +3075,7 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
@@ -3064,14 +3084,14 @@
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>80181</v>
+        <v>82667</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
@@ -3114,7 +3134,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -3123,14 +3143,14 @@
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>82769</v>
+        <v>82796</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
@@ -3173,23 +3193,23 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>721</v>
+        <v>80792</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
@@ -3232,23 +3252,23 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>729</v>
+        <v>80181</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z31" s="7" t="inlineStr">
@@ -3300,23 +3320,23 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>717</v>
+        <v>82769</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
@@ -3340,7 +3360,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D8)</f>
+        <f>AVERAGE(D2:D9)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3350,7 +3370,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H8)</f>
+        <f>AVERAGE(H2:H9)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3373,23 +3393,23 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>753</v>
+        <v>82955</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
@@ -3414,7 +3434,7 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3423,23 +3443,23 @@
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3455,7 +3475,7 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -3464,23 +3484,23 @@
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="X35" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB35" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Y35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB35" s="7" t="n">
-        <v>10</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3496,32 +3516,32 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>717</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>743</v>
-      </c>
-      <c r="X36" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="Z36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3537,32 +3557,32 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>50559</v>
+        <v>753</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3578,28 +3598,28 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>51501</v>
+        <v>696</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB38" s="4" t="n">
@@ -3619,28 +3639,28 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>51715</v>
+        <v>723</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB39" s="7" t="n">
@@ -3660,23 +3680,23 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V40" s="4" t="n">
-        <v>50240</v>
+        <v>743</v>
       </c>
       <c r="X40" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z40" s="4" t="inlineStr">
@@ -3701,23 +3721,23 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>48948</v>
+        <v>714</v>
       </c>
       <c r="X41" s="7" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z41" s="7" t="inlineStr">
@@ -3742,7 +3762,7 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
@@ -3751,14 +3771,14 @@
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>48922</v>
+        <v>50559</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z42" s="4" t="inlineStr">
@@ -3767,7 +3787,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3783,7 +3803,7 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -3792,14 +3812,14 @@
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>51004</v>
+        <v>51501</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z43" s="7" t="inlineStr">
@@ -3824,23 +3844,23 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>1</v>
+        <v>51715</v>
       </c>
       <c r="X44" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
@@ -3849,7 +3869,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3865,23 +3885,23 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>1</v>
+        <v>50240</v>
       </c>
       <c r="X45" s="7" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z45" s="7" t="inlineStr">
@@ -3906,23 +3926,23 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>11599</v>
+        <v>48948</v>
       </c>
       <c r="X46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
@@ -3931,7 +3951,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3947,32 +3967,32 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>11522</v>
+        <v>48922</v>
       </c>
       <c r="X47" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -3988,28 +4008,28 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>11614</v>
+        <v>51004</v>
       </c>
       <c r="X48" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z48" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB48" s="4" t="n">
@@ -4029,32 +4049,32 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>11098</v>
+        <v>50744</v>
       </c>
       <c r="X49" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z49" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4075,23 +4095,23 @@
       </c>
       <c r="U50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>11097</v>
+        <v>1</v>
       </c>
       <c r="X50" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB50" s="4" t="n">
@@ -4116,27 +4136,27 @@
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>11410</v>
+        <v>1</v>
       </c>
       <c r="X51" s="7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Y51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4152,28 +4172,28 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>11599</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y52" s="4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>11482</v>
-      </c>
-      <c r="X52" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="Z52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB52" s="4" t="n">
@@ -4193,28 +4213,28 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V53" s="7" t="n">
+        <v>11522</v>
+      </c>
+      <c r="X53" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y53" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z53" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>26509</v>
-      </c>
-      <c r="X53" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB53" s="7" t="n">
@@ -4234,28 +4254,28 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>11614</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z54" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>26876</v>
-      </c>
-      <c r="X54" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB54" s="4" t="n">
@@ -4275,32 +4295,32 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="n">
+        <v>11098</v>
+      </c>
+      <c r="X55" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z55" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V55" s="7" t="n">
-        <v>27154</v>
-      </c>
-      <c r="X55" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB55" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4316,23 +4336,23 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>26655</v>
+        <v>11097</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
@@ -4357,32 +4377,32 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V57" s="7" t="n">
-        <v>25267</v>
+        <v>11410</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4398,28 +4418,28 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V58" s="4" t="n">
-        <v>24712</v>
+        <v>11482</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB58" s="4" t="n">
@@ -4439,28 +4459,28 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>26356</v>
+        <v>11322</v>
       </c>
       <c r="X59" s="7" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB59" s="7" t="n">
@@ -4485,23 +4505,23 @@
       </c>
       <c r="U60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V60" s="4" t="n">
-        <v>17949</v>
+        <v>26509</v>
       </c>
       <c r="X60" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB60" s="4" t="n">
@@ -4526,23 +4546,23 @@
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V61" s="7" t="n">
-        <v>17549</v>
+        <v>26876</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z61" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB61" s="7" t="n">
@@ -4567,23 +4587,23 @@
       </c>
       <c r="U62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V62" s="4" t="n">
-        <v>17646</v>
+        <v>27154</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB62" s="4" t="n">
@@ -4608,27 +4628,27 @@
       </c>
       <c r="U63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V63" s="7" t="n">
-        <v>17131</v>
+        <v>26655</v>
       </c>
       <c r="X63" s="7" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="Y63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4649,27 +4669,27 @@
       </c>
       <c r="U64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V64" s="4" t="n">
-        <v>17470</v>
+        <v>25267</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4690,27 +4710,27 @@
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V65" s="7" t="n">
-        <v>17485</v>
+        <v>24712</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4731,23 +4751,23 @@
       </c>
       <c r="U66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>17825</v>
+        <v>26356</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB66" s="4" t="n">
@@ -4767,28 +4787,28 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>745</v>
+        <v>25640</v>
       </c>
       <c r="X67" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Y67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB67" s="7" t="n">
@@ -4808,23 +4828,23 @@
     <row r="68">
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>763</v>
+        <v>17949</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Y68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z68" s="4" t="inlineStr">
@@ -4833,7 +4853,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4849,23 +4869,23 @@
     <row r="69">
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>740</v>
+        <v>17549</v>
       </c>
       <c r="X69" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z69" s="7" t="inlineStr">
@@ -4874,7 +4894,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4890,23 +4910,23 @@
     <row r="70">
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U70" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>783</v>
+        <v>17646</v>
       </c>
       <c r="X70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z70" s="4" t="inlineStr">
@@ -4915,7 +4935,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4931,23 +4951,23 @@
     <row r="71">
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>763</v>
+        <v>17131</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z71" s="7" t="inlineStr">
@@ -4956,7 +4976,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -4972,23 +4992,23 @@
     <row r="72">
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U72" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>735</v>
+        <v>17470</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z72" s="4" t="inlineStr">
@@ -4997,7 +5017,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -5013,23 +5033,23 @@
     <row r="73">
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U73" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>841</v>
+        <v>17485</v>
       </c>
       <c r="X73" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z73" s="7" t="inlineStr">
@@ -5038,7 +5058,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5054,23 +5074,23 @@
     <row r="74">
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>2142</v>
+        <v>17825</v>
       </c>
       <c r="X74" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z74" s="4" t="inlineStr">
@@ -5095,23 +5115,23 @@
     <row r="75">
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>2408</v>
+        <v>17897</v>
       </c>
       <c r="X75" s="7" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z75" s="7" t="inlineStr">
@@ -5136,19 +5156,19 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>2141</v>
+        <v>745</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y76" s="4" t="inlineStr">
         <is>
@@ -5157,7 +5177,7 @@
       </c>
       <c r="Z76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB76" s="4" t="n">
@@ -5177,28 +5197,28 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V77" s="7" t="n">
+        <v>763</v>
+      </c>
+      <c r="X77" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y77" s="7" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>2082</v>
-      </c>
-      <c r="X77" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="Z77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB77" s="7" t="n">
@@ -5218,28 +5238,28 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>1990</v>
+        <v>740</v>
       </c>
       <c r="X78" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB78" s="4" t="n">
@@ -5259,28 +5279,28 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>2043</v>
+        <v>783</v>
       </c>
       <c r="X79" s="7" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB79" s="7" t="n">
@@ -5300,28 +5320,28 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>2148</v>
+        <v>763</v>
       </c>
       <c r="X80" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB80" s="4" t="n">
@@ -5339,20 +5359,30 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="n"/>
-      <c r="U81" s="7" t="n"/>
-      <c r="V81" s="7" t="n"/>
+      <c r="T81" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U81" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V81" s="7" t="n">
+        <v>735</v>
+      </c>
       <c r="X81" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z81" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB81" s="7" t="n">
@@ -5370,20 +5400,30 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="n"/>
-      <c r="U82" s="4" t="n"/>
-      <c r="V82" s="4" t="n"/>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U82" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>841</v>
+      </c>
       <c r="X82" s="4" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB82" s="4" t="n">
@@ -5401,11 +5441,21 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="n"/>
-      <c r="U83" s="7" t="n"/>
-      <c r="V83" s="7" t="n"/>
+      <c r="T83" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U83" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V83" s="7" t="n">
+        <v>767</v>
+      </c>
       <c r="X83" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y83" s="7" t="inlineStr">
         <is>
@@ -5414,7 +5464,7 @@
       </c>
       <c r="Z83" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB83" s="7" t="n">
@@ -5432,25 +5482,35 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="n"/>
-      <c r="U84" s="4" t="n"/>
-      <c r="V84" s="4" t="n"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>2142</v>
+      </c>
       <c r="X84" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB84" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Y84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB84" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -5463,9 +5523,19 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="n"/>
-      <c r="U85" s="7" t="n"/>
-      <c r="V85" s="7" t="n"/>
+      <c r="T85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V85" s="7" t="n">
+        <v>2408</v>
+      </c>
       <c r="X85" s="7" t="n">
         <v>6</v>
       </c>
@@ -5476,131 +5546,171 @@
       </c>
       <c r="Z85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB85" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="T86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>2141</v>
+      </c>
+      <c r="X86" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB86" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="T87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V87" s="7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="X87" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB87" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC85" s="7" t="inlineStr">
+      <c r="AC87" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="T86" s="4" t="n"/>
-      <c r="U86" s="4" t="n"/>
-      <c r="V86" s="4" t="n"/>
-      <c r="X86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y86" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC86" s="4" t="inlineStr">
+      <c r="AD87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="T88" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD86" s="4" t="inlineStr">
+      <c r="U88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V88" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="X88" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB88" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD88" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="T87" s="7" t="n"/>
-      <c r="U87" s="7" t="n"/>
-      <c r="V87" s="7" t="n"/>
-      <c r="X87" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB87" s="7" t="n">
-        <v>157</v>
-      </c>
-      <c r="AC87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="T88" s="4" t="n"/>
-      <c r="U88" s="4" t="n"/>
-      <c r="V88" s="4" t="n"/>
-      <c r="X88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="AB88" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
     <row r="89">
-      <c r="T89" s="7" t="n"/>
-      <c r="U89" s="7" t="n"/>
-      <c r="V89" s="7" t="n"/>
+      <c r="T89" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U89" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V89" s="7" t="n">
+        <v>2043</v>
+      </c>
       <c r="X89" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB89" s="7" t="n">
@@ -5618,14 +5728,34 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="n"/>
-      <c r="U90" s="4" t="n"/>
-      <c r="V90" s="4" t="n"/>
-      <c r="X90" s="4" t="n"/>
-      <c r="Y90" s="4" t="n"/>
-      <c r="Z90" s="4" t="n"/>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U90" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V90" s="4" t="n">
+        <v>2148</v>
+      </c>
+      <c r="X90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z90" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB90" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5639,14 +5769,34 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="n"/>
-      <c r="U91" s="7" t="n"/>
-      <c r="V91" s="7" t="n"/>
-      <c r="X91" s="7" t="n"/>
-      <c r="Y91" s="7" t="n"/>
-      <c r="Z91" s="7" t="n"/>
+      <c r="T91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U91" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V91" s="7" t="n">
+        <v>2096</v>
+      </c>
+      <c r="X91" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z91" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB91" s="7" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -5663,11 +5813,21 @@
       <c r="T92" s="4" t="n"/>
       <c r="U92" s="4" t="n"/>
       <c r="V92" s="4" t="n"/>
-      <c r="X92" s="4" t="n"/>
-      <c r="Y92" s="4" t="n"/>
-      <c r="Z92" s="4" t="n"/>
+      <c r="X92" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z92" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB92" s="4" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -5684,9 +5844,19 @@
       <c r="T93" s="7" t="n"/>
       <c r="U93" s="7" t="n"/>
       <c r="V93" s="7" t="n"/>
-      <c r="X93" s="7" t="n"/>
-      <c r="Y93" s="7" t="n"/>
-      <c r="Z93" s="7" t="n"/>
+      <c r="X93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y93" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z93" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB93" s="7" t="n">
         <v>4</v>
       </c>
@@ -5705,9 +5875,19 @@
       <c r="T94" s="4" t="n"/>
       <c r="U94" s="4" t="n"/>
       <c r="V94" s="4" t="n"/>
-      <c r="X94" s="4" t="n"/>
-      <c r="Y94" s="4" t="n"/>
-      <c r="Z94" s="4" t="n"/>
+      <c r="X94" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z94" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB94" s="4" t="n">
         <v>1</v>
       </c>
@@ -5726,9 +5906,19 @@
       <c r="T95" s="7" t="n"/>
       <c r="U95" s="7" t="n"/>
       <c r="V95" s="7" t="n"/>
-      <c r="X95" s="7" t="n"/>
-      <c r="Y95" s="7" t="n"/>
-      <c r="Z95" s="7" t="n"/>
+      <c r="X95" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z95" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB95" s="7" t="n">
         <v>44</v>
       </c>
@@ -5747,11 +5937,21 @@
       <c r="T96" s="4" t="n"/>
       <c r="U96" s="4" t="n"/>
       <c r="V96" s="4" t="n"/>
-      <c r="X96" s="4" t="n"/>
-      <c r="Y96" s="4" t="n"/>
-      <c r="Z96" s="4" t="n"/>
+      <c r="X96" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z96" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB96" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -5768,11 +5968,21 @@
       <c r="T97" s="7" t="n"/>
       <c r="U97" s="7" t="n"/>
       <c r="V97" s="7" t="n"/>
-      <c r="X97" s="7" t="n"/>
-      <c r="Y97" s="7" t="n"/>
-      <c r="Z97" s="7" t="n"/>
+      <c r="X97" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y97" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z97" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB97" s="7" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -5789,11 +5999,21 @@
       <c r="T98" s="4" t="n"/>
       <c r="U98" s="4" t="n"/>
       <c r="V98" s="4" t="n"/>
-      <c r="X98" s="4" t="n"/>
-      <c r="Y98" s="4" t="n"/>
-      <c r="Z98" s="4" t="n"/>
+      <c r="X98" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB98" s="4" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
@@ -5810,11 +6030,21 @@
       <c r="T99" s="7" t="n"/>
       <c r="U99" s="7" t="n"/>
       <c r="V99" s="7" t="n"/>
-      <c r="X99" s="7" t="n"/>
-      <c r="Y99" s="7" t="n"/>
-      <c r="Z99" s="7" t="n"/>
+      <c r="X99" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z99" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB99" s="7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC99" s="7" t="inlineStr">
         <is>
@@ -5831,9 +6061,19 @@
       <c r="T100" s="4" t="n"/>
       <c r="U100" s="4" t="n"/>
       <c r="V100" s="4" t="n"/>
-      <c r="X100" s="4" t="n"/>
-      <c r="Y100" s="4" t="n"/>
-      <c r="Z100" s="4" t="n"/>
+      <c r="X100" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y100" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z100" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB100" s="4" t="n">
         <v>1</v>
       </c>
@@ -5852,9 +6092,19 @@
       <c r="T101" s="7" t="n"/>
       <c r="U101" s="7" t="n"/>
       <c r="V101" s="7" t="n"/>
-      <c r="X101" s="7" t="n"/>
-      <c r="Y101" s="7" t="n"/>
-      <c r="Z101" s="7" t="n"/>
+      <c r="X101" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z101" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB101" s="7" t="n">
         <v>6</v>
       </c>
@@ -5873,9 +6123,19 @@
       <c r="T102" s="4" t="n"/>
       <c r="U102" s="4" t="n"/>
       <c r="V102" s="4" t="n"/>
-      <c r="X102" s="4" t="n"/>
-      <c r="Y102" s="4" t="n"/>
-      <c r="Z102" s="4" t="n"/>
+      <c r="X102" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y102" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z102" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB102" s="4" t="n">
         <v>3</v>
       </c>
@@ -5894,11 +6154,21 @@
       <c r="T103" s="7" t="n"/>
       <c r="U103" s="7" t="n"/>
       <c r="V103" s="7" t="n"/>
-      <c r="X103" s="7" t="n"/>
-      <c r="Y103" s="7" t="n"/>
-      <c r="Z103" s="7" t="n"/>
+      <c r="X103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z103" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB103" s="7" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -5915,11 +6185,21 @@
       <c r="T104" s="4" t="n"/>
       <c r="U104" s="4" t="n"/>
       <c r="V104" s="4" t="n"/>
-      <c r="X104" s="4" t="n"/>
-      <c r="Y104" s="4" t="n"/>
-      <c r="Z104" s="4" t="n"/>
+      <c r="X104" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y104" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z104" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB104" s="4" t="n">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
@@ -5961,7 +6241,7 @@
       <c r="Y106" s="4" t="n"/>
       <c r="Z106" s="4" t="n"/>
       <c r="AB106" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -5982,7 +6262,7 @@
       <c r="Y107" s="7" t="n"/>
       <c r="Z107" s="7" t="n"/>
       <c r="AB107" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -6003,7 +6283,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6045,7 +6325,7 @@
       <c r="Y110" s="4" t="n"/>
       <c r="Z110" s="4" t="n"/>
       <c r="AB110" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6192,7 +6472,7 @@
       <c r="Y117" s="7" t="n"/>
       <c r="Z117" s="7" t="n"/>
       <c r="AB117" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -6213,7 +6493,7 @@
       <c r="Y118" s="4" t="n"/>
       <c r="Z118" s="4" t="n"/>
       <c r="AB118" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -6234,7 +6514,7 @@
       <c r="Y119" s="7" t="n"/>
       <c r="Z119" s="7" t="n"/>
       <c r="AB119" s="7" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -6255,7 +6535,7 @@
       <c r="Y120" s="4" t="n"/>
       <c r="Z120" s="4" t="n"/>
       <c r="AB120" s="4" t="n">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -6423,7 +6703,7 @@
       <c r="Y128" s="4" t="n"/>
       <c r="Z128" s="4" t="n"/>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6444,7 +6724,7 @@
       <c r="Y129" s="7" t="n"/>
       <c r="Z129" s="7" t="n"/>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6465,7 +6745,7 @@
       <c r="Y130" s="4" t="n"/>
       <c r="Z130" s="4" t="n"/>
       <c r="AB130" s="4" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -6486,7 +6766,7 @@
       <c r="Y131" s="7" t="n"/>
       <c r="Z131" s="7" t="n"/>
       <c r="AB131" s="7" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -6507,7 +6787,7 @@
       <c r="Y132" s="4" t="n"/>
       <c r="Z132" s="4" t="n"/>
       <c r="AB132" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -6528,7 +6808,7 @@
       <c r="Y133" s="7" t="n"/>
       <c r="Z133" s="7" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6549,7 +6829,7 @@
       <c r="Y134" s="4" t="n"/>
       <c r="Z134" s="4" t="n"/>
       <c r="AB134" s="4" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -6570,7 +6850,7 @@
       <c r="Y135" s="7" t="n"/>
       <c r="Z135" s="7" t="n"/>
       <c r="AB135" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -6591,7 +6871,7 @@
       <c r="Y136" s="4" t="n"/>
       <c r="Z136" s="4" t="n"/>
       <c r="AB136" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -6696,7 +6976,7 @@
       <c r="Y141" s="7" t="n"/>
       <c r="Z141" s="7" t="n"/>
       <c r="AB141" s="7" t="n">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -6738,7 +7018,7 @@
       <c r="Y143" s="7" t="n"/>
       <c r="Z143" s="7" t="n"/>
       <c r="AB143" s="7" t="n">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -6780,7 +7060,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -6801,7 +7081,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -6830,6 +7110,426 @@
         </is>
       </c>
       <c r="AD147" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="n"/>
+      <c r="X148" s="4" t="n"/>
+      <c r="Y148" s="4" t="n"/>
+      <c r="Z148" s="4" t="n"/>
+      <c r="AB148" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD148" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="T149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
+      <c r="X149" s="7" t="n"/>
+      <c r="Y149" s="7" t="n"/>
+      <c r="Z149" s="7" t="n"/>
+      <c r="AB149" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="AC149" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD149" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="n"/>
+      <c r="V150" s="4" t="n"/>
+      <c r="X150" s="4" t="n"/>
+      <c r="Y150" s="4" t="n"/>
+      <c r="Z150" s="4" t="n"/>
+      <c r="AB150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD150" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="T151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
+      <c r="X151" s="7" t="n"/>
+      <c r="Y151" s="7" t="n"/>
+      <c r="Z151" s="7" t="n"/>
+      <c r="AB151" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC151" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD151" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="n"/>
+      <c r="V152" s="4" t="n"/>
+      <c r="X152" s="4" t="n"/>
+      <c r="Y152" s="4" t="n"/>
+      <c r="Z152" s="4" t="n"/>
+      <c r="AB152" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD152" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="T153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
+      <c r="X153" s="7" t="n"/>
+      <c r="Y153" s="7" t="n"/>
+      <c r="Z153" s="7" t="n"/>
+      <c r="AB153" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="AC153" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="n"/>
+      <c r="X154" s="4" t="n"/>
+      <c r="Y154" s="4" t="n"/>
+      <c r="Z154" s="4" t="n"/>
+      <c r="AB154" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD154" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="T155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
+      <c r="X155" s="7" t="n"/>
+      <c r="Y155" s="7" t="n"/>
+      <c r="Z155" s="7" t="n"/>
+      <c r="AB155" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC155" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD155" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="n"/>
+      <c r="V156" s="4" t="n"/>
+      <c r="X156" s="4" t="n"/>
+      <c r="Y156" s="4" t="n"/>
+      <c r="Z156" s="4" t="n"/>
+      <c r="AB156" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD156" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="T157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
+      <c r="X157" s="7" t="n"/>
+      <c r="Y157" s="7" t="n"/>
+      <c r="Z157" s="7" t="n"/>
+      <c r="AB157" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC157" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD157" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="4" t="n"/>
+      <c r="V158" s="4" t="n"/>
+      <c r="X158" s="4" t="n"/>
+      <c r="Y158" s="4" t="n"/>
+      <c r="Z158" s="4" t="n"/>
+      <c r="AB158" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD158" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="T159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
+      <c r="X159" s="7" t="n"/>
+      <c r="Y159" s="7" t="n"/>
+      <c r="Z159" s="7" t="n"/>
+      <c r="AB159" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC159" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD159" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="4" t="n"/>
+      <c r="V160" s="4" t="n"/>
+      <c r="X160" s="4" t="n"/>
+      <c r="Y160" s="4" t="n"/>
+      <c r="Z160" s="4" t="n"/>
+      <c r="AB160" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD160" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="T161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
+      <c r="X161" s="7" t="n"/>
+      <c r="Y161" s="7" t="n"/>
+      <c r="Z161" s="7" t="n"/>
+      <c r="AB161" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC161" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD161" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="n"/>
+      <c r="V162" s="4" t="n"/>
+      <c r="X162" s="4" t="n"/>
+      <c r="Y162" s="4" t="n"/>
+      <c r="Z162" s="4" t="n"/>
+      <c r="AB162" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD162" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="T163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
+      <c r="X163" s="7" t="n"/>
+      <c r="Y163" s="7" t="n"/>
+      <c r="Z163" s="7" t="n"/>
+      <c r="AB163" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC163" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD163" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="n"/>
+      <c r="V164" s="4" t="n"/>
+      <c r="X164" s="4" t="n"/>
+      <c r="Y164" s="4" t="n"/>
+      <c r="Z164" s="4" t="n"/>
+      <c r="AB164" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD164" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="T165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
+      <c r="X165" s="7" t="n"/>
+      <c r="Y165" s="7" t="n"/>
+      <c r="Z165" s="7" t="n"/>
+      <c r="AB165" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC165" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="n"/>
+      <c r="X166" s="4" t="n"/>
+      <c r="Y166" s="4" t="n"/>
+      <c r="Z166" s="4" t="n"/>
+      <c r="AB166" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="T167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
+      <c r="X167" s="7" t="n"/>
+      <c r="Y167" s="7" t="n"/>
+      <c r="Z167" s="7" t="n"/>
+      <c r="AB167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC167" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD167" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -6851,7 +7551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AD133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7039,7 +7739,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -7125,7 +7825,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -7211,7 +7911,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -7289,7 +7989,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -7375,7 +8075,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -7461,7 +8161,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -7566,21 +8266,53 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="D9">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C9)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C9)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>ROUND(MAX(0,MIN(100,(1-E9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>MIN(1,(G9-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C9)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>MAX(0,(L9-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>$B$2+H9+M9</f>
+        <v/>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1530</v>
+        <v>56380</v>
       </c>
       <c r="X9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -7624,7 +8356,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -7633,10 +8365,10 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2311</v>
+        <v>1530</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -7649,7 +8381,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -7670,7 +8402,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -7679,23 +8411,23 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2868</v>
+        <v>2311</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -7716,7 +8448,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -7725,14 +8457,14 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>4059</v>
+        <v>2868</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -7741,7 +8473,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -7762,7 +8494,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -7771,14 +8503,14 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>5092</v>
+        <v>4059</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -7787,7 +8519,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -7808,7 +8540,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -7817,14 +8549,14 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>6962</v>
+        <v>5092</v>
       </c>
       <c r="X14" t="n">
         <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -7854,7 +8586,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -7863,14 +8595,14 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>9959</v>
+        <v>6962</v>
       </c>
       <c r="X15" t="n">
         <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -7900,23 +8632,23 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1815</v>
+        <v>9959</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -7946,28 +8678,28 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>2333</v>
+        <v>11290</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -7992,7 +8724,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -8001,19 +8733,19 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3182</v>
+        <v>1815</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8038,7 +8770,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -8047,14 +8779,14 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>4129</v>
+        <v>2333</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -8084,7 +8816,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -8093,14 +8825,14 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5644</v>
+        <v>3182</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -8130,7 +8862,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -8139,14 +8871,14 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>7963</v>
+        <v>4129</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -8176,7 +8908,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -8185,14 +8917,14 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>11169</v>
+        <v>5644</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -8222,23 +8954,23 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>2322</v>
+        <v>7963</v>
       </c>
       <c r="X23" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -8247,7 +8979,7 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -8268,23 +9000,23 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>3533</v>
+        <v>11169</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -8293,7 +9025,7 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -8314,23 +9046,23 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>4891</v>
+        <v>12345</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -8360,7 +9092,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -8369,14 +9101,14 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>6461</v>
+        <v>2322</v>
       </c>
       <c r="X26" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -8385,7 +9117,7 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -8406,7 +9138,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -8415,23 +9147,23 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>8274</v>
+        <v>3533</v>
       </c>
       <c r="X27" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
         <v>1</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB27" t="n">
-        <v>16</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -8452,7 +9184,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -8461,19 +9193,19 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>12174</v>
+        <v>4891</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -8498,7 +9230,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -8507,19 +9239,19 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>19723</v>
+        <v>6461</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -8544,23 +9276,23 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>8274</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>1827</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -8590,23 +9322,23 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>2275</v>
+        <v>12174</v>
       </c>
       <c r="X31" t="n">
         <v>5</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -8651,23 +9383,23 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>2882</v>
+        <v>19723</v>
       </c>
       <c r="X32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -8691,7 +9423,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D8)</f>
+        <f>AVERAGE(D2:D9)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -8699,7 +9431,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H8)</f>
+        <f>AVERAGE(H2:H9)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -8720,32 +9452,32 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>20836</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>3280</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="Z33" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -8761,32 +9493,32 @@
     <row r="34">
       <c r="T34" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1827</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>3951</v>
-      </c>
-      <c r="X34" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -8802,7 +9534,7 @@
     <row r="35">
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -8811,14 +9543,14 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>5096</v>
+        <v>2275</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -8843,7 +9575,7 @@
     <row r="36">
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -8852,19 +9584,19 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>6277</v>
+        <v>2882</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -8884,32 +9616,32 @@
     <row r="37">
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>250</v>
+        <v>3280</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -8925,32 +9657,32 @@
     <row r="38">
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>428</v>
+        <v>3951</v>
       </c>
       <c r="X38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
         <v>1</v>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB38" t="n">
-        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -8966,32 +9698,32 @@
     <row r="39">
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>365</v>
+        <v>5096</v>
       </c>
       <c r="X39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9007,28 +9739,28 @@
     <row r="40">
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>471</v>
+        <v>6277</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -9048,23 +9780,23 @@
     <row r="41">
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>554</v>
+        <v>6297</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -9073,7 +9805,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9089,7 +9821,7 @@
     <row r="42">
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9098,14 +9830,14 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>902</v>
+        <v>250</v>
       </c>
       <c r="X42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -9114,7 +9846,7 @@
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -9130,7 +9862,7 @@
     <row r="43">
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -9139,14 +9871,14 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>1420</v>
+        <v>428</v>
       </c>
       <c r="X43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -9155,7 +9887,7 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -9171,23 +9903,23 @@
     <row r="44">
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>6249</v>
+        <v>365</v>
       </c>
       <c r="X44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -9212,32 +9944,32 @@
     <row r="45">
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>8329</v>
+        <v>471</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -9253,28 +9985,28 @@
     <row r="46">
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>10619</v>
+        <v>554</v>
       </c>
       <c r="X46" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -9294,32 +10026,32 @@
     <row r="47">
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>13894</v>
+        <v>902</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -9335,28 +10067,28 @@
     <row r="48">
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>17235</v>
+        <v>1420</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -9376,28 +10108,28 @@
     <row r="49">
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>23145</v>
+        <v>1561</v>
       </c>
       <c r="X49" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -9417,7 +10149,7 @@
     <row r="50">
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -9426,19 +10158,19 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>32675</v>
+        <v>6249</v>
       </c>
       <c r="X50" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -9458,23 +10190,23 @@
     <row r="51">
       <c r="T51" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>8329</v>
+      </c>
+      <c r="X51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>30</v>
-      </c>
-      <c r="X51" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -9499,23 +10231,23 @@
     <row r="52">
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>81</v>
+        <v>10619</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -9540,23 +10272,23 @@
     <row r="53">
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>103</v>
+        <v>13894</v>
       </c>
       <c r="X53" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -9581,23 +10313,23 @@
     <row r="54">
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>154</v>
+        <v>17235</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -9622,23 +10354,23 @@
     <row r="55">
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>183</v>
+        <v>23145</v>
       </c>
       <c r="X55" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -9663,23 +10395,23 @@
     <row r="56">
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>238</v>
+        <v>32675</v>
       </c>
       <c r="X56" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -9688,7 +10420,7 @@
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -9704,23 +10436,23 @@
     <row r="57">
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>354</v>
+        <v>34857</v>
       </c>
       <c r="X57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -9729,7 +10461,7 @@
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -9750,18 +10482,18 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>603</v>
+        <v>30</v>
       </c>
       <c r="X58" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -9770,7 +10502,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -9791,27 +10523,27 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>820</v>
+        <v>81</v>
       </c>
       <c r="X59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -9832,27 +10564,27 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>1204</v>
+        <v>103</v>
       </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -9873,23 +10605,23 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>1689</v>
+        <v>154</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB61" t="n">
@@ -9914,27 +10646,27 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>2042</v>
+        <v>183</v>
       </c>
       <c r="X62" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9955,27 +10687,27 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>2581</v>
+        <v>238</v>
       </c>
       <c r="X63" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
         <v>1</v>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB63" t="n">
-        <v>5</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -9996,23 +10728,23 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>3880</v>
+        <v>354</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB64" t="n">
@@ -10032,28 +10764,28 @@
     <row r="65">
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>90</v>
+        <v>347</v>
       </c>
       <c r="X65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB65" t="n">
@@ -10073,28 +10805,28 @@
     <row r="66">
       <c r="T66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>119</v>
+        <v>603</v>
       </c>
       <c r="X66" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB66" t="n">
@@ -10114,28 +10846,28 @@
     <row r="67">
       <c r="T67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V67" t="n">
-        <v>157</v>
+        <v>820</v>
       </c>
       <c r="X67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB67" t="n">
@@ -10155,28 +10887,28 @@
     <row r="68">
       <c r="T68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V68" t="n">
-        <v>244</v>
+        <v>1204</v>
       </c>
       <c r="X68" t="n">
         <v>1</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB68" t="n">
@@ -10196,28 +10928,28 @@
     <row r="69">
       <c r="T69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V69" t="n">
-        <v>270</v>
+        <v>1689</v>
       </c>
       <c r="X69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB69" t="n">
@@ -10237,16 +10969,29 @@
     <row r="70">
       <c r="T70" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V70" t="n">
-        <v>341</v>
+        <v>2042</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB70" t="n">
         <v>1</v>
@@ -10265,16 +11010,29 @@
     <row r="71">
       <c r="T71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V71" t="n">
-        <v>409</v>
+        <v>2581</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB71" t="n">
         <v>58</v>
@@ -10291,6 +11049,32 @@
       </c>
     </row>
     <row r="72">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>3880</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB72" t="n">
         <v>3</v>
       </c>
@@ -10306,8 +11090,34 @@
       </c>
     </row>
     <row r="73">
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>3997</v>
+      </c>
+      <c r="X73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB73" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -10321,6 +11131,32 @@
       </c>
     </row>
     <row r="74">
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>90</v>
+      </c>
+      <c r="X74" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB74" t="n">
         <v>6</v>
       </c>
@@ -10336,66 +11172,183 @@
       </c>
     </row>
     <row r="75">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>119</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB75" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>157</v>
+      </c>
+      <c r="X76" t="n">
         <v>1</v>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC76" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="AB76" t="n">
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>244</v>
+      </c>
+      <c r="X77" t="n">
         <v>1</v>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD76" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="AB77" t="n">
+    <row r="78">
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>270</v>
+      </c>
+      <c r="X78" t="n">
         <v>2</v>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD77" t="inlineStr">
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="AB78" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>341</v>
+      </c>
       <c r="AB79" t="n">
         <v>67</v>
       </c>
@@ -10411,6 +11364,19 @@
       </c>
     </row>
     <row r="80">
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>409</v>
+      </c>
       <c r="AB80" t="n">
         <v>4</v>
       </c>
@@ -10426,6 +11392,19 @@
       </c>
     </row>
     <row r="81">
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>401</v>
+      </c>
       <c r="AB81" t="n">
         <v>4</v>
       </c>
@@ -10487,7 +11466,7 @@
     </row>
     <row r="85">
       <c r="AB85" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
@@ -10502,7 +11481,7 @@
     </row>
     <row r="86">
       <c r="AB86" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -10547,7 +11526,7 @@
     </row>
     <row r="89">
       <c r="AB89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -10577,7 +11556,7 @@
     </row>
     <row r="91">
       <c r="AB91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -10592,7 +11571,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -10622,7 +11601,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -10682,7 +11661,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -10712,7 +11691,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -10742,7 +11721,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -10757,7 +11736,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -10832,7 +11811,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -10847,7 +11826,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -10937,7 +11916,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -10952,7 +11931,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -10967,7 +11946,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -11020,6 +11999,201 @@
         </is>
       </c>
       <c r="AD120" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="AB121" t="n">
+        <v>204</v>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="AB122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="AB123" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="AB124" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="AB125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="AB126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="AB127" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="AB128" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="AB129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="AB130" t="n">
+        <v>109</v>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="AB131" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="AB132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -11825,16 +12999,16 @@
         <v>3208</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -11899,28 +13073,28 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>7785</v>
       </c>
       <c r="X4" t="n">
         <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -11977,28 +13151,28 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>705</v>
-      </c>
-      <c r="X5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -12063,28 +13237,28 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>705</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -12149,28 +13323,28 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>969</v>
+        <v>1439</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -12240,11 +13414,24 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
         <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
@@ -12266,6 +13453,38 @@
           <t>2026-09-08</t>
         </is>
       </c>
+      <c r="D9">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C9)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C9)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>ROUND(MAX(0,MIN(100,(1-E9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>MIN(1,(G9-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C9)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K9/IF(D9&gt;0,D9,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>MAX(0,(L9-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>$B$2+H9+M9</f>
+        <v/>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -12273,11 +13492,37 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1063</v>
+        <v>969</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -12298,16 +13543,42 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1940</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -12318,16 +13589,42 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>904</v>
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -12338,16 +13635,42 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1063</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -12358,16 +13681,42 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>2234</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>113</v>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -12383,11 +13732,24 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
           <t>com.logistics.rider.glovo</t>
         </is>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -12403,11 +13765,24 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3024</v>
+        <v>904</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -12418,16 +13793,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>34</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="17">
@@ -12443,7 +13818,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V17" t="n">
@@ -12463,11 +13838,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>354</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -12478,16 +13853,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
@@ -12498,16 +13873,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -12516,6 +13891,19 @@
           <t>2026-09-20</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>3024</v>
+      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -12523,6 +13911,19 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>5423</v>
+      </c>
     </row>
     <row r="23">
       <c r="C23" t="inlineStr">
@@ -12530,6 +13931,19 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
@@ -12537,6 +13951,19 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -12544,6 +13971,19 @@
           <t>2026-09-24</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="C26" t="inlineStr">
@@ -12551,6 +13991,19 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>354</v>
+      </c>
     </row>
     <row r="27">
       <c r="C27" t="inlineStr">
@@ -12558,6 +14011,19 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>609</v>
+      </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
@@ -12565,6 +14031,19 @@
           <t>2026-09-27</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
@@ -12572,6 +14051,19 @@
           <t>2026-09-28</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="30">
       <c r="C30" t="inlineStr">
@@ -12579,6 +14071,19 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
@@ -12611,7 +14116,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D8)</f>
+        <f>AVERAGE(D2:D9)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -12619,7 +14124,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H8)</f>
+        <f>AVERAGE(H2:H9)</f>
         <v/>
       </c>
       <c r="I33" s="38">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="7" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>5519</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>15493</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>14553</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>14491</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2851,20 +2851,20 @@
         <v>15132</v>
       </c>
       <c r="X24" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB24" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB24" s="4" t="n">
-        <v>29</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>80792</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3332,20 +3332,20 @@
         <v>82769</v>
       </c>
       <c r="X32" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="n">
-        <v>51</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>729</v>
       </c>
       <c r="X35" s="7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>753</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>696</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>723</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>198</v>
+        <v>10</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>11410</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>11482</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>25267</v>
       </c>
       <c r="X64" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>24712</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>17131</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>17470</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>17825</v>
       </c>
       <c r="X74" s="4" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>17897</v>
       </c>
       <c r="X75" s="7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>735</v>
       </c>
       <c r="X81" s="7" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>841</v>
       </c>
       <c r="X82" s="4" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>2142</v>
       </c>
       <c r="X84" s="4" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>2141</v>
       </c>
       <c r="X86" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>2082</v>
       </c>
       <c r="X87" s="7" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>2043</v>
       </c>
       <c r="X89" s="7" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AB103" s="7" t="n">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       <c r="Y106" s="4" t="n"/>
       <c r="Z106" s="4" t="n"/>
       <c r="AB106" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
       <c r="Y107" s="7" t="n"/>
       <c r="Z107" s="7" t="n"/>
       <c r="AB107" s="7" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
       <c r="Y109" s="7" t="n"/>
       <c r="Z109" s="7" t="n"/>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
       <c r="Y111" s="7" t="n"/>
       <c r="Z111" s="7" t="n"/>
       <c r="AB111" s="7" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       <c r="Y112" s="4" t="n"/>
       <c r="Z112" s="4" t="n"/>
       <c r="AB112" s="4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
       <c r="Y114" s="4" t="n"/>
       <c r="Z114" s="4" t="n"/>
       <c r="AB114" s="4" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       <c r="Y115" s="7" t="n"/>
       <c r="Z115" s="7" t="n"/>
       <c r="AB115" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
       <c r="Y116" s="4" t="n"/>
       <c r="Z116" s="4" t="n"/>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       <c r="Y117" s="7" t="n"/>
       <c r="Z117" s="7" t="n"/>
       <c r="AB117" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       <c r="Y119" s="7" t="n"/>
       <c r="Z119" s="7" t="n"/>
       <c r="AB119" s="7" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
       <c r="Y120" s="4" t="n"/>
       <c r="Z120" s="4" t="n"/>
       <c r="AB120" s="4" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
       <c r="Y122" s="4" t="n"/>
       <c r="Z122" s="4" t="n"/>
       <c r="AB122" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
       <c r="Y123" s="7" t="n"/>
       <c r="Z123" s="7" t="n"/>
       <c r="AB123" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
       <c r="Y130" s="4" t="n"/>
       <c r="Z130" s="4" t="n"/>
       <c r="AB130" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
       <c r="Y132" s="4" t="n"/>
       <c r="Z132" s="4" t="n"/>
       <c r="AB132" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
       <c r="Y133" s="7" t="n"/>
       <c r="Z133" s="7" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
       <c r="Y136" s="4" t="n"/>
       <c r="Z136" s="4" t="n"/>
       <c r="AB136" s="4" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
       <c r="Y137" s="7" t="n"/>
       <c r="Z137" s="7" t="n"/>
       <c r="AB137" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
       <c r="Y139" s="7" t="n"/>
       <c r="Z139" s="7" t="n"/>
       <c r="AB139" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
       <c r="Y140" s="4" t="n"/>
       <c r="Z140" s="4" t="n"/>
       <c r="AB140" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       <c r="Y141" s="7" t="n"/>
       <c r="Z141" s="7" t="n"/>
       <c r="AB141" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       <c r="Y142" s="4" t="n"/>
       <c r="Z142" s="4" t="n"/>
       <c r="AB142" s="4" t="n">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
       <c r="Y143" s="7" t="n"/>
       <c r="Z143" s="7" t="n"/>
       <c r="AB143" s="7" t="n">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
       <c r="AB153" s="7" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n"/>
       <c r="AB154" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
       <c r="Y155" s="7" t="n"/>
       <c r="Z155" s="7" t="n"/>
       <c r="AB155" s="7" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
       <c r="Y159" s="7" t="n"/>
       <c r="Z159" s="7" t="n"/>
       <c r="AB159" s="7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="AC159" s="7" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n"/>
       <c r="AB160" s="4" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
       <c r="AB161" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
       <c r="AB162" s="4" t="n">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
       <c r="AB163" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
       <c r="Y164" s="4" t="n"/>
       <c r="Z164" s="4" t="n"/>
       <c r="AB164" s="4" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
       <c r="Y165" s="7" t="n"/>
       <c r="Z165" s="7" t="n"/>
       <c r="AB165" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
       <c r="Y166" s="4" t="n"/>
       <c r="Z166" s="4" t="n"/>
       <c r="AB166" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>1530</v>
       </c>
       <c r="X10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>12345</v>
       </c>
       <c r="X25" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>2322</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>19723</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>20836</v>
       </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>3280</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>3951</v>
       </c>
       <c r="X38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>5096</v>
       </c>
       <c r="X39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>6277</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="87">
       <c r="AB87" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="88">
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
     </row>
     <row r="110">
       <c r="AB110" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
     </row>
     <row r="126">
       <c r="AB126" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
     </row>
     <row r="127">
       <c r="AB127" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
     </row>
     <row r="129">
       <c r="AB129" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -737,10 +737,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -773,10 +773,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -809,10 +809,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -845,10 +845,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -881,10 +881,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -917,10 +917,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -953,10 +953,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -989,10 +989,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1025,10 +1025,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1061,10 +1061,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1365,15 +1365,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>68</v>
       </c>
@@ -1450,15 +1444,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>68</v>
       </c>
@@ -1535,15 +1523,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>91</v>
       </c>
@@ -1558,7 +1540,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1614,15 +1596,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>75</v>
       </c>
@@ -1637,7 +1613,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1699,15 +1675,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>1</v>
       </c>
@@ -1722,7 +1692,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1784,15 +1754,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>88</v>
       </c>
@@ -1807,7 +1771,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1869,15 +1833,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>115</v>
       </c>
@@ -1892,7 +1850,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1948,17 +1906,11 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="7" t="inlineStr">
         <is>
@@ -1971,7 +1923,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2011,21 +1963,11 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>5519</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2038,7 +1980,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2070,21 +2012,11 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>5569</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -2097,7 +2029,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2129,19 +2061,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>5621</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>90</v>
       </c>
@@ -2188,19 +2110,9 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>8</v>
       </c>
@@ -2247,19 +2159,9 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>5196</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>14</v>
       </c>
@@ -2306,19 +2208,9 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>5203</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>12</v>
       </c>
@@ -2365,19 +2257,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>5687</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>14</v>
       </c>
@@ -2424,19 +2306,9 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>5395</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>16</v>
       </c>
@@ -2483,19 +2355,9 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>15184</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>12</v>
       </c>
@@ -2542,19 +2404,9 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>15708</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>10</v>
       </c>
@@ -2601,19 +2453,9 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>15056</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>13</v>
       </c>
@@ -2660,21 +2502,11 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>15493</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
@@ -2719,21 +2551,11 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>14553</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
@@ -2778,34 +2600,24 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>14491</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB23" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB23" s="7" t="n">
-        <v>29</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2837,21 +2649,11 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>15132</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
@@ -2864,7 +2666,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -2896,19 +2698,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>15616</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>36</v>
       </c>
@@ -2955,19 +2747,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>87207</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>56</v>
       </c>
@@ -2982,7 +2764,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3014,19 +2796,9 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>86030</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
         <v>4</v>
       </c>
@@ -3041,7 +2813,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3073,19 +2845,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>82667</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>34</v>
       </c>
@@ -3100,7 +2862,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -3132,19 +2894,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>82796</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>1</v>
       </c>
@@ -3159,7 +2911,7 @@
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
@@ -3191,21 +2943,11 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>80792</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -3250,19 +2992,9 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>80181</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
         <v>1</v>
       </c>
@@ -3318,21 +3050,11 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>82769</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
@@ -3391,19 +3113,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>82955</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>2</v>
       </c>
@@ -3432,19 +3144,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>721</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>41</v>
       </c>
@@ -3473,21 +3175,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>729</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
@@ -3514,19 +3206,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>717</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>2</v>
       </c>
@@ -3555,21 +3237,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>753</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
@@ -3596,21 +3268,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>696</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3637,21 +3299,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>723</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
@@ -3678,19 +3330,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>743</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>15</v>
       </c>
@@ -3719,19 +3361,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>714</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>2</v>
       </c>
@@ -3760,19 +3392,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>50559</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>8</v>
       </c>
@@ -3801,19 +3423,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>51501</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>15</v>
       </c>
@@ -3842,19 +3454,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>51715</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>3</v>
       </c>
@@ -3883,19 +3485,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>50240</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>27</v>
       </c>
@@ -3924,19 +3516,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>48948</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>1</v>
       </c>
@@ -3951,7 +3533,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3965,19 +3547,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>48922</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>18</v>
       </c>
@@ -3992,7 +3564,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4006,19 +3578,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>51004</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>1</v>
       </c>
@@ -4033,7 +3595,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4047,19 +3609,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>50744</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>3</v>
       </c>
@@ -4074,7 +3626,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4088,19 +3640,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>25</v>
       </c>
@@ -4129,19 +3671,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>13</v>
       </c>
@@ -4156,7 +3688,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4170,19 +3702,9 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>11599</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
         <v>2</v>
       </c>
@@ -4211,19 +3733,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>11522</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>2</v>
       </c>
@@ -4252,19 +3764,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>11614</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>1</v>
       </c>
@@ -4293,19 +3795,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>11098</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>9</v>
       </c>
@@ -4334,19 +3826,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>11097</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>19</v>
       </c>
@@ -4375,21 +3857,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>11410</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
@@ -4416,21 +3888,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>11482</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4457,19 +3919,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>11322</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>3</v>
       </c>
@@ -4498,19 +3950,9 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>26509</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
         <v>19</v>
       </c>
@@ -4539,19 +3981,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>26876</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>21</v>
       </c>
@@ -4580,19 +4012,9 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>27154</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
         <v>15</v>
       </c>
@@ -4621,19 +4043,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>26655</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>14</v>
       </c>
@@ -4662,21 +4074,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>25267</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
@@ -4703,21 +4105,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>24712</v>
-      </c>
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
@@ -4744,101 +4136,71 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>26356</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z66" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB66" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD66" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
+      <c r="X67" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Y66" s="4" t="inlineStr">
+      <c r="Y67" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="Z66" s="4" t="inlineStr">
+      <c r="Z67" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="AB66" s="4" t="n">
+      <c r="AB67" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr">
+      <c r="AC67" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD66" s="4" t="inlineStr">
+      <c r="AD67" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>25640</v>
-      </c>
-      <c r="X67" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB67" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>17949</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>55</v>
       </c>
@@ -4867,19 +4229,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>17549</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>4</v>
       </c>
@@ -4894,7 +4246,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4908,19 +4260,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>17646</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>2</v>
       </c>
@@ -4935,7 +4277,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4949,101 +4291,71 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
+      <c r="X71" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB71" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>17131</v>
-      </c>
-      <c r="X71" s="7" t="n">
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Y71" s="7" t="inlineStr">
+      <c r="Y72" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="Z71" s="7" t="inlineStr">
+      <c r="Z72" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB71" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC71" s="7" t="inlineStr">
+      <c r="AB72" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC72" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD71" s="7" t="inlineStr">
+      <c r="AD72" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>17470</v>
-      </c>
-      <c r="X72" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>17485</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>7</v>
       </c>
@@ -5058,7 +4370,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5072,21 +4384,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>17825</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
@@ -5113,21 +4415,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>17897</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
@@ -5154,19 +4446,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>745</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>2</v>
       </c>
@@ -5195,19 +4477,9 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>763</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
         <v>58</v>
       </c>
@@ -5236,19 +4508,9 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>740</v>
-      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
         <v>3</v>
       </c>
@@ -5277,19 +4539,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>783</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>58</v>
       </c>
@@ -5318,19 +4570,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>763</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>3</v>
       </c>
@@ -5359,21 +4601,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>735</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
@@ -5400,21 +4632,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>841</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
@@ -5441,19 +4663,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>767</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>5</v>
       </c>
@@ -5482,21 +4694,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>2142</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -5523,19 +4725,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>2408</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
         <v>6</v>
       </c>
@@ -5564,21 +4756,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>2141</v>
-      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
@@ -5591,7 +4773,7 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5605,21 +4787,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>2082</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
@@ -5646,19 +4818,9 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>1990</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
         <v>5</v>
       </c>
@@ -5687,21 +4849,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>2043</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
@@ -5714,7 +4866,7 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -5728,19 +4880,9 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>2148</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>1</v>
       </c>
@@ -5755,7 +4897,7 @@
         </is>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5769,19 +4911,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>2096</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>9</v>
       </c>
@@ -5827,7 +4959,7 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -6283,7 +5415,7 @@
       <c r="Y108" s="4" t="n"/>
       <c r="Z108" s="4" t="n"/>
       <c r="AB108" s="4" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6304,7 +5436,7 @@
       <c r="Y109" s="7" t="n"/>
       <c r="Z109" s="7" t="n"/>
       <c r="AB109" s="7" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6325,7 +5457,7 @@
       <c r="Y110" s="4" t="n"/>
       <c r="Z110" s="4" t="n"/>
       <c r="AB110" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6346,7 +5478,7 @@
       <c r="Y111" s="7" t="n"/>
       <c r="Z111" s="7" t="n"/>
       <c r="AB111" s="7" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6367,7 +5499,7 @@
       <c r="Y112" s="4" t="n"/>
       <c r="Z112" s="4" t="n"/>
       <c r="AB112" s="4" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6703,7 +5835,7 @@
       <c r="Y128" s="4" t="n"/>
       <c r="Z128" s="4" t="n"/>
       <c r="AB128" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6724,7 +5856,7 @@
       <c r="Y129" s="7" t="n"/>
       <c r="Z129" s="7" t="n"/>
       <c r="AB129" s="7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6808,7 +5940,7 @@
       <c r="Y133" s="7" t="n"/>
       <c r="Z133" s="7" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6850,7 +5982,7 @@
       <c r="Y135" s="7" t="n"/>
       <c r="Z135" s="7" t="n"/>
       <c r="AB135" s="7" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -7186,7 +6318,7 @@
       <c r="Y151" s="7" t="n"/>
       <c r="Z151" s="7" t="n"/>
       <c r="AB151" s="7" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AC151" s="7" t="inlineStr">
         <is>
@@ -7207,7 +6339,7 @@
       <c r="Y152" s="4" t="n"/>
       <c r="Z152" s="4" t="n"/>
       <c r="AB152" s="4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
@@ -7312,7 +6444,7 @@
       <c r="Y157" s="7" t="n"/>
       <c r="Z157" s="7" t="n"/>
       <c r="AB157" s="7" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="AC157" s="7" t="inlineStr">
         <is>
@@ -7333,7 +6465,7 @@
       <c r="Y158" s="4" t="n"/>
       <c r="Z158" s="4" t="n"/>
       <c r="AB158" s="4" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="AC158" s="4" t="inlineStr">
         <is>
@@ -7712,19 +6844,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>7773</v>
-      </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
@@ -7739,7 +6858,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -7798,19 +6917,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10781</v>
-      </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
@@ -7825,7 +6931,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -7884,19 +6990,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>14077</v>
-      </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
@@ -7911,7 +7004,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -7962,19 +7055,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>19486</v>
-      </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
@@ -7989,7 +7069,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -8048,19 +7128,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>25421</v>
-      </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -8075,7 +7142,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -8134,19 +7201,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>36128</v>
-      </c>
       <c r="X7" t="n">
         <v>35</v>
       </c>
@@ -8161,7 +7215,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -8220,19 +7274,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>51111</v>
-      </c>
       <c r="X8" t="n">
         <v>55</v>
       </c>
@@ -8298,21 +7339,8 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>56380</v>
-      </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -8354,21 +7382,8 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>1530</v>
-      </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -8400,19 +7415,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2311</v>
-      </c>
       <c r="X11" t="n">
         <v>62</v>
       </c>
@@ -8446,19 +7448,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>2868</v>
-      </c>
       <c r="X12" t="n">
         <v>6</v>
       </c>
@@ -8492,19 +7481,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>4059</v>
-      </c>
       <c r="X13" t="n">
         <v>4</v>
       </c>
@@ -8519,7 +7495,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -8538,19 +7514,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>5092</v>
-      </c>
       <c r="X14" t="n">
         <v>5</v>
       </c>
@@ -8565,7 +7528,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -8584,19 +7547,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>6962</v>
-      </c>
       <c r="X15" t="n">
         <v>5</v>
       </c>
@@ -8630,19 +7580,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>9959</v>
-      </c>
       <c r="X16" t="n">
         <v>5</v>
       </c>
@@ -8676,19 +7613,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>11290</v>
-      </c>
       <c r="X17" t="n">
         <v>10</v>
       </c>
@@ -8722,19 +7646,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>1815</v>
-      </c>
       <c r="X18" t="n">
         <v>9</v>
       </c>
@@ -8768,19 +7679,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>2333</v>
-      </c>
       <c r="X19" t="n">
         <v>2</v>
       </c>
@@ -8814,19 +7712,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>3182</v>
-      </c>
       <c r="X20" t="n">
         <v>6</v>
       </c>
@@ -8860,19 +7745,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>4129</v>
-      </c>
       <c r="X21" t="n">
         <v>20</v>
       </c>
@@ -8906,19 +7778,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>5644</v>
-      </c>
       <c r="X22" t="n">
         <v>9</v>
       </c>
@@ -8952,34 +7811,21 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V23" t="n">
-        <v>7963</v>
-      </c>
-      <c r="X23" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -8998,34 +7844,21 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V24" t="n">
-        <v>11169</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -9044,34 +7877,21 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V25" t="n">
-        <v>12345</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AB25" t="n">
         <v>1</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB25" t="n">
-        <v>2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -9090,21 +7910,8 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>2322</v>
-      </c>
       <c r="X26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -9136,21 +7943,8 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>3533</v>
-      </c>
       <c r="X27" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -9182,21 +7976,8 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>4891</v>
-      </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -9209,7 +7990,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -9228,19 +8009,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>6461</v>
-      </c>
       <c r="X29" t="n">
         <v>28</v>
       </c>
@@ -9274,19 +8042,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>8274</v>
-      </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
@@ -9301,7 +8056,7 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -9320,19 +8075,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>12174</v>
-      </c>
       <c r="X31" t="n">
         <v>5</v>
       </c>
@@ -9380,19 +8122,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>19723</v>
       </c>
       <c r="X32" t="n">
         <v>4</v>
@@ -9450,19 +8179,6 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>20836</v>
-      </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
@@ -9491,19 +8207,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>1827</v>
-      </c>
       <c r="X34" t="n">
         <v>5</v>
       </c>
@@ -9532,19 +8235,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>2275</v>
-      </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
@@ -9573,19 +8263,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>2882</v>
-      </c>
       <c r="X36" t="n">
         <v>9</v>
       </c>
@@ -9600,35 +8277,22 @@
         </is>
       </c>
       <c r="AB36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="X37" t="n">
         <v>1</v>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>3280</v>
-      </c>
-      <c r="X37" t="n">
-        <v>9</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -9655,35 +8319,22 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>3951</v>
-      </c>
       <c r="X38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
         <v>1</v>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB38" t="n">
-        <v>3</v>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -9696,19 +8347,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>5096</v>
-      </c>
       <c r="X39" t="n">
         <v>1</v>
       </c>
@@ -9737,19 +8375,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>6277</v>
-      </c>
       <c r="X40" t="n">
         <v>6</v>
       </c>
@@ -9764,7 +8389,7 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9778,19 +8403,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>6297</v>
-      </c>
       <c r="X41" t="n">
         <v>1</v>
       </c>
@@ -9805,7 +8417,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9819,19 +8431,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>250</v>
-      </c>
       <c r="X42" t="n">
         <v>6</v>
       </c>
@@ -9846,7 +8445,7 @@
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -9860,19 +8459,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>428</v>
-      </c>
       <c r="X43" t="n">
         <v>1</v>
       </c>
@@ -9887,7 +8473,7 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -9901,19 +8487,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>365</v>
-      </c>
       <c r="X44" t="n">
         <v>3</v>
       </c>
@@ -9928,7 +8501,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -9942,19 +8515,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>471</v>
-      </c>
       <c r="X45" t="n">
         <v>3</v>
       </c>
@@ -9969,7 +8529,7 @@
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -9983,19 +8543,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>554</v>
-      </c>
       <c r="X46" t="n">
         <v>8</v>
       </c>
@@ -10024,19 +8571,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>902</v>
-      </c>
       <c r="X47" t="n">
         <v>7</v>
       </c>
@@ -10051,7 +8585,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -10065,19 +8599,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>1420</v>
-      </c>
       <c r="X48" t="n">
         <v>8</v>
       </c>
@@ -10106,19 +8627,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>1561</v>
-      </c>
       <c r="X49" t="n">
         <v>7</v>
       </c>
@@ -10147,19 +8655,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>6249</v>
-      </c>
       <c r="X50" t="n">
         <v>11</v>
       </c>
@@ -10188,19 +8683,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>8329</v>
-      </c>
       <c r="X51" t="n">
         <v>5</v>
       </c>
@@ -10229,21 +8711,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>10619</v>
-      </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -10270,21 +8739,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>13894</v>
-      </c>
       <c r="X53" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -10311,183 +8767,118 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="V54" t="n">
-        <v>17235</v>
-      </c>
-      <c r="X54" t="n">
+      <c r="AB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="X55" t="n">
         <v>17</v>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB54" t="n">
+      <c r="AB55" t="n">
         <v>3</v>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
+    <row r="56">
+      <c r="X56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="V55" t="n">
-        <v>23145</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AB56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="X57" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB55" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AB57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>32675</v>
-      </c>
-      <c r="X56" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB56" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>34857</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>30</v>
-      </c>
       <c r="X58" t="n">
         <v>31</v>
       </c>
@@ -10502,7 +8893,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -10516,19 +8907,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>81</v>
-      </c>
       <c r="X59" t="n">
         <v>1</v>
       </c>
@@ -10543,7 +8921,7 @@
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -10557,19 +8935,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>103</v>
-      </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
@@ -10584,7 +8949,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -10598,19 +8963,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>154</v>
-      </c>
       <c r="X61" t="n">
         <v>2</v>
       </c>
@@ -10639,19 +8991,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>183</v>
-      </c>
       <c r="X62" t="n">
         <v>33</v>
       </c>
@@ -10680,21 +9019,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V63" t="n">
-        <v>238</v>
-      </c>
       <c r="X63" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -10721,21 +9047,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>354</v>
-      </c>
       <c r="X64" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -10762,21 +9075,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>347</v>
-      </c>
       <c r="X65" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -10803,21 +9103,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>603</v>
-      </c>
       <c r="X66" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -10844,19 +9131,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>820</v>
-      </c>
       <c r="X67" t="n">
         <v>3</v>
       </c>
@@ -10885,19 +9159,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V68" t="n">
-        <v>1204</v>
-      </c>
       <c r="X68" t="n">
         <v>1</v>
       </c>
@@ -10926,19 +9187,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V69" t="n">
-        <v>1689</v>
-      </c>
       <c r="X69" t="n">
         <v>1</v>
       </c>
@@ -10967,19 +9215,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V70" t="n">
-        <v>2042</v>
-      </c>
       <c r="X70" t="n">
         <v>1</v>
       </c>
@@ -10994,7 +9229,7 @@
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11008,19 +9243,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V71" t="n">
-        <v>2581</v>
-      </c>
       <c r="X71" t="n">
         <v>1</v>
       </c>
@@ -11035,7 +9257,7 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -11049,19 +9271,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V72" t="n">
-        <v>3880</v>
-      </c>
       <c r="X72" t="n">
         <v>1</v>
       </c>
@@ -11076,7 +9285,7 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -11090,19 +9299,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V73" t="n">
-        <v>3997</v>
-      </c>
       <c r="X73" t="n">
         <v>5</v>
       </c>
@@ -11131,19 +9327,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V74" t="n">
-        <v>90</v>
-      </c>
       <c r="X74" t="n">
         <v>6</v>
       </c>
@@ -11172,19 +9355,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V75" t="n">
-        <v>119</v>
-      </c>
       <c r="X75" t="n">
         <v>8</v>
       </c>
@@ -11213,19 +9383,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V76" t="n">
-        <v>157</v>
-      </c>
       <c r="X76" t="n">
         <v>1</v>
       </c>
@@ -11240,7 +9397,7 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
@@ -11254,19 +9411,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V77" t="n">
-        <v>244</v>
-      </c>
       <c r="X77" t="n">
         <v>1</v>
       </c>
@@ -11295,19 +9439,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V78" t="n">
-        <v>270</v>
-      </c>
       <c r="X78" t="n">
         <v>2</v>
       </c>
@@ -11322,7 +9453,7 @@
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -11336,75 +9467,36 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V79" t="n">
-        <v>341</v>
-      </c>
       <c r="AB79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="AB80" t="n">
         <v>67</v>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD79" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V80" t="n">
-        <v>409</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V81" t="n">
-        <v>401</v>
-      </c>
       <c r="AB81" t="n">
         <v>4</v>
       </c>
@@ -11466,7 +9558,7 @@
     </row>
     <row r="85">
       <c r="AB85" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
@@ -11481,7 +9573,7 @@
     </row>
     <row r="86">
       <c r="AB86" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -11496,7 +9588,7 @@
     </row>
     <row r="87">
       <c r="AB87" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -11511,7 +9603,7 @@
     </row>
     <row r="88">
       <c r="AB88" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -11526,7 +9618,7 @@
     </row>
     <row r="89">
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -11556,7 +9648,7 @@
     </row>
     <row r="91">
       <c r="AB91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -11571,7 +9663,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -11586,7 +9678,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -11601,7 +9693,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -11616,7 +9708,7 @@
     </row>
     <row r="95">
       <c r="AB95" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -11631,7 +9723,7 @@
     </row>
     <row r="96">
       <c r="AB96" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -11646,7 +9738,7 @@
     </row>
     <row r="97">
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -11661,7 +9753,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -11676,7 +9768,7 @@
     </row>
     <row r="99">
       <c r="AB99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -11691,7 +9783,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -11721,7 +9813,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -11736,7 +9828,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -11811,7 +9903,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -11826,7 +9918,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -11841,7 +9933,7 @@
     </row>
     <row r="110">
       <c r="AB110" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -11856,7 +9948,7 @@
     </row>
     <row r="111">
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
@@ -11871,7 +9963,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -11886,7 +9978,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -11901,7 +9993,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -11931,7 +10023,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -11946,7 +10038,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -12051,7 +10143,7 @@
     </row>
     <row r="124">
       <c r="AB124" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -12066,7 +10158,7 @@
     </row>
     <row r="125">
       <c r="AB125" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
@@ -12081,7 +10173,7 @@
     </row>
     <row r="126">
       <c r="AB126" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
@@ -12096,7 +10188,7 @@
     </row>
     <row r="127">
       <c r="AB127" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -12126,7 +10218,7 @@
     </row>
     <row r="129">
       <c r="AB129" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -12141,7 +10233,7 @@
     </row>
     <row r="130">
       <c r="AB130" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
@@ -12156,7 +10248,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
@@ -12899,19 +10991,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="X2" t="n">
         <v>3</v>
       </c>
@@ -12985,19 +11064,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3208</v>
-      </c>
       <c r="X3" t="n">
         <v>8</v>
       </c>
@@ -13071,19 +11137,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>7785</v>
-      </c>
       <c r="X4" t="n">
         <v>2</v>
       </c>
@@ -13149,19 +11202,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
@@ -13235,19 +11275,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>705</v>
-      </c>
       <c r="X6" t="n">
         <v>4</v>
       </c>
@@ -13321,19 +11348,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>1439</v>
-      </c>
       <c r="X7" t="n">
         <v>2</v>
       </c>
@@ -13407,19 +11421,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="X8" t="n">
         <v>2</v>
       </c>
@@ -13485,19 +11486,6 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>969</v>
-      </c>
       <c r="X9" t="n">
         <v>3</v>
       </c>
@@ -13541,19 +11529,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>1940</v>
-      </c>
       <c r="X10" t="n">
         <v>6</v>
       </c>
@@ -13587,19 +11562,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
       <c r="X11" t="n">
         <v>9</v>
       </c>
@@ -13633,19 +11595,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1063</v>
-      </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
@@ -13679,19 +11628,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>2234</v>
-      </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
@@ -13725,19 +11661,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
       <c r="AB14" t="n">
         <v>11</v>
       </c>
@@ -13758,19 +11681,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>904</v>
-      </c>
       <c r="AB15" t="n">
         <v>5</v>
       </c>
@@ -13791,19 +11701,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>1597</v>
-      </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
@@ -13811,19 +11708,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="C18" t="inlineStr">
@@ -13831,19 +11715,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>113</v>
-      </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
@@ -13851,19 +11722,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>210</v>
-      </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
@@ -13871,19 +11729,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -13891,19 +11736,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>3024</v>
-      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -13911,19 +11743,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>5423</v>
-      </c>
     </row>
     <row r="23">
       <c r="C23" t="inlineStr">
@@ -13931,19 +11750,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>34</v>
-      </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
@@ -13951,19 +11757,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>76</v>
-      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -13971,19 +11764,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="C26" t="inlineStr">
@@ -13991,19 +11771,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>354</v>
-      </c>
     </row>
     <row r="27">
       <c r="C27" t="inlineStr">
@@ -14011,19 +11778,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>609</v>
-      </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
@@ -14031,19 +11785,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
@@ -14051,38 +11792,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>45</v>
-      </c>
     </row>
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="31">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -737,10 +737,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -773,10 +773,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -809,10 +809,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -845,10 +845,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -881,10 +881,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -917,10 +917,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -953,10 +953,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -989,10 +989,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1025,10 +1025,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1061,10 +1061,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD167"/>
+  <dimension ref="A1:AD191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2000,29 +2000,49 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="D10" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C10)</f>
+        <v/>
+      </c>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
+      <c r="G10" s="4">
+        <f>ROUND(MAX(0,MIN(100,(1-E10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>MIN(1,(G10-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="K10" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>MAX(0,(L10-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>$B$2+H10+M10</f>
+        <v/>
+      </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="n">
-        <v>5519</v>
+        <v>1</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>73</v>
@@ -2038,7 +2058,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2072,16 +2092,16 @@
       <c r="N11" s="7" t="n"/>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.Stedor.InstaShop</t>
         </is>
       </c>
       <c r="V11" s="7" t="n">
-        <v>5569</v>
+        <v>55</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>3</v>
@@ -2097,7 +2117,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2131,7 +2151,7 @@
       <c r="N12" s="4" t="n"/>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -2140,7 +2160,7 @@
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5621</v>
+        <v>5519</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>90</v>
@@ -2190,7 +2210,7 @@
       <c r="N13" s="7" t="n"/>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
@@ -2199,7 +2219,7 @@
         </is>
       </c>
       <c r="V13" s="7" t="n">
-        <v>5557</v>
+        <v>5569</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>8</v>
@@ -2249,7 +2269,7 @@
       <c r="N14" s="4" t="n"/>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
@@ -2258,19 +2278,19 @@
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5196</v>
+        <v>5621</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB14" s="4" t="n">
@@ -2308,7 +2328,7 @@
       <c r="N15" s="7" t="n"/>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
@@ -2317,23 +2337,23 @@
         </is>
       </c>
       <c r="V15" s="7" t="n">
-        <v>5203</v>
+        <v>5557</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="Y15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z15" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2367,7 +2387,7 @@
       <c r="N16" s="4" t="n"/>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
@@ -2376,14 +2396,14 @@
         </is>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5687</v>
+        <v>5196</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
@@ -2392,7 +2412,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2426,7 +2446,7 @@
       <c r="N17" s="7" t="n"/>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -2435,14 +2455,14 @@
         </is>
       </c>
       <c r="V17" s="7" t="n">
-        <v>5395</v>
+        <v>5203</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z17" s="7" t="inlineStr">
@@ -2485,23 +2505,23 @@
       <c r="N18" s="4" t="n"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>15184</v>
+        <v>5687</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
@@ -2544,23 +2564,23 @@
       <c r="N19" s="7" t="n"/>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V19" s="7" t="n">
-        <v>15708</v>
+        <v>5395</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z19" s="7" t="inlineStr">
@@ -2603,23 +2623,23 @@
       <c r="N20" s="4" t="n"/>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>15056</v>
+        <v>5472</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
@@ -2662,7 +2682,7 @@
       <c r="N21" s="7" t="n"/>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -2671,14 +2691,14 @@
         </is>
       </c>
       <c r="V21" s="7" t="n">
-        <v>15493</v>
+        <v>15184</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
@@ -2687,7 +2707,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>4</v>
+        <v>327</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2721,7 +2741,7 @@
       <c r="N22" s="4" t="n"/>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
@@ -2730,14 +2750,14 @@
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>14553</v>
+        <v>15708</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
@@ -2746,7 +2766,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2780,7 +2800,7 @@
       <c r="N23" s="7" t="n"/>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
@@ -2789,23 +2809,23 @@
         </is>
       </c>
       <c r="V23" s="7" t="n">
-        <v>14491</v>
+        <v>15056</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2839,7 +2859,7 @@
       <c r="N24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -2848,23 +2868,23 @@
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>15132</v>
+        <v>15493</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2918,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
@@ -2907,23 +2927,23 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>15616</v>
+        <v>14553</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z25" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2957,32 +2977,32 @@
       <c r="N26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>87207</v>
+        <v>14491</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z26" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3016,23 +3036,23 @@
       <c r="N27" s="7" t="n"/>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V27" s="7" t="n">
-        <v>86030</v>
+        <v>15132</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
@@ -3041,7 +3061,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3075,23 +3095,23 @@
       <c r="N28" s="4" t="n"/>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V28" s="4" t="n">
-        <v>82667</v>
+        <v>15616</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
@@ -3134,23 +3154,23 @@
       <c r="N29" s="7" t="n"/>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V29" s="7" t="n">
-        <v>82796</v>
+        <v>15857</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
@@ -3193,7 +3213,7 @@
       <c r="N30" s="4" t="n"/>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3202,14 +3222,14 @@
         </is>
       </c>
       <c r="V30" s="4" t="n">
-        <v>80792</v>
+        <v>87207</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
@@ -3252,7 +3272,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -3261,14 +3281,14 @@
         </is>
       </c>
       <c r="V31" s="7" t="n">
-        <v>80181</v>
+        <v>86030</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z31" s="7" t="inlineStr">
@@ -3320,7 +3340,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3329,14 +3349,14 @@
         </is>
       </c>
       <c r="V32" s="4" t="n">
-        <v>82769</v>
+        <v>82667</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
@@ -3360,7 +3380,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D9)</f>
+        <f>AVERAGE(D2:D10)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3370,7 +3390,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H9)</f>
+        <f>AVERAGE(H2:H10)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3393,7 +3413,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -3402,14 +3422,14 @@
         </is>
       </c>
       <c r="V33" s="7" t="n">
-        <v>82955</v>
+        <v>82796</v>
       </c>
       <c r="X33" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
@@ -3434,23 +3454,23 @@
     <row r="34">
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V34" s="4" t="n">
-        <v>721</v>
+        <v>80792</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
@@ -3475,23 +3495,23 @@
     <row r="35">
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V35" s="7" t="n">
-        <v>729</v>
+        <v>80181</v>
       </c>
       <c r="X35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z35" s="7" t="inlineStr">
@@ -3500,7 +3520,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3516,23 +3536,23 @@
     <row r="36">
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V36" s="4" t="n">
-        <v>717</v>
+        <v>82769</v>
       </c>
       <c r="X36" s="4" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
@@ -3541,7 +3561,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3557,23 +3577,23 @@
     <row r="37">
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V37" s="7" t="n">
-        <v>753</v>
+        <v>82955</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z37" s="7" t="inlineStr">
@@ -3582,7 +3602,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3598,23 +3618,23 @@
     <row r="38">
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V38" s="4" t="n">
-        <v>696</v>
+        <v>84463</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
@@ -3639,7 +3659,7 @@
     <row r="39">
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U39" s="7" t="inlineStr">
@@ -3648,14 +3668,14 @@
         </is>
       </c>
       <c r="V39" s="7" t="n">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z39" s="7" t="inlineStr">
@@ -3680,28 +3700,28 @@
     <row r="40">
       <c r="T40" s="4" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>729</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" s="4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>743</v>
-      </c>
-      <c r="X40" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="Z40" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB40" s="4" t="n">
@@ -3721,7 +3741,7 @@
     <row r="41">
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -3730,19 +3750,19 @@
         </is>
       </c>
       <c r="V41" s="7" t="n">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="X41" s="7" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z41" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB41" s="7" t="n">
@@ -3762,32 +3782,32 @@
     <row r="42">
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V42" s="4" t="n">
-        <v>50559</v>
+        <v>753</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z42" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3803,28 +3823,28 @@
     <row r="43">
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V43" s="7" t="n">
-        <v>51501</v>
+        <v>696</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z43" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB43" s="7" t="n">
@@ -3844,32 +3864,32 @@
     <row r="44">
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V44" s="4" t="n">
-        <v>51715</v>
+        <v>723</v>
       </c>
       <c r="X44" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3885,28 +3905,28 @@
     <row r="45">
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V45" s="7" t="n">
-        <v>50240</v>
+        <v>743</v>
       </c>
       <c r="X45" s="7" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z45" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB45" s="7" t="n">
@@ -3926,32 +3946,32 @@
     <row r="46">
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V46" s="4" t="n">
-        <v>48948</v>
+        <v>714</v>
       </c>
       <c r="X46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3967,23 +3987,23 @@
     <row r="47">
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foody</t>
         </is>
       </c>
       <c r="V47" s="7" t="n">
-        <v>48922</v>
+        <v>733</v>
       </c>
       <c r="X47" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z47" s="7" t="inlineStr">
@@ -3992,7 +4012,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4008,7 +4028,7 @@
     <row r="48">
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -4017,14 +4037,14 @@
         </is>
       </c>
       <c r="V48" s="4" t="n">
-        <v>51004</v>
+        <v>50559</v>
       </c>
       <c r="X48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z48" s="4" t="inlineStr">
@@ -4049,7 +4069,7 @@
     <row r="49">
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -4058,14 +4078,14 @@
         </is>
       </c>
       <c r="V49" s="7" t="n">
-        <v>50744</v>
+        <v>51501</v>
       </c>
       <c r="X49" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z49" s="7" t="inlineStr">
@@ -4090,23 +4110,23 @@
     <row r="50">
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V50" s="4" t="n">
-        <v>1</v>
+        <v>51715</v>
       </c>
       <c r="X50" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
@@ -4131,23 +4151,23 @@
     <row r="51">
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V51" s="7" t="n">
-        <v>1</v>
+        <v>50240</v>
       </c>
       <c r="X51" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z51" s="7" t="inlineStr">
@@ -4172,32 +4192,32 @@
     <row r="52">
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V52" s="4" t="n">
-        <v>11599</v>
+        <v>48948</v>
       </c>
       <c r="X52" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z52" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB52" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB52" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -4213,23 +4233,23 @@
     <row r="53">
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U53" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V53" s="7" t="n">
-        <v>11522</v>
+        <v>48922</v>
       </c>
       <c r="X53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z53" s="7" t="inlineStr">
@@ -4238,7 +4258,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4254,23 +4274,23 @@
     <row r="54">
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V54" s="4" t="n">
-        <v>11614</v>
+        <v>51004</v>
       </c>
       <c r="X54" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z54" s="4" t="inlineStr">
@@ -4295,23 +4315,23 @@
     <row r="55">
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V55" s="7" t="n">
-        <v>11098</v>
+        <v>50744</v>
       </c>
       <c r="X55" s="7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z55" s="7" t="inlineStr">
@@ -4320,7 +4340,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4336,32 +4356,32 @@
     <row r="56">
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V56" s="4" t="n">
-        <v>11097</v>
+        <v>50396</v>
       </c>
       <c r="X56" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4377,28 +4397,28 @@
     <row r="57">
       <c r="T57" s="7" t="inlineStr">
         <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U57" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+        </is>
+      </c>
+      <c r="V57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y57" s="7" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>11410</v>
-      </c>
-      <c r="X57" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="Z57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB57" s="7" t="n">
@@ -4418,28 +4438,28 @@
     <row r="58">
       <c r="T58" s="4" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y58" s="4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>11482</v>
-      </c>
-      <c r="X58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="Z58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB58" s="4" t="n">
@@ -4459,7 +4479,7 @@
     <row r="59">
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -4468,19 +4488,19 @@
         </is>
       </c>
       <c r="V59" s="7" t="n">
-        <v>11322</v>
+        <v>11599</v>
       </c>
       <c r="X59" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB59" s="7" t="n">
@@ -4500,32 +4520,32 @@
     <row r="60">
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U60" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>11522</v>
+      </c>
+      <c r="X60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z60" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V60" s="4" t="n">
-        <v>26509</v>
-      </c>
-      <c r="X60" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y60" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB60" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4541,32 +4561,32 @@
     <row r="61">
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V61" s="7" t="n">
+        <v>11614</v>
+      </c>
+      <c r="X61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z61" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V61" s="7" t="n">
-        <v>26876</v>
-      </c>
-      <c r="X61" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB61" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4582,28 +4602,28 @@
     <row r="62">
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U62" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>11098</v>
+      </c>
+      <c r="X62" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z62" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>27154</v>
-      </c>
-      <c r="X62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB62" s="4" t="n">
@@ -4623,32 +4643,32 @@
     <row r="63">
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V63" s="7" t="n">
+        <v>11097</v>
+      </c>
+      <c r="X63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z63" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V63" s="7" t="n">
-        <v>26655</v>
-      </c>
-      <c r="X63" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB63" s="7" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4664,32 +4684,32 @@
     <row r="64">
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>11410</v>
+      </c>
+      <c r="X64" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V64" s="4" t="n">
-        <v>25267</v>
-      </c>
-      <c r="X64" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB64" s="4" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4705,32 +4725,32 @@
     <row r="65">
       <c r="T65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V65" s="7" t="n">
+        <v>11482</v>
+      </c>
+      <c r="X65" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z65" s="7" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V65" s="7" t="n">
-        <v>24712</v>
-      </c>
-      <c r="X65" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
       <c r="AB65" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4746,23 +4766,23 @@
     <row r="66">
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V66" s="4" t="n">
-        <v>26356</v>
+        <v>11322</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z66" s="4" t="inlineStr">
@@ -4771,7 +4791,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4787,23 +4807,23 @@
     <row r="67">
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V67" s="7" t="n">
-        <v>25640</v>
+        <v>11380</v>
       </c>
       <c r="X67" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z67" s="7" t="inlineStr">
@@ -4812,7 +4832,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4833,27 +4853,27 @@
       </c>
       <c r="U68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V68" s="4" t="n">
-        <v>17949</v>
+        <v>26509</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="Y68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z68" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4874,27 +4894,27 @@
       </c>
       <c r="U69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V69" s="7" t="n">
-        <v>17549</v>
+        <v>26876</v>
       </c>
       <c r="X69" s="7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z69" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4915,27 +4935,27 @@
       </c>
       <c r="U70" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V70" s="4" t="n">
-        <v>17646</v>
+        <v>27154</v>
       </c>
       <c r="X70" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>151</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4956,23 +4976,23 @@
       </c>
       <c r="U71" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V71" s="7" t="n">
-        <v>17131</v>
+        <v>26655</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z71" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB71" s="7" t="n">
@@ -4997,27 +5017,27 @@
       </c>
       <c r="U72" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V72" s="4" t="n">
-        <v>17470</v>
+        <v>25267</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z72" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -5038,27 +5058,27 @@
       </c>
       <c r="U73" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V73" s="7" t="n">
-        <v>17485</v>
+        <v>24712</v>
       </c>
       <c r="X73" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z73" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5079,27 +5099,27 @@
       </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V74" s="4" t="n">
-        <v>17825</v>
+        <v>26356</v>
       </c>
       <c r="X74" s="4" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z74" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5120,27 +5140,27 @@
       </c>
       <c r="U75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V75" s="7" t="n">
-        <v>17897</v>
+        <v>25640</v>
       </c>
       <c r="X75" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z75" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5156,32 +5176,32 @@
     <row r="76">
       <c r="T76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V76" s="4" t="n">
-        <v>745</v>
+        <v>26277</v>
       </c>
       <c r="X76" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB76" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Y76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB76" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -5197,32 +5217,32 @@
     <row r="77">
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V77" s="7" t="n">
-        <v>763</v>
+        <v>17949</v>
       </c>
       <c r="X77" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Y77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
@@ -5238,32 +5258,32 @@
     <row r="78">
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V78" s="4" t="n">
-        <v>740</v>
+        <v>17549</v>
       </c>
       <c r="X78" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -5279,28 +5299,28 @@
     <row r="79">
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V79" s="7" t="n">
-        <v>783</v>
+        <v>17646</v>
       </c>
       <c r="X79" s="7" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB79" s="7" t="n">
@@ -5320,23 +5340,23 @@
     <row r="80">
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V80" s="4" t="n">
-        <v>763</v>
+        <v>17131</v>
       </c>
       <c r="X80" s="4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z80" s="4" t="inlineStr">
@@ -5361,23 +5381,23 @@
     <row r="81">
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U81" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V81" s="7" t="n">
-        <v>735</v>
+        <v>17470</v>
       </c>
       <c r="X81" s="7" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z81" s="7" t="inlineStr">
@@ -5402,23 +5422,23 @@
     <row r="82">
       <c r="T82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U82" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V82" s="4" t="n">
-        <v>841</v>
+        <v>17485</v>
       </c>
       <c r="X82" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
@@ -5427,7 +5447,7 @@
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>3</v>
+        <v>327</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
@@ -5443,23 +5463,23 @@
     <row r="83">
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U83" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V83" s="7" t="n">
-        <v>767</v>
+        <v>17825</v>
       </c>
       <c r="X83" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z83" s="7" t="inlineStr">
@@ -5468,7 +5488,7 @@
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>327</v>
+        <v>3</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
@@ -5484,23 +5504,23 @@
     <row r="84">
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U84" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V84" s="4" t="n">
-        <v>2142</v>
+        <v>17897</v>
       </c>
       <c r="X84" s="4" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z84" s="4" t="inlineStr">
@@ -5509,7 +5529,7 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -5525,23 +5545,23 @@
     <row r="85">
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V85" s="7" t="n">
-        <v>2408</v>
+        <v>17613</v>
       </c>
       <c r="X85" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z85" s="7" t="inlineStr">
@@ -5550,7 +5570,7 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -5566,32 +5586,32 @@
     <row r="86">
       <c r="T86" s="4" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>745</v>
+      </c>
+      <c r="X86" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>2141</v>
-      </c>
-      <c r="X86" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y86" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z86" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5607,23 +5627,23 @@
     <row r="87">
       <c r="T87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U87" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V87" s="7" t="n">
-        <v>2082</v>
+        <v>763</v>
       </c>
       <c r="X87" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z87" s="7" t="inlineStr">
@@ -5648,23 +5668,23 @@
     <row r="88">
       <c r="T88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U88" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V88" s="4" t="n">
-        <v>1990</v>
+        <v>740</v>
       </c>
       <c r="X88" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z88" s="4" t="inlineStr">
@@ -5689,23 +5709,23 @@
     <row r="89">
       <c r="T89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V89" s="7" t="n">
-        <v>2043</v>
+        <v>783</v>
       </c>
       <c r="X89" s="7" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z89" s="7" t="inlineStr">
@@ -5714,7 +5734,7 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -5730,19 +5750,19 @@
     <row r="90">
       <c r="T90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V90" s="4" t="n">
-        <v>2148</v>
+        <v>763</v>
       </c>
       <c r="X90" s="4" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="Y90" s="4" t="inlineStr">
         <is>
@@ -5751,11 +5771,11 @@
       </c>
       <c r="Z90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5771,28 +5791,28 @@
     <row r="91">
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V91" s="7" t="n">
-        <v>2096</v>
+        <v>735</v>
       </c>
       <c r="X91" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB91" s="7" t="n">
@@ -5810,25 +5830,35 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" s="4" t="n"/>
-      <c r="U92" s="4" t="n"/>
-      <c r="V92" s="4" t="n"/>
+      <c r="T92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U92" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V92" s="4" t="n">
+        <v>841</v>
+      </c>
       <c r="X92" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z92" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB92" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Y92" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB92" s="4" t="n">
-        <v>67</v>
-      </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -5841,20 +5871,30 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" s="7" t="n"/>
-      <c r="U93" s="7" t="n"/>
-      <c r="V93" s="7" t="n"/>
+      <c r="T93" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U93" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V93" s="7" t="n">
+        <v>767</v>
+      </c>
       <c r="X93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Y93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB93" s="7" t="n">
@@ -5872,206 +5912,276 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="n"/>
-      <c r="U94" s="4" t="n"/>
-      <c r="V94" s="4" t="n"/>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U94" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V94" s="4" t="n">
+        <v>748</v>
+      </c>
       <c r="X94" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z94" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB94" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y94" s="4" t="inlineStr">
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD94" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="T95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U95" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V95" s="7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="X95" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z95" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD95" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="T96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U96" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V96" s="4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="X96" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z96" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB96" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD96" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="T97" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="T95" s="7" t="n"/>
-      <c r="U95" s="7" t="n"/>
-      <c r="V95" s="7" t="n"/>
-      <c r="X95" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y95" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB95" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC95" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="T96" s="4" t="n"/>
-      <c r="U96" s="4" t="n"/>
-      <c r="V96" s="4" t="n"/>
-      <c r="X96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y96" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB96" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="T97" s="7" t="n"/>
-      <c r="U97" s="7" t="n"/>
-      <c r="V97" s="7" t="n"/>
+      <c r="U97" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V97" s="7" t="n">
+        <v>2141</v>
+      </c>
       <c r="X97" s="7" t="n">
         <v>6</v>
       </c>
       <c r="Y97" s="7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z97" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD97" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V98" s="4" t="n">
+        <v>2082</v>
+      </c>
+      <c r="X98" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB98" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="T99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U99" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V99" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="X99" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z99" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB99" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD99" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="T100" s="4" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="Z97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB97" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC97" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD97" s="7" t="inlineStr">
+      <c r="U100" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V100" s="4" t="n">
+        <v>2043</v>
+      </c>
+      <c r="X100" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y100" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z100" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="T98" s="4" t="n"/>
-      <c r="U98" s="4" t="n"/>
-      <c r="V98" s="4" t="n"/>
-      <c r="X98" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y98" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB98" s="4" t="n">
-        <v>173</v>
-      </c>
-      <c r="AC98" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="T99" s="7" t="n"/>
-      <c r="U99" s="7" t="n"/>
-      <c r="V99" s="7" t="n"/>
-      <c r="X99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="T100" s="4" t="n"/>
-      <c r="U100" s="4" t="n"/>
-      <c r="V100" s="4" t="n"/>
-      <c r="X100" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y100" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB100" s="4" t="n">
@@ -6089,20 +6199,30 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="n"/>
-      <c r="U101" s="7" t="n"/>
-      <c r="V101" s="7" t="n"/>
+      <c r="T101" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U101" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V101" s="7" t="n">
+        <v>2148</v>
+      </c>
       <c r="X101" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB101" s="7" t="n">
@@ -6120,20 +6240,30 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="n"/>
-      <c r="U102" s="4" t="n"/>
-      <c r="V102" s="4" t="n"/>
+      <c r="T102" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U102" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V102" s="4" t="n">
+        <v>2096</v>
+      </c>
       <c r="X102" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB102" s="4" t="n">
@@ -6151,20 +6281,30 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="n"/>
-      <c r="U103" s="7" t="n"/>
-      <c r="V103" s="7" t="n"/>
+      <c r="T103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U103" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.yemeksepeti</t>
+        </is>
+      </c>
+      <c r="V103" s="7" t="n">
+        <v>2265</v>
+      </c>
       <c r="X103" s="7" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB103" s="7" t="n">
@@ -6186,20 +6326,20 @@
       <c r="U104" s="4" t="n"/>
       <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>339</v>
+        <v>8</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
@@ -6216,11 +6356,21 @@
       <c r="T105" s="7" t="n"/>
       <c r="U105" s="7" t="n"/>
       <c r="V105" s="7" t="n"/>
-      <c r="X105" s="7" t="n"/>
-      <c r="Y105" s="7" t="n"/>
-      <c r="Z105" s="7" t="n"/>
+      <c r="X105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z105" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB105" s="7" t="n">
-        <v>8</v>
+        <v>339</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
@@ -6237,11 +6387,21 @@
       <c r="T106" s="4" t="n"/>
       <c r="U106" s="4" t="n"/>
       <c r="V106" s="4" t="n"/>
-      <c r="X106" s="4" t="n"/>
-      <c r="Y106" s="4" t="n"/>
-      <c r="Z106" s="4" t="n"/>
+      <c r="X106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z106" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB106" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -6258,11 +6418,21 @@
       <c r="T107" s="7" t="n"/>
       <c r="U107" s="7" t="n"/>
       <c r="V107" s="7" t="n"/>
-      <c r="X107" s="7" t="n"/>
-      <c r="Y107" s="7" t="n"/>
-      <c r="Z107" s="7" t="n"/>
+      <c r="X107" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y107" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z107" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB107" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -6279,11 +6449,21 @@
       <c r="T108" s="4" t="n"/>
       <c r="U108" s="4" t="n"/>
       <c r="V108" s="4" t="n"/>
-      <c r="X108" s="4" t="n"/>
-      <c r="Y108" s="4" t="n"/>
-      <c r="Z108" s="4" t="n"/>
+      <c r="X108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y108" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z108" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB108" s="4" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6300,11 +6480,21 @@
       <c r="T109" s="7" t="n"/>
       <c r="U109" s="7" t="n"/>
       <c r="V109" s="7" t="n"/>
-      <c r="X109" s="7" t="n"/>
-      <c r="Y109" s="7" t="n"/>
-      <c r="Z109" s="7" t="n"/>
+      <c r="X109" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y109" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z109" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB109" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6321,11 +6511,21 @@
       <c r="T110" s="4" t="n"/>
       <c r="U110" s="4" t="n"/>
       <c r="V110" s="4" t="n"/>
-      <c r="X110" s="4" t="n"/>
-      <c r="Y110" s="4" t="n"/>
-      <c r="Z110" s="4" t="n"/>
+      <c r="X110" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y110" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z110" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB110" s="4" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6342,11 +6542,21 @@
       <c r="T111" s="7" t="n"/>
       <c r="U111" s="7" t="n"/>
       <c r="V111" s="7" t="n"/>
-      <c r="X111" s="7" t="n"/>
-      <c r="Y111" s="7" t="n"/>
-      <c r="Z111" s="7" t="n"/>
+      <c r="X111" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y111" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z111" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB111" s="7" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6363,11 +6573,21 @@
       <c r="T112" s="4" t="n"/>
       <c r="U112" s="4" t="n"/>
       <c r="V112" s="4" t="n"/>
-      <c r="X112" s="4" t="n"/>
-      <c r="Y112" s="4" t="n"/>
-      <c r="Z112" s="4" t="n"/>
+      <c r="X112" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y112" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z112" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB112" s="4" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6384,11 +6604,21 @@
       <c r="T113" s="7" t="n"/>
       <c r="U113" s="7" t="n"/>
       <c r="V113" s="7" t="n"/>
-      <c r="X113" s="7" t="n"/>
-      <c r="Y113" s="7" t="n"/>
-      <c r="Z113" s="7" t="n"/>
+      <c r="X113" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y113" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z113" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB113" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -6405,11 +6635,21 @@
       <c r="T114" s="4" t="n"/>
       <c r="U114" s="4" t="n"/>
       <c r="V114" s="4" t="n"/>
-      <c r="X114" s="4" t="n"/>
-      <c r="Y114" s="4" t="n"/>
-      <c r="Z114" s="4" t="n"/>
+      <c r="X114" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y114" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z114" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB114" s="4" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6426,11 +6666,21 @@
       <c r="T115" s="7" t="n"/>
       <c r="U115" s="7" t="n"/>
       <c r="V115" s="7" t="n"/>
-      <c r="X115" s="7" t="n"/>
-      <c r="Y115" s="7" t="n"/>
-      <c r="Z115" s="7" t="n"/>
+      <c r="X115" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z115" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB115" s="7" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6447,9 +6697,19 @@
       <c r="T116" s="4" t="n"/>
       <c r="U116" s="4" t="n"/>
       <c r="V116" s="4" t="n"/>
-      <c r="X116" s="4" t="n"/>
-      <c r="Y116" s="4" t="n"/>
-      <c r="Z116" s="4" t="n"/>
+      <c r="X116" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y116" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z116" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB116" s="4" t="n">
         <v>1</v>
       </c>
@@ -6468,11 +6728,21 @@
       <c r="T117" s="7" t="n"/>
       <c r="U117" s="7" t="n"/>
       <c r="V117" s="7" t="n"/>
-      <c r="X117" s="7" t="n"/>
-      <c r="Y117" s="7" t="n"/>
-      <c r="Z117" s="7" t="n"/>
+      <c r="X117" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y117" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z117" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB117" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -6489,11 +6759,21 @@
       <c r="T118" s="4" t="n"/>
       <c r="U118" s="4" t="n"/>
       <c r="V118" s="4" t="n"/>
-      <c r="X118" s="4" t="n"/>
-      <c r="Y118" s="4" t="n"/>
-      <c r="Z118" s="4" t="n"/>
+      <c r="X118" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y118" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z118" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB118" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -6510,11 +6790,21 @@
       <c r="T119" s="7" t="n"/>
       <c r="U119" s="7" t="n"/>
       <c r="V119" s="7" t="n"/>
-      <c r="X119" s="7" t="n"/>
-      <c r="Y119" s="7" t="n"/>
-      <c r="Z119" s="7" t="n"/>
+      <c r="X119" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y119" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z119" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB119" s="7" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -6531,11 +6821,21 @@
       <c r="T120" s="4" t="n"/>
       <c r="U120" s="4" t="n"/>
       <c r="V120" s="4" t="n"/>
-      <c r="X120" s="4" t="n"/>
-      <c r="Y120" s="4" t="n"/>
-      <c r="Z120" s="4" t="n"/>
+      <c r="X120" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y120" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z120" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB120" s="4" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -6552,9 +6852,19 @@
       <c r="T121" s="7" t="n"/>
       <c r="U121" s="7" t="n"/>
       <c r="V121" s="7" t="n"/>
-      <c r="X121" s="7" t="n"/>
-      <c r="Y121" s="7" t="n"/>
-      <c r="Z121" s="7" t="n"/>
+      <c r="X121" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y121" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z121" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB121" s="7" t="n">
         <v>3</v>
       </c>
@@ -6573,9 +6883,19 @@
       <c r="T122" s="4" t="n"/>
       <c r="U122" s="4" t="n"/>
       <c r="V122" s="4" t="n"/>
-      <c r="X122" s="4" t="n"/>
-      <c r="Y122" s="4" t="n"/>
-      <c r="Z122" s="4" t="n"/>
+      <c r="X122" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y122" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z122" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB122" s="4" t="n">
         <v>14</v>
       </c>
@@ -6594,9 +6914,19 @@
       <c r="T123" s="7" t="n"/>
       <c r="U123" s="7" t="n"/>
       <c r="V123" s="7" t="n"/>
-      <c r="X123" s="7" t="n"/>
-      <c r="Y123" s="7" t="n"/>
-      <c r="Z123" s="7" t="n"/>
+      <c r="X123" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z123" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB123" s="7" t="n">
         <v>1</v>
       </c>
@@ -6640,7 +6970,7 @@
       <c r="Y125" s="7" t="n"/>
       <c r="Z125" s="7" t="n"/>
       <c r="AB125" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
@@ -6661,7 +6991,7 @@
       <c r="Y126" s="4" t="n"/>
       <c r="Z126" s="4" t="n"/>
       <c r="AB126" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -6829,7 +7159,7 @@
       <c r="Y134" s="4" t="n"/>
       <c r="Z134" s="4" t="n"/>
       <c r="AB134" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -6850,7 +7180,7 @@
       <c r="Y135" s="7" t="n"/>
       <c r="Z135" s="7" t="n"/>
       <c r="AB135" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -6892,7 +7222,7 @@
       <c r="Y137" s="7" t="n"/>
       <c r="Z137" s="7" t="n"/>
       <c r="AB137" s="7" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -6913,7 +7243,7 @@
       <c r="Y138" s="4" t="n"/>
       <c r="Z138" s="4" t="n"/>
       <c r="AB138" s="4" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -6934,7 +7264,7 @@
       <c r="Y139" s="7" t="n"/>
       <c r="Z139" s="7" t="n"/>
       <c r="AB139" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -6955,7 +7285,7 @@
       <c r="Y140" s="4" t="n"/>
       <c r="Z140" s="4" t="n"/>
       <c r="AB140" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -6976,7 +7306,7 @@
       <c r="Y141" s="7" t="n"/>
       <c r="Z141" s="7" t="n"/>
       <c r="AB141" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -7018,7 +7348,7 @@
       <c r="Y143" s="7" t="n"/>
       <c r="Z143" s="7" t="n"/>
       <c r="AB143" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -7060,7 +7390,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -7081,7 +7411,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -7123,7 +7453,7 @@
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n"/>
       <c r="AB148" s="4" t="n">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
@@ -7144,7 +7474,7 @@
       <c r="Y149" s="7" t="n"/>
       <c r="Z149" s="7" t="n"/>
       <c r="AB149" s="7" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="AC149" s="7" t="inlineStr">
         <is>
@@ -7165,7 +7495,7 @@
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n"/>
       <c r="AB150" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -7228,7 +7558,7 @@
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
       <c r="AB153" s="7" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -7270,7 +7600,7 @@
       <c r="Y155" s="7" t="n"/>
       <c r="Z155" s="7" t="n"/>
       <c r="AB155" s="7" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
@@ -7354,7 +7684,7 @@
       <c r="Y159" s="7" t="n"/>
       <c r="Z159" s="7" t="n"/>
       <c r="AB159" s="7" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AC159" s="7" t="inlineStr">
         <is>
@@ -7375,7 +7705,7 @@
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n"/>
       <c r="AB160" s="4" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
@@ -7396,7 +7726,7 @@
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
       <c r="AB161" s="7" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -7417,7 +7747,7 @@
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
       <c r="AB162" s="4" t="n">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -7438,7 +7768,7 @@
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
       <c r="AB163" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -7480,7 +7810,7 @@
       <c r="Y165" s="7" t="n"/>
       <c r="Z165" s="7" t="n"/>
       <c r="AB165" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
@@ -7501,7 +7831,7 @@
       <c r="Y166" s="4" t="n"/>
       <c r="Z166" s="4" t="n"/>
       <c r="AB166" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
@@ -7530,6 +7860,510 @@
         </is>
       </c>
       <c r="AD167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="n"/>
+      <c r="V168" s="4" t="n"/>
+      <c r="X168" s="4" t="n"/>
+      <c r="Y168" s="4" t="n"/>
+      <c r="Z168" s="4" t="n"/>
+      <c r="AB168" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="T169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
+      <c r="X169" s="7" t="n"/>
+      <c r="Y169" s="7" t="n"/>
+      <c r="Z169" s="7" t="n"/>
+      <c r="AB169" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC169" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD169" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="n"/>
+      <c r="V170" s="4" t="n"/>
+      <c r="X170" s="4" t="n"/>
+      <c r="Y170" s="4" t="n"/>
+      <c r="Z170" s="4" t="n"/>
+      <c r="AB170" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="T171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
+      <c r="X171" s="7" t="n"/>
+      <c r="Y171" s="7" t="n"/>
+      <c r="Z171" s="7" t="n"/>
+      <c r="AB171" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC171" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="n"/>
+      <c r="V172" s="4" t="n"/>
+      <c r="X172" s="4" t="n"/>
+      <c r="Y172" s="4" t="n"/>
+      <c r="Z172" s="4" t="n"/>
+      <c r="AB172" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD172" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="T173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
+      <c r="X173" s="7" t="n"/>
+      <c r="Y173" s="7" t="n"/>
+      <c r="Z173" s="7" t="n"/>
+      <c r="AB173" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC173" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD173" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="n"/>
+      <c r="V174" s="4" t="n"/>
+      <c r="X174" s="4" t="n"/>
+      <c r="Y174" s="4" t="n"/>
+      <c r="Z174" s="4" t="n"/>
+      <c r="AB174" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD174" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="T175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
+      <c r="X175" s="7" t="n"/>
+      <c r="Y175" s="7" t="n"/>
+      <c r="Z175" s="7" t="n"/>
+      <c r="AB175" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC175" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD175" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="n"/>
+      <c r="V176" s="4" t="n"/>
+      <c r="X176" s="4" t="n"/>
+      <c r="Y176" s="4" t="n"/>
+      <c r="Z176" s="4" t="n"/>
+      <c r="AB176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD176" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="T177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
+      <c r="X177" s="7" t="n"/>
+      <c r="Y177" s="7" t="n"/>
+      <c r="Z177" s="7" t="n"/>
+      <c r="AB177" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC177" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD177" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="4" t="n"/>
+      <c r="V178" s="4" t="n"/>
+      <c r="X178" s="4" t="n"/>
+      <c r="Y178" s="4" t="n"/>
+      <c r="Z178" s="4" t="n"/>
+      <c r="AB178" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD178" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="T179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
+      <c r="X179" s="7" t="n"/>
+      <c r="Y179" s="7" t="n"/>
+      <c r="Z179" s="7" t="n"/>
+      <c r="AB179" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="AC179" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD179" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="4" t="n"/>
+      <c r="V180" s="4" t="n"/>
+      <c r="X180" s="4" t="n"/>
+      <c r="Y180" s="4" t="n"/>
+      <c r="Z180" s="4" t="n"/>
+      <c r="AB180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD180" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="T181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
+      <c r="X181" s="7" t="n"/>
+      <c r="Y181" s="7" t="n"/>
+      <c r="Z181" s="7" t="n"/>
+      <c r="AB181" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC181" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD181" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="4" t="n"/>
+      <c r="V182" s="4" t="n"/>
+      <c r="X182" s="4" t="n"/>
+      <c r="Y182" s="4" t="n"/>
+      <c r="Z182" s="4" t="n"/>
+      <c r="AB182" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD182" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="T183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
+      <c r="X183" s="7" t="n"/>
+      <c r="Y183" s="7" t="n"/>
+      <c r="Z183" s="7" t="n"/>
+      <c r="AB183" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC183" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD183" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="4" t="n"/>
+      <c r="V184" s="4" t="n"/>
+      <c r="X184" s="4" t="n"/>
+      <c r="Y184" s="4" t="n"/>
+      <c r="Z184" s="4" t="n"/>
+      <c r="AB184" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD184" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="T185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
+      <c r="X185" s="7" t="n"/>
+      <c r="Y185" s="7" t="n"/>
+      <c r="Z185" s="7" t="n"/>
+      <c r="AB185" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC185" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD185" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="4" t="n"/>
+      <c r="V186" s="4" t="n"/>
+      <c r="X186" s="4" t="n"/>
+      <c r="Y186" s="4" t="n"/>
+      <c r="Z186" s="4" t="n"/>
+      <c r="AB186" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD186" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="T187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
+      <c r="X187" s="7" t="n"/>
+      <c r="Y187" s="7" t="n"/>
+      <c r="Z187" s="7" t="n"/>
+      <c r="AB187" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC187" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD187" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="4" t="n"/>
+      <c r="V188" s="4" t="n"/>
+      <c r="X188" s="4" t="n"/>
+      <c r="Y188" s="4" t="n"/>
+      <c r="Z188" s="4" t="n"/>
+      <c r="AB188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD188" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="T189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
+      <c r="X189" s="7" t="n"/>
+      <c r="Y189" s="7" t="n"/>
+      <c r="Z189" s="7" t="n"/>
+      <c r="AB189" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC189" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD189" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="n"/>
+      <c r="X190" s="4" t="n"/>
+      <c r="Y190" s="4" t="n"/>
+      <c r="Z190" s="4" t="n"/>
+      <c r="AB190" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD190" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="T191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
+      <c r="X191" s="7" t="n"/>
+      <c r="Y191" s="7" t="n"/>
+      <c r="Z191" s="7" t="n"/>
+      <c r="AB191" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC191" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD191" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -7551,7 +8385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD133"/>
+  <dimension ref="A1:AD147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7739,7 +8573,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -7825,7 +8659,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -8062,7 +8896,7 @@
         <v>25421</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -8075,7 +8909,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -8148,7 +8982,7 @@
         <v>36128</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -8161,7 +8995,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -8247,7 +9081,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -8312,7 +9146,7 @@
         <v>56380</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -8325,7 +9159,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -8354,21 +9188,53 @@
           <t>2026-09-09</t>
         </is>
       </c>
+      <c r="D10">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C10)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>ROUND(MAX(0,MIN(100,(1-E10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>MIN(1,(G10-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C10)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>MAX(0,(L10-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>$B$2+H10+M10</f>
+        <v/>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1530</v>
+        <v>56145</v>
       </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -8402,7 +9268,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -8411,7 +9277,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2311</v>
+        <v>1530</v>
       </c>
       <c r="X11" t="n">
         <v>62</v>
@@ -8448,7 +9314,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -8457,19 +9323,19 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2868</v>
+        <v>2311</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -8494,7 +9360,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -8503,14 +9369,14 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>4059</v>
+        <v>2868</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -8519,7 +9385,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -8540,7 +9406,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -8549,14 +9415,14 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5092</v>
+        <v>4059</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -8565,7 +9431,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -8586,7 +9452,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -8595,14 +9461,14 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>6962</v>
+        <v>5092</v>
       </c>
       <c r="X15" t="n">
         <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -8632,7 +9498,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -8641,14 +9507,14 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>9959</v>
+        <v>6962</v>
       </c>
       <c r="X16" t="n">
         <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -8678,7 +9544,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -8687,14 +9553,14 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>11290</v>
+        <v>9959</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -8703,7 +9569,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -8724,23 +9590,23 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1815</v>
+        <v>11290</v>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -8749,7 +9615,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -8770,32 +9636,32 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2333</v>
+        <v>11188</v>
       </c>
       <c r="X19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
         <v>2</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>8</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -8816,7 +9682,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -8825,23 +9691,23 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3182</v>
+        <v>1815</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -8862,7 +9728,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -8871,14 +9737,14 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4129</v>
+        <v>2333</v>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -8887,7 +9753,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -8908,7 +9774,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -8917,14 +9783,14 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5644</v>
+        <v>3182</v>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -8933,7 +9799,7 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -8954,7 +9820,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -8963,14 +9829,14 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>7963</v>
+        <v>4129</v>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -8979,7 +9845,7 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -9000,7 +9866,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -9009,23 +9875,23 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>11169</v>
+        <v>5644</v>
       </c>
       <c r="X24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
         <v>1</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB24" t="n">
-        <v>4</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -9046,7 +9912,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -9055,14 +9921,14 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>12345</v>
+        <v>7963</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -9071,7 +9937,7 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -9092,23 +9958,23 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>2322</v>
+        <v>11169</v>
       </c>
       <c r="X26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -9138,23 +10004,23 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>3533</v>
+        <v>12345</v>
       </c>
       <c r="X27" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -9184,23 +10050,23 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>4891</v>
+        <v>12001</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -9230,7 +10096,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -9239,14 +10105,14 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>6461</v>
+        <v>2322</v>
       </c>
       <c r="X29" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -9255,7 +10121,7 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -9276,7 +10142,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -9285,23 +10151,23 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>8274</v>
+        <v>3533</v>
       </c>
       <c r="X30" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
         <v>1</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB30" t="n">
-        <v>21</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -9322,7 +10188,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -9331,19 +10197,19 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>12174</v>
+        <v>4891</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -9383,7 +10249,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -9392,19 +10258,19 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>19723</v>
+        <v>6461</v>
       </c>
       <c r="X32" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -9423,7 +10289,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D9)</f>
+        <f>AVERAGE(D2:D10)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -9431,7 +10297,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H9)</f>
+        <f>AVERAGE(H2:H10)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -9452,7 +10318,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -9461,23 +10327,23 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>20836</v>
+        <v>8274</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -9493,32 +10359,32 @@
     <row r="34">
       <c r="T34" t="inlineStr">
         <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>12174</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>1827</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -9534,23 +10400,23 @@
     <row r="35">
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>2275</v>
+        <v>19723</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -9575,23 +10441,23 @@
     <row r="36">
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>2882</v>
+        <v>20836</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -9616,32 +10482,32 @@
     <row r="37">
       <c r="T37" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>20942</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>3280</v>
-      </c>
-      <c r="X37" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z37" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -9657,32 +10523,32 @@
     <row r="38">
       <c r="T38" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1827</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>3951</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z38" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -9698,7 +10564,7 @@
     <row r="39">
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -9707,14 +10573,14 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>5096</v>
+        <v>2275</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -9723,7 +10589,7 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9739,7 +10605,7 @@
     <row r="40">
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -9748,14 +10614,14 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>6277</v>
+        <v>2882</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -9764,7 +10630,7 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9780,7 +10646,7 @@
     <row r="41">
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -9789,23 +10655,23 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>6297</v>
+        <v>3280</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9821,32 +10687,32 @@
     <row r="42">
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>250</v>
+        <v>3951</v>
       </c>
       <c r="X42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -9862,32 +10728,32 @@
     <row r="43">
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>428</v>
+        <v>5096</v>
       </c>
       <c r="X43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
         <v>1</v>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB43" t="n">
-        <v>2</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -9903,28 +10769,28 @@
     <row r="44">
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>365</v>
+        <v>6277</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -9944,32 +10810,32 @@
     <row r="45">
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>471</v>
+        <v>6297</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -9985,32 +10851,32 @@
     <row r="46">
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>554</v>
+        <v>6082</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -10026,7 +10892,7 @@
     <row r="47">
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -10035,14 +10901,14 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>902</v>
+        <v>250</v>
       </c>
       <c r="X47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -10067,7 +10933,7 @@
     <row r="48">
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -10076,14 +10942,14 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>1420</v>
+        <v>428</v>
       </c>
       <c r="X48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -10108,7 +10974,7 @@
     <row r="49">
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -10117,14 +10983,14 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>1561</v>
+        <v>365</v>
       </c>
       <c r="X49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -10149,23 +11015,23 @@
     <row r="50">
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>6249</v>
+        <v>471</v>
       </c>
       <c r="X50" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -10174,7 +11040,7 @@
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -10190,32 +11056,32 @@
     <row r="51">
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>8329</v>
+        <v>554</v>
       </c>
       <c r="X51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -10231,32 +11097,32 @@
     <row r="52">
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>10619</v>
+        <v>902</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -10272,32 +11138,32 @@
     <row r="53">
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>13894</v>
+        <v>1420</v>
       </c>
       <c r="X53" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10313,32 +11179,32 @@
     <row r="54">
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>17235</v>
+        <v>1561</v>
       </c>
       <c r="X54" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -10354,32 +11220,32 @@
     <row r="55">
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>23145</v>
+        <v>1642</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -10395,7 +11261,7 @@
     <row r="56">
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -10404,23 +11270,23 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>32675</v>
+        <v>6249</v>
       </c>
       <c r="X56" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -10436,7 +11302,7 @@
     <row r="57">
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -10445,23 +11311,23 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>34857</v>
+        <v>8329</v>
       </c>
       <c r="X57" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10477,32 +11343,32 @@
     <row r="58">
       <c r="T58" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>10619</v>
+      </c>
+      <c r="X58" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>30</v>
-      </c>
-      <c r="X58" t="n">
-        <v>31</v>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="Z58" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -10518,32 +11384,32 @@
     <row r="59">
       <c r="T59" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>13894</v>
+      </c>
+      <c r="X59" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>81</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="Z59" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -10559,23 +11425,23 @@
     <row r="60">
       <c r="T60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>103</v>
+        <v>17235</v>
       </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -10584,7 +11450,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -10600,23 +11466,23 @@
     <row r="61">
       <c r="T61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>154</v>
+        <v>23145</v>
       </c>
       <c r="X61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -10625,7 +11491,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -10641,23 +11507,23 @@
     <row r="62">
       <c r="T62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>183</v>
+        <v>32675</v>
       </c>
       <c r="X62" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -10682,23 +11548,23 @@
     <row r="63">
       <c r="T63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>238</v>
+        <v>34857</v>
       </c>
       <c r="X63" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -10707,7 +11573,7 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -10723,23 +11589,23 @@
     <row r="64">
       <c r="T64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>354</v>
+        <v>34093</v>
       </c>
       <c r="X64" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -10764,7 +11630,7 @@
     <row r="65">
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -10773,14 +11639,14 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>347</v>
+        <v>30</v>
       </c>
       <c r="X65" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -10805,23 +11671,23 @@
     <row r="66">
       <c r="T66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>603</v>
+        <v>81</v>
       </c>
       <c r="X66" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -10830,7 +11696,7 @@
         </is>
       </c>
       <c r="AB66" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
@@ -10846,32 +11712,32 @@
     <row r="67">
       <c r="T67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V67" t="n">
-        <v>820</v>
+        <v>103</v>
       </c>
       <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
         <v>3</v>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB67" t="n">
-        <v>140</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
@@ -10887,28 +11753,28 @@
     <row r="68">
       <c r="T68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V68" t="n">
-        <v>1204</v>
+        <v>154</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB68" t="n">
@@ -10928,28 +11794,28 @@
     <row r="69">
       <c r="T69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V69" t="n">
-        <v>1689</v>
+        <v>183</v>
       </c>
       <c r="X69" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB69" t="n">
@@ -10969,32 +11835,32 @@
     <row r="70">
       <c r="T70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V70" t="n">
-        <v>2042</v>
+        <v>238</v>
       </c>
       <c r="X70" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
         <v>1</v>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB70" t="n">
-        <v>3</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11010,32 +11876,32 @@
     <row r="71">
       <c r="T71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V71" t="n">
-        <v>2581</v>
+        <v>354</v>
       </c>
       <c r="X71" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -11051,32 +11917,32 @@
     <row r="72">
       <c r="T72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V72" t="n">
-        <v>3880</v>
+        <v>347</v>
       </c>
       <c r="X72" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -11092,28 +11958,28 @@
     <row r="73">
       <c r="T73" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>324</v>
+      </c>
+      <c r="X73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V73" t="n">
-        <v>3997</v>
-      </c>
-      <c r="X73" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB73" t="n">
@@ -11138,23 +12004,23 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V74" t="n">
-        <v>90</v>
+        <v>603</v>
       </c>
       <c r="X74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB74" t="n">
@@ -11179,23 +12045,23 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V75" t="n">
-        <v>119</v>
+        <v>820</v>
       </c>
       <c r="X75" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB75" t="n">
@@ -11220,23 +12086,23 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V76" t="n">
-        <v>157</v>
+        <v>1204</v>
       </c>
       <c r="X76" t="n">
         <v>1</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB76" t="n">
@@ -11261,27 +12127,27 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V77" t="n">
-        <v>244</v>
+        <v>1689</v>
       </c>
       <c r="X77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -11302,27 +12168,27 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V78" t="n">
-        <v>270</v>
+        <v>2042</v>
       </c>
       <c r="X78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -11343,14 +12209,27 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V79" t="n">
-        <v>341</v>
+        <v>2581</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB79" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -11371,11 +12250,24 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V80" t="n">
-        <v>409</v>
+        <v>3880</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB80" t="n">
         <v>4</v>
@@ -11399,14 +12291,27 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="V81" t="n">
-        <v>401</v>
+        <v>3997</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
       <c r="AB81" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -11420,6 +12325,32 @@
       </c>
     </row>
     <row r="82">
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>3987</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB82" t="n">
         <v>1</v>
       </c>
@@ -11435,6 +12366,32 @@
       </c>
     </row>
     <row r="83">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>90</v>
+      </c>
+      <c r="X83" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB83" t="n">
         <v>3</v>
       </c>
@@ -11450,6 +12407,32 @@
       </c>
     </row>
     <row r="84">
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>119</v>
+      </c>
+      <c r="X84" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB84" t="n">
         <v>1</v>
       </c>
@@ -11465,6 +12448,32 @@
       </c>
     </row>
     <row r="85">
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>157</v>
+      </c>
+      <c r="X85" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB85" t="n">
         <v>8</v>
       </c>
@@ -11480,6 +12489,32 @@
       </c>
     </row>
     <row r="86">
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>244</v>
+      </c>
+      <c r="X86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB86" t="n">
         <v>179</v>
       </c>
@@ -11495,44 +12530,122 @@
       </c>
     </row>
     <row r="87">
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>270</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB87" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>341</v>
+      </c>
+      <c r="X88" t="n">
         <v>1</v>
       </c>
-      <c r="AC87" t="inlineStr">
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="AD87" t="inlineStr">
+      <c r="AD88" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="AB88" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC88" t="inlineStr">
+    <row r="89">
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>409</v>
+      </c>
+      <c r="X89" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC89" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="AB89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="AD89" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
@@ -11540,6 +12653,32 @@
       </c>
     </row>
     <row r="90">
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>401</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB90" t="n">
         <v>90</v>
       </c>
@@ -11555,8 +12694,21 @@
       </c>
     </row>
     <row r="91">
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>396</v>
+      </c>
       <c r="AB91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -11571,7 +12723,7 @@
     </row>
     <row r="92">
       <c r="AB92" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -11586,7 +12738,7 @@
     </row>
     <row r="93">
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -11601,7 +12753,7 @@
     </row>
     <row r="94">
       <c r="AB94" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -11616,7 +12768,7 @@
     </row>
     <row r="95">
       <c r="AB95" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -11631,7 +12783,7 @@
     </row>
     <row r="96">
       <c r="AB96" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -11661,7 +12813,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -11691,7 +12843,7 @@
     </row>
     <row r="100">
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -11766,7 +12918,7 @@
     </row>
     <row r="105">
       <c r="AB105" t="n">
-        <v>4</v>
+        <v>196</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
@@ -11781,7 +12933,7 @@
     </row>
     <row r="106">
       <c r="AB106" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -11811,7 +12963,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -11826,7 +12978,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -11841,7 +12993,7 @@
     </row>
     <row r="110">
       <c r="AB110" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -11871,7 +13023,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -11886,7 +13038,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -11901,7 +13053,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -11916,7 +13068,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -11946,7 +13098,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -12081,7 +13233,7 @@
     </row>
     <row r="126">
       <c r="AB126" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
@@ -12096,7 +13248,7 @@
     </row>
     <row r="127">
       <c r="AB127" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -12126,7 +13278,7 @@
     </row>
     <row r="129">
       <c r="AB129" t="n">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -12141,7 +13293,7 @@
     </row>
     <row r="130">
       <c r="AB130" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
@@ -12156,7 +13308,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
@@ -12194,6 +13346,216 @@
         </is>
       </c>
       <c r="AD133" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="AB134" t="n">
+        <v>226</v>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="AB135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="AB136" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="AB137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="AB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="AB139" t="n">
+        <v>103</v>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="AB140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="AB141" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="AB142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="AB143" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="AB144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="AB145" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="AB146" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="AB147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -12738,7 +14100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:AD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13085,16 +14447,16 @@
         <v>7785</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -13151,28 +14513,28 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>11515</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -13237,7 +14599,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -13246,19 +14608,19 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>705</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -13323,7 +14685,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -13332,19 +14694,19 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1439</v>
+        <v>705</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -13409,28 +14771,28 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1439</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -13487,28 +14849,28 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>2388</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>969</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -13541,30 +14903,62 @@
           <t>2026-09-09</t>
         </is>
       </c>
+      <c r="D10">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C10)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>ROUND(MAX(0,MIN(100,(1-E10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>MIN(1,(G10-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C10)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K10/IF(D10&gt;0,D10,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>MAX(0,(L10-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>$B$2+H10+M10</f>
+        <v/>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>1940</v>
-      </c>
-      <c r="X10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -13589,28 +14983,28 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>969</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -13635,28 +15029,28 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1940</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1063</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -13681,28 +15075,28 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>2713</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>2234</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -13732,12 +15126,25 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V14" t="n">
         <v>2</v>
       </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
       <c r="AB14" t="n">
         <v>11</v>
       </c>
@@ -13765,11 +15172,24 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>904</v>
+        <v>1063</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
       </c>
       <c r="AB15" t="n">
         <v>5</v>
@@ -13798,11 +15218,37 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1597</v>
+        <v>2234</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -13813,16 +15259,42 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>3474</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -13833,16 +15305,42 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>113</v>
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13853,16 +15351,42 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.yemeksepeti</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>210</v>
+        <v>904</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -13873,16 +15397,42 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1597</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -13893,16 +15443,29 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>2233</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
           <t>com.logistics.rider.glovo</t>
         </is>
-      </c>
-      <c r="V21" t="n">
-        <v>3024</v>
       </c>
     </row>
     <row r="22">
@@ -13913,16 +15476,29 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5423</v>
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -13938,11 +15514,11 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>34</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
@@ -13958,11 +15534,11 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>76</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25">
@@ -13973,16 +15549,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.yemeksepeti</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26">
@@ -13993,16 +15569,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>354</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -14013,16 +15589,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>609</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="28">
@@ -14033,16 +15609,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>5423</v>
       </c>
     </row>
     <row r="29">
@@ -14053,16 +15629,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>45</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="30">
@@ -14073,16 +15649,16 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -14091,6 +15667,19 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="32">
       <c r="G32" s="36" t="inlineStr">
@@ -14113,10 +15702,23 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D9)</f>
+        <f>AVERAGE(D2:D10)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -14124,7 +15726,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H9)</f>
+        <f>AVERAGE(H2:H10)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -14142,6 +15744,124 @@
       <c r="N33" s="38">
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -737,10 +737,10 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -773,10 +773,10 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -809,10 +809,10 @@
         <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -845,10 +845,10 @@
         <v>1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -881,10 +881,10 @@
         <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -917,10 +917,10 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -953,10 +953,10 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -989,10 +989,10 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1025,10 +1025,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1061,10 +1061,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1365,15 +1365,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>68</v>
       </c>
@@ -1388,7 +1382,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1450,15 +1444,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>68</v>
       </c>
@@ -1473,7 +1461,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1535,15 +1523,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>91</v>
       </c>
@@ -1614,15 +1596,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>75</v>
       </c>
@@ -1699,15 +1675,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>1</v>
       </c>
@@ -1722,7 +1692,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1784,15 +1754,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>88</v>
       </c>
@@ -1807,7 +1771,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1869,15 +1833,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>115</v>
       </c>
@@ -1948,15 +1906,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>1</v>
       </c>
@@ -1971,7 +1923,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2035,15 +1987,9 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
         <v>73</v>
       </c>
@@ -2058,7 +2004,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2090,19 +2036,9 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>com.Stedor.InstaShop</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>55</v>
-      </c>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
         <v>3</v>
       </c>
@@ -2149,19 +2085,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>5519</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>90</v>
       </c>
@@ -2208,19 +2134,9 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>5569</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
         <v>8</v>
       </c>
@@ -2267,19 +2183,9 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>5621</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
         <v>18</v>
       </c>
@@ -2326,19 +2232,9 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>73</v>
       </c>
@@ -2353,7 +2249,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2385,19 +2281,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>5196</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>14</v>
       </c>
@@ -2412,7 +2298,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2444,19 +2330,9 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>5203</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>12</v>
       </c>
@@ -2503,19 +2379,9 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>5687</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>14</v>
       </c>
@@ -2562,19 +2428,9 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>5395</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>16</v>
       </c>
@@ -2621,19 +2477,9 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>5472</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>12</v>
       </c>
@@ -2648,7 +2494,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2680,19 +2526,9 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>15184</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>10</v>
       </c>
@@ -2707,7 +2543,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2739,19 +2575,9 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>15708</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>13</v>
       </c>
@@ -2766,7 +2592,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2798,19 +2624,9 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>15056</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>2</v>
       </c>
@@ -2857,19 +2673,9 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>15493</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>14</v>
       </c>
@@ -2916,19 +2722,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>14553</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>10</v>
       </c>
@@ -2943,7 +2739,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2975,19 +2771,9 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>14491</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
         <v>2</v>
       </c>
@@ -3002,7 +2788,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3034,21 +2820,11 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="n">
-        <v>15132</v>
-      </c>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
@@ -3093,21 +2869,11 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>15616</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
@@ -3152,19 +2918,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>15857</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>36</v>
       </c>
@@ -3211,21 +2967,11 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>87207</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -3270,21 +3016,11 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="n">
-        <v>86030</v>
-      </c>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
@@ -3297,7 +3033,7 @@
         </is>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3338,19 +3074,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>82667</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>34</v>
       </c>
@@ -3365,7 +3091,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3411,19 +3137,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>82796</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>1</v>
       </c>
@@ -3452,19 +3168,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>80792</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>1</v>
       </c>
@@ -3479,7 +3185,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3493,19 +3199,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>80181</v>
-      </c>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
         <v>1</v>
       </c>
@@ -3520,7 +3216,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3534,19 +3230,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>82769</v>
-      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
         <v>48</v>
       </c>
@@ -3575,21 +3261,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>82955</v>
-      </c>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
@@ -3616,21 +3292,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>84463</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3657,19 +3323,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>721</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>1</v>
       </c>
@@ -3698,19 +3354,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
         <v>2</v>
       </c>
@@ -3739,19 +3385,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>717</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
         <v>54</v>
       </c>
@@ -3780,101 +3416,71 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>753</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z42" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD42" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
+      <c r="X43" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="Y42" s="4" t="inlineStr">
+      <c r="Y43" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="Z42" s="4" t="inlineStr">
+      <c r="Z43" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="AB42" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC42" s="4" t="inlineStr">
+      <c r="AB43" s="7" t="n">
+        <v>276</v>
+      </c>
+      <c r="AC43" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AD43" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>696</v>
-      </c>
-      <c r="X43" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>723</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
         <v>11</v>
       </c>
@@ -3889,7 +3495,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3903,19 +3509,9 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>743</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
         <v>43</v>
       </c>
@@ -3944,19 +3540,9 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>714</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
         <v>1</v>
       </c>
@@ -3985,19 +3571,9 @@
       </c>
     </row>
     <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>733</v>
-      </c>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
         <v>15</v>
       </c>
@@ -4012,7 +3588,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4026,19 +3602,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>50559</v>
-      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
         <v>2</v>
       </c>
@@ -4053,7 +3619,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -4067,19 +3633,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>51501</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
         <v>8</v>
       </c>
@@ -4094,7 +3650,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -4108,19 +3664,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>51715</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>3</v>
       </c>
@@ -4149,19 +3695,9 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>50240</v>
-      </c>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
         <v>15</v>
       </c>
@@ -4176,7 +3712,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -4190,21 +3726,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>48948</v>
-      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
@@ -4231,21 +3757,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>48922</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
@@ -4272,19 +3788,9 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>51004</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
         <v>1</v>
       </c>
@@ -4313,19 +3819,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>50744</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>18</v>
       </c>
@@ -4340,7 +3836,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4354,19 +3850,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>50396</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>3</v>
       </c>
@@ -4381,7 +3867,7 @@
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4395,19 +3881,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>25</v>
       </c>
@@ -4436,21 +3912,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4477,21 +3943,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>11599</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
@@ -4518,21 +3974,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>11522</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
@@ -4545,7 +3991,7 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4559,19 +4005,9 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>11614</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
         <v>1</v>
       </c>
@@ -4586,7 +4022,7 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4600,21 +4036,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>11098</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -4641,19 +4067,9 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>11097</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
         <v>1</v>
       </c>
@@ -4668,115 +4084,85 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
+      <c r="X64" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
+      <c r="X65" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z65" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB65" s="7" t="n">
         <v>316</v>
       </c>
-      <c r="AC63" s="7" t="inlineStr">
+      <c r="AC65" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD63" s="7" t="inlineStr">
+      <c r="AD65" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>11410</v>
-      </c>
-      <c r="X64" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB64" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>11482</v>
-      </c>
-      <c r="X65" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>11322</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>19</v>
       </c>
@@ -4791,7 +4177,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4805,19 +4191,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>11380</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>1</v>
       </c>
@@ -4832,7 +4208,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4846,19 +4222,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>26509</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>21</v>
       </c>
@@ -4887,21 +4253,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>26876</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
@@ -4928,21 +4284,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>27154</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y70" s="4" t="inlineStr">
         <is>
@@ -4969,19 +4315,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>26655</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>21</v>
       </c>
@@ -4996,7 +4332,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -5010,19 +4346,9 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>25267</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
         <v>15</v>
       </c>
@@ -5037,7 +4363,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -5051,19 +4377,9 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>24712</v>
-      </c>
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
         <v>14</v>
       </c>
@@ -5078,7 +4394,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5092,19 +4408,9 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>26356</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
         <v>2</v>
       </c>
@@ -5119,7 +4425,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5133,19 +4439,9 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V75" s="7" t="n">
-        <v>25640</v>
-      </c>
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
         <v>13</v>
       </c>
@@ -5160,7 +4456,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5174,144 +4470,104 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
+      <c r="X76" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD76" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
+      <c r="X77" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB77" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
+      <c r="X78" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y78" s="4" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>26277</v>
-      </c>
-      <c r="X76" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z76" s="4" t="inlineStr">
+      <c r="Z78" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="AB76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
+      <c r="AB78" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>17949</v>
-      </c>
-      <c r="X77" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB77" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD77" s="7" t="inlineStr">
+      <c r="AD78" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>17549</v>
-      </c>
-      <c r="X78" s="4" t="n">
+    <row r="79">
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
+      <c r="X79" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="Y78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB78" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>17646</v>
-      </c>
-      <c r="X79" s="7" t="n">
-        <v>18</v>
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
@@ -5338,19 +4594,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>17131</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>55</v>
       </c>
@@ -5379,19 +4625,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>17470</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>4</v>
       </c>
@@ -5420,21 +4656,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>17485</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
@@ -5461,19 +4687,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>17825</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>2</v>
       </c>
@@ -5502,103 +4718,73 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>17897</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB84" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD84" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
+      <c r="X85" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB85" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Y84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB84" s="4" t="n">
+      <c r="AC85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD85" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
+      <c r="X86" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="AC84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>17613</v>
-      </c>
-      <c r="X85" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y85" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB85" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC85" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>745</v>
-      </c>
-      <c r="X86" s="4" t="n">
-        <v>49</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
@@ -5625,21 +4811,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>763</v>
-      </c>
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
@@ -5652,7 +4828,7 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
@@ -5666,21 +4842,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>740</v>
-      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Y88" s="4" t="inlineStr">
         <is>
@@ -5707,19 +4873,9 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>783</v>
-      </c>
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
         <v>2</v>
       </c>
@@ -5734,7 +4890,7 @@
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -5748,142 +4904,102 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
+      <c r="X90" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z90" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB90" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC90" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>763</v>
-      </c>
-      <c r="X90" s="4" t="n">
+      <c r="AD90" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
+      <c r="X91" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="Y90" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z90" s="4" t="inlineStr">
+      <c r="Y91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z91" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB90" s="4" t="n">
+      <c r="AB91" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr">
+      <c r="AC91" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD90" s="4" t="inlineStr">
+      <c r="AD91" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>735</v>
-      </c>
-      <c r="X91" s="7" t="n">
+    <row r="92">
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
+      <c r="X92" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Y91" s="7" t="inlineStr">
+      <c r="Y92" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="Z91" s="7" t="inlineStr">
+      <c r="Z92" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB91" s="7" t="n">
+      <c r="AB92" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AC91" s="7" t="inlineStr">
+      <c r="AC92" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD91" s="7" t="inlineStr">
+      <c r="AD92" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>841</v>
-      </c>
-      <c r="X92" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y92" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB92" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
     <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>767</v>
-      </c>
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
         <v>1</v>
       </c>
@@ -5898,7 +5014,7 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5912,21 +5028,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>748</v>
-      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="Y94" s="4" t="inlineStr">
         <is>
@@ -5953,21 +5059,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>2142</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="Y95" s="7" t="inlineStr">
         <is>
@@ -5980,7 +5076,7 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -5994,19 +5090,9 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>2408</v>
-      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
         <v>6</v>
       </c>
@@ -6021,7 +5107,7 @@
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -6035,19 +5121,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>2141</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>6</v>
       </c>
@@ -6062,7 +5138,7 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -6076,19 +5152,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>2082</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
         <v>61</v>
       </c>
@@ -6103,7 +5169,7 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
@@ -6117,19 +5183,9 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>1990</v>
-      </c>
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
         <v>9</v>
       </c>
@@ -6158,21 +5214,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>2043</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="Y100" s="4" t="inlineStr">
         <is>
@@ -6199,21 +5245,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>2148</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
@@ -6240,21 +5276,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>2096</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
@@ -6281,34 +5307,24 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
+      <c r="X103" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y103" s="7" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>2265</v>
-      </c>
-      <c r="X103" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y103" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="Z103" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB103" s="7" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -6326,7 +5342,7 @@
       <c r="U104" s="4" t="n"/>
       <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
@@ -6370,7 +5386,7 @@
         </is>
       </c>
       <c r="AB105" s="7" t="n">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
@@ -6401,7 +5417,7 @@
         </is>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -6432,7 +5448,7 @@
         </is>
       </c>
       <c r="AB107" s="7" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -6463,7 +5479,7 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6494,7 +5510,7 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6525,7 +5541,7 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6556,7 +5572,7 @@
         </is>
       </c>
       <c r="AB111" s="7" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6587,7 +5603,7 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6618,7 +5634,7 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -6649,7 +5665,7 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6711,7 +5727,7 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -6742,7 +5758,7 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -6773,7 +5789,7 @@
         </is>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -6804,7 +5820,7 @@
         </is>
       </c>
       <c r="AB119" s="7" t="n">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -6835,7 +5851,7 @@
         </is>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -6970,7 +5986,7 @@
       <c r="Y125" s="7" t="n"/>
       <c r="Z125" s="7" t="n"/>
       <c r="AB125" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
@@ -6991,7 +6007,7 @@
       <c r="Y126" s="4" t="n"/>
       <c r="Z126" s="4" t="n"/>
       <c r="AB126" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -7075,7 +6091,7 @@
       <c r="Y130" s="4" t="n"/>
       <c r="Z130" s="4" t="n"/>
       <c r="AB130" s="4" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -7096,7 +6112,7 @@
       <c r="Y131" s="7" t="n"/>
       <c r="Z131" s="7" t="n"/>
       <c r="AB131" s="7" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -7138,7 +6154,7 @@
       <c r="Y133" s="7" t="n"/>
       <c r="Z133" s="7" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -7159,7 +6175,7 @@
       <c r="Y134" s="4" t="n"/>
       <c r="Z134" s="4" t="n"/>
       <c r="AB134" s="4" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -7222,7 +6238,7 @@
       <c r="Y137" s="7" t="n"/>
       <c r="Z137" s="7" t="n"/>
       <c r="AB137" s="7" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -7243,7 +6259,7 @@
       <c r="Y138" s="4" t="n"/>
       <c r="Z138" s="4" t="n"/>
       <c r="AB138" s="4" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -7285,7 +6301,7 @@
       <c r="Y140" s="4" t="n"/>
       <c r="Z140" s="4" t="n"/>
       <c r="AB140" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -7306,7 +6322,7 @@
       <c r="Y141" s="7" t="n"/>
       <c r="Z141" s="7" t="n"/>
       <c r="AB141" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -7327,7 +6343,7 @@
       <c r="Y142" s="4" t="n"/>
       <c r="Z142" s="4" t="n"/>
       <c r="AB142" s="4" t="n">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -7348,7 +6364,7 @@
       <c r="Y143" s="7" t="n"/>
       <c r="Z143" s="7" t="n"/>
       <c r="AB143" s="7" t="n">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -7390,7 +6406,7 @@
       <c r="Y145" s="7" t="n"/>
       <c r="Z145" s="7" t="n"/>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -7411,7 +6427,7 @@
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n"/>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -7453,7 +6469,7 @@
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n"/>
       <c r="AB148" s="4" t="n">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
@@ -7495,7 +6511,7 @@
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n"/>
       <c r="AB150" s="4" t="n">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -7558,7 +6574,7 @@
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
       <c r="AB153" s="7" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -7579,7 +6595,7 @@
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n"/>
       <c r="AB154" s="4" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -7600,7 +6616,7 @@
       <c r="Y155" s="7" t="n"/>
       <c r="Z155" s="7" t="n"/>
       <c r="AB155" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
@@ -7621,7 +6637,7 @@
       <c r="Y156" s="4" t="n"/>
       <c r="Z156" s="4" t="n"/>
       <c r="AB156" s="4" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="AC156" s="4" t="inlineStr">
         <is>
@@ -7663,7 +6679,7 @@
       <c r="Y158" s="4" t="n"/>
       <c r="Z158" s="4" t="n"/>
       <c r="AB158" s="4" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="AC158" s="4" t="inlineStr">
         <is>
@@ -7684,7 +6700,7 @@
       <c r="Y159" s="7" t="n"/>
       <c r="Z159" s="7" t="n"/>
       <c r="AB159" s="7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="AC159" s="7" t="inlineStr">
         <is>
@@ -7705,7 +6721,7 @@
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n"/>
       <c r="AB160" s="4" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
@@ -7726,7 +6742,7 @@
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
       <c r="AB161" s="7" t="n">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -7747,7 +6763,7 @@
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
       <c r="AB162" s="4" t="n">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -7768,7 +6784,7 @@
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
       <c r="AB163" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -7810,7 +6826,7 @@
       <c r="Y165" s="7" t="n"/>
       <c r="Z165" s="7" t="n"/>
       <c r="AB165" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
@@ -7831,7 +6847,7 @@
       <c r="Y166" s="4" t="n"/>
       <c r="Z166" s="4" t="n"/>
       <c r="AB166" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
@@ -7873,7 +6889,7 @@
       <c r="Y168" s="4" t="n"/>
       <c r="Z168" s="4" t="n"/>
       <c r="AB168" s="4" t="n">
-        <v>2</v>
+        <v>291</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -7915,7 +6931,7 @@
       <c r="Y170" s="4" t="n"/>
       <c r="Z170" s="4" t="n"/>
       <c r="AB170" s="4" t="n">
-        <v>291</v>
+        <v>2</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
@@ -7978,7 +6994,7 @@
       <c r="Y173" s="7" t="n"/>
       <c r="Z173" s="7" t="n"/>
       <c r="AB173" s="7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AC173" s="7" t="inlineStr">
         <is>
@@ -7999,7 +7015,7 @@
       <c r="Y174" s="4" t="n"/>
       <c r="Z174" s="4" t="n"/>
       <c r="AB174" s="4" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
@@ -8020,7 +7036,7 @@
       <c r="Y175" s="7" t="n"/>
       <c r="Z175" s="7" t="n"/>
       <c r="AB175" s="7" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="AC175" s="7" t="inlineStr">
         <is>
@@ -8041,7 +7057,7 @@
       <c r="Y176" s="4" t="n"/>
       <c r="Z176" s="4" t="n"/>
       <c r="AB176" s="4" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AC176" s="4" t="inlineStr">
         <is>
@@ -8062,7 +7078,7 @@
       <c r="Y177" s="7" t="n"/>
       <c r="Z177" s="7" t="n"/>
       <c r="AB177" s="7" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="AC177" s="7" t="inlineStr">
         <is>
@@ -8104,7 +7120,7 @@
       <c r="Y179" s="7" t="n"/>
       <c r="Z179" s="7" t="n"/>
       <c r="AB179" s="7" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="AC179" s="7" t="inlineStr">
         <is>
@@ -8209,7 +7225,7 @@
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
       <c r="AB184" s="4" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
@@ -8251,7 +7267,7 @@
       <c r="Y186" s="4" t="n"/>
       <c r="Z186" s="4" t="n"/>
       <c r="AB186" s="4" t="n">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="AC186" s="4" t="inlineStr">
         <is>
@@ -8546,19 +7562,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>7773</v>
-      </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
@@ -8573,7 +7576,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -8632,19 +7635,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10781</v>
-      </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
@@ -8659,7 +7649,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -8718,19 +7708,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>14077</v>
-      </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
@@ -8796,19 +7773,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>19486</v>
-      </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
@@ -8882,21 +7846,8 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>25421</v>
-      </c>
       <c r="X6" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -8968,21 +7919,8 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>36128</v>
-      </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -9054,19 +7992,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>51111</v>
-      </c>
       <c r="X8" t="n">
         <v>55</v>
       </c>
@@ -9132,21 +8057,8 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>56380</v>
-      </c>
       <c r="X9" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -9220,21 +8132,8 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>56145</v>
-      </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -9266,19 +8165,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>1530</v>
-      </c>
       <c r="X11" t="n">
         <v>62</v>
       </c>
@@ -9312,19 +8198,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>2311</v>
-      </c>
       <c r="X12" t="n">
         <v>52</v>
       </c>
@@ -9358,19 +8231,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>2868</v>
-      </c>
       <c r="X13" t="n">
         <v>6</v>
       </c>
@@ -9385,7 +8245,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -9404,19 +8264,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>4059</v>
-      </c>
       <c r="X14" t="n">
         <v>4</v>
       </c>
@@ -9431,7 +8278,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -9450,19 +8297,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>5092</v>
-      </c>
       <c r="X15" t="n">
         <v>5</v>
       </c>
@@ -9496,19 +8330,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>6962</v>
-      </c>
       <c r="X16" t="n">
         <v>5</v>
       </c>
@@ -9542,19 +8363,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>9959</v>
-      </c>
       <c r="X17" t="n">
         <v>5</v>
       </c>
@@ -9588,19 +8396,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>11290</v>
-      </c>
       <c r="X18" t="n">
         <v>10</v>
       </c>
@@ -9634,19 +8429,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>11188</v>
-      </c>
       <c r="X19" t="n">
         <v>9</v>
       </c>
@@ -9680,19 +8462,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>1815</v>
-      </c>
       <c r="X20" t="n">
         <v>7</v>
       </c>
@@ -9726,19 +8495,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>2333</v>
-      </c>
       <c r="X21" t="n">
         <v>2</v>
       </c>
@@ -9772,19 +8528,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>3182</v>
-      </c>
       <c r="X22" t="n">
         <v>6</v>
       </c>
@@ -9818,19 +8561,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>4129</v>
-      </c>
       <c r="X23" t="n">
         <v>20</v>
       </c>
@@ -9864,19 +8594,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>5644</v>
-      </c>
       <c r="X24" t="n">
         <v>9</v>
       </c>
@@ -9910,19 +8627,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>7963</v>
-      </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
@@ -9956,19 +8660,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>11169</v>
-      </c>
       <c r="X26" t="n">
         <v>22</v>
       </c>
@@ -10002,21 +8693,8 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>12345</v>
-      </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -10048,34 +8726,21 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V28" t="n">
-        <v>12001</v>
-      </c>
-      <c r="X28" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -10094,19 +8759,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>2322</v>
-      </c>
       <c r="X29" t="n">
         <v>2</v>
       </c>
@@ -10121,7 +8773,7 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -10140,19 +8792,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>3533</v>
-      </c>
       <c r="X30" t="n">
         <v>44</v>
       </c>
@@ -10167,7 +8806,7 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -10186,19 +8825,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>4891</v>
-      </c>
       <c r="X31" t="n">
         <v>28</v>
       </c>
@@ -10246,19 +8872,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>6461</v>
       </c>
       <c r="X32" t="n">
         <v>36</v>
@@ -10316,19 +8929,6 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>8274</v>
-      </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
@@ -10343,7 +8943,7 @@
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -10357,19 +8957,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>12174</v>
-      </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
@@ -10384,7 +8971,7 @@
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -10398,19 +8985,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>19723</v>
-      </c>
       <c r="X35" t="n">
         <v>5</v>
       </c>
@@ -10439,101 +9013,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V36" t="n">
-        <v>20836</v>
-      </c>
-      <c r="X36" t="n">
+      <c r="AB36" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="X37" t="n">
         <v>1</v>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="AB36" t="n">
+      <c r="AB37" t="n">
         <v>1</v>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>20942</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>1827</v>
-      </c>
       <c r="X38" t="n">
         <v>5</v>
       </c>
@@ -10548,7 +9083,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -10562,19 +9097,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>2275</v>
-      </c>
       <c r="X39" t="n">
         <v>1</v>
       </c>
@@ -10603,19 +9125,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>2882</v>
-      </c>
       <c r="X40" t="n">
         <v>9</v>
       </c>
@@ -10644,19 +9153,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>3280</v>
-      </c>
       <c r="X41" t="n">
         <v>1</v>
       </c>
@@ -10685,19 +9181,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>3951</v>
-      </c>
       <c r="X42" t="n">
         <v>9</v>
       </c>
@@ -10726,183 +9209,118 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V43" t="n">
-        <v>5096</v>
-      </c>
-      <c r="X43" t="n">
+    </row>
+    <row r="44">
+      <c r="X44" t="n">
         <v>6</v>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="AB43" t="n">
+      <c r="AB44" t="n">
         <v>1</v>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>6277</v>
-      </c>
-      <c r="X44" t="n">
+    <row r="45">
+      <c r="X45" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
         <v>1</v>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="AB44" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AB46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>6297</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>6082</v>
-      </c>
-      <c r="X46" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>250</v>
-      </c>
       <c r="X47" t="n">
         <v>1</v>
       </c>
@@ -10917,7 +9335,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -10931,19 +9349,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>428</v>
-      </c>
       <c r="X48" t="n">
         <v>6</v>
       </c>
@@ -10972,19 +9377,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>365</v>
-      </c>
       <c r="X49" t="n">
         <v>1</v>
       </c>
@@ -11013,19 +9405,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>471</v>
-      </c>
       <c r="X50" t="n">
         <v>3</v>
       </c>
@@ -11054,19 +9433,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>554</v>
-      </c>
       <c r="X51" t="n">
         <v>3</v>
       </c>
@@ -11095,19 +9461,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>902</v>
-      </c>
       <c r="X52" t="n">
         <v>8</v>
       </c>
@@ -11136,19 +9489,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>1420</v>
-      </c>
       <c r="X53" t="n">
         <v>7</v>
       </c>
@@ -11177,19 +9517,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V54" t="n">
-        <v>1561</v>
-      </c>
       <c r="X54" t="n">
         <v>8</v>
       </c>
@@ -11204,7 +9531,7 @@
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -11218,19 +9545,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>1642</v>
-      </c>
       <c r="X55" t="n">
         <v>7</v>
       </c>
@@ -11245,7 +9559,7 @@
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -11259,19 +9573,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>6249</v>
-      </c>
       <c r="X56" t="n">
         <v>11</v>
       </c>
@@ -11300,19 +9601,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>8329</v>
-      </c>
       <c r="X57" t="n">
         <v>11</v>
       </c>
@@ -11341,19 +9629,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>10619</v>
-      </c>
       <c r="X58" t="n">
         <v>5</v>
       </c>
@@ -11368,7 +9643,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11382,19 +9657,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>13894</v>
-      </c>
       <c r="X59" t="n">
         <v>13</v>
       </c>
@@ -11423,19 +9685,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>17235</v>
-      </c>
       <c r="X60" t="n">
         <v>1</v>
       </c>
@@ -11450,7 +9699,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11464,19 +9713,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>23145</v>
-      </c>
       <c r="X61" t="n">
         <v>1</v>
       </c>
@@ -11505,19 +9741,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>32675</v>
-      </c>
       <c r="X62" t="n">
         <v>17</v>
       </c>
@@ -11546,19 +9769,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V63" t="n">
-        <v>34857</v>
-      </c>
       <c r="X63" t="n">
         <v>2</v>
       </c>
@@ -11587,19 +9797,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>34093</v>
-      </c>
       <c r="X64" t="n">
         <v>18</v>
       </c>
@@ -11628,19 +9825,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>30</v>
-      </c>
       <c r="X65" t="n">
         <v>31</v>
       </c>
@@ -11669,19 +9853,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>81</v>
-      </c>
       <c r="X66" t="n">
         <v>1</v>
       </c>
@@ -11710,19 +9881,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>103</v>
-      </c>
       <c r="X67" t="n">
         <v>1</v>
       </c>
@@ -11751,19 +9909,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V68" t="n">
-        <v>154</v>
-      </c>
       <c r="X68" t="n">
         <v>2</v>
       </c>
@@ -11792,19 +9937,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V69" t="n">
-        <v>183</v>
-      </c>
       <c r="X69" t="n">
         <v>33</v>
       </c>
@@ -11833,19 +9965,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V70" t="n">
-        <v>238</v>
-      </c>
       <c r="X70" t="n">
         <v>4</v>
       </c>
@@ -11860,7 +9979,7 @@
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11874,19 +9993,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V71" t="n">
-        <v>354</v>
-      </c>
       <c r="X71" t="n">
         <v>43</v>
       </c>
@@ -11901,7 +10007,7 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -11915,19 +10021,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V72" t="n">
-        <v>347</v>
-      </c>
       <c r="X72" t="n">
         <v>34</v>
       </c>
@@ -11942,7 +10035,7 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -11956,19 +10049,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V73" t="n">
-        <v>324</v>
-      </c>
       <c r="X73" t="n">
         <v>3</v>
       </c>
@@ -11997,19 +10077,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V74" t="n">
-        <v>603</v>
-      </c>
       <c r="X74" t="n">
         <v>2</v>
       </c>
@@ -12038,19 +10105,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V75" t="n">
-        <v>820</v>
-      </c>
       <c r="X75" t="n">
         <v>38</v>
       </c>
@@ -12079,19 +10133,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V76" t="n">
-        <v>1204</v>
-      </c>
       <c r="X76" t="n">
         <v>1</v>
       </c>
@@ -12120,19 +10161,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V77" t="n">
-        <v>1689</v>
-      </c>
       <c r="X77" t="n">
         <v>3</v>
       </c>
@@ -12161,19 +10189,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V78" t="n">
-        <v>2042</v>
-      </c>
       <c r="X78" t="n">
         <v>1</v>
       </c>
@@ -12202,19 +10217,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V79" t="n">
-        <v>2581</v>
-      </c>
       <c r="X79" t="n">
         <v>1</v>
       </c>
@@ -12243,19 +10245,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V80" t="n">
-        <v>3880</v>
-      </c>
       <c r="X80" t="n">
         <v>1</v>
       </c>
@@ -12270,7 +10259,7 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -12284,19 +10273,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V81" t="n">
-        <v>3997</v>
-      </c>
       <c r="X81" t="n">
         <v>1</v>
       </c>
@@ -12311,7 +10287,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -12325,19 +10301,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V82" t="n">
-        <v>3987</v>
-      </c>
       <c r="X82" t="n">
         <v>1</v>
       </c>
@@ -12366,19 +10329,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V83" t="n">
-        <v>90</v>
-      </c>
       <c r="X83" t="n">
         <v>5</v>
       </c>
@@ -12407,19 +10357,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V84" t="n">
-        <v>119</v>
-      </c>
       <c r="X84" t="n">
         <v>6</v>
       </c>
@@ -12448,19 +10385,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V85" t="n">
-        <v>157</v>
-      </c>
       <c r="X85" t="n">
         <v>8</v>
       </c>
@@ -12489,19 +10413,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V86" t="n">
-        <v>244</v>
-      </c>
       <c r="X86" t="n">
         <v>4</v>
       </c>
@@ -12530,19 +10441,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V87" t="n">
-        <v>270</v>
-      </c>
       <c r="X87" t="n">
         <v>1</v>
       </c>
@@ -12571,19 +10469,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V88" t="n">
-        <v>341</v>
-      </c>
       <c r="X88" t="n">
         <v>1</v>
       </c>
@@ -12612,19 +10497,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V89" t="n">
-        <v>409</v>
-      </c>
       <c r="X89" t="n">
         <v>2</v>
       </c>
@@ -12639,7 +10511,7 @@
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -12653,19 +10525,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V90" t="n">
-        <v>401</v>
-      </c>
       <c r="X90" t="n">
         <v>1</v>
       </c>
@@ -12680,7 +10539,7 @@
         </is>
       </c>
       <c r="AB90" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -12694,19 +10553,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V91" t="n">
-        <v>396</v>
-      </c>
       <c r="AB91" t="n">
         <v>2</v>
       </c>
@@ -12813,7 +10659,7 @@
     </row>
     <row r="98">
       <c r="AB98" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -12828,7 +10674,7 @@
     </row>
     <row r="99">
       <c r="AB99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
@@ -12873,7 +10719,7 @@
     </row>
     <row r="102">
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -12888,7 +10734,7 @@
     </row>
     <row r="103">
       <c r="AB103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -12918,7 +10764,7 @@
     </row>
     <row r="105">
       <c r="AB105" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
@@ -12933,7 +10779,7 @@
     </row>
     <row r="106">
       <c r="AB106" t="n">
-        <v>4</v>
+        <v>196</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -12963,7 +10809,7 @@
     </row>
     <row r="108">
       <c r="AB108" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
@@ -12978,7 +10824,7 @@
     </row>
     <row r="109">
       <c r="AB109" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
@@ -13038,7 +10884,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -13053,7 +10899,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -13083,7 +10929,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -13098,7 +10944,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -13203,7 +11049,7 @@
     </row>
     <row r="124">
       <c r="AB124" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -13218,7 +11064,7 @@
     </row>
     <row r="125">
       <c r="AB125" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
@@ -13293,7 +11139,7 @@
     </row>
     <row r="130">
       <c r="AB130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
@@ -13308,7 +11154,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
@@ -13353,7 +11199,7 @@
     </row>
     <row r="134">
       <c r="AB134" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
@@ -13368,7 +11214,7 @@
     </row>
     <row r="135">
       <c r="AB135" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
@@ -13398,7 +11244,7 @@
     </row>
     <row r="137">
       <c r="AB137" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
@@ -13428,7 +11274,7 @@
     </row>
     <row r="139">
       <c r="AB139" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
@@ -14100,7 +11946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD40"/>
+  <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14261,19 +12107,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="X2" t="n">
         <v>3</v>
       </c>
@@ -14347,19 +12180,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3208</v>
-      </c>
       <c r="X3" t="n">
         <v>8</v>
       </c>
@@ -14433,19 +12253,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>7785</v>
-      </c>
       <c r="X4" t="n">
         <v>18</v>
       </c>
@@ -14511,19 +12318,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>11515</v>
-      </c>
       <c r="X5" t="n">
         <v>2</v>
       </c>
@@ -14597,19 +12391,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="X6" t="n">
         <v>2</v>
       </c>
@@ -14683,19 +12464,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>705</v>
-      </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
@@ -14769,19 +12537,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1439</v>
-      </c>
       <c r="X8" t="n">
         <v>4</v>
       </c>
@@ -14847,19 +12602,6 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>2388</v>
-      </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
@@ -14935,19 +12677,6 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
       <c r="X10" t="n">
         <v>2</v>
       </c>
@@ -14981,19 +12710,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>969</v>
-      </c>
       <c r="X11" t="n">
         <v>3</v>
       </c>
@@ -15027,19 +12743,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1940</v>
-      </c>
       <c r="X12" t="n">
         <v>2</v>
       </c>
@@ -15073,19 +12776,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>2713</v>
-      </c>
       <c r="X13" t="n">
         <v>3</v>
       </c>
@@ -15119,19 +12809,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
       <c r="X14" t="n">
         <v>4</v>
       </c>
@@ -15165,19 +12842,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>1063</v>
-      </c>
       <c r="X15" t="n">
         <v>6</v>
       </c>
@@ -15211,19 +12875,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>2234</v>
-      </c>
       <c r="X16" t="n">
         <v>9</v>
       </c>
@@ -15257,19 +12908,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>3474</v>
-      </c>
       <c r="X17" t="n">
         <v>15</v>
       </c>
@@ -15303,19 +12941,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
@@ -15349,19 +12974,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>904</v>
-      </c>
       <c r="X19" t="n">
         <v>1</v>
       </c>
@@ -15395,19 +13007,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>1597</v>
-      </c>
       <c r="X20" t="n">
         <v>2</v>
       </c>
@@ -15441,19 +13040,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>2233</v>
-      </c>
       <c r="AB21" t="n">
         <v>22</v>
       </c>
@@ -15474,19 +13060,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
       <c r="AB22" t="n">
         <v>2</v>
       </c>
@@ -15507,19 +13080,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>113</v>
-      </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
@@ -15527,19 +13087,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>210</v>
-      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -15547,19 +13094,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="26">
       <c r="C26" t="inlineStr">
@@ -15567,19 +13101,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="C27" t="inlineStr">
@@ -15587,19 +13108,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>3024</v>
-      </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
@@ -15607,19 +13115,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>5423</v>
-      </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
@@ -15627,19 +13122,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>7736</v>
-      </c>
     </row>
     <row r="30">
       <c r="C30" t="inlineStr">
@@ -15647,19 +13129,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>34</v>
-      </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
@@ -15667,19 +13136,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>76</v>
-      </c>
     </row>
     <row r="32">
       <c r="G32" s="36" t="inlineStr">
@@ -15701,19 +13157,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>97</v>
       </c>
     </row>
     <row r="33">
@@ -15744,124 +13187,6 @@
       <c r="N33" s="38">
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Consolidation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v4.2636.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="v4.2636.1 Cons" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="v4.2637.1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="v4.2637.1 Cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -737,10 +737,10 @@
         <v>1.162</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>78203</v>
@@ -773,10 +773,10 @@
         <v>1.162</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>14946</v>
@@ -809,10 +809,10 @@
         <v>1.162</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>16988</v>
@@ -845,10 +845,10 @@
         <v>1.162</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>20641</v>
@@ -881,10 +881,10 @@
         <v>1.162</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>10630</v>
@@ -917,10 +917,10 @@
         <v>1.162</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>2186</v>
@@ -953,10 +953,10 @@
         <v>1.162</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>46896</v>
@@ -989,10 +989,10 @@
         <v>1.162</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>731</v>
@@ -1025,10 +1025,10 @@
         <v>1.162</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>5258</v>
@@ -1061,10 +1061,10 @@
         <v>1.162</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>729</v>
@@ -1365,15 +1365,9 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
         <v>1</v>
       </c>
@@ -1450,15 +1444,9 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="X3" s="7" t="n">
         <v>68</v>
       </c>
@@ -1535,15 +1523,9 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
         <v>68</v>
       </c>
@@ -1558,7 +1540,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1614,15 +1596,9 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="X5" s="7" t="n">
         <v>91</v>
       </c>
@@ -1637,7 +1613,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1699,15 +1675,9 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
         <v>75</v>
       </c>
@@ -1722,7 +1692,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1784,15 +1754,9 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="X7" s="7" t="n">
         <v>1</v>
       </c>
@@ -1869,15 +1833,9 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
         <v>88</v>
       </c>
@@ -1892,7 +1850,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1948,15 +1906,9 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="X9" s="7" t="n">
         <v>115</v>
       </c>
@@ -1971,7 +1923,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2035,17 +1987,11 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2058,7 +2004,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2114,17 +2060,11 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="n">
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="X11" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="X11" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -2169,19 +2109,9 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>com.Stedor.InstaShop</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>55</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>73</v>
       </c>
@@ -2196,7 +2126,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2228,21 +2158,11 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>5519</v>
-      </c>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
@@ -2255,7 +2175,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2287,21 +2207,11 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>5569</v>
-      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
@@ -2314,7 +2224,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2346,19 +2256,9 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>5621</v>
-      </c>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
         <v>18</v>
       </c>
@@ -2405,19 +2305,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>5557</v>
-      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
         <v>73</v>
       </c>
@@ -2432,7 +2322,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>13</v>
+        <v>188</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2464,19 +2354,9 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>5196</v>
-      </c>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="X17" s="7" t="n">
         <v>77</v>
       </c>
@@ -2523,19 +2403,9 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>5203</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
         <v>8</v>
       </c>
@@ -2582,19 +2452,9 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>5687</v>
-      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
         <v>14</v>
       </c>
@@ -2641,19 +2501,9 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>5395</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
         <v>12</v>
       </c>
@@ -2700,19 +2550,9 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>5472</v>
-      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
         <v>14</v>
       </c>
@@ -2727,7 +2567,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2759,19 +2599,9 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>5687</v>
-      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
         <v>16</v>
       </c>
@@ -2786,7 +2616,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>4</v>
+        <v>327</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2818,19 +2648,9 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="n">
-        <v>15184</v>
-      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
         <v>12</v>
       </c>
@@ -2845,7 +2665,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2877,19 +2697,9 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>15708</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
         <v>10</v>
       </c>
@@ -2904,7 +2714,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -2936,19 +2746,9 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>15056</v>
-      </c>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
         <v>13</v>
       </c>
@@ -2963,7 +2763,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2995,21 +2795,11 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>15493</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
@@ -3054,34 +2844,24 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
+      <c r="X27" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V27" s="7" t="n">
-        <v>14553</v>
-      </c>
-      <c r="X27" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
       <c r="AB27" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3113,19 +2893,9 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>14491</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
         <v>10</v>
       </c>
@@ -3140,7 +2910,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -3172,19 +2942,9 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>15132</v>
-      </c>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
         <v>2</v>
       </c>
@@ -3231,34 +2991,24 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
+      <c r="X30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z30" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V30" s="4" t="n">
-        <v>15616</v>
-      </c>
-      <c r="X30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z30" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
       <c r="AB30" s="4" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3290,34 +3040,24 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n"/>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
+      <c r="X31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z31" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodora</t>
         </is>
       </c>
-      <c r="V31" s="7" t="n">
-        <v>15857</v>
-      </c>
-      <c r="X31" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
       <c r="AB31" s="7" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3358,19 +3098,9 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>15396</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
         <v>2</v>
       </c>
@@ -3431,19 +3161,9 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V33" s="7" t="n">
-        <v>87207</v>
-      </c>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
         <v>37</v>
       </c>
@@ -3458,7 +3178,7 @@
         </is>
       </c>
       <c r="AB33" s="7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC33" s="7" t="inlineStr">
         <is>
@@ -3472,19 +3192,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>86030</v>
-      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
         <v>36</v>
       </c>
@@ -3499,158 +3209,118 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
+      <c r="X35" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB35" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD35" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
+      <c r="X36" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z36" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB36" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AD36" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V35" s="7" t="n">
-        <v>82667</v>
-      </c>
-      <c r="X35" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y35" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z35" s="7" t="inlineStr">
+    <row r="37">
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
+      <c r="X37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z37" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="AB35" s="7" t="n">
+      <c r="AB37" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AC35" s="7" t="inlineStr">
+      <c r="AC37" s="7" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AD35" s="7" t="inlineStr">
+      <c r="AD37" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>82796</v>
-      </c>
-      <c r="X36" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB36" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AD36" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V37" s="7" t="n">
-        <v>80792</v>
-      </c>
-      <c r="X37" s="7" t="n">
+    <row r="38">
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
+      <c r="X38" s="4" t="n">
         <v>34</v>
-      </c>
-      <c r="Y37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB37" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AC37" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AD37" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>80181</v>
-      </c>
-      <c r="X38" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3677,19 +3347,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V39" s="7" t="n">
-        <v>82769</v>
-      </c>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
         <v>1</v>
       </c>
@@ -3718,21 +3378,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>82955</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
@@ -3759,21 +3409,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V41" s="7" t="n">
-        <v>84463</v>
-      </c>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
@@ -3800,19 +3440,9 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>81914</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
         <v>41</v>
       </c>
@@ -3827,7 +3457,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3841,19 +3471,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U43" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V43" s="7" t="n">
-        <v>721</v>
-      </c>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
         <v>2</v>
       </c>
@@ -3882,21 +3502,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>729</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
@@ -3909,7 +3519,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3923,21 +3533,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U45" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V45" s="7" t="n">
-        <v>717</v>
-      </c>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
@@ -3964,21 +3564,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>753</v>
-      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
@@ -3991,76 +3581,56 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD46" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
+      <c r="X47" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z47" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB47" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr">
+      <c r="AC47" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD46" s="4" t="inlineStr">
+      <c r="AD47" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V47" s="7" t="n">
-        <v>696</v>
-      </c>
-      <c r="X47" s="7" t="n">
+    <row r="48">
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
+      <c r="X48" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="Y47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB47" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC47" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD47" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="T48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V48" s="4" t="n">
-        <v>723</v>
-      </c>
-      <c r="X48" s="4" t="n">
-        <v>35</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
@@ -4087,21 +3657,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U49" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V49" s="7" t="n">
-        <v>743</v>
-      </c>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
@@ -4128,19 +3688,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U50" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>714</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>43</v>
       </c>
@@ -4155,95 +3705,75 @@
         </is>
       </c>
       <c r="AB50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD50" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
+      <c r="X51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z51" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB51" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr">
+      <c r="AC51" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD50" s="4" t="inlineStr">
+      <c r="AD51" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V51" s="7" t="n">
-        <v>733</v>
-      </c>
-      <c r="X51" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y51" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z51" s="7" t="inlineStr">
+    <row r="52">
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
+      <c r="X52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z52" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="AB51" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC51" s="7" t="inlineStr">
+      <c r="AB52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC52" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD51" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>737</v>
-      </c>
-      <c r="X52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z52" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="AD52" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
@@ -4251,19 +3781,9 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U53" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V53" s="7" t="n">
-        <v>50559</v>
-      </c>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
         <v>32</v>
       </c>
@@ -4278,7 +3798,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4292,21 +3812,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>51501</v>
-      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
@@ -4333,19 +3843,9 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U55" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V55" s="7" t="n">
-        <v>51715</v>
-      </c>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
         <v>15</v>
       </c>
@@ -4360,7 +3860,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4374,19 +3874,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>50240</v>
-      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
         <v>2</v>
       </c>
@@ -4401,7 +3891,7 @@
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4415,19 +3905,9 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U57" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V57" s="7" t="n">
-        <v>48948</v>
-      </c>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
         <v>8</v>
       </c>
@@ -4442,7 +3922,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4456,19 +3936,9 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>48922</v>
-      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
         <v>3</v>
       </c>
@@ -4497,19 +3967,9 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U59" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V59" s="7" t="n">
-        <v>51004</v>
-      </c>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
         <v>15</v>
       </c>
@@ -4538,21 +3998,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U60" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V60" s="4" t="n">
-        <v>50744</v>
-      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
@@ -4579,21 +4029,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V61" s="7" t="n">
-        <v>50396</v>
-      </c>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
@@ -4620,21 +4060,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U62" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>51782</v>
-      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -4661,21 +4091,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U63" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V63" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y63" s="7" t="inlineStr">
         <is>
@@ -4702,101 +4122,71 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" s="4" t="inlineStr">
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
+      <c r="X64" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y64" s="4" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo.8PDW8D52VJ</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" s="4" t="n">
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB64" s="4" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="T65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
+      <c r="X65" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="Y64" s="4" t="inlineStr">
+      <c r="Y65" s="7" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="Z64" s="4" t="inlineStr">
+      <c r="Z65" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="AB64" s="4" t="n">
+      <c r="AB65" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr">
+      <c r="AC65" s="7" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD64" s="4" t="inlineStr">
+      <c r="AD65" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V65" s="7" t="n">
-        <v>11599</v>
-      </c>
-      <c r="X65" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB65" s="7" t="n">
-        <v>316</v>
-      </c>
-      <c r="AC65" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD65" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
     <row r="66">
-      <c r="T66" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U66" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V66" s="4" t="n">
-        <v>11522</v>
-      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
         <v>13</v>
       </c>
@@ -4811,7 +4201,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -4825,19 +4215,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U67" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V67" s="7" t="n">
-        <v>11614</v>
-      </c>
+      <c r="T67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
         <v>2</v>
       </c>
@@ -4852,7 +4232,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -4866,19 +4246,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>11098</v>
-      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
         <v>9</v>
       </c>
@@ -4893,7 +4263,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4907,19 +4277,9 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U69" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V69" s="7" t="n">
-        <v>11097</v>
-      </c>
+      <c r="T69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
         <v>2</v>
       </c>
@@ -4948,19 +4308,9 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>11410</v>
-      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
         <v>1</v>
       </c>
@@ -4975,7 +4325,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4989,19 +4339,9 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U71" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V71" s="7" t="n">
-        <v>11482</v>
-      </c>
+      <c r="T71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
         <v>1</v>
       </c>
@@ -5016,76 +4356,56 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB72" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="AC71" s="7" t="inlineStr">
+      <c r="AC72" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD71" s="7" t="inlineStr">
+      <c r="AD72" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>11322</v>
-      </c>
-      <c r="X72" s="4" t="n">
+    <row r="73">
+      <c r="T73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
+      <c r="X73" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="Y72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD72" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="T73" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U73" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V73" s="7" t="n">
-        <v>11380</v>
-      </c>
-      <c r="X73" s="7" t="n">
-        <v>19</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
@@ -5112,21 +4432,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>11597</v>
-      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
@@ -5153,34 +4463,24 @@
       </c>
     </row>
     <row r="75">
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U75" s="7" t="inlineStr">
+      <c r="T75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
+      <c r="X75" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y75" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z75" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
-      <c r="V75" s="7" t="n">
-        <v>26509</v>
-      </c>
-      <c r="X75" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y75" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z75" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
       <c r="AB75" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5194,19 +4494,9 @@
       </c>
     </row>
     <row r="76">
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>26876</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
         <v>19</v>
       </c>
@@ -5221,7 +4511,7 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -5235,101 +4525,71 @@
       </c>
     </row>
     <row r="77">
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U77" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V77" s="7" t="n">
-        <v>27154</v>
-      </c>
+      <c r="T77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB77" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD77" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
+      <c r="X78" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="Y77" s="7" t="inlineStr">
+      <c r="Y78" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="Z77" s="7" t="inlineStr">
+      <c r="Z78" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="AB77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC77" s="7" t="inlineStr">
+      <c r="AB78" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AD77" s="7" t="inlineStr">
+      <c r="AD78" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>26655</v>
-      </c>
-      <c r="X78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB78" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AD78" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
-      <c r="T79" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U79" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V79" s="7" t="n">
-        <v>25267</v>
-      </c>
+      <c r="T79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
         <v>3</v>
       </c>
@@ -5344,7 +4604,7 @@
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
@@ -5358,19 +4618,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>24712</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
         <v>19</v>
       </c>
@@ -5399,19 +4649,9 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U81" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V81" s="7" t="n">
-        <v>26356</v>
-      </c>
+      <c r="T81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
         <v>21</v>
       </c>
@@ -5440,19 +4680,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>25640</v>
-      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
         <v>15</v>
       </c>
@@ -5481,19 +4711,9 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V83" s="7" t="n">
-        <v>26277</v>
-      </c>
+      <c r="T83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
         <v>14</v>
       </c>
@@ -5522,21 +4742,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U84" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>27017</v>
-      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -5563,21 +4773,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U85" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V85" s="7" t="n">
-        <v>17949</v>
-      </c>
+      <c r="T85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y85" s="7" t="inlineStr">
         <is>
@@ -5604,183 +4804,133 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
+      <c r="X86" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z86" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD86" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
-      <c r="V86" s="4" t="n">
-        <v>17549</v>
-      </c>
-      <c r="X86" s="4" t="n">
+    </row>
+    <row r="87">
+      <c r="T87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
+      <c r="X87" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Y86" s="4" t="inlineStr">
+      <c r="Y87" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="Z86" s="4" t="inlineStr">
+      <c r="Z87" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="AB86" s="4" t="n">
+      <c r="AB87" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD87" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
+      <c r="X88" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB88" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD88" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="T89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
+      <c r="X89" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z89" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB89" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr">
+      <c r="AC89" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD86" s="4" t="inlineStr">
+      <c r="AD89" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V87" s="7" t="n">
-        <v>17646</v>
-      </c>
-      <c r="X87" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB87" s="7" t="n">
-        <v>157</v>
-      </c>
-      <c r="AC87" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD87" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="T88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>17131</v>
-      </c>
-      <c r="X88" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC88" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD88" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V89" s="7" t="n">
-        <v>17470</v>
-      </c>
-      <c r="X89" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y89" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB89" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC89" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD89" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
-      <c r="T90" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U90" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>17485</v>
-      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
         <v>6</v>
       </c>
@@ -5795,7 +4945,7 @@
         </is>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5809,19 +4959,9 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U91" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V91" s="7" t="n">
-        <v>17825</v>
-      </c>
+      <c r="T91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
         <v>21</v>
       </c>
@@ -5836,158 +4976,118 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD91" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
+      <c r="X92" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AC91" s="7" t="inlineStr">
+      <c r="Y92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z92" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB92" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC92" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD91" s="7" t="inlineStr">
+      <c r="AD92" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="T92" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V92" s="4" t="n">
-        <v>17897</v>
-      </c>
-      <c r="X92" s="4" t="n">
+    <row r="93">
+      <c r="T93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
+      <c r="X93" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="Y92" s="4" t="inlineStr">
+      <c r="Y93" s="7" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z92" s="4" t="inlineStr">
+      <c r="Z93" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB92" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr">
+      <c r="AB93" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC93" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD92" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="T93" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U93" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V93" s="7" t="n">
-        <v>17613</v>
-      </c>
-      <c r="X93" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y93" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z93" s="7" t="inlineStr">
+      <c r="AD93" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
+      <c r="X94" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z94" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB93" s="7" t="n">
+      <c r="AB94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AC93" s="7" t="inlineStr">
+      <c r="AC94" s="4" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD93" s="7" t="inlineStr">
+      <c r="AD94" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="T94" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V94" s="4" t="n">
-        <v>17704</v>
-      </c>
-      <c r="X94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y94" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB94" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD94" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
     <row r="95">
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U95" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V95" s="7" t="n">
-        <v>745</v>
-      </c>
+      <c r="T95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y95" s="7" t="inlineStr">
         <is>
@@ -6014,34 +5114,24 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" s="4" t="inlineStr">
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
+      <c r="X96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U96" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V96" s="4" t="n">
-        <v>763</v>
-      </c>
-      <c r="X96" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y96" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="Z96" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -6055,19 +5145,9 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U97" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V97" s="7" t="n">
-        <v>740</v>
-      </c>
+      <c r="T97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
         <v>1</v>
       </c>
@@ -6082,7 +5162,7 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -6096,103 +5176,73 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V98" s="4" t="n">
-        <v>783</v>
-      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB98" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD98" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="T99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
+      <c r="X99" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Y98" s="4" t="inlineStr">
+      <c r="Y99" s="7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z98" s="4" t="inlineStr">
+      <c r="Z99" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB98" s="4" t="n">
+      <c r="AB99" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AC98" s="4" t="inlineStr">
+      <c r="AC99" s="7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD98" s="4" t="inlineStr">
+      <c r="AD99" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="T99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V99" s="7" t="n">
-        <v>763</v>
-      </c>
-      <c r="X99" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB99" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC99" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD99" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
     <row r="100">
-      <c r="T100" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>735</v>
-      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y100" s="4" t="inlineStr">
         <is>
@@ -6219,21 +5269,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U101" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V101" s="7" t="n">
-        <v>841</v>
-      </c>
+      <c r="T101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
@@ -6260,21 +5300,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n">
-        <v>767</v>
-      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
@@ -6301,62 +5331,42 @@
       </c>
     </row>
     <row r="103">
-      <c r="T103" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V103" s="7" t="n">
-        <v>748</v>
-      </c>
+      <c r="T103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z103" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB103" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD103" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="4" t="n"/>
+      <c r="V104" s="4" t="n"/>
+      <c r="X104" s="4" t="n">
         <v>58</v>
-      </c>
-      <c r="Y103" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB103" s="7" t="n">
-        <v>339</v>
-      </c>
-      <c r="AC103" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="AD103" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="T104" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n">
-        <v>751</v>
-      </c>
-      <c r="X104" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
@@ -6383,19 +5393,9 @@
       </c>
     </row>
     <row r="105">
-      <c r="T105" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U105" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>2142</v>
-      </c>
+      <c r="T105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
         <v>1</v>
       </c>
@@ -6410,7 +5410,7 @@
         </is>
       </c>
       <c r="AB105" s="7" t="n">
-        <v>8</v>
+        <v>339</v>
       </c>
       <c r="AC105" s="7" t="inlineStr">
         <is>
@@ -6424,21 +5424,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="n">
-        <v>2408</v>
-      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="4" t="n"/>
+      <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="Y106" s="4" t="inlineStr">
         <is>
@@ -6465,21 +5455,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="T107" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U107" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V107" s="7" t="n">
-        <v>2141</v>
-      </c>
+      <c r="T107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="Y107" s="7" t="inlineStr">
         <is>
@@ -6506,19 +5486,9 @@
       </c>
     </row>
     <row r="108">
-      <c r="T108" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U108" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V108" s="4" t="n">
-        <v>2082</v>
-      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="4" t="n"/>
+      <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
         <v>61</v>
       </c>
@@ -6533,7 +5503,7 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6547,19 +5517,9 @@
       </c>
     </row>
     <row r="109">
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U109" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>1990</v>
-      </c>
+      <c r="T109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
         <v>6</v>
       </c>
@@ -6574,7 +5534,7 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6588,19 +5548,9 @@
       </c>
     </row>
     <row r="110">
-      <c r="T110" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U110" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>2043</v>
-      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
         <v>6</v>
       </c>
@@ -6615,7 +5565,7 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6629,21 +5579,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="T111" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U111" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V111" s="7" t="n">
-        <v>2148</v>
-      </c>
+      <c r="T111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="Y111" s="7" t="inlineStr">
         <is>
@@ -6670,34 +5610,24 @@
       </c>
     </row>
     <row r="112">
-      <c r="T112" s="4" t="inlineStr">
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="4" t="n"/>
+      <c r="V112" s="4" t="n"/>
+      <c r="X112" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y112" s="4" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U112" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V112" s="4" t="n">
-        <v>2096</v>
-      </c>
-      <c r="X112" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y112" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="Z112" s="4" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6711,19 +5641,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="T113" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U113" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V113" s="7" t="n">
-        <v>2265</v>
-      </c>
+      <c r="T113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
         <v>9</v>
       </c>
@@ -6738,7 +5658,7 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -6752,19 +5672,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="T114" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U114" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>2187</v>
-      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
         <v>48</v>
       </c>
@@ -6779,7 +5689,7 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6810,7 +5720,7 @@
         </is>
       </c>
       <c r="AB115" s="7" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6841,7 +5751,7 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -6859,7 +5769,7 @@
       <c r="U117" s="7" t="n"/>
       <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="Y117" s="7" t="inlineStr">
         <is>
@@ -6872,7 +5782,7 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -6890,7 +5800,7 @@
       <c r="U118" s="4" t="n"/>
       <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Y118" s="4" t="inlineStr">
         <is>
@@ -6903,7 +5813,7 @@
         </is>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -6921,7 +5831,7 @@
       <c r="U119" s="7" t="n"/>
       <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y119" s="7" t="inlineStr">
         <is>
@@ -7076,7 +5986,7 @@
       <c r="U124" s="4" t="n"/>
       <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y124" s="4" t="inlineStr">
         <is>
@@ -7107,7 +6017,7 @@
       <c r="U125" s="7" t="n"/>
       <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="7" t="inlineStr">
         <is>
@@ -7151,7 +6061,7 @@
         </is>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -7182,7 +6092,7 @@
         </is>
       </c>
       <c r="AB127" s="7" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
@@ -7213,7 +6123,7 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -7244,7 +6154,7 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -7262,7 +6172,7 @@
       <c r="U130" s="4" t="n"/>
       <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
@@ -7275,7 +6185,7 @@
         </is>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -7293,20 +6203,20 @@
       <c r="U131" s="7" t="n"/>
       <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y131" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z131" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB131" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="Y131" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z131" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB131" s="7" t="n">
-        <v>11</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -7337,7 +6247,7 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -7368,7 +6278,7 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -7399,7 +6309,7 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -7430,7 +6340,7 @@
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -7461,7 +6371,7 @@
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -7585,7 +6495,7 @@
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -7647,7 +6557,7 @@
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -7668,7 +6578,7 @@
       <c r="Y143" s="7" t="n"/>
       <c r="Z143" s="7" t="n"/>
       <c r="AB143" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -7773,7 +6683,7 @@
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n"/>
       <c r="AB148" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
@@ -7794,7 +6704,7 @@
       <c r="Y149" s="7" t="n"/>
       <c r="Z149" s="7" t="n"/>
       <c r="AB149" s="7" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="AC149" s="7" t="inlineStr">
         <is>
@@ -7815,7 +6725,7 @@
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n"/>
       <c r="AB150" s="4" t="n">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -7836,7 +6746,7 @@
       <c r="Y151" s="7" t="n"/>
       <c r="Z151" s="7" t="n"/>
       <c r="AB151" s="7" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AC151" s="7" t="inlineStr">
         <is>
@@ -7857,7 +6767,7 @@
       <c r="Y152" s="4" t="n"/>
       <c r="Z152" s="4" t="n"/>
       <c r="AB152" s="4" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
@@ -7878,7 +6788,7 @@
       <c r="Y153" s="7" t="n"/>
       <c r="Z153" s="7" t="n"/>
       <c r="AB153" s="7" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -7899,7 +6809,7 @@
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n"/>
       <c r="AB154" s="4" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -8046,7 +6956,7 @@
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
       <c r="AB161" s="7" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -8067,7 +6977,7 @@
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
       <c r="AB162" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -8088,7 +6998,7 @@
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
       <c r="AB163" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -8109,7 +7019,7 @@
       <c r="Y164" s="4" t="n"/>
       <c r="Z164" s="4" t="n"/>
       <c r="AB164" s="4" t="n">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
@@ -8193,7 +7103,7 @@
       <c r="Y168" s="4" t="n"/>
       <c r="Z168" s="4" t="n"/>
       <c r="AB168" s="4" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -8235,7 +7145,7 @@
       <c r="Y170" s="4" t="n"/>
       <c r="Z170" s="4" t="n"/>
       <c r="AB170" s="4" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
@@ -8319,7 +7229,7 @@
       <c r="Y174" s="4" t="n"/>
       <c r="Z174" s="4" t="n"/>
       <c r="AB174" s="4" t="n">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
@@ -8340,7 +7250,7 @@
       <c r="Y175" s="7" t="n"/>
       <c r="Z175" s="7" t="n"/>
       <c r="AB175" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC175" s="7" t="inlineStr">
         <is>
@@ -8361,7 +7271,7 @@
       <c r="Y176" s="4" t="n"/>
       <c r="Z176" s="4" t="n"/>
       <c r="AB176" s="4" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="AC176" s="4" t="inlineStr">
         <is>
@@ -8382,7 +7292,7 @@
       <c r="Y177" s="7" t="n"/>
       <c r="Z177" s="7" t="n"/>
       <c r="AB177" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC177" s="7" t="inlineStr">
         <is>
@@ -8403,7 +7313,7 @@
       <c r="Y178" s="4" t="n"/>
       <c r="Z178" s="4" t="n"/>
       <c r="AB178" s="4" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
@@ -8424,7 +7334,7 @@
       <c r="Y179" s="7" t="n"/>
       <c r="Z179" s="7" t="n"/>
       <c r="AB179" s="7" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="AC179" s="7" t="inlineStr">
         <is>
@@ -8445,7 +7355,7 @@
       <c r="Y180" s="4" t="n"/>
       <c r="Z180" s="4" t="n"/>
       <c r="AB180" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC180" s="4" t="inlineStr">
         <is>
@@ -8487,7 +7397,7 @@
       <c r="Y182" s="4" t="n"/>
       <c r="Z182" s="4" t="n"/>
       <c r="AB182" s="4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="AC182" s="4" t="inlineStr">
         <is>
@@ -8508,7 +7418,7 @@
       <c r="Y183" s="7" t="n"/>
       <c r="Z183" s="7" t="n"/>
       <c r="AB183" s="7" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="AC183" s="7" t="inlineStr">
         <is>
@@ -8529,7 +7439,7 @@
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
       <c r="AB184" s="4" t="n">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
@@ -8550,7 +7460,7 @@
       <c r="Y185" s="7" t="n"/>
       <c r="Z185" s="7" t="n"/>
       <c r="AB185" s="7" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="AC185" s="7" t="inlineStr">
         <is>
@@ -8739,7 +7649,7 @@
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n"/>
       <c r="AB194" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AC194" s="4" t="inlineStr">
         <is>
@@ -8760,7 +7670,7 @@
       <c r="Y195" s="7" t="n"/>
       <c r="Z195" s="7" t="n"/>
       <c r="AB195" s="7" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AC195" s="7" t="inlineStr">
         <is>
@@ -8781,7 +7691,7 @@
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="n"/>
       <c r="AB196" s="4" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="AC196" s="4" t="inlineStr">
         <is>
@@ -8802,7 +7712,7 @@
       <c r="Y197" s="7" t="n"/>
       <c r="Z197" s="7" t="n"/>
       <c r="AB197" s="7" t="n">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="AC197" s="7" t="inlineStr">
         <is>
@@ -8844,7 +7754,7 @@
       <c r="Y199" s="7" t="n"/>
       <c r="Z199" s="7" t="n"/>
       <c r="AB199" s="7" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AC199" s="7" t="inlineStr">
         <is>
@@ -8865,7 +7775,7 @@
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n"/>
       <c r="AB200" s="4" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AC200" s="4" t="inlineStr">
         <is>
@@ -8886,7 +7796,7 @@
       <c r="Y201" s="7" t="n"/>
       <c r="Z201" s="7" t="n"/>
       <c r="AB201" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC201" s="7" t="inlineStr">
         <is>
@@ -8907,7 +7817,7 @@
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
       <c r="AB202" s="4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AC202" s="4" t="inlineStr">
         <is>
@@ -8949,7 +7859,7 @@
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
       <c r="AB204" s="4" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AC204" s="4" t="inlineStr">
         <is>
@@ -8970,7 +7880,7 @@
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
       <c r="AB205" s="7" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="AC205" s="7" t="inlineStr">
         <is>
@@ -8991,7 +7901,7 @@
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
       <c r="AB206" s="4" t="n">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="AC206" s="4" t="inlineStr">
         <is>
@@ -9012,7 +7922,7 @@
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
       <c r="AB207" s="7" t="n">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="AC207" s="7" t="inlineStr">
         <is>
@@ -9307,19 +8217,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>7773</v>
-      </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
@@ -9393,19 +8290,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10781</v>
-      </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
@@ -9479,19 +8363,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>14077</v>
-      </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
@@ -9557,19 +8428,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>19486</v>
-      </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
@@ -9643,19 +8501,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>25421</v>
-      </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -9729,19 +8574,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>36128</v>
-      </c>
       <c r="X7" t="n">
         <v>35</v>
       </c>
@@ -9815,19 +8647,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>51111</v>
-      </c>
       <c r="X8" t="n">
         <v>55</v>
       </c>
@@ -9893,19 +8712,6 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>56380</v>
-      </c>
       <c r="X9" t="n">
         <v>42</v>
       </c>
@@ -9981,19 +8787,6 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>56145</v>
-      </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
@@ -10008,7 +8801,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -10059,19 +8852,6 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>52633</v>
-      </c>
       <c r="X11" t="n">
         <v>62</v>
       </c>
@@ -10086,7 +8866,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -10105,19 +8885,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1530</v>
-      </c>
       <c r="X12" t="n">
         <v>52</v>
       </c>
@@ -10132,7 +8899,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -10151,19 +8918,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>2311</v>
-      </c>
       <c r="X13" t="n">
         <v>61</v>
       </c>
@@ -10197,19 +8951,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>2868</v>
-      </c>
       <c r="X14" t="n">
         <v>6</v>
       </c>
@@ -10224,7 +8965,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -10243,19 +8984,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>4059</v>
-      </c>
       <c r="X15" t="n">
         <v>4</v>
       </c>
@@ -10289,19 +9017,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>5092</v>
-      </c>
       <c r="X16" t="n">
         <v>5</v>
       </c>
@@ -10335,19 +9050,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>6962</v>
-      </c>
       <c r="X17" t="n">
         <v>5</v>
       </c>
@@ -10362,7 +9064,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -10381,19 +9083,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>9959</v>
-      </c>
       <c r="X18" t="n">
         <v>5</v>
       </c>
@@ -10408,7 +9097,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -10427,19 +9116,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>11290</v>
-      </c>
       <c r="X19" t="n">
         <v>10</v>
       </c>
@@ -10473,19 +9149,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>11188</v>
-      </c>
       <c r="X20" t="n">
         <v>9</v>
       </c>
@@ -10519,19 +9182,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>10576</v>
-      </c>
       <c r="X21" t="n">
         <v>7</v>
       </c>
@@ -10565,19 +9215,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>1815</v>
-      </c>
       <c r="X22" t="n">
         <v>5</v>
       </c>
@@ -10611,19 +9248,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>2333</v>
-      </c>
       <c r="X23" t="n">
         <v>2</v>
       </c>
@@ -10657,19 +9281,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>3182</v>
-      </c>
       <c r="X24" t="n">
         <v>6</v>
       </c>
@@ -10703,19 +9314,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>4129</v>
-      </c>
       <c r="X25" t="n">
         <v>20</v>
       </c>
@@ -10749,19 +9347,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>5644</v>
-      </c>
       <c r="X26" t="n">
         <v>9</v>
       </c>
@@ -10776,7 +9361,7 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -10795,19 +9380,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>7963</v>
-      </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
@@ -10822,7 +9394,7 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -10841,19 +9413,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>11169</v>
-      </c>
       <c r="X28" t="n">
         <v>22</v>
       </c>
@@ -10868,7 +9427,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -10887,19 +9446,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>12345</v>
-      </c>
       <c r="X29" t="n">
         <v>27</v>
       </c>
@@ -10914,7 +9460,7 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -10933,19 +9479,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>12001</v>
-      </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
@@ -10960,7 +9493,7 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -10979,19 +9512,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>11593</v>
-      </c>
       <c r="X31" t="n">
         <v>2</v>
       </c>
@@ -11039,19 +9559,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>2322</v>
       </c>
       <c r="X32" t="n">
         <v>44</v>
@@ -11109,19 +9616,6 @@
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>3533</v>
-      </c>
       <c r="X33" t="n">
         <v>28</v>
       </c>
@@ -11150,19 +9644,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>4891</v>
-      </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
@@ -11191,19 +9672,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>6461</v>
-      </c>
       <c r="X35" t="n">
         <v>36</v>
       </c>
@@ -11232,19 +9700,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>8274</v>
-      </c>
       <c r="X36" t="n">
         <v>22</v>
       </c>
@@ -11273,19 +9728,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>12174</v>
-      </c>
       <c r="X37" t="n">
         <v>1</v>
       </c>
@@ -11300,7 +9742,7 @@
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -11314,19 +9756,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>19723</v>
-      </c>
       <c r="X38" t="n">
         <v>5</v>
       </c>
@@ -11341,7 +9770,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -11355,21 +9784,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>20836</v>
-      </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -11396,21 +9812,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>20942</v>
-      </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -11437,19 +9840,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>20742</v>
-      </c>
       <c r="X41" t="n">
         <v>5</v>
       </c>
@@ -11478,21 +9868,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>1827</v>
-      </c>
       <c r="X42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -11519,60 +9896,34 @@
       </c>
     </row>
     <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
-      <c r="V43" t="n">
-        <v>2275</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB43" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>2882</v>
-      </c>
       <c r="X44" t="n">
         <v>9</v>
       </c>
@@ -11587,7 +9938,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -11601,19 +9952,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>3280</v>
-      </c>
       <c r="X45" t="n">
         <v>1</v>
       </c>
@@ -11628,76 +9966,50 @@
         </is>
       </c>
       <c r="AB45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="X46" t="n">
         <v>1</v>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>3951</v>
-      </c>
-      <c r="X46" t="n">
+    <row r="47">
+      <c r="X47" t="n">
         <v>6</v>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>5096</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -11724,21 +10036,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>6277</v>
-      </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -11765,21 +10064,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>6297</v>
-      </c>
       <c r="X49" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -11806,19 +10092,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>6082</v>
-      </c>
       <c r="X50" t="n">
         <v>19</v>
       </c>
@@ -11847,19 +10120,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>5937</v>
-      </c>
       <c r="X51" t="n">
         <v>1</v>
       </c>
@@ -11888,21 +10148,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>250</v>
-      </c>
       <c r="X52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -11929,21 +10176,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>428</v>
-      </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -11970,19 +10204,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V54" t="n">
-        <v>365</v>
-      </c>
       <c r="X54" t="n">
         <v>3</v>
       </c>
@@ -12011,19 +10232,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>471</v>
-      </c>
       <c r="X55" t="n">
         <v>3</v>
       </c>
@@ -12052,19 +10260,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>554</v>
-      </c>
       <c r="X56" t="n">
         <v>8</v>
       </c>
@@ -12093,19 +10288,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>902</v>
-      </c>
       <c r="X57" t="n">
         <v>7</v>
       </c>
@@ -12134,19 +10316,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>1420</v>
-      </c>
       <c r="X58" t="n">
         <v>8</v>
       </c>
@@ -12161,7 +10330,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -12175,19 +10344,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>1561</v>
-      </c>
       <c r="X59" t="n">
         <v>7</v>
       </c>
@@ -12202,7 +10358,7 @@
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -12216,19 +10372,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>1642</v>
-      </c>
       <c r="X60" t="n">
         <v>11</v>
       </c>
@@ -12243,7 +10386,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -12257,19 +10400,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V61" t="n">
-        <v>1559</v>
-      </c>
       <c r="X61" t="n">
         <v>11</v>
       </c>
@@ -12284,7 +10414,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -12298,19 +10428,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>6249</v>
-      </c>
       <c r="X62" t="n">
         <v>12</v>
       </c>
@@ -12325,7 +10442,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -12339,19 +10456,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V63" t="n">
-        <v>8329</v>
-      </c>
       <c r="X63" t="n">
         <v>5</v>
       </c>
@@ -12380,19 +10484,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>10619</v>
-      </c>
       <c r="X64" t="n">
         <v>13</v>
       </c>
@@ -12421,19 +10512,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>13894</v>
-      </c>
       <c r="X65" t="n">
         <v>1</v>
       </c>
@@ -12462,19 +10540,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>17235</v>
-      </c>
       <c r="X66" t="n">
         <v>1</v>
       </c>
@@ -12503,19 +10568,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>23145</v>
-      </c>
       <c r="X67" t="n">
         <v>17</v>
       </c>
@@ -12544,21 +10596,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V68" t="n">
-        <v>32675</v>
-      </c>
       <c r="X68" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -12585,21 +10624,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V69" t="n">
-        <v>34857</v>
-      </c>
       <c r="X69" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -12626,19 +10652,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V70" t="n">
-        <v>34093</v>
-      </c>
       <c r="X70" t="n">
         <v>31</v>
       </c>
@@ -12667,19 +10680,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V71" t="n">
-        <v>33649</v>
-      </c>
       <c r="X71" t="n">
         <v>1</v>
       </c>
@@ -12708,19 +10708,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V72" t="n">
-        <v>30</v>
-      </c>
       <c r="X72" t="n">
         <v>1</v>
       </c>
@@ -12749,21 +10736,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V73" t="n">
-        <v>81</v>
-      </c>
       <c r="X73" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -12790,21 +10764,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V74" t="n">
-        <v>103</v>
-      </c>
       <c r="X74" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -12817,158 +10778,106 @@
         </is>
       </c>
       <c r="AB74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="X75" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
         <v>6</v>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD74" t="inlineStr">
+      <c r="AD75" t="inlineStr">
         <is>
           <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V75" t="n">
-        <v>154</v>
-      </c>
-      <c r="X75" t="n">
+    <row r="76">
+      <c r="X76" t="n">
         <v>4</v>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>com.logistics.rider.glovo</t>
         </is>
       </c>
-      <c r="AB75" t="n">
+      <c r="AB76" t="n">
         <v>1</v>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="T76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="X77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC77" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V76" t="n">
-        <v>183</v>
-      </c>
-      <c r="X76" t="n">
-        <v>43</v>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB76" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V77" t="n">
-        <v>238</v>
-      </c>
-      <c r="X77" t="n">
+    <row r="78">
+      <c r="X78" t="n">
         <v>34</v>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V78" t="n">
-        <v>354</v>
-      </c>
-      <c r="X78" t="n">
-        <v>3</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -12995,19 +10904,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V79" t="n">
-        <v>347</v>
-      </c>
       <c r="X79" t="n">
         <v>2</v>
       </c>
@@ -13022,7 +10918,7 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -13036,19 +10932,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V80" t="n">
-        <v>324</v>
-      </c>
       <c r="X80" t="n">
         <v>38</v>
       </c>
@@ -13077,19 +10960,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V81" t="n">
-        <v>307</v>
-      </c>
       <c r="X81" t="n">
         <v>2</v>
       </c>
@@ -13104,7 +10974,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -13118,19 +10988,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V82" t="n">
-        <v>603</v>
-      </c>
       <c r="X82" t="n">
         <v>26</v>
       </c>
@@ -13159,19 +11016,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V83" t="n">
-        <v>820</v>
-      </c>
       <c r="X83" t="n">
         <v>1</v>
       </c>
@@ -13200,19 +11044,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V84" t="n">
-        <v>1204</v>
-      </c>
       <c r="X84" t="n">
         <v>1</v>
       </c>
@@ -13241,19 +11072,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V85" t="n">
-        <v>1689</v>
-      </c>
       <c r="X85" t="n">
         <v>3</v>
       </c>
@@ -13282,19 +11100,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V86" t="n">
-        <v>2042</v>
-      </c>
       <c r="X86" t="n">
         <v>1</v>
       </c>
@@ -13323,19 +11128,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V87" t="n">
-        <v>2581</v>
-      </c>
       <c r="X87" t="n">
         <v>1</v>
       </c>
@@ -13364,19 +11156,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V88" t="n">
-        <v>3880</v>
-      </c>
       <c r="X88" t="n">
         <v>1</v>
       </c>
@@ -13405,19 +11184,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V89" t="n">
-        <v>3997</v>
-      </c>
       <c r="X89" t="n">
         <v>1</v>
       </c>
@@ -13432,7 +11198,7 @@
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -13446,19 +11212,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V90" t="n">
-        <v>3987</v>
-      </c>
       <c r="X90" t="n">
         <v>1</v>
       </c>
@@ -13487,19 +11240,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V91" t="n">
-        <v>3921</v>
-      </c>
       <c r="X91" t="n">
         <v>5</v>
       </c>
@@ -13514,7 +11254,7 @@
         </is>
       </c>
       <c r="AB91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -13528,19 +11268,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V92" t="n">
-        <v>90</v>
-      </c>
       <c r="X92" t="n">
         <v>6</v>
       </c>
@@ -13569,19 +11296,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V93" t="n">
-        <v>119</v>
-      </c>
       <c r="X93" t="n">
         <v>8</v>
       </c>
@@ -13610,19 +11324,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V94" t="n">
-        <v>157</v>
-      </c>
       <c r="X94" t="n">
         <v>4</v>
       </c>
@@ -13651,19 +11352,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V95" t="n">
-        <v>244</v>
-      </c>
       <c r="X95" t="n">
         <v>11</v>
       </c>
@@ -13678,7 +11366,7 @@
         </is>
       </c>
       <c r="AB95" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -13692,19 +11380,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V96" t="n">
-        <v>270</v>
-      </c>
       <c r="X96" t="n">
         <v>1</v>
       </c>
@@ -13719,7 +11394,7 @@
         </is>
       </c>
       <c r="AB96" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -13733,19 +11408,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V97" t="n">
-        <v>341</v>
-      </c>
       <c r="X97" t="n">
         <v>1</v>
       </c>
@@ -13760,7 +11422,7 @@
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -13774,19 +11436,6 @@
       </c>
     </row>
     <row r="98">
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V98" t="n">
-        <v>409</v>
-      </c>
       <c r="X98" t="n">
         <v>2</v>
       </c>
@@ -13815,19 +11464,6 @@
       </c>
     </row>
     <row r="99">
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V99" t="n">
-        <v>401</v>
-      </c>
       <c r="X99" t="n">
         <v>1</v>
       </c>
@@ -13856,19 +11492,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V100" t="n">
-        <v>396</v>
-      </c>
       <c r="X100" t="n">
         <v>1</v>
       </c>
@@ -13897,19 +11520,6 @@
       </c>
     </row>
     <row r="101">
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V101" t="n">
-        <v>369</v>
-      </c>
       <c r="AB101" t="n">
         <v>1</v>
       </c>
@@ -13971,7 +11581,7 @@
     </row>
     <row r="105">
       <c r="AB105" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
@@ -13986,7 +11596,7 @@
     </row>
     <row r="106">
       <c r="AB106" t="n">
-        <v>4</v>
+        <v>196</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -14091,7 +11701,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -14106,7 +11716,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -14121,7 +11731,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -14151,7 +11761,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -14211,7 +11821,7 @@
     </row>
     <row r="121">
       <c r="AB121" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
@@ -14226,7 +11836,7 @@
     </row>
     <row r="122">
       <c r="AB122" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
@@ -14256,7 +11866,7 @@
     </row>
     <row r="124">
       <c r="AB124" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -14271,7 +11881,7 @@
     </row>
     <row r="125">
       <c r="AB125" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
@@ -14331,7 +11941,7 @@
     </row>
     <row r="129">
       <c r="AB129" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -14346,7 +11956,7 @@
     </row>
     <row r="130">
       <c r="AB130" t="n">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
@@ -14361,7 +11971,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
@@ -14451,7 +12061,7 @@
     </row>
     <row r="137">
       <c r="AB137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
@@ -14481,7 +12091,7 @@
     </row>
     <row r="139">
       <c r="AB139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
@@ -15348,7 +12958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD50"/>
+  <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15509,19 +13119,6 @@
         <f>$B$2+H2+M2</f>
         <v/>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="X2" t="n">
         <v>3</v>
       </c>
@@ -15595,19 +13192,6 @@
         <f>$B$2+H3+M3</f>
         <v/>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3208</v>
-      </c>
       <c r="X3" t="n">
         <v>8</v>
       </c>
@@ -15681,19 +13265,6 @@
         <f>$B$2+H4+M4</f>
         <v/>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>7785</v>
-      </c>
       <c r="X4" t="n">
         <v>18</v>
       </c>
@@ -15759,19 +13330,6 @@
         <f>$B$2+H5+M5</f>
         <v/>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>11515</v>
-      </c>
       <c r="X5" t="n">
         <v>8</v>
       </c>
@@ -15845,19 +13403,6 @@
         <f>$B$2+H6+M6</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodpanda</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>14741</v>
-      </c>
       <c r="X6" t="n">
         <v>2</v>
       </c>
@@ -15931,19 +13476,6 @@
         <f>$B$2+H7+M7</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="X7" t="n">
         <v>2</v>
       </c>
@@ -16017,19 +13549,6 @@
         <f>$B$2+H8+M8</f>
         <v/>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>705</v>
-      </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
@@ -16095,19 +13614,6 @@
         <f>$B$2+H9+M9</f>
         <v/>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>1439</v>
-      </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
@@ -16183,19 +13689,6 @@
         <f>$B$2+H10+M10</f>
         <v/>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>2388</v>
-      </c>
       <c r="X10" t="n">
         <v>4</v>
       </c>
@@ -16261,19 +13754,6 @@
         <f>$B$2+H11+M11</f>
         <v/>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2991</v>
-      </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
@@ -16307,19 +13787,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="X12" t="n">
         <v>15</v>
       </c>
@@ -16353,19 +13820,6 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>969</v>
-      </c>
       <c r="X13" t="n">
         <v>2</v>
       </c>
@@ -16399,19 +13853,6 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>1940</v>
-      </c>
       <c r="X14" t="n">
         <v>3</v>
       </c>
@@ -16445,19 +13886,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>2713</v>
-      </c>
       <c r="X15" t="n">
         <v>7</v>
       </c>
@@ -16491,19 +13919,6 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>3546</v>
-      </c>
       <c r="X16" t="n">
         <v>2</v>
       </c>
@@ -16537,19 +13952,6 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
       <c r="X17" t="n">
         <v>3</v>
       </c>
@@ -16583,19 +13985,6 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>1063</v>
-      </c>
       <c r="X18" t="n">
         <v>4</v>
       </c>
@@ -16629,19 +14018,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>2234</v>
-      </c>
       <c r="X19" t="n">
         <v>6</v>
       </c>
@@ -16675,19 +14051,6 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>3474</v>
-      </c>
       <c r="X20" t="n">
         <v>6</v>
       </c>
@@ -16721,19 +14084,6 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>4843</v>
-      </c>
       <c r="X21" t="n">
         <v>9</v>
       </c>
@@ -16767,19 +14117,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>2</v>
-      </c>
       <c r="X22" t="n">
         <v>15</v>
       </c>
@@ -16813,19 +14150,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>904</v>
-      </c>
       <c r="X23" t="n">
         <v>15</v>
       </c>
@@ -16859,19 +14183,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>1597</v>
-      </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
@@ -16905,19 +14216,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>2233</v>
-      </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
@@ -16951,19 +14249,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>2756</v>
-      </c>
       <c r="X26" t="n">
         <v>2</v>
       </c>
@@ -16997,19 +14282,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="X27" t="n">
         <v>2</v>
       </c>
@@ -17043,19 +14315,6 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>113</v>
-      </c>
       <c r="AB28" t="n">
         <v>37</v>
       </c>
@@ -17076,19 +14335,6 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>210</v>
-      </c>
       <c r="AB29" t="n">
         <v>5</v>
       </c>
@@ -17109,19 +14355,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
@@ -17129,19 +14362,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.yemeksepeti</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>428</v>
-      </c>
     </row>
     <row r="32">
       <c r="G32" s="36" t="inlineStr">
@@ -17163,19 +14383,6 @@
         <is>
           <t>Projected AQS including hangs</t>
         </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -17206,274 +14413,6 @@
       <c r="N33" s="38">
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>3024</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>5423</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>7736</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>10704</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V44" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foody</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD212"/>
+  <dimension ref="A1:AD237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="7" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2098,17 +2098,41 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="D12" s="4">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C12)</f>
+        <v/>
+      </c>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="G12" s="4">
+        <f>ROUND(MAX(0,MIN(100,(1-E12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>MIN(1,(G12-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
+      <c r="K12" s="4">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>MAX(0,(L12-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>$B$2+H12+M12</f>
+        <v/>
+      </c>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
@@ -2126,7 +2150,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
@@ -2175,7 +2199,7 @@
         </is>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AC13" s="7" t="inlineStr">
         <is>
@@ -2456,16 +2480,16 @@
       <c r="U19" s="7" t="n"/>
       <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z19" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB19" s="7" t="n">
@@ -2505,20 +2529,20 @@
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2558,7 +2582,7 @@
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
@@ -2603,11 +2627,11 @@
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
@@ -2616,7 +2640,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>327</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2652,11 +2676,11 @@
       <c r="U23" s="7" t="n"/>
       <c r="V23" s="7" t="n"/>
       <c r="X23" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
@@ -2701,11 +2725,11 @@
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
@@ -2750,11 +2774,11 @@
       <c r="U25" s="7" t="n"/>
       <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z25" s="7" t="inlineStr">
@@ -2799,11 +2823,11 @@
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z26" s="4" t="inlineStr">
@@ -2848,11 +2872,11 @@
       <c r="U27" s="7" t="n"/>
       <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
@@ -2897,11 +2921,11 @@
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
@@ -2946,11 +2970,11 @@
       <c r="U29" s="7" t="n"/>
       <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
@@ -2995,11 +3019,11 @@
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
@@ -3044,20 +3068,20 @@
       <c r="U31" s="7" t="n"/>
       <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z31" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="AB31" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="Y31" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z31" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="AB31" s="7" t="n">
-        <v>51</v>
       </c>
       <c r="AC31" s="7" t="inlineStr">
         <is>
@@ -3102,20 +3126,20 @@
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC32" s="4" t="inlineStr">
         <is>
@@ -3130,7 +3154,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D11)</f>
+        <f>AVERAGE(D2:D12)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3140,7 +3164,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H11)</f>
+        <f>AVERAGE(H2:H12)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3165,16 +3189,16 @@
       <c r="U33" s="7" t="n"/>
       <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB33" s="7" t="n">
@@ -3196,20 +3220,20 @@
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3227,20 +3251,20 @@
       <c r="U35" s="7" t="n"/>
       <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z35" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3258,11 +3282,11 @@
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
@@ -3271,7 +3295,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3289,11 +3313,11 @@
       <c r="U37" s="7" t="n"/>
       <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z37" s="7" t="inlineStr">
@@ -3302,7 +3326,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3320,11 +3344,11 @@
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
@@ -3351,11 +3375,11 @@
       <c r="U39" s="7" t="n"/>
       <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z39" s="7" t="inlineStr">
@@ -3382,11 +3406,11 @@
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z40" s="4" t="inlineStr">
@@ -3413,11 +3437,11 @@
       <c r="U41" s="7" t="n"/>
       <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z41" s="7" t="inlineStr">
@@ -3444,11 +3468,11 @@
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z42" s="4" t="inlineStr">
@@ -3457,7 +3481,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3475,11 +3499,11 @@
       <c r="U43" s="7" t="n"/>
       <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z43" s="7" t="inlineStr">
@@ -3506,11 +3530,11 @@
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
@@ -3519,7 +3543,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3537,11 +3561,11 @@
       <c r="U45" s="7" t="n"/>
       <c r="V45" s="7" t="n"/>
       <c r="X45" s="7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z45" s="7" t="inlineStr">
@@ -3568,11 +3592,11 @@
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
@@ -3581,7 +3605,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3599,11 +3623,11 @@
       <c r="U47" s="7" t="n"/>
       <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z47" s="7" t="inlineStr">
@@ -3630,11 +3654,11 @@
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z48" s="4" t="inlineStr">
@@ -3643,7 +3667,7 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="AC48" s="4" t="inlineStr">
         <is>
@@ -3661,11 +3685,11 @@
       <c r="U49" s="7" t="n"/>
       <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z49" s="7" t="inlineStr">
@@ -3674,7 +3698,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -3692,11 +3716,11 @@
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
@@ -3723,11 +3747,11 @@
       <c r="U51" s="7" t="n"/>
       <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z51" s="7" t="inlineStr">
@@ -3736,7 +3760,7 @@
         </is>
       </c>
       <c r="AB51" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="7" t="inlineStr">
         <is>
@@ -3754,11 +3778,11 @@
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z52" s="4" t="inlineStr">
@@ -3767,7 +3791,7 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -3785,11 +3809,11 @@
       <c r="U53" s="7" t="n"/>
       <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z53" s="7" t="inlineStr">
@@ -3798,7 +3822,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -3820,7 +3844,7 @@
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z54" s="4" t="inlineStr">
@@ -3847,20 +3871,20 @@
       <c r="U55" s="7" t="n"/>
       <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z55" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -3878,20 +3902,20 @@
       <c r="U56" s="4" t="n"/>
       <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>198</v>
+        <v>10</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -3909,20 +3933,20 @@
       <c r="U57" s="7" t="n"/>
       <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z57" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -3940,16 +3964,16 @@
       <c r="U58" s="4" t="n"/>
       <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z58" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB58" s="4" t="n">
@@ -3971,16 +3995,16 @@
       <c r="U59" s="7" t="n"/>
       <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z59" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB59" s="7" t="n">
@@ -4002,20 +4026,20 @@
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z60" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4033,20 +4057,20 @@
       <c r="U61" s="7" t="n"/>
       <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z61" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB61" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="Y61" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z61" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB61" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4064,11 +4088,11 @@
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
       <c r="X62" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z62" s="4" t="inlineStr">
@@ -4095,11 +4119,11 @@
       <c r="U63" s="7" t="n"/>
       <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z63" s="7" t="inlineStr">
@@ -4108,7 +4132,7 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4126,11 +4150,11 @@
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z64" s="4" t="inlineStr">
@@ -4139,7 +4163,7 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4157,11 +4181,11 @@
       <c r="U65" s="7" t="n"/>
       <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z65" s="7" t="inlineStr">
@@ -4170,7 +4194,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -4188,11 +4212,11 @@
       <c r="U66" s="4" t="n"/>
       <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z66" s="4" t="inlineStr">
@@ -4219,11 +4243,11 @@
       <c r="U67" s="7" t="n"/>
       <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z67" s="7" t="inlineStr">
@@ -4250,11 +4274,11 @@
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="Y68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z68" s="4" t="inlineStr">
@@ -4263,7 +4287,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4281,11 +4305,11 @@
       <c r="U69" s="7" t="n"/>
       <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z69" s="7" t="inlineStr">
@@ -4294,7 +4318,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4316,7 +4340,7 @@
       </c>
       <c r="Y70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z70" s="4" t="inlineStr">
@@ -4325,7 +4349,7 @@
         </is>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="AC70" s="4" t="inlineStr">
         <is>
@@ -4343,11 +4367,11 @@
       <c r="U71" s="7" t="n"/>
       <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z71" s="7" t="inlineStr">
@@ -4356,7 +4380,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -4374,11 +4398,11 @@
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z72" s="4" t="inlineStr">
@@ -4387,7 +4411,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -4405,11 +4429,11 @@
       <c r="U73" s="7" t="n"/>
       <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z73" s="7" t="inlineStr">
@@ -4436,11 +4460,11 @@
       <c r="U74" s="4" t="n"/>
       <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z74" s="4" t="inlineStr">
@@ -4467,11 +4491,11 @@
       <c r="U75" s="7" t="n"/>
       <c r="V75" s="7" t="n"/>
       <c r="X75" s="7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z75" s="7" t="inlineStr">
@@ -4480,7 +4504,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -4498,20 +4522,20 @@
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z76" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -4529,20 +4553,20 @@
       <c r="U77" s="7" t="n"/>
       <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z77" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
@@ -4560,20 +4584,20 @@
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z78" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -4595,16 +4619,16 @@
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z79" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
@@ -4626,12 +4650,12 @@
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z80" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB80" s="4" t="n">
@@ -4653,16 +4677,16 @@
       <c r="U81" s="7" t="n"/>
       <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z81" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB81" s="7" t="n">
@@ -4684,20 +4708,20 @@
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>327</v>
+        <v>3</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
@@ -4715,20 +4739,20 @@
       <c r="U83" s="7" t="n"/>
       <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z83" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>3</v>
+        <v>327</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
@@ -4746,20 +4770,20 @@
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z84" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -4777,11 +4801,11 @@
       <c r="U85" s="7" t="n"/>
       <c r="V85" s="7" t="n"/>
       <c r="X85" s="7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z85" s="7" t="inlineStr">
@@ -4790,7 +4814,7 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -4808,11 +4832,11 @@
       <c r="U86" s="4" t="n"/>
       <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z86" s="4" t="inlineStr">
@@ -4821,7 +4845,7 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -4839,11 +4863,11 @@
       <c r="U87" s="7" t="n"/>
       <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z87" s="7" t="inlineStr">
@@ -4870,11 +4894,11 @@
       <c r="U88" s="4" t="n"/>
       <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z88" s="4" t="inlineStr">
@@ -4883,7 +4907,7 @@
         </is>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -4901,11 +4925,11 @@
       <c r="U89" s="7" t="n"/>
       <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z89" s="7" t="inlineStr">
@@ -4932,11 +4956,11 @@
       <c r="U90" s="4" t="n"/>
       <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z90" s="4" t="inlineStr">
@@ -4963,11 +4987,11 @@
       <c r="U91" s="7" t="n"/>
       <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z91" s="7" t="inlineStr">
@@ -4976,7 +5000,7 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -4994,20 +5018,20 @@
       <c r="U92" s="4" t="n"/>
       <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -5025,20 +5049,20 @@
       <c r="U93" s="7" t="n"/>
       <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="Y93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z93" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5056,20 +5080,20 @@
       <c r="U94" s="4" t="n"/>
       <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z94" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -5087,20 +5111,20 @@
       <c r="U95" s="7" t="n"/>
       <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="Y95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z95" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -5118,20 +5142,20 @@
       <c r="U96" s="4" t="n"/>
       <c r="V96" s="4" t="n"/>
       <c r="X96" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z96" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -5149,20 +5173,20 @@
       <c r="U97" s="7" t="n"/>
       <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z97" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -5180,16 +5204,16 @@
       <c r="U98" s="4" t="n"/>
       <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="Y98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z98" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB98" s="4" t="n">
@@ -5211,16 +5235,16 @@
       <c r="U99" s="7" t="n"/>
       <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z99" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB99" s="7" t="n">
@@ -5242,16 +5266,16 @@
       <c r="U100" s="4" t="n"/>
       <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Y100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z100" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB100" s="4" t="n">
@@ -5273,16 +5297,16 @@
       <c r="U101" s="7" t="n"/>
       <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z101" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB101" s="7" t="n">
@@ -5304,16 +5328,16 @@
       <c r="U102" s="4" t="n"/>
       <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z102" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB102" s="4" t="n">
@@ -5335,20 +5359,20 @@
       <c r="U103" s="7" t="n"/>
       <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z103" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB103" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="7" t="inlineStr">
         <is>
@@ -5366,11 +5390,11 @@
       <c r="U104" s="4" t="n"/>
       <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z104" s="4" t="inlineStr">
@@ -5379,7 +5403,7 @@
         </is>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
@@ -5397,11 +5421,11 @@
       <c r="U105" s="7" t="n"/>
       <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z105" s="7" t="inlineStr">
@@ -5428,11 +5452,11 @@
       <c r="U106" s="4" t="n"/>
       <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="Y106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z106" s="4" t="inlineStr">
@@ -5441,7 +5465,7 @@
         </is>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -5459,11 +5483,11 @@
       <c r="U107" s="7" t="n"/>
       <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="Y107" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z107" s="7" t="inlineStr">
@@ -5472,7 +5496,7 @@
         </is>
       </c>
       <c r="AB107" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -5490,11 +5514,11 @@
       <c r="U108" s="4" t="n"/>
       <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Y108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z108" s="4" t="inlineStr">
@@ -5503,7 +5527,7 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -5521,11 +5545,11 @@
       <c r="U109" s="7" t="n"/>
       <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z109" s="7" t="inlineStr">
@@ -5552,11 +5576,11 @@
       <c r="U110" s="4" t="n"/>
       <c r="V110" s="4" t="n"/>
       <c r="X110" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z110" s="4" t="inlineStr">
@@ -5565,7 +5589,7 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -5587,7 +5611,7 @@
       </c>
       <c r="Y111" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z111" s="7" t="inlineStr">
@@ -5596,7 +5620,7 @@
         </is>
       </c>
       <c r="AB111" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -5614,11 +5638,11 @@
       <c r="U112" s="4" t="n"/>
       <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="Y112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z112" s="4" t="inlineStr">
@@ -5627,7 +5651,7 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -5645,11 +5669,11 @@
       <c r="U113" s="7" t="n"/>
       <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y113" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z113" s="7" t="inlineStr">
@@ -5658,7 +5682,7 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -5676,11 +5700,11 @@
       <c r="U114" s="4" t="n"/>
       <c r="V114" s="4" t="n"/>
       <c r="X114" s="4" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z114" s="4" t="inlineStr">
@@ -5689,7 +5713,7 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -5707,11 +5731,11 @@
       <c r="U115" s="7" t="n"/>
       <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="Y115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z115" s="7" t="inlineStr">
@@ -5742,7 +5766,7 @@
       </c>
       <c r="Y116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z116" s="4" t="inlineStr">
@@ -5751,7 +5775,7 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -5769,11 +5793,11 @@
       <c r="U117" s="7" t="n"/>
       <c r="V117" s="7" t="n"/>
       <c r="X117" s="7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z117" s="7" t="inlineStr">
@@ -5800,11 +5824,11 @@
       <c r="U118" s="4" t="n"/>
       <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z118" s="4" t="inlineStr">
@@ -5831,11 +5855,11 @@
       <c r="U119" s="7" t="n"/>
       <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z119" s="7" t="inlineStr">
@@ -5844,7 +5868,7 @@
         </is>
       </c>
       <c r="AB119" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -5862,20 +5886,20 @@
       <c r="U120" s="4" t="n"/>
       <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y120" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z120" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB120" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y120" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="Z120" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="AB120" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC120" s="4" t="inlineStr">
         <is>
@@ -5893,16 +5917,16 @@
       <c r="U121" s="7" t="n"/>
       <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y121" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z121" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB121" s="7" t="n">
@@ -5924,16 +5948,16 @@
       <c r="U122" s="4" t="n"/>
       <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="Y122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z122" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB122" s="4" t="n">
@@ -5959,12 +5983,12 @@
       </c>
       <c r="Y123" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z123" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB123" s="7" t="n">
@@ -5986,16 +6010,16 @@
       <c r="U124" s="4" t="n"/>
       <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Y124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z124" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB124" s="4" t="n">
@@ -6017,16 +6041,16 @@
       <c r="U125" s="7" t="n"/>
       <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z125" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB125" s="7" t="n">
@@ -6048,16 +6072,16 @@
       <c r="U126" s="4" t="n"/>
       <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z126" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB126" s="4" t="n">
@@ -6079,16 +6103,16 @@
       <c r="U127" s="7" t="n"/>
       <c r="V127" s="7" t="n"/>
       <c r="X127" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y127" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z127" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB127" s="7" t="n">
@@ -6110,20 +6134,20 @@
       <c r="U128" s="4" t="n"/>
       <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z128" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6141,20 +6165,20 @@
       <c r="U129" s="7" t="n"/>
       <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y129" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z129" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6172,20 +6196,20 @@
       <c r="U130" s="4" t="n"/>
       <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z130" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -6203,20 +6227,20 @@
       <c r="U131" s="7" t="n"/>
       <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y131" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z131" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB131" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -6234,20 +6258,20 @@
       <c r="U132" s="4" t="n"/>
       <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="Y132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z132" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -6265,20 +6289,20 @@
       <c r="U133" s="7" t="n"/>
       <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="Y133" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z133" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6296,16 +6320,16 @@
       <c r="U134" s="4" t="n"/>
       <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z134" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB134" s="4" t="n">
@@ -6327,20 +6351,20 @@
       <c r="U135" s="7" t="n"/>
       <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y135" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -6358,20 +6382,20 @@
       <c r="U136" s="4" t="n"/>
       <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -6393,16 +6417,16 @@
       </c>
       <c r="Y137" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z137" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB137" s="7" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -6420,20 +6444,20 @@
       <c r="U138" s="4" t="n"/>
       <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -6451,16 +6475,16 @@
       <c r="U139" s="7" t="n"/>
       <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y139" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB139" s="7" t="n">
@@ -6482,20 +6506,20 @@
       <c r="U140" s="4" t="n"/>
       <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -6513,16 +6537,16 @@
       <c r="U141" s="7" t="n"/>
       <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y141" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB141" s="7" t="n">
@@ -6544,20 +6568,20 @@
       <c r="U142" s="4" t="n"/>
       <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z142" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -6574,11 +6598,21 @@
       <c r="T143" s="7" t="n"/>
       <c r="U143" s="7" t="n"/>
       <c r="V143" s="7" t="n"/>
-      <c r="X143" s="7" t="n"/>
-      <c r="Y143" s="7" t="n"/>
-      <c r="Z143" s="7" t="n"/>
+      <c r="X143" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y143" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z143" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB143" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -6595,9 +6629,19 @@
       <c r="T144" s="4" t="n"/>
       <c r="U144" s="4" t="n"/>
       <c r="V144" s="4" t="n"/>
-      <c r="X144" s="4" t="n"/>
-      <c r="Y144" s="4" t="n"/>
-      <c r="Z144" s="4" t="n"/>
+      <c r="X144" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z144" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB144" s="4" t="n">
         <v>1</v>
       </c>
@@ -6616,11 +6660,21 @@
       <c r="T145" s="7" t="n"/>
       <c r="U145" s="7" t="n"/>
       <c r="V145" s="7" t="n"/>
-      <c r="X145" s="7" t="n"/>
-      <c r="Y145" s="7" t="n"/>
-      <c r="Z145" s="7" t="n"/>
+      <c r="X145" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z145" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -6637,11 +6691,21 @@
       <c r="T146" s="4" t="n"/>
       <c r="U146" s="4" t="n"/>
       <c r="V146" s="4" t="n"/>
-      <c r="X146" s="4" t="n"/>
-      <c r="Y146" s="4" t="n"/>
-      <c r="Z146" s="4" t="n"/>
+      <c r="X146" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y146" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z146" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -6658,9 +6722,19 @@
       <c r="T147" s="7" t="n"/>
       <c r="U147" s="7" t="n"/>
       <c r="V147" s="7" t="n"/>
-      <c r="X147" s="7" t="n"/>
-      <c r="Y147" s="7" t="n"/>
-      <c r="Z147" s="7" t="n"/>
+      <c r="X147" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y147" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z147" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB147" s="7" t="n">
         <v>6</v>
       </c>
@@ -6679,9 +6753,19 @@
       <c r="T148" s="4" t="n"/>
       <c r="U148" s="4" t="n"/>
       <c r="V148" s="4" t="n"/>
-      <c r="X148" s="4" t="n"/>
-      <c r="Y148" s="4" t="n"/>
-      <c r="Z148" s="4" t="n"/>
+      <c r="X148" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z148" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB148" s="4" t="n">
         <v>35</v>
       </c>
@@ -6700,11 +6784,21 @@
       <c r="T149" s="7" t="n"/>
       <c r="U149" s="7" t="n"/>
       <c r="V149" s="7" t="n"/>
-      <c r="X149" s="7" t="n"/>
-      <c r="Y149" s="7" t="n"/>
-      <c r="Z149" s="7" t="n"/>
+      <c r="X149" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y149" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z149" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB149" s="7" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="AC149" s="7" t="inlineStr">
         <is>
@@ -6721,11 +6815,21 @@
       <c r="T150" s="4" t="n"/>
       <c r="U150" s="4" t="n"/>
       <c r="V150" s="4" t="n"/>
-      <c r="X150" s="4" t="n"/>
-      <c r="Y150" s="4" t="n"/>
-      <c r="Z150" s="4" t="n"/>
+      <c r="X150" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z150" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB150" s="4" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -6742,11 +6846,21 @@
       <c r="T151" s="7" t="n"/>
       <c r="U151" s="7" t="n"/>
       <c r="V151" s="7" t="n"/>
-      <c r="X151" s="7" t="n"/>
-      <c r="Y151" s="7" t="n"/>
-      <c r="Z151" s="7" t="n"/>
+      <c r="X151" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y151" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z151" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB151" s="7" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AC151" s="7" t="inlineStr">
         <is>
@@ -6763,11 +6877,21 @@
       <c r="T152" s="4" t="n"/>
       <c r="U152" s="4" t="n"/>
       <c r="V152" s="4" t="n"/>
-      <c r="X152" s="4" t="n"/>
-      <c r="Y152" s="4" t="n"/>
-      <c r="Z152" s="4" t="n"/>
+      <c r="X152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z152" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB152" s="4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
@@ -6784,11 +6908,21 @@
       <c r="T153" s="7" t="n"/>
       <c r="U153" s="7" t="n"/>
       <c r="V153" s="7" t="n"/>
-      <c r="X153" s="7" t="n"/>
-      <c r="Y153" s="7" t="n"/>
-      <c r="Z153" s="7" t="n"/>
+      <c r="X153" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y153" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB153" s="7" t="n">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -6805,11 +6939,21 @@
       <c r="T154" s="4" t="n"/>
       <c r="U154" s="4" t="n"/>
       <c r="V154" s="4" t="n"/>
-      <c r="X154" s="4" t="n"/>
-      <c r="Y154" s="4" t="n"/>
-      <c r="Z154" s="4" t="n"/>
+      <c r="X154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z154" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB154" s="4" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -6826,9 +6970,19 @@
       <c r="T155" s="7" t="n"/>
       <c r="U155" s="7" t="n"/>
       <c r="V155" s="7" t="n"/>
-      <c r="X155" s="7" t="n"/>
-      <c r="Y155" s="7" t="n"/>
-      <c r="Z155" s="7" t="n"/>
+      <c r="X155" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y155" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z155" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB155" s="7" t="n">
         <v>5</v>
       </c>
@@ -6847,11 +7001,21 @@
       <c r="T156" s="4" t="n"/>
       <c r="U156" s="4" t="n"/>
       <c r="V156" s="4" t="n"/>
-      <c r="X156" s="4" t="n"/>
-      <c r="Y156" s="4" t="n"/>
-      <c r="Z156" s="4" t="n"/>
+      <c r="X156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z156" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB156" s="4" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="AC156" s="4" t="inlineStr">
         <is>
@@ -6868,11 +7032,21 @@
       <c r="T157" s="7" t="n"/>
       <c r="U157" s="7" t="n"/>
       <c r="V157" s="7" t="n"/>
-      <c r="X157" s="7" t="n"/>
-      <c r="Y157" s="7" t="n"/>
-      <c r="Z157" s="7" t="n"/>
+      <c r="X157" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y157" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z157" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB157" s="7" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="AC157" s="7" t="inlineStr">
         <is>
@@ -6889,9 +7063,19 @@
       <c r="T158" s="4" t="n"/>
       <c r="U158" s="4" t="n"/>
       <c r="V158" s="4" t="n"/>
-      <c r="X158" s="4" t="n"/>
-      <c r="Y158" s="4" t="n"/>
-      <c r="Z158" s="4" t="n"/>
+      <c r="X158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z158" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB158" s="4" t="n">
         <v>7</v>
       </c>
@@ -6910,11 +7094,21 @@
       <c r="T159" s="7" t="n"/>
       <c r="U159" s="7" t="n"/>
       <c r="V159" s="7" t="n"/>
-      <c r="X159" s="7" t="n"/>
-      <c r="Y159" s="7" t="n"/>
-      <c r="Z159" s="7" t="n"/>
+      <c r="X159" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y159" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z159" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB159" s="7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="AC159" s="7" t="inlineStr">
         <is>
@@ -6931,11 +7125,21 @@
       <c r="T160" s="4" t="n"/>
       <c r="U160" s="4" t="n"/>
       <c r="V160" s="4" t="n"/>
-      <c r="X160" s="4" t="n"/>
-      <c r="Y160" s="4" t="n"/>
-      <c r="Z160" s="4" t="n"/>
+      <c r="X160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z160" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB160" s="4" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
@@ -6956,7 +7160,7 @@
       <c r="Y161" s="7" t="n"/>
       <c r="Z161" s="7" t="n"/>
       <c r="AB161" s="7" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -6977,7 +7181,7 @@
       <c r="Y162" s="4" t="n"/>
       <c r="Z162" s="4" t="n"/>
       <c r="AB162" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -6998,7 +7202,7 @@
       <c r="Y163" s="7" t="n"/>
       <c r="Z163" s="7" t="n"/>
       <c r="AB163" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -7019,7 +7223,7 @@
       <c r="Y164" s="4" t="n"/>
       <c r="Z164" s="4" t="n"/>
       <c r="AB164" s="4" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
@@ -7040,7 +7244,7 @@
       <c r="Y165" s="7" t="n"/>
       <c r="Z165" s="7" t="n"/>
       <c r="AB165" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
@@ -7061,7 +7265,7 @@
       <c r="Y166" s="4" t="n"/>
       <c r="Z166" s="4" t="n"/>
       <c r="AB166" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
@@ -7103,7 +7307,7 @@
       <c r="Y168" s="4" t="n"/>
       <c r="Z168" s="4" t="n"/>
       <c r="AB168" s="4" t="n">
-        <v>55</v>
+        <v>291</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7328,7 @@
       <c r="Y169" s="7" t="n"/>
       <c r="Z169" s="7" t="n"/>
       <c r="AB169" s="7" t="n">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="AC169" s="7" t="inlineStr">
         <is>
@@ -7166,7 +7370,7 @@
       <c r="Y171" s="7" t="n"/>
       <c r="Z171" s="7" t="n"/>
       <c r="AB171" s="7" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AC171" s="7" t="inlineStr">
         <is>
@@ -7187,7 +7391,7 @@
       <c r="Y172" s="4" t="n"/>
       <c r="Z172" s="4" t="n"/>
       <c r="AB172" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
@@ -7208,7 +7412,7 @@
       <c r="Y173" s="7" t="n"/>
       <c r="Z173" s="7" t="n"/>
       <c r="AB173" s="7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AC173" s="7" t="inlineStr">
         <is>
@@ -7229,7 +7433,7 @@
       <c r="Y174" s="4" t="n"/>
       <c r="Z174" s="4" t="n"/>
       <c r="AB174" s="4" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
@@ -7397,7 +7601,7 @@
       <c r="Y182" s="4" t="n"/>
       <c r="Z182" s="4" t="n"/>
       <c r="AB182" s="4" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="AC182" s="4" t="inlineStr">
         <is>
@@ -7418,7 +7622,7 @@
       <c r="Y183" s="7" t="n"/>
       <c r="Z183" s="7" t="n"/>
       <c r="AB183" s="7" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="AC183" s="7" t="inlineStr">
         <is>
@@ -7439,7 +7643,7 @@
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
       <c r="AB184" s="4" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
@@ -7460,7 +7664,7 @@
       <c r="Y185" s="7" t="n"/>
       <c r="Z185" s="7" t="n"/>
       <c r="AB185" s="7" t="n">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="AC185" s="7" t="inlineStr">
         <is>
@@ -7481,7 +7685,7 @@
       <c r="Y186" s="4" t="n"/>
       <c r="Z186" s="4" t="n"/>
       <c r="AB186" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AC186" s="4" t="inlineStr">
         <is>
@@ -7544,7 +7748,7 @@
       <c r="Y189" s="7" t="n"/>
       <c r="Z189" s="7" t="n"/>
       <c r="AB189" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC189" s="7" t="inlineStr">
         <is>
@@ -7565,7 +7769,7 @@
       <c r="Y190" s="4" t="n"/>
       <c r="Z190" s="4" t="n"/>
       <c r="AB190" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC190" s="4" t="inlineStr">
         <is>
@@ -7649,7 +7853,7 @@
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n"/>
       <c r="AB194" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AC194" s="4" t="inlineStr">
         <is>
@@ -7670,7 +7874,7 @@
       <c r="Y195" s="7" t="n"/>
       <c r="Z195" s="7" t="n"/>
       <c r="AB195" s="7" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AC195" s="7" t="inlineStr">
         <is>
@@ -7754,7 +7958,7 @@
       <c r="Y199" s="7" t="n"/>
       <c r="Z199" s="7" t="n"/>
       <c r="AB199" s="7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AC199" s="7" t="inlineStr">
         <is>
@@ -7775,7 +7979,7 @@
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n"/>
       <c r="AB200" s="4" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AC200" s="4" t="inlineStr">
         <is>
@@ -7817,7 +8021,7 @@
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
       <c r="AB202" s="4" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="AC202" s="4" t="inlineStr">
         <is>
@@ -7838,7 +8042,7 @@
       <c r="Y203" s="7" t="n"/>
       <c r="Z203" s="7" t="n"/>
       <c r="AB203" s="7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AC203" s="7" t="inlineStr">
         <is>
@@ -7859,7 +8063,7 @@
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
       <c r="AB204" s="4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AC204" s="4" t="inlineStr">
         <is>
@@ -7880,7 +8084,7 @@
       <c r="Y205" s="7" t="n"/>
       <c r="Z205" s="7" t="n"/>
       <c r="AB205" s="7" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="AC205" s="7" t="inlineStr">
         <is>
@@ -7901,7 +8105,7 @@
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
       <c r="AB206" s="4" t="n">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="AC206" s="4" t="inlineStr">
         <is>
@@ -7922,7 +8126,7 @@
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
       <c r="AB207" s="7" t="n">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="AC207" s="7" t="inlineStr">
         <is>
@@ -7943,7 +8147,7 @@
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
       <c r="AB208" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC208" s="4" t="inlineStr">
         <is>
@@ -7964,7 +8168,7 @@
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
       <c r="AB209" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC209" s="7" t="inlineStr">
         <is>
@@ -8035,6 +8239,531 @@
         </is>
       </c>
       <c r="AD212" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="T213" s="7" t="n"/>
+      <c r="U213" s="7" t="n"/>
+      <c r="V213" s="7" t="n"/>
+      <c r="X213" s="7" t="n"/>
+      <c r="Y213" s="7" t="n"/>
+      <c r="Z213" s="7" t="n"/>
+      <c r="AB213" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC213" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD213" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="T214" s="4" t="n"/>
+      <c r="U214" s="4" t="n"/>
+      <c r="V214" s="4" t="n"/>
+      <c r="X214" s="4" t="n"/>
+      <c r="Y214" s="4" t="n"/>
+      <c r="Z214" s="4" t="n"/>
+      <c r="AB214" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="AC214" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD214" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="T215" s="7" t="n"/>
+      <c r="U215" s="7" t="n"/>
+      <c r="V215" s="7" t="n"/>
+      <c r="X215" s="7" t="n"/>
+      <c r="Y215" s="7" t="n"/>
+      <c r="Z215" s="7" t="n"/>
+      <c r="AB215" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC215" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD215" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="T216" s="4" t="n"/>
+      <c r="U216" s="4" t="n"/>
+      <c r="V216" s="4" t="n"/>
+      <c r="X216" s="4" t="n"/>
+      <c r="Y216" s="4" t="n"/>
+      <c r="Z216" s="4" t="n"/>
+      <c r="AB216" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD216" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="T217" s="7" t="n"/>
+      <c r="U217" s="7" t="n"/>
+      <c r="V217" s="7" t="n"/>
+      <c r="X217" s="7" t="n"/>
+      <c r="Y217" s="7" t="n"/>
+      <c r="Z217" s="7" t="n"/>
+      <c r="AB217" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC217" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD217" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="T218" s="4" t="n"/>
+      <c r="U218" s="4" t="n"/>
+      <c r="V218" s="4" t="n"/>
+      <c r="X218" s="4" t="n"/>
+      <c r="Y218" s="4" t="n"/>
+      <c r="Z218" s="4" t="n"/>
+      <c r="AB218" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD218" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="T219" s="7" t="n"/>
+      <c r="U219" s="7" t="n"/>
+      <c r="V219" s="7" t="n"/>
+      <c r="X219" s="7" t="n"/>
+      <c r="Y219" s="7" t="n"/>
+      <c r="Z219" s="7" t="n"/>
+      <c r="AB219" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC219" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD219" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="T220" s="4" t="n"/>
+      <c r="U220" s="4" t="n"/>
+      <c r="V220" s="4" t="n"/>
+      <c r="X220" s="4" t="n"/>
+      <c r="Y220" s="4" t="n"/>
+      <c r="Z220" s="4" t="n"/>
+      <c r="AB220" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD220" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="T221" s="7" t="n"/>
+      <c r="U221" s="7" t="n"/>
+      <c r="V221" s="7" t="n"/>
+      <c r="X221" s="7" t="n"/>
+      <c r="Y221" s="7" t="n"/>
+      <c r="Z221" s="7" t="n"/>
+      <c r="AB221" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC221" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD221" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="T222" s="4" t="n"/>
+      <c r="U222" s="4" t="n"/>
+      <c r="V222" s="4" t="n"/>
+      <c r="X222" s="4" t="n"/>
+      <c r="Y222" s="4" t="n"/>
+      <c r="Z222" s="4" t="n"/>
+      <c r="AB222" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC222" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD222" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="T223" s="7" t="n"/>
+      <c r="U223" s="7" t="n"/>
+      <c r="V223" s="7" t="n"/>
+      <c r="X223" s="7" t="n"/>
+      <c r="Y223" s="7" t="n"/>
+      <c r="Z223" s="7" t="n"/>
+      <c r="AB223" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC223" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD223" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="T224" s="4" t="n"/>
+      <c r="U224" s="4" t="n"/>
+      <c r="V224" s="4" t="n"/>
+      <c r="X224" s="4" t="n"/>
+      <c r="Y224" s="4" t="n"/>
+      <c r="Z224" s="4" t="n"/>
+      <c r="AB224" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD224" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="T225" s="7" t="n"/>
+      <c r="U225" s="7" t="n"/>
+      <c r="V225" s="7" t="n"/>
+      <c r="X225" s="7" t="n"/>
+      <c r="Y225" s="7" t="n"/>
+      <c r="Z225" s="7" t="n"/>
+      <c r="AB225" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC225" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD225" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="T226" s="4" t="n"/>
+      <c r="U226" s="4" t="n"/>
+      <c r="V226" s="4" t="n"/>
+      <c r="X226" s="4" t="n"/>
+      <c r="Y226" s="4" t="n"/>
+      <c r="Z226" s="4" t="n"/>
+      <c r="AB226" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC226" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD226" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="T227" s="7" t="n"/>
+      <c r="U227" s="7" t="n"/>
+      <c r="V227" s="7" t="n"/>
+      <c r="X227" s="7" t="n"/>
+      <c r="Y227" s="7" t="n"/>
+      <c r="Z227" s="7" t="n"/>
+      <c r="AB227" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC227" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD227" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="T228" s="4" t="n"/>
+      <c r="U228" s="4" t="n"/>
+      <c r="V228" s="4" t="n"/>
+      <c r="X228" s="4" t="n"/>
+      <c r="Y228" s="4" t="n"/>
+      <c r="Z228" s="4" t="n"/>
+      <c r="AB228" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD228" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="T229" s="7" t="n"/>
+      <c r="U229" s="7" t="n"/>
+      <c r="V229" s="7" t="n"/>
+      <c r="X229" s="7" t="n"/>
+      <c r="Y229" s="7" t="n"/>
+      <c r="Z229" s="7" t="n"/>
+      <c r="AB229" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC229" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD229" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="T230" s="4" t="n"/>
+      <c r="U230" s="4" t="n"/>
+      <c r="V230" s="4" t="n"/>
+      <c r="X230" s="4" t="n"/>
+      <c r="Y230" s="4" t="n"/>
+      <c r="Z230" s="4" t="n"/>
+      <c r="AB230" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC230" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD230" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="T231" s="7" t="n"/>
+      <c r="U231" s="7" t="n"/>
+      <c r="V231" s="7" t="n"/>
+      <c r="X231" s="7" t="n"/>
+      <c r="Y231" s="7" t="n"/>
+      <c r="Z231" s="7" t="n"/>
+      <c r="AB231" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="AC231" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD231" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="T232" s="4" t="n"/>
+      <c r="U232" s="4" t="n"/>
+      <c r="V232" s="4" t="n"/>
+      <c r="X232" s="4" t="n"/>
+      <c r="Y232" s="4" t="n"/>
+      <c r="Z232" s="4" t="n"/>
+      <c r="AB232" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD232" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="T233" s="7" t="n"/>
+      <c r="U233" s="7" t="n"/>
+      <c r="V233" s="7" t="n"/>
+      <c r="X233" s="7" t="n"/>
+      <c r="Y233" s="7" t="n"/>
+      <c r="Z233" s="7" t="n"/>
+      <c r="AB233" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC233" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD233" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="T234" s="4" t="n"/>
+      <c r="U234" s="4" t="n"/>
+      <c r="V234" s="4" t="n"/>
+      <c r="X234" s="4" t="n"/>
+      <c r="Y234" s="4" t="n"/>
+      <c r="Z234" s="4" t="n"/>
+      <c r="AB234" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC234" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD234" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="T235" s="7" t="n"/>
+      <c r="U235" s="7" t="n"/>
+      <c r="V235" s="7" t="n"/>
+      <c r="X235" s="7" t="n"/>
+      <c r="Y235" s="7" t="n"/>
+      <c r="Z235" s="7" t="n"/>
+      <c r="AB235" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC235" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD235" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="T236" s="4" t="n"/>
+      <c r="U236" s="4" t="n"/>
+      <c r="V236" s="4" t="n"/>
+      <c r="X236" s="4" t="n"/>
+      <c r="Y236" s="4" t="n"/>
+      <c r="Z236" s="4" t="n"/>
+      <c r="AB236" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD236" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="T237" s="7" t="n"/>
+      <c r="U237" s="7" t="n"/>
+      <c r="V237" s="7" t="n"/>
+      <c r="X237" s="7" t="n"/>
+      <c r="Y237" s="7" t="n"/>
+      <c r="Z237" s="7" t="n"/>
+      <c r="AB237" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC237" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD237" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -8056,7 +8785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD160"/>
+  <dimension ref="A1:AD176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8231,7 +8960,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -8304,7 +9033,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -8502,7 +9231,7 @@
         <v/>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -8575,7 +9304,7 @@
         <v/>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -8661,7 +9390,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -8726,7 +9455,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -8885,6 +9614,38 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="D12">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C12)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C12)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>ROUND(MAX(0,MIN(100,(1-E12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>MIN(1,(G12-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C12)</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>MAX(0,(L12-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>$B$2+H12+M12</f>
+        <v/>
+      </c>
       <c r="X12" t="n">
         <v>52</v>
       </c>
@@ -8899,7 +9660,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -8952,20 +9713,20 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -8985,11 +9746,11 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -9018,11 +9779,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -9055,7 +9816,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -9088,7 +9849,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -9117,11 +9878,11 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -9150,11 +9911,11 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -9183,11 +9944,11 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -9216,11 +9977,11 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -9249,20 +10010,20 @@
         </is>
       </c>
       <c r="X23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
         <v>2</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -9282,20 +10043,20 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -9315,11 +10076,11 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -9348,11 +10109,11 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -9381,11 +10142,11 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -9414,11 +10175,11 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -9427,7 +10188,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -9447,11 +10208,11 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -9460,7 +10221,7 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -9480,11 +10241,11 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -9513,11 +10274,11 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -9561,11 +10322,11 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -9589,7 +10350,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D11)</f>
+        <f>AVERAGE(D2:D12)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -9597,7 +10358,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H11)</f>
+        <f>AVERAGE(H2:H12)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -9617,11 +10378,11 @@
         <v/>
       </c>
       <c r="X33" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -9645,11 +10406,11 @@
     </row>
     <row r="34">
       <c r="X34" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -9673,11 +10434,11 @@
     </row>
     <row r="35">
       <c r="X35" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -9701,11 +10462,11 @@
     </row>
     <row r="36">
       <c r="X36" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -9733,12 +10494,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -9757,16 +10518,16 @@
     </row>
     <row r="38">
       <c r="X38" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -9785,20 +10546,20 @@
     </row>
     <row r="39">
       <c r="X39" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -9813,20 +10574,20 @@
     </row>
     <row r="40">
       <c r="X40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -9841,11 +10602,11 @@
     </row>
     <row r="41">
       <c r="X41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -9854,7 +10615,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -9869,20 +10630,20 @@
     </row>
     <row r="42">
       <c r="X42" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
         <v>1</v>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB42" t="n">
-        <v>2</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -9897,11 +10658,11 @@
     </row>
     <row r="43">
       <c r="X43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -9910,7 +10671,7 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -9925,11 +10686,11 @@
     </row>
     <row r="44">
       <c r="X44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -9938,7 +10699,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -9953,20 +10714,20 @@
     </row>
     <row r="45">
       <c r="X45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
         <v>1</v>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB45" t="n">
-        <v>7</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -9985,7 +10746,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -9994,7 +10755,7 @@
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -10009,11 +10770,11 @@
     </row>
     <row r="47">
       <c r="X47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -10022,7 +10783,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -10037,11 +10798,11 @@
     </row>
     <row r="48">
       <c r="X48" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -10069,7 +10830,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -10093,11 +10854,11 @@
     </row>
     <row r="50">
       <c r="X50" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -10106,7 +10867,7 @@
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -10121,20 +10882,20 @@
     </row>
     <row r="51">
       <c r="X51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -10149,16 +10910,16 @@
     </row>
     <row r="52">
       <c r="X52" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -10177,16 +10938,16 @@
     </row>
     <row r="53">
       <c r="X53" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -10205,16 +10966,16 @@
     </row>
     <row r="54">
       <c r="X54" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -10233,16 +10994,16 @@
     </row>
     <row r="55">
       <c r="X55" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -10261,11 +11022,11 @@
     </row>
     <row r="56">
       <c r="X56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -10289,11 +11050,11 @@
     </row>
     <row r="57">
       <c r="X57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -10317,11 +11078,11 @@
     </row>
     <row r="58">
       <c r="X58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -10345,11 +11106,11 @@
     </row>
     <row r="59">
       <c r="X59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -10373,11 +11134,11 @@
     </row>
     <row r="60">
       <c r="X60" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -10401,11 +11162,11 @@
     </row>
     <row r="61">
       <c r="X61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -10414,7 +11175,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -10429,11 +11190,11 @@
     </row>
     <row r="62">
       <c r="X62" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -10442,7 +11203,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -10457,20 +11218,20 @@
     </row>
     <row r="63">
       <c r="X63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -10485,16 +11246,16 @@
     </row>
     <row r="64">
       <c r="X64" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB64" t="n">
@@ -10513,16 +11274,16 @@
     </row>
     <row r="65">
       <c r="X65" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB65" t="n">
@@ -10541,16 +11302,16 @@
     </row>
     <row r="66">
       <c r="X66" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB66" t="n">
@@ -10569,16 +11330,16 @@
     </row>
     <row r="67">
       <c r="X67" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB67" t="n">
@@ -10597,16 +11358,16 @@
     </row>
     <row r="68">
       <c r="X68" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB68" t="n">
@@ -10625,16 +11386,16 @@
     </row>
     <row r="69">
       <c r="X69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB69" t="n">
@@ -10653,11 +11414,11 @@
     </row>
     <row r="70">
       <c r="X70" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -10681,11 +11442,11 @@
     </row>
     <row r="71">
       <c r="X71" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -10713,7 +11474,7 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -10737,11 +11498,11 @@
     </row>
     <row r="73">
       <c r="X73" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -10750,7 +11511,7 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -10765,11 +11526,11 @@
     </row>
     <row r="74">
       <c r="X74" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -10778,7 +11539,7 @@
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -10793,11 +11554,11 @@
     </row>
     <row r="75">
       <c r="X75" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -10806,7 +11567,7 @@
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -10821,11 +11582,11 @@
     </row>
     <row r="76">
       <c r="X76" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -10849,11 +11610,11 @@
     </row>
     <row r="77">
       <c r="X77" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -10877,11 +11638,11 @@
     </row>
     <row r="78">
       <c r="X78" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -10905,11 +11666,11 @@
     </row>
     <row r="79">
       <c r="X79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
@@ -10918,7 +11679,7 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -10933,11 +11694,11 @@
     </row>
     <row r="80">
       <c r="X80" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
@@ -10965,7 +11726,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
@@ -10974,7 +11735,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -10989,11 +11750,11 @@
     </row>
     <row r="82">
       <c r="X82" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
@@ -11017,16 +11778,16 @@
     </row>
     <row r="83">
       <c r="X83" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB83" t="n">
@@ -11045,16 +11806,16 @@
     </row>
     <row r="84">
       <c r="X84" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB84" t="n">
@@ -11077,16 +11838,16 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB85" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
@@ -11101,20 +11862,20 @@
     </row>
     <row r="86">
       <c r="X86" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB86" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -11129,16 +11890,16 @@
     </row>
     <row r="87">
       <c r="X87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB87" t="n">
@@ -11157,16 +11918,16 @@
     </row>
     <row r="88">
       <c r="X88" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB88" t="n">
@@ -11185,16 +11946,16 @@
     </row>
     <row r="89">
       <c r="X89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB89" t="n">
@@ -11213,16 +11974,16 @@
     </row>
     <row r="90">
       <c r="X90" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB90" t="n">
@@ -11241,16 +12002,16 @@
     </row>
     <row r="91">
       <c r="X91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB91" t="n">
@@ -11269,16 +12030,16 @@
     </row>
     <row r="92">
       <c r="X92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB92" t="n">
@@ -11297,20 +12058,20 @@
     </row>
     <row r="93">
       <c r="X93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -11325,11 +12086,11 @@
     </row>
     <row r="94">
       <c r="X94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
@@ -11338,7 +12099,7 @@
         </is>
       </c>
       <c r="AB94" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -11353,11 +12114,11 @@
     </row>
     <row r="95">
       <c r="X95" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
@@ -11390,11 +12151,11 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB96" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -11418,11 +12179,11 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -11437,16 +12198,16 @@
     </row>
     <row r="98">
       <c r="X98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB98" t="n">
@@ -11469,12 +12230,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB99" t="n">
@@ -11493,16 +12254,16 @@
     </row>
     <row r="100">
       <c r="X100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB100" t="n">
@@ -11520,6 +12281,19 @@
       </c>
     </row>
     <row r="101">
+      <c r="X101" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB101" t="n">
         <v>1</v>
       </c>
@@ -11535,36 +12309,75 @@
       </c>
     </row>
     <row r="102">
+      <c r="X102" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="X103" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
         <v>7</v>
       </c>
-      <c r="AC102" t="inlineStr">
+      <c r="AC103" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="AD102" t="inlineStr">
+      <c r="AD103" t="inlineStr">
         <is>
           <t>com.logistics.rider.efood</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="AB103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
+    <row r="104">
+      <c r="X104" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
         <is>
           <t>com.logistics.rider.efood</t>
         </is>
       </c>
-    </row>
-    <row r="104">
       <c r="AB104" t="n">
         <v>2</v>
       </c>
@@ -11580,6 +12393,19 @@
       </c>
     </row>
     <row r="105">
+      <c r="X105" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB105" t="n">
         <v>4</v>
       </c>
@@ -11595,6 +12421,19 @@
       </c>
     </row>
     <row r="106">
+      <c r="X106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB106" t="n">
         <v>196</v>
       </c>
@@ -11610,6 +12449,19 @@
       </c>
     </row>
     <row r="107">
+      <c r="X107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB107" t="n">
         <v>15</v>
       </c>
@@ -11625,6 +12477,19 @@
       </c>
     </row>
     <row r="108">
+      <c r="X108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB108" t="n">
         <v>1</v>
       </c>
@@ -11640,6 +12505,19 @@
       </c>
     </row>
     <row r="109">
+      <c r="X109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB109" t="n">
         <v>101</v>
       </c>
@@ -11655,23 +12533,49 @@
       </c>
     </row>
     <row r="110">
+      <c r="X110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB111" t="n">
         <v>2</v>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="AB111" t="n">
-        <v>39</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
@@ -11686,7 +12590,7 @@
     </row>
     <row r="112">
       <c r="AB112" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
@@ -11701,7 +12605,7 @@
     </row>
     <row r="113">
       <c r="AB113" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
@@ -11716,7 +12620,7 @@
     </row>
     <row r="114">
       <c r="AB114" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
@@ -11731,7 +12635,7 @@
     </row>
     <row r="115">
       <c r="AB115" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -11746,7 +12650,7 @@
     </row>
     <row r="116">
       <c r="AB116" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
@@ -11761,7 +12665,7 @@
     </row>
     <row r="117">
       <c r="AB117" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -11941,7 +12845,7 @@
     </row>
     <row r="129">
       <c r="AB129" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -11956,7 +12860,7 @@
     </row>
     <row r="130">
       <c r="AB130" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
@@ -11971,7 +12875,7 @@
     </row>
     <row r="131">
       <c r="AB131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
@@ -12016,7 +12920,7 @@
     </row>
     <row r="134">
       <c r="AB134" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
@@ -12031,7 +12935,7 @@
     </row>
     <row r="135">
       <c r="AB135" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
@@ -12076,7 +12980,7 @@
     </row>
     <row r="138">
       <c r="AB138" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
@@ -12091,7 +12995,7 @@
     </row>
     <row r="139">
       <c r="AB139" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
@@ -12106,7 +13010,7 @@
     </row>
     <row r="140">
       <c r="AB140" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
@@ -12121,7 +13025,7 @@
     </row>
     <row r="141">
       <c r="AB141" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
@@ -12136,7 +13040,7 @@
     </row>
     <row r="142">
       <c r="AB142" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
@@ -12151,7 +13055,7 @@
     </row>
     <row r="143">
       <c r="AB143" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
@@ -12286,7 +13190,7 @@
     </row>
     <row r="152">
       <c r="AB152" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
@@ -12301,7 +13205,7 @@
     </row>
     <row r="153">
       <c r="AB153" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
@@ -12414,6 +13318,246 @@
         </is>
       </c>
       <c r="AD160" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="AB161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="AB162" t="n">
+        <v>170</v>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="AB163" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="AB164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="AB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="AB166" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="AB167" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="AB168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="AB169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="AB170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="AB171" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="AB172" t="n">
+        <v>97</v>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="AB173" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="AB174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="AB175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="AB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -12958,7 +14102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:AD37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13404,16 +14548,16 @@
         <v/>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -13481,7 +14625,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -13550,11 +14694,11 @@
         <v/>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -13619,12 +14763,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -13690,16 +14834,16 @@
         <v/>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -13755,11 +14899,11 @@
         <v/>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -13787,12 +14931,44 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="D12">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C12)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C12)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>ROUND(MAX(0,MIN(100,(1-E12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>MIN(1,(G12-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C12)</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K12/IF(D12&gt;0,D12,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>MAX(0,(L12-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>$B$2+H12+M12</f>
+        <v/>
+      </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -13821,16 +14997,16 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -13854,16 +15030,16 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -13887,16 +15063,16 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -13924,12 +15100,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -13957,12 +15133,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -13986,16 +15162,16 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -14023,12 +15199,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -14052,7 +15228,7 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -14061,7 +15237,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -14085,7 +15261,7 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -14094,7 +15270,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -14118,7 +15294,7 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -14127,7 +15303,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -14151,7 +15327,7 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -14160,7 +15336,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -14184,16 +15360,16 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -14217,7 +15393,7 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -14226,7 +15402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -14250,16 +15426,16 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -14283,16 +15459,16 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -14315,6 +15491,19 @@
           <t>2026-09-27</t>
         </is>
       </c>
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB28" t="n">
         <v>37</v>
       </c>
@@ -14335,6 +15524,19 @@
           <t>2026-09-28</t>
         </is>
       </c>
+      <c r="X29" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB29" t="n">
         <v>5</v>
       </c>
@@ -14355,6 +15557,32 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
@@ -14362,6 +15590,32 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="G32" s="36" t="inlineStr">
@@ -14384,10 +15638,36 @@
           <t>Projected AQS including hangs</t>
         </is>
       </c>
+      <c r="X32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D11)</f>
+        <f>AVERAGE(D2:D12)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -14395,7 +15675,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H11)</f>
+        <f>AVERAGE(H2:H12)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -14413,6 +15693,105 @@
       <c r="N33" s="38">
         <f>$B$2+MAX(0,(G33-$B$3)/($B$4-$B$3)*($B$1-$B$8))+M33</f>
         <v/>
+      </c>
+      <c r="X33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="X34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="AB35" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="AB36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="AB37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD237"/>
+  <dimension ref="A1:AD257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC5" s="7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="U11" s="7" t="n"/>
       <c r="V11" s="7" t="n"/>
       <c r="X11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -2171,22 +2171,46 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="D13" s="7">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C13)</f>
+        <v/>
+      </c>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="G13" s="7">
+        <f>ROUND(MAX(0,MIN(100,(1-E13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H13" s="7">
+        <f>MIN(1,(G13-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
+      <c r="K13" s="7">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="7">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M13" s="7">
+        <f>MAX(0,(L13-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N13" s="7">
+        <f>$B$2+H13+M13</f>
+        <v/>
+      </c>
       <c r="T13" s="7" t="n"/>
       <c r="U13" s="7" t="n"/>
       <c r="V13" s="7" t="n"/>
       <c r="X13" s="7" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
@@ -2235,7 +2259,7 @@
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
@@ -2248,7 +2272,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2284,7 +2308,7 @@
       <c r="U15" s="7" t="n"/>
       <c r="V15" s="7" t="n"/>
       <c r="X15" s="7" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="Y15" s="7" t="inlineStr">
         <is>
@@ -2297,7 +2321,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2333,7 +2357,7 @@
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
@@ -2346,7 +2370,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2480,7 +2504,7 @@
       <c r="U19" s="7" t="n"/>
       <c r="V19" s="7" t="n"/>
       <c r="X19" s="7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
@@ -2529,7 +2553,7 @@
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
@@ -2542,7 +2566,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>327</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2578,20 +2602,20 @@
       <c r="U21" s="7" t="n"/>
       <c r="V21" s="7" t="n"/>
       <c r="X21" s="7" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="Y21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z21" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>4</v>
+        <v>327</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2627,20 +2651,20 @@
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2680,7 +2704,7 @@
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z23" s="7" t="inlineStr">
@@ -2725,11 +2749,11 @@
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
@@ -2774,11 +2798,11 @@
       <c r="U25" s="7" t="n"/>
       <c r="V25" s="7" t="n"/>
       <c r="X25" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z25" s="7" t="inlineStr">
@@ -2787,7 +2811,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -2823,11 +2847,11 @@
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z26" s="4" t="inlineStr">
@@ -2836,7 +2860,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -2872,11 +2896,11 @@
       <c r="U27" s="7" t="n"/>
       <c r="V27" s="7" t="n"/>
       <c r="X27" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z27" s="7" t="inlineStr">
@@ -2921,11 +2945,11 @@
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
@@ -2934,7 +2958,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -2970,11 +2994,11 @@
       <c r="U29" s="7" t="n"/>
       <c r="V29" s="7" t="n"/>
       <c r="X29" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z29" s="7" t="inlineStr">
@@ -3019,11 +3043,11 @@
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z30" s="4" t="inlineStr">
@@ -3032,7 +3056,7 @@
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
@@ -3068,11 +3092,11 @@
       <c r="U31" s="7" t="n"/>
       <c r="V31" s="7" t="n"/>
       <c r="X31" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z31" s="7" t="inlineStr">
@@ -3126,11 +3150,11 @@
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z32" s="4" t="inlineStr">
@@ -3154,7 +3178,7 @@
     </row>
     <row r="33">
       <c r="D33" s="26">
-        <f>AVERAGE(D2:D12)</f>
+        <f>AVERAGE(D2:D13)</f>
         <v/>
       </c>
       <c r="E33" s="27" t="n"/>
@@ -3164,7 +3188,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>AVERAGE(H2:H12)</f>
+        <f>AVERAGE(H2:H13)</f>
         <v/>
       </c>
       <c r="I33" s="29">
@@ -3189,11 +3213,11 @@
       <c r="U33" s="7" t="n"/>
       <c r="V33" s="7" t="n"/>
       <c r="X33" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z33" s="7" t="inlineStr">
@@ -3220,11 +3244,11 @@
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z34" s="4" t="inlineStr">
@@ -3233,7 +3257,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3251,11 +3275,11 @@
       <c r="U35" s="7" t="n"/>
       <c r="V35" s="7" t="n"/>
       <c r="X35" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z35" s="7" t="inlineStr">
@@ -3264,7 +3288,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3282,20 +3306,20 @@
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3313,20 +3337,20 @@
       <c r="U37" s="7" t="n"/>
       <c r="V37" s="7" t="n"/>
       <c r="X37" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z37" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3344,16 +3368,16 @@
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB38" s="4" t="n">
@@ -3375,16 +3399,16 @@
       <c r="U39" s="7" t="n"/>
       <c r="V39" s="7" t="n"/>
       <c r="X39" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z39" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB39" s="7" t="n">
@@ -3406,11 +3430,11 @@
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z40" s="4" t="inlineStr">
@@ -3437,11 +3461,11 @@
       <c r="U41" s="7" t="n"/>
       <c r="V41" s="7" t="n"/>
       <c r="X41" s="7" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z41" s="7" t="inlineStr">
@@ -3468,11 +3492,11 @@
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="X42" s="4" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z42" s="4" t="inlineStr">
@@ -3481,7 +3505,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3499,11 +3523,11 @@
       <c r="U43" s="7" t="n"/>
       <c r="V43" s="7" t="n"/>
       <c r="X43" s="7" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z43" s="7" t="inlineStr">
@@ -3530,11 +3554,11 @@
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="X44" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z44" s="4" t="inlineStr">
@@ -3543,7 +3567,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -3565,7 +3589,7 @@
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z45" s="7" t="inlineStr">
@@ -3592,11 +3616,11 @@
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="X46" s="4" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
@@ -3605,7 +3629,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -3623,11 +3647,11 @@
       <c r="U47" s="7" t="n"/>
       <c r="V47" s="7" t="n"/>
       <c r="X47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z47" s="7" t="inlineStr">
@@ -3636,7 +3660,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -3654,11 +3678,11 @@
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="X48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z48" s="4" t="inlineStr">
@@ -3685,11 +3709,11 @@
       <c r="U49" s="7" t="n"/>
       <c r="V49" s="7" t="n"/>
       <c r="X49" s="7" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z49" s="7" t="inlineStr">
@@ -3698,7 +3722,7 @@
         </is>
       </c>
       <c r="AB49" s="7" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="7" t="inlineStr">
         <is>
@@ -3716,11 +3740,11 @@
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z50" s="4" t="inlineStr">
@@ -3729,7 +3753,7 @@
         </is>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="AC50" s="4" t="inlineStr">
         <is>
@@ -3747,11 +3771,11 @@
       <c r="U51" s="7" t="n"/>
       <c r="V51" s="7" t="n"/>
       <c r="X51" s="7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Y51" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z51" s="7" t="inlineStr">
@@ -3778,11 +3802,11 @@
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="X52" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z52" s="4" t="inlineStr">
@@ -3791,7 +3815,7 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -3809,11 +3833,11 @@
       <c r="U53" s="7" t="n"/>
       <c r="V53" s="7" t="n"/>
       <c r="X53" s="7" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z53" s="7" t="inlineStr">
@@ -3822,7 +3846,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -3840,20 +3864,20 @@
       <c r="U54" s="4" t="n"/>
       <c r="V54" s="4" t="n"/>
       <c r="X54" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z54" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB54" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y54" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB54" s="4" t="n">
-        <v>59</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
@@ -3871,11 +3895,11 @@
       <c r="U55" s="7" t="n"/>
       <c r="V55" s="7" t="n"/>
       <c r="X55" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z55" s="7" t="inlineStr">
@@ -3884,7 +3908,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -3902,11 +3926,11 @@
       <c r="U56" s="4" t="n"/>
       <c r="V56" s="4" t="n"/>
       <c r="X56" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z56" s="4" t="inlineStr">
@@ -3933,11 +3957,11 @@
       <c r="U57" s="7" t="n"/>
       <c r="V57" s="7" t="n"/>
       <c r="X57" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z57" s="7" t="inlineStr">
@@ -3946,7 +3970,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -3964,11 +3988,11 @@
       <c r="U58" s="4" t="n"/>
       <c r="V58" s="4" t="n"/>
       <c r="X58" s="4" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z58" s="4" t="inlineStr">
@@ -3995,11 +4019,11 @@
       <c r="U59" s="7" t="n"/>
       <c r="V59" s="7" t="n"/>
       <c r="X59" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z59" s="7" t="inlineStr">
@@ -4026,11 +4050,11 @@
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
       <c r="X60" s="4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Y60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z60" s="4" t="inlineStr">
@@ -4039,7 +4063,7 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4057,11 +4081,11 @@
       <c r="U61" s="7" t="n"/>
       <c r="V61" s="7" t="n"/>
       <c r="X61" s="7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z61" s="7" t="inlineStr">
@@ -4070,7 +4094,7 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4092,12 +4116,12 @@
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z62" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB62" s="4" t="n">
@@ -4119,16 +4143,16 @@
       <c r="U63" s="7" t="n"/>
       <c r="V63" s="7" t="n"/>
       <c r="X63" s="7" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Y63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z63" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB63" s="7" t="n">
@@ -4150,16 +4174,16 @@
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="X64" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z64" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB64" s="4" t="n">
@@ -4181,16 +4205,16 @@
       <c r="U65" s="7" t="n"/>
       <c r="V65" s="7" t="n"/>
       <c r="X65" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z65" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB65" s="7" t="n">
@@ -4212,16 +4236,16 @@
       <c r="U66" s="4" t="n"/>
       <c r="V66" s="4" t="n"/>
       <c r="X66" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z66" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB66" s="4" t="n">
@@ -4243,16 +4267,16 @@
       <c r="U67" s="7" t="n"/>
       <c r="V67" s="7" t="n"/>
       <c r="X67" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z67" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB67" s="7" t="n">
@@ -4274,11 +4298,11 @@
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Y68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z68" s="4" t="inlineStr">
@@ -4287,7 +4311,7 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
@@ -4305,11 +4329,11 @@
       <c r="U69" s="7" t="n"/>
       <c r="V69" s="7" t="n"/>
       <c r="X69" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y69" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z69" s="7" t="inlineStr">
@@ -4318,7 +4342,7 @@
         </is>
       </c>
       <c r="AB69" s="7" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="AC69" s="7" t="inlineStr">
         <is>
@@ -4336,11 +4360,11 @@
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
       <c r="X70" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z70" s="4" t="inlineStr">
@@ -4367,11 +4391,11 @@
       <c r="U71" s="7" t="n"/>
       <c r="V71" s="7" t="n"/>
       <c r="X71" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z71" s="7" t="inlineStr">
@@ -4398,11 +4422,11 @@
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="X72" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z72" s="4" t="inlineStr">
@@ -4411,7 +4435,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -4429,11 +4453,11 @@
       <c r="U73" s="7" t="n"/>
       <c r="V73" s="7" t="n"/>
       <c r="X73" s="7" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Y73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z73" s="7" t="inlineStr">
@@ -4442,7 +4466,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -4460,11 +4484,11 @@
       <c r="U74" s="4" t="n"/>
       <c r="V74" s="4" t="n"/>
       <c r="X74" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z74" s="4" t="inlineStr">
@@ -4495,7 +4519,7 @@
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z75" s="7" t="inlineStr">
@@ -4504,7 +4528,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -4522,11 +4546,11 @@
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="X76" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z76" s="4" t="inlineStr">
@@ -4535,7 +4559,7 @@
         </is>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -4553,11 +4577,11 @@
       <c r="U77" s="7" t="n"/>
       <c r="V77" s="7" t="n"/>
       <c r="X77" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z77" s="7" t="inlineStr">
@@ -4566,7 +4590,7 @@
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
@@ -4584,11 +4608,11 @@
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
       <c r="X78" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z78" s="4" t="inlineStr">
@@ -4597,7 +4621,7 @@
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -4615,11 +4639,11 @@
       <c r="U79" s="7" t="n"/>
       <c r="V79" s="7" t="n"/>
       <c r="X79" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z79" s="7" t="inlineStr">
@@ -4628,7 +4652,7 @@
         </is>
       </c>
       <c r="AB79" s="7" t="n">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="AC79" s="7" t="inlineStr">
         <is>
@@ -4646,11 +4670,11 @@
       <c r="U80" s="4" t="n"/>
       <c r="V80" s="4" t="n"/>
       <c r="X80" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z80" s="4" t="inlineStr">
@@ -4677,11 +4701,11 @@
       <c r="U81" s="7" t="n"/>
       <c r="V81" s="7" t="n"/>
       <c r="X81" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z81" s="7" t="inlineStr">
@@ -4708,11 +4732,11 @@
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
       <c r="X82" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
@@ -4721,7 +4745,7 @@
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>3</v>
+        <v>327</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
@@ -4739,11 +4763,11 @@
       <c r="U83" s="7" t="n"/>
       <c r="V83" s="7" t="n"/>
       <c r="X83" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z83" s="7" t="inlineStr">
@@ -4752,7 +4776,7 @@
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>327</v>
+        <v>3</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
@@ -4770,11 +4794,11 @@
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="X84" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z84" s="4" t="inlineStr">
@@ -4783,7 +4807,7 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -4805,16 +4829,16 @@
       </c>
       <c r="Y85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z85" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -4832,20 +4856,20 @@
       <c r="U86" s="4" t="n"/>
       <c r="V86" s="4" t="n"/>
       <c r="X86" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z86" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -4863,16 +4887,16 @@
       <c r="U87" s="7" t="n"/>
       <c r="V87" s="7" t="n"/>
       <c r="X87" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z87" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB87" s="7" t="n">
@@ -4894,20 +4918,20 @@
       <c r="U88" s="4" t="n"/>
       <c r="V88" s="4" t="n"/>
       <c r="X88" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z88" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -4925,20 +4949,20 @@
       <c r="U89" s="7" t="n"/>
       <c r="V89" s="7" t="n"/>
       <c r="X89" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z89" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB89" s="7" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="AC89" s="7" t="inlineStr">
         <is>
@@ -4956,16 +4980,16 @@
       <c r="U90" s="4" t="n"/>
       <c r="V90" s="4" t="n"/>
       <c r="X90" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z90" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB90" s="4" t="n">
@@ -4987,16 +5011,16 @@
       <c r="U91" s="7" t="n"/>
       <c r="V91" s="7" t="n"/>
       <c r="X91" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z91" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB91" s="7" t="n">
@@ -5018,16 +5042,16 @@
       <c r="U92" s="4" t="n"/>
       <c r="V92" s="4" t="n"/>
       <c r="X92" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z92" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB92" s="4" t="n">
@@ -5049,11 +5073,11 @@
       <c r="U93" s="7" t="n"/>
       <c r="V93" s="7" t="n"/>
       <c r="X93" s="7" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z93" s="7" t="inlineStr">
@@ -5062,7 +5086,7 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -5080,11 +5104,11 @@
       <c r="U94" s="4" t="n"/>
       <c r="V94" s="4" t="n"/>
       <c r="X94" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z94" s="4" t="inlineStr">
@@ -5093,7 +5117,7 @@
         </is>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -5111,11 +5135,11 @@
       <c r="U95" s="7" t="n"/>
       <c r="V95" s="7" t="n"/>
       <c r="X95" s="7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z95" s="7" t="inlineStr">
@@ -5124,7 +5148,7 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -5146,7 +5170,7 @@
       </c>
       <c r="Y96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z96" s="4" t="inlineStr">
@@ -5155,7 +5179,7 @@
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -5173,11 +5197,11 @@
       <c r="U97" s="7" t="n"/>
       <c r="V97" s="7" t="n"/>
       <c r="X97" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z97" s="7" t="inlineStr">
@@ -5186,7 +5210,7 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -5204,11 +5228,11 @@
       <c r="U98" s="4" t="n"/>
       <c r="V98" s="4" t="n"/>
       <c r="X98" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z98" s="4" t="inlineStr">
@@ -5217,7 +5241,7 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
@@ -5235,11 +5259,11 @@
       <c r="U99" s="7" t="n"/>
       <c r="V99" s="7" t="n"/>
       <c r="X99" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z99" s="7" t="inlineStr">
@@ -5248,7 +5272,7 @@
         </is>
       </c>
       <c r="AB99" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC99" s="7" t="inlineStr">
         <is>
@@ -5266,11 +5290,11 @@
       <c r="U100" s="4" t="n"/>
       <c r="V100" s="4" t="n"/>
       <c r="X100" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z100" s="4" t="inlineStr">
@@ -5297,11 +5321,11 @@
       <c r="U101" s="7" t="n"/>
       <c r="V101" s="7" t="n"/>
       <c r="X101" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z101" s="7" t="inlineStr">
@@ -5328,11 +5352,11 @@
       <c r="U102" s="4" t="n"/>
       <c r="V102" s="4" t="n"/>
       <c r="X102" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z102" s="4" t="inlineStr">
@@ -5359,11 +5383,11 @@
       <c r="U103" s="7" t="n"/>
       <c r="V103" s="7" t="n"/>
       <c r="X103" s="7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z103" s="7" t="inlineStr">
@@ -5390,16 +5414,16 @@
       <c r="U104" s="4" t="n"/>
       <c r="V104" s="4" t="n"/>
       <c r="X104" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z104" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB104" s="4" t="n">
@@ -5421,16 +5445,16 @@
       <c r="U105" s="7" t="n"/>
       <c r="V105" s="7" t="n"/>
       <c r="X105" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z105" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB105" s="7" t="n">
@@ -5452,16 +5476,16 @@
       <c r="U106" s="4" t="n"/>
       <c r="V106" s="4" t="n"/>
       <c r="X106" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z106" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB106" s="4" t="n">
@@ -5483,16 +5507,16 @@
       <c r="U107" s="7" t="n"/>
       <c r="V107" s="7" t="n"/>
       <c r="X107" s="7" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="Y107" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z107" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB107" s="7" t="n">
@@ -5514,20 +5538,20 @@
       <c r="U108" s="4" t="n"/>
       <c r="V108" s="4" t="n"/>
       <c r="X108" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z108" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -5545,20 +5569,20 @@
       <c r="U109" s="7" t="n"/>
       <c r="V109" s="7" t="n"/>
       <c r="X109" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z109" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -5580,16 +5604,16 @@
       </c>
       <c r="Y110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z110" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -5607,16 +5631,16 @@
       <c r="U111" s="7" t="n"/>
       <c r="V111" s="7" t="n"/>
       <c r="X111" s="7" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="Y111" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z111" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB111" s="7" t="n">
@@ -5638,16 +5662,16 @@
       <c r="U112" s="4" t="n"/>
       <c r="V112" s="4" t="n"/>
       <c r="X112" s="4" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="Y112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z112" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB112" s="4" t="n">
@@ -5669,16 +5693,16 @@
       <c r="U113" s="7" t="n"/>
       <c r="V113" s="7" t="n"/>
       <c r="X113" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y113" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z113" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB113" s="7" t="n">
@@ -5704,16 +5728,16 @@
       </c>
       <c r="Y114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z114" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -5731,11 +5755,11 @@
       <c r="U115" s="7" t="n"/>
       <c r="V115" s="7" t="n"/>
       <c r="X115" s="7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Y115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z115" s="7" t="inlineStr">
@@ -5744,7 +5768,7 @@
         </is>
       </c>
       <c r="AB115" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -5762,11 +5786,11 @@
       <c r="U116" s="4" t="n"/>
       <c r="V116" s="4" t="n"/>
       <c r="X116" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z116" s="4" t="inlineStr">
@@ -5797,7 +5821,7 @@
       </c>
       <c r="Y117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z117" s="7" t="inlineStr">
@@ -5806,7 +5830,7 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -5824,11 +5848,11 @@
       <c r="U118" s="4" t="n"/>
       <c r="V118" s="4" t="n"/>
       <c r="X118" s="4" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="Y118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z118" s="4" t="inlineStr">
@@ -5855,11 +5879,11 @@
       <c r="U119" s="7" t="n"/>
       <c r="V119" s="7" t="n"/>
       <c r="X119" s="7" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="Y119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z119" s="7" t="inlineStr">
@@ -5868,7 +5892,7 @@
         </is>
       </c>
       <c r="AB119" s="7" t="n">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="AC119" s="7" t="inlineStr">
         <is>
@@ -5886,11 +5910,11 @@
       <c r="U120" s="4" t="n"/>
       <c r="V120" s="4" t="n"/>
       <c r="X120" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z120" s="4" t="inlineStr">
@@ -5917,11 +5941,11 @@
       <c r="U121" s="7" t="n"/>
       <c r="V121" s="7" t="n"/>
       <c r="X121" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y121" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z121" s="7" t="inlineStr">
@@ -5948,11 +5972,11 @@
       <c r="U122" s="4" t="n"/>
       <c r="V122" s="4" t="n"/>
       <c r="X122" s="4" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="Y122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z122" s="4" t="inlineStr">
@@ -5961,7 +5985,7 @@
         </is>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
@@ -5979,11 +6003,11 @@
       <c r="U123" s="7" t="n"/>
       <c r="V123" s="7" t="n"/>
       <c r="X123" s="7" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="Y123" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z123" s="7" t="inlineStr">
@@ -5992,7 +6016,7 @@
         </is>
       </c>
       <c r="AB123" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AC123" s="7" t="inlineStr">
         <is>
@@ -6010,11 +6034,11 @@
       <c r="U124" s="4" t="n"/>
       <c r="V124" s="4" t="n"/>
       <c r="X124" s="4" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="Y124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z124" s="4" t="inlineStr">
@@ -6041,11 +6065,11 @@
       <c r="U125" s="7" t="n"/>
       <c r="V125" s="7" t="n"/>
       <c r="X125" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y125" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z125" s="7" t="inlineStr">
@@ -6054,7 +6078,7 @@
         </is>
       </c>
       <c r="AB125" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC125" s="7" t="inlineStr">
         <is>
@@ -6072,11 +6096,11 @@
       <c r="U126" s="4" t="n"/>
       <c r="V126" s="4" t="n"/>
       <c r="X126" s="4" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z126" s="4" t="inlineStr">
@@ -6085,7 +6109,7 @@
         </is>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>302</v>
+        <v>12</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -6107,7 +6131,7 @@
       </c>
       <c r="Y127" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z127" s="7" t="inlineStr">
@@ -6116,7 +6140,7 @@
         </is>
       </c>
       <c r="AB127" s="7" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
@@ -6134,11 +6158,11 @@
       <c r="U128" s="4" t="n"/>
       <c r="V128" s="4" t="n"/>
       <c r="X128" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z128" s="4" t="inlineStr">
@@ -6147,7 +6171,7 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -6165,11 +6189,11 @@
       <c r="U129" s="7" t="n"/>
       <c r="V129" s="7" t="n"/>
       <c r="X129" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y129" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z129" s="7" t="inlineStr">
@@ -6178,7 +6202,7 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -6196,11 +6220,11 @@
       <c r="U130" s="4" t="n"/>
       <c r="V130" s="4" t="n"/>
       <c r="X130" s="4" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z130" s="4" t="inlineStr">
@@ -6209,7 +6233,7 @@
         </is>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
@@ -6227,11 +6251,11 @@
       <c r="U131" s="7" t="n"/>
       <c r="V131" s="7" t="n"/>
       <c r="X131" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y131" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z131" s="7" t="inlineStr">
@@ -6258,11 +6282,11 @@
       <c r="U132" s="4" t="n"/>
       <c r="V132" s="4" t="n"/>
       <c r="X132" s="4" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="Y132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z132" s="4" t="inlineStr">
@@ -6271,7 +6295,7 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -6289,11 +6313,11 @@
       <c r="U133" s="7" t="n"/>
       <c r="V133" s="7" t="n"/>
       <c r="X133" s="7" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="Y133" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z133" s="7" t="inlineStr">
@@ -6302,7 +6326,7 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -6320,11 +6344,11 @@
       <c r="U134" s="4" t="n"/>
       <c r="V134" s="4" t="n"/>
       <c r="X134" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z134" s="4" t="inlineStr">
@@ -6333,7 +6357,7 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -6351,16 +6375,16 @@
       <c r="U135" s="7" t="n"/>
       <c r="V135" s="7" t="n"/>
       <c r="X135" s="7" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Y135" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z135" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB135" s="7" t="n">
@@ -6382,16 +6406,16 @@
       <c r="U136" s="4" t="n"/>
       <c r="V136" s="4" t="n"/>
       <c r="X136" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z136" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB136" s="4" t="n">
@@ -6413,20 +6437,20 @@
       <c r="U137" s="7" t="n"/>
       <c r="V137" s="7" t="n"/>
       <c r="X137" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y137" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z137" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB137" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="Y137" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z137" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.woowabros</t>
-        </is>
-      </c>
-      <c r="AB137" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -6444,16 +6468,16 @@
       <c r="U138" s="4" t="n"/>
       <c r="V138" s="4" t="n"/>
       <c r="X138" s="4" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="Y138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z138" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB138" s="4" t="n">
@@ -6475,20 +6499,20 @@
       <c r="U139" s="7" t="n"/>
       <c r="V139" s="7" t="n"/>
       <c r="X139" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y139" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z139" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB139" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -6506,20 +6530,20 @@
       <c r="U140" s="4" t="n"/>
       <c r="V140" s="4" t="n"/>
       <c r="X140" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z140" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -6537,20 +6561,20 @@
       <c r="U141" s="7" t="n"/>
       <c r="V141" s="7" t="n"/>
       <c r="X141" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y141" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z141" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB141" s="7" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -6568,20 +6592,20 @@
       <c r="U142" s="4" t="n"/>
       <c r="V142" s="4" t="n"/>
       <c r="X142" s="4" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="Y142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z142" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -6599,20 +6623,20 @@
       <c r="U143" s="7" t="n"/>
       <c r="V143" s="7" t="n"/>
       <c r="X143" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y143" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z143" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB143" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -6630,16 +6654,16 @@
       <c r="U144" s="4" t="n"/>
       <c r="V144" s="4" t="n"/>
       <c r="X144" s="4" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="Y144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z144" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB144" s="4" t="n">
@@ -6661,16 +6685,16 @@
       <c r="U145" s="7" t="n"/>
       <c r="V145" s="7" t="n"/>
       <c r="X145" s="7" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="Y145" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z145" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB145" s="7" t="n">
@@ -6692,16 +6716,16 @@
       <c r="U146" s="4" t="n"/>
       <c r="V146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="Y146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z146" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB146" s="4" t="n">
@@ -6723,16 +6747,16 @@
       <c r="U147" s="7" t="n"/>
       <c r="V147" s="7" t="n"/>
       <c r="X147" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y147" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z147" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB147" s="7" t="n">
@@ -6754,16 +6778,16 @@
       <c r="U148" s="4" t="n"/>
       <c r="V148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="Y148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z148" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB148" s="4" t="n">
@@ -6785,16 +6809,16 @@
       <c r="U149" s="7" t="n"/>
       <c r="V149" s="7" t="n"/>
       <c r="X149" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y149" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z149" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB149" s="7" t="n">
@@ -6816,16 +6840,16 @@
       <c r="U150" s="4" t="n"/>
       <c r="V150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z150" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB150" s="4" t="n">
@@ -6847,7 +6871,7 @@
       <c r="U151" s="7" t="n"/>
       <c r="V151" s="7" t="n"/>
       <c r="X151" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y151" s="7" t="inlineStr">
         <is>
@@ -6856,7 +6880,7 @@
       </c>
       <c r="Z151" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB151" s="7" t="n">
@@ -6878,16 +6902,16 @@
       <c r="U152" s="4" t="n"/>
       <c r="V152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z152" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB152" s="4" t="n">
@@ -6909,11 +6933,11 @@
       <c r="U153" s="7" t="n"/>
       <c r="V153" s="7" t="n"/>
       <c r="X153" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y153" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z153" s="7" t="inlineStr">
@@ -6922,7 +6946,7 @@
         </is>
       </c>
       <c r="AB153" s="7" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -6940,7 +6964,7 @@
       <c r="U154" s="4" t="n"/>
       <c r="V154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y154" s="4" t="inlineStr">
         <is>
@@ -6949,11 +6973,11 @@
       </c>
       <c r="Z154" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -6971,20 +6995,20 @@
       <c r="U155" s="7" t="n"/>
       <c r="V155" s="7" t="n"/>
       <c r="X155" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y155" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z155" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB155" s="7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
@@ -7002,16 +7026,16 @@
       <c r="U156" s="4" t="n"/>
       <c r="V156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z156" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB156" s="4" t="n">
@@ -7033,20 +7057,20 @@
       <c r="U157" s="7" t="n"/>
       <c r="V157" s="7" t="n"/>
       <c r="X157" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y157" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z157" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB157" s="7" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="AC157" s="7" t="inlineStr">
         <is>
@@ -7064,20 +7088,20 @@
       <c r="U158" s="4" t="n"/>
       <c r="V158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z158" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB158" s="4" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="AC158" s="4" t="inlineStr">
         <is>
@@ -7095,16 +7119,16 @@
       <c r="U159" s="7" t="n"/>
       <c r="V159" s="7" t="n"/>
       <c r="X159" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y159" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z159" s="7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB159" s="7" t="n">
@@ -7126,16 +7150,16 @@
       <c r="U160" s="4" t="n"/>
       <c r="V160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z160" s="4" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB160" s="4" t="n">
@@ -7156,11 +7180,21 @@
       <c r="T161" s="7" t="n"/>
       <c r="U161" s="7" t="n"/>
       <c r="V161" s="7" t="n"/>
-      <c r="X161" s="7" t="n"/>
-      <c r="Y161" s="7" t="n"/>
-      <c r="Z161" s="7" t="n"/>
+      <c r="X161" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z161" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB161" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -7177,11 +7211,21 @@
       <c r="T162" s="4" t="n"/>
       <c r="U162" s="4" t="n"/>
       <c r="V162" s="4" t="n"/>
-      <c r="X162" s="4" t="n"/>
-      <c r="Y162" s="4" t="n"/>
-      <c r="Z162" s="4" t="n"/>
+      <c r="X162" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z162" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB162" s="4" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
@@ -7198,11 +7242,21 @@
       <c r="T163" s="7" t="n"/>
       <c r="U163" s="7" t="n"/>
       <c r="V163" s="7" t="n"/>
-      <c r="X163" s="7" t="n"/>
-      <c r="Y163" s="7" t="n"/>
-      <c r="Z163" s="7" t="n"/>
+      <c r="X163" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y163" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z163" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB163" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -7219,11 +7273,21 @@
       <c r="T164" s="4" t="n"/>
       <c r="U164" s="4" t="n"/>
       <c r="V164" s="4" t="n"/>
-      <c r="X164" s="4" t="n"/>
-      <c r="Y164" s="4" t="n"/>
-      <c r="Z164" s="4" t="n"/>
+      <c r="X164" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z164" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB164" s="4" t="n">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
@@ -7240,9 +7304,19 @@
       <c r="T165" s="7" t="n"/>
       <c r="U165" s="7" t="n"/>
       <c r="V165" s="7" t="n"/>
-      <c r="X165" s="7" t="n"/>
-      <c r="Y165" s="7" t="n"/>
-      <c r="Z165" s="7" t="n"/>
+      <c r="X165" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y165" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z165" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB165" s="7" t="n">
         <v>5</v>
       </c>
@@ -7261,9 +7335,19 @@
       <c r="T166" s="4" t="n"/>
       <c r="U166" s="4" t="n"/>
       <c r="V166" s="4" t="n"/>
-      <c r="X166" s="4" t="n"/>
-      <c r="Y166" s="4" t="n"/>
-      <c r="Z166" s="4" t="n"/>
+      <c r="X166" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z166" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB166" s="4" t="n">
         <v>9</v>
       </c>
@@ -7282,9 +7366,19 @@
       <c r="T167" s="7" t="n"/>
       <c r="U167" s="7" t="n"/>
       <c r="V167" s="7" t="n"/>
-      <c r="X167" s="7" t="n"/>
-      <c r="Y167" s="7" t="n"/>
-      <c r="Z167" s="7" t="n"/>
+      <c r="X167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y167" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z167" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB167" s="7" t="n">
         <v>1</v>
       </c>
@@ -7303,11 +7397,21 @@
       <c r="T168" s="4" t="n"/>
       <c r="U168" s="4" t="n"/>
       <c r="V168" s="4" t="n"/>
-      <c r="X168" s="4" t="n"/>
-      <c r="Y168" s="4" t="n"/>
-      <c r="Z168" s="4" t="n"/>
+      <c r="X168" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z168" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB168" s="4" t="n">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -7324,11 +7428,21 @@
       <c r="T169" s="7" t="n"/>
       <c r="U169" s="7" t="n"/>
       <c r="V169" s="7" t="n"/>
-      <c r="X169" s="7" t="n"/>
-      <c r="Y169" s="7" t="n"/>
-      <c r="Z169" s="7" t="n"/>
+      <c r="X169" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y169" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z169" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB169" s="7" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="AC169" s="7" t="inlineStr">
         <is>
@@ -7345,11 +7459,21 @@
       <c r="T170" s="4" t="n"/>
       <c r="U170" s="4" t="n"/>
       <c r="V170" s="4" t="n"/>
-      <c r="X170" s="4" t="n"/>
-      <c r="Y170" s="4" t="n"/>
-      <c r="Z170" s="4" t="n"/>
+      <c r="X170" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z170" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB170" s="4" t="n">
-        <v>2</v>
+        <v>291</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
@@ -7366,11 +7490,21 @@
       <c r="T171" s="7" t="n"/>
       <c r="U171" s="7" t="n"/>
       <c r="V171" s="7" t="n"/>
-      <c r="X171" s="7" t="n"/>
-      <c r="Y171" s="7" t="n"/>
-      <c r="Z171" s="7" t="n"/>
+      <c r="X171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z171" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB171" s="7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AC171" s="7" t="inlineStr">
         <is>
@@ -7387,11 +7521,21 @@
       <c r="T172" s="4" t="n"/>
       <c r="U172" s="4" t="n"/>
       <c r="V172" s="4" t="n"/>
-      <c r="X172" s="4" t="n"/>
-      <c r="Y172" s="4" t="n"/>
-      <c r="Z172" s="4" t="n"/>
+      <c r="X172" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z172" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB172" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
@@ -7408,11 +7552,21 @@
       <c r="T173" s="7" t="n"/>
       <c r="U173" s="7" t="n"/>
       <c r="V173" s="7" t="n"/>
-      <c r="X173" s="7" t="n"/>
-      <c r="Y173" s="7" t="n"/>
-      <c r="Z173" s="7" t="n"/>
+      <c r="X173" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y173" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z173" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB173" s="7" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AC173" s="7" t="inlineStr">
         <is>
@@ -7429,11 +7583,21 @@
       <c r="T174" s="4" t="n"/>
       <c r="U174" s="4" t="n"/>
       <c r="V174" s="4" t="n"/>
-      <c r="X174" s="4" t="n"/>
-      <c r="Y174" s="4" t="n"/>
-      <c r="Z174" s="4" t="n"/>
+      <c r="X174" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z174" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB174" s="4" t="n">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
@@ -7450,11 +7614,21 @@
       <c r="T175" s="7" t="n"/>
       <c r="U175" s="7" t="n"/>
       <c r="V175" s="7" t="n"/>
-      <c r="X175" s="7" t="n"/>
-      <c r="Y175" s="7" t="n"/>
-      <c r="Z175" s="7" t="n"/>
+      <c r="X175" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y175" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z175" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB175" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC175" s="7" t="inlineStr">
         <is>
@@ -7471,11 +7645,21 @@
       <c r="T176" s="4" t="n"/>
       <c r="U176" s="4" t="n"/>
       <c r="V176" s="4" t="n"/>
-      <c r="X176" s="4" t="n"/>
-      <c r="Y176" s="4" t="n"/>
-      <c r="Z176" s="4" t="n"/>
+      <c r="X176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z176" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB176" s="4" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="AC176" s="4" t="inlineStr">
         <is>
@@ -7492,9 +7676,19 @@
       <c r="T177" s="7" t="n"/>
       <c r="U177" s="7" t="n"/>
       <c r="V177" s="7" t="n"/>
-      <c r="X177" s="7" t="n"/>
-      <c r="Y177" s="7" t="n"/>
-      <c r="Z177" s="7" t="n"/>
+      <c r="X177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y177" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z177" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB177" s="7" t="n">
         <v>2</v>
       </c>
@@ -7513,11 +7707,21 @@
       <c r="T178" s="4" t="n"/>
       <c r="U178" s="4" t="n"/>
       <c r="V178" s="4" t="n"/>
-      <c r="X178" s="4" t="n"/>
-      <c r="Y178" s="4" t="n"/>
-      <c r="Z178" s="4" t="n"/>
+      <c r="X178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z178" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB178" s="4" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
@@ -7534,11 +7738,21 @@
       <c r="T179" s="7" t="n"/>
       <c r="U179" s="7" t="n"/>
       <c r="V179" s="7" t="n"/>
-      <c r="X179" s="7" t="n"/>
-      <c r="Y179" s="7" t="n"/>
-      <c r="Z179" s="7" t="n"/>
+      <c r="X179" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y179" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z179" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB179" s="7" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="AC179" s="7" t="inlineStr">
         <is>
@@ -7559,7 +7773,7 @@
       <c r="Y180" s="4" t="n"/>
       <c r="Z180" s="4" t="n"/>
       <c r="AB180" s="4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="AC180" s="4" t="inlineStr">
         <is>
@@ -7580,7 +7794,7 @@
       <c r="Y181" s="7" t="n"/>
       <c r="Z181" s="7" t="n"/>
       <c r="AB181" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC181" s="7" t="inlineStr">
         <is>
@@ -7601,7 +7815,7 @@
       <c r="Y182" s="4" t="n"/>
       <c r="Z182" s="4" t="n"/>
       <c r="AB182" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC182" s="4" t="inlineStr">
         <is>
@@ -7622,7 +7836,7 @@
       <c r="Y183" s="7" t="n"/>
       <c r="Z183" s="7" t="n"/>
       <c r="AB183" s="7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AC183" s="7" t="inlineStr">
         <is>
@@ -7643,7 +7857,7 @@
       <c r="Y184" s="4" t="n"/>
       <c r="Z184" s="4" t="n"/>
       <c r="AB184" s="4" t="n">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
@@ -7664,7 +7878,7 @@
       <c r="Y185" s="7" t="n"/>
       <c r="Z185" s="7" t="n"/>
       <c r="AB185" s="7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AC185" s="7" t="inlineStr">
         <is>
@@ -7685,7 +7899,7 @@
       <c r="Y186" s="4" t="n"/>
       <c r="Z186" s="4" t="n"/>
       <c r="AB186" s="4" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="AC186" s="4" t="inlineStr">
         <is>
@@ -7748,7 +7962,7 @@
       <c r="Y189" s="7" t="n"/>
       <c r="Z189" s="7" t="n"/>
       <c r="AB189" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC189" s="7" t="inlineStr">
         <is>
@@ -7769,7 +7983,7 @@
       <c r="Y190" s="4" t="n"/>
       <c r="Z190" s="4" t="n"/>
       <c r="AB190" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC190" s="4" t="inlineStr">
         <is>
@@ -7811,7 +8025,7 @@
       <c r="Y192" s="4" t="n"/>
       <c r="Z192" s="4" t="n"/>
       <c r="AB192" s="4" t="n">
-        <v>268</v>
+        <v>72</v>
       </c>
       <c r="AC192" s="4" t="inlineStr">
         <is>
@@ -7832,7 +8046,7 @@
       <c r="Y193" s="7" t="n"/>
       <c r="Z193" s="7" t="n"/>
       <c r="AB193" s="7" t="n">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="AC193" s="7" t="inlineStr">
         <is>
@@ -7853,7 +8067,7 @@
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n"/>
       <c r="AB194" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AC194" s="4" t="inlineStr">
         <is>
@@ -7874,7 +8088,7 @@
       <c r="Y195" s="7" t="n"/>
       <c r="Z195" s="7" t="n"/>
       <c r="AB195" s="7" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AC195" s="7" t="inlineStr">
         <is>
@@ -8021,7 +8235,7 @@
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="n"/>
       <c r="AB202" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AC202" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8256,7 @@
       <c r="Y203" s="7" t="n"/>
       <c r="Z203" s="7" t="n"/>
       <c r="AB203" s="7" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AC203" s="7" t="inlineStr">
         <is>
@@ -8063,7 +8277,7 @@
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="n"/>
       <c r="AB204" s="4" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="AC204" s="4" t="inlineStr">
         <is>
@@ -8105,7 +8319,7 @@
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n"/>
       <c r="AB206" s="4" t="n">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="AC206" s="4" t="inlineStr">
         <is>
@@ -8126,7 +8340,7 @@
       <c r="Y207" s="7" t="n"/>
       <c r="Z207" s="7" t="n"/>
       <c r="AB207" s="7" t="n">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="AC207" s="7" t="inlineStr">
         <is>
@@ -8147,7 +8361,7 @@
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n"/>
       <c r="AB208" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC208" s="4" t="inlineStr">
         <is>
@@ -8168,7 +8382,7 @@
       <c r="Y209" s="7" t="n"/>
       <c r="Z209" s="7" t="n"/>
       <c r="AB209" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC209" s="7" t="inlineStr">
         <is>
@@ -8252,7 +8466,7 @@
       <c r="Y213" s="7" t="n"/>
       <c r="Z213" s="7" t="n"/>
       <c r="AB213" s="7" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="AC213" s="7" t="inlineStr">
         <is>
@@ -8273,7 +8487,7 @@
       <c r="Y214" s="4" t="n"/>
       <c r="Z214" s="4" t="n"/>
       <c r="AB214" s="4" t="n">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="AC214" s="4" t="inlineStr">
         <is>
@@ -8294,7 +8508,7 @@
       <c r="Y215" s="7" t="n"/>
       <c r="Z215" s="7" t="n"/>
       <c r="AB215" s="7" t="n">
-        <v>87</v>
+        <v>216</v>
       </c>
       <c r="AC215" s="7" t="inlineStr">
         <is>
@@ -8315,7 +8529,7 @@
       <c r="Y216" s="4" t="n"/>
       <c r="Z216" s="4" t="n"/>
       <c r="AB216" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AC216" s="4" t="inlineStr">
         <is>
@@ -8336,7 +8550,7 @@
       <c r="Y217" s="7" t="n"/>
       <c r="Z217" s="7" t="n"/>
       <c r="AB217" s="7" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AC217" s="7" t="inlineStr">
         <is>
@@ -8357,7 +8571,7 @@
       <c r="Y218" s="4" t="n"/>
       <c r="Z218" s="4" t="n"/>
       <c r="AB218" s="4" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="AC218" s="4" t="inlineStr">
         <is>
@@ -8378,7 +8592,7 @@
       <c r="Y219" s="7" t="n"/>
       <c r="Z219" s="7" t="n"/>
       <c r="AB219" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC219" s="7" t="inlineStr">
         <is>
@@ -8441,7 +8655,7 @@
       <c r="Y222" s="4" t="n"/>
       <c r="Z222" s="4" t="n"/>
       <c r="AB222" s="4" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AC222" s="4" t="inlineStr">
         <is>
@@ -8462,7 +8676,7 @@
       <c r="Y223" s="7" t="n"/>
       <c r="Z223" s="7" t="n"/>
       <c r="AB223" s="7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AC223" s="7" t="inlineStr">
         <is>
@@ -8525,7 +8739,7 @@
       <c r="Y226" s="4" t="n"/>
       <c r="Z226" s="4" t="n"/>
       <c r="AB226" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AC226" s="4" t="inlineStr">
         <is>
@@ -8567,7 +8781,7 @@
       <c r="Y228" s="4" t="n"/>
       <c r="Z228" s="4" t="n"/>
       <c r="AB228" s="4" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="AC228" s="4" t="inlineStr">
         <is>
@@ -8588,7 +8802,7 @@
       <c r="Y229" s="7" t="n"/>
       <c r="Z229" s="7" t="n"/>
       <c r="AB229" s="7" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AC229" s="7" t="inlineStr">
         <is>
@@ -8764,6 +8978,426 @@
         </is>
       </c>
       <c r="AD237" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="T238" s="4" t="n"/>
+      <c r="U238" s="4" t="n"/>
+      <c r="V238" s="4" t="n"/>
+      <c r="X238" s="4" t="n"/>
+      <c r="Y238" s="4" t="n"/>
+      <c r="Z238" s="4" t="n"/>
+      <c r="AB238" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="AC238" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD238" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="T239" s="7" t="n"/>
+      <c r="U239" s="7" t="n"/>
+      <c r="V239" s="7" t="n"/>
+      <c r="X239" s="7" t="n"/>
+      <c r="Y239" s="7" t="n"/>
+      <c r="Z239" s="7" t="n"/>
+      <c r="AB239" s="7" t="n">
+        <v>248</v>
+      </c>
+      <c r="AC239" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD239" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="T240" s="4" t="n"/>
+      <c r="U240" s="4" t="n"/>
+      <c r="V240" s="4" t="n"/>
+      <c r="X240" s="4" t="n"/>
+      <c r="Y240" s="4" t="n"/>
+      <c r="Z240" s="4" t="n"/>
+      <c r="AB240" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD240" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="T241" s="7" t="n"/>
+      <c r="U241" s="7" t="n"/>
+      <c r="V241" s="7" t="n"/>
+      <c r="X241" s="7" t="n"/>
+      <c r="Y241" s="7" t="n"/>
+      <c r="Z241" s="7" t="n"/>
+      <c r="AB241" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC241" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD241" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="T242" s="4" t="n"/>
+      <c r="U242" s="4" t="n"/>
+      <c r="V242" s="4" t="n"/>
+      <c r="X242" s="4" t="n"/>
+      <c r="Y242" s="4" t="n"/>
+      <c r="Z242" s="4" t="n"/>
+      <c r="AB242" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC242" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD242" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="T243" s="7" t="n"/>
+      <c r="U243" s="7" t="n"/>
+      <c r="V243" s="7" t="n"/>
+      <c r="X243" s="7" t="n"/>
+      <c r="Y243" s="7" t="n"/>
+      <c r="Z243" s="7" t="n"/>
+      <c r="AB243" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC243" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD243" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="T244" s="4" t="n"/>
+      <c r="U244" s="4" t="n"/>
+      <c r="V244" s="4" t="n"/>
+      <c r="X244" s="4" t="n"/>
+      <c r="Y244" s="4" t="n"/>
+      <c r="Z244" s="4" t="n"/>
+      <c r="AB244" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC244" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD244" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="T245" s="7" t="n"/>
+      <c r="U245" s="7" t="n"/>
+      <c r="V245" s="7" t="n"/>
+      <c r="X245" s="7" t="n"/>
+      <c r="Y245" s="7" t="n"/>
+      <c r="Z245" s="7" t="n"/>
+      <c r="AB245" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC245" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD245" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="T246" s="4" t="n"/>
+      <c r="U246" s="4" t="n"/>
+      <c r="V246" s="4" t="n"/>
+      <c r="X246" s="4" t="n"/>
+      <c r="Y246" s="4" t="n"/>
+      <c r="Z246" s="4" t="n"/>
+      <c r="AB246" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC246" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD246" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="T247" s="7" t="n"/>
+      <c r="U247" s="7" t="n"/>
+      <c r="V247" s="7" t="n"/>
+      <c r="X247" s="7" t="n"/>
+      <c r="Y247" s="7" t="n"/>
+      <c r="Z247" s="7" t="n"/>
+      <c r="AB247" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC247" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD247" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="T248" s="4" t="n"/>
+      <c r="U248" s="4" t="n"/>
+      <c r="V248" s="4" t="n"/>
+      <c r="X248" s="4" t="n"/>
+      <c r="Y248" s="4" t="n"/>
+      <c r="Z248" s="4" t="n"/>
+      <c r="AB248" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC248" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD248" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="T249" s="7" t="n"/>
+      <c r="U249" s="7" t="n"/>
+      <c r="V249" s="7" t="n"/>
+      <c r="X249" s="7" t="n"/>
+      <c r="Y249" s="7" t="n"/>
+      <c r="Z249" s="7" t="n"/>
+      <c r="AB249" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC249" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD249" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="T250" s="4" t="n"/>
+      <c r="U250" s="4" t="n"/>
+      <c r="V250" s="4" t="n"/>
+      <c r="X250" s="4" t="n"/>
+      <c r="Y250" s="4" t="n"/>
+      <c r="Z250" s="4" t="n"/>
+      <c r="AB250" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC250" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD250" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="T251" s="7" t="n"/>
+      <c r="U251" s="7" t="n"/>
+      <c r="V251" s="7" t="n"/>
+      <c r="X251" s="7" t="n"/>
+      <c r="Y251" s="7" t="n"/>
+      <c r="Z251" s="7" t="n"/>
+      <c r="AB251" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC251" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD251" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="T252" s="4" t="n"/>
+      <c r="U252" s="4" t="n"/>
+      <c r="V252" s="4" t="n"/>
+      <c r="X252" s="4" t="n"/>
+      <c r="Y252" s="4" t="n"/>
+      <c r="Z252" s="4" t="n"/>
+      <c r="AB252" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC252" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD252" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="T253" s="7" t="n"/>
+      <c r="U253" s="7" t="n"/>
+      <c r="V253" s="7" t="n"/>
+      <c r="X253" s="7" t="n"/>
+      <c r="Y253" s="7" t="n"/>
+      <c r="Z253" s="7" t="n"/>
+      <c r="AB253" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC253" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD253" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="T254" s="4" t="n"/>
+      <c r="U254" s="4" t="n"/>
+      <c r="V254" s="4" t="n"/>
+      <c r="X254" s="4" t="n"/>
+      <c r="Y254" s="4" t="n"/>
+      <c r="Z254" s="4" t="n"/>
+      <c r="AB254" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC254" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD254" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="T255" s="7" t="n"/>
+      <c r="U255" s="7" t="n"/>
+      <c r="V255" s="7" t="n"/>
+      <c r="X255" s="7" t="n"/>
+      <c r="Y255" s="7" t="n"/>
+      <c r="Z255" s="7" t="n"/>
+      <c r="AB255" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC255" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD255" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="T256" s="4" t="n"/>
+      <c r="U256" s="4" t="n"/>
+      <c r="V256" s="4" t="n"/>
+      <c r="X256" s="4" t="n"/>
+      <c r="Y256" s="4" t="n"/>
+      <c r="Z256" s="4" t="n"/>
+      <c r="AB256" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC256" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD256" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="T257" s="7" t="n"/>
+      <c r="U257" s="7" t="n"/>
+      <c r="V257" s="7" t="n"/>
+      <c r="X257" s="7" t="n"/>
+      <c r="Y257" s="7" t="n"/>
+      <c r="Z257" s="7" t="n"/>
+      <c r="AB257" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC257" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD257" s="7" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -8785,7 +9419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD176"/>
+  <dimension ref="A1:AD187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8960,7 +9594,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -9033,7 +9667,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -9106,7 +9740,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -9171,7 +9805,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -9231,7 +9865,7 @@
         <v/>
       </c>
       <c r="X6" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -9304,7 +9938,7 @@
         <v/>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -9390,7 +10024,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -9455,7 +10089,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -9679,6 +10313,38 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="D13">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C13)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C13)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>ROUND(MAX(0,MIN(100,(1-E13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>MIN(1,(G13-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C13)</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>MAX(0,(L13-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>$B$2+H13+M13</f>
+        <v/>
+      </c>
       <c r="X13" t="n">
         <v>61</v>
       </c>
@@ -9693,7 +10359,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -9726,7 +10392,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -9746,16 +10412,16 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -9779,11 +10445,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -9812,11 +10478,11 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -9849,7 +10515,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -9882,7 +10548,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -9891,7 +10557,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -9911,11 +10577,11 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -9924,7 +10590,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -9944,11 +10610,11 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -9977,11 +10643,11 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -10010,11 +10676,11 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -10047,7 +10713,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -10056,7 +10722,7 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -10076,20 +10742,20 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -10109,16 +10775,16 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -10142,11 +10808,11 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -10175,11 +10841,11 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -10188,7 +10854,7 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -10208,20 +10874,20 @@
         </is>
       </c>
       <c r="X29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
         <v>1</v>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB29" t="n">
-        <v>5</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -10241,11 +10907,11 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -10254,7 +10920,7 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -10274,11 +10940,11 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -10322,11 +10988,11 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -10350,7 +11016,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D12)</f>
+        <f>AVERAGE(D2:D13)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -10358,7 +11024,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H12)</f>
+        <f>AVERAGE(H2:H13)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -10378,11 +11044,11 @@
         <v/>
       </c>
       <c r="X33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -10406,11 +11072,11 @@
     </row>
     <row r="34">
       <c r="X34" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -10434,11 +11100,11 @@
     </row>
     <row r="35">
       <c r="X35" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -10462,11 +11128,11 @@
     </row>
     <row r="36">
       <c r="X36" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -10490,11 +11156,11 @@
     </row>
     <row r="37">
       <c r="X37" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -10518,11 +11184,11 @@
     </row>
     <row r="38">
       <c r="X38" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -10546,11 +11212,11 @@
     </row>
     <row r="39">
       <c r="X39" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -10559,7 +11225,7 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -10574,20 +11240,20 @@
     </row>
     <row r="40">
       <c r="X40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
         <v>5</v>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB40" t="n">
-        <v>2</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -10602,20 +11268,20 @@
     </row>
     <row r="41">
       <c r="X41" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -10634,16 +11300,16 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -10658,20 +11324,20 @@
     </row>
     <row r="43">
       <c r="X43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -10690,7 +11356,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -10699,7 +11365,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -10718,7 +11384,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -10742,11 +11408,11 @@
     </row>
     <row r="46">
       <c r="X46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -10755,7 +11421,7 @@
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -10770,11 +11436,11 @@
     </row>
     <row r="47">
       <c r="X47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -10783,7 +11449,7 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -10798,11 +11464,11 @@
     </row>
     <row r="48">
       <c r="X48" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -10830,7 +11496,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -10854,11 +11520,11 @@
     </row>
     <row r="50">
       <c r="X50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -10882,11 +11548,11 @@
     </row>
     <row r="51">
       <c r="X51" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -10910,11 +11576,11 @@
     </row>
     <row r="52">
       <c r="X52" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -10923,7 +11589,7 @@
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -10938,20 +11604,20 @@
     </row>
     <row r="53">
       <c r="X53" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
         <v>1</v>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB53" t="n">
-        <v>12</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10966,11 +11632,11 @@
     </row>
     <row r="54">
       <c r="X54" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -10994,11 +11660,11 @@
     </row>
     <row r="55">
       <c r="X55" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -11022,20 +11688,20 @@
     </row>
     <row r="56">
       <c r="X56" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -11050,20 +11716,20 @@
     </row>
     <row r="57">
       <c r="X57" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -11078,20 +11744,20 @@
     </row>
     <row r="58">
       <c r="X58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11106,20 +11772,20 @@
     </row>
     <row r="59">
       <c r="X59" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -11134,11 +11800,11 @@
     </row>
     <row r="60">
       <c r="X60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -11147,7 +11813,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11162,11 +11828,11 @@
     </row>
     <row r="61">
       <c r="X61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -11175,7 +11841,7 @@
         </is>
       </c>
       <c r="AB61" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -11190,11 +11856,11 @@
     </row>
     <row r="62">
       <c r="X62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -11203,7 +11869,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -11218,11 +11884,11 @@
     </row>
     <row r="63">
       <c r="X63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -11246,11 +11912,11 @@
     </row>
     <row r="64">
       <c r="X64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -11274,11 +11940,11 @@
     </row>
     <row r="65">
       <c r="X65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -11302,11 +11968,11 @@
     </row>
     <row r="66">
       <c r="X66" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -11330,11 +11996,11 @@
     </row>
     <row r="67">
       <c r="X67" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -11358,11 +12024,11 @@
     </row>
     <row r="68">
       <c r="X68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -11371,7 +12037,7 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -11386,11 +12052,11 @@
     </row>
     <row r="69">
       <c r="X69" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -11399,7 +12065,7 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -11414,20 +12080,20 @@
     </row>
     <row r="70">
       <c r="X70" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11442,20 +12108,20 @@
     </row>
     <row r="71">
       <c r="X71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -11470,20 +12136,20 @@
     </row>
     <row r="72">
       <c r="X72" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
         <v>1</v>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB72" t="n">
-        <v>58</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -11502,16 +12168,16 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -11526,20 +12192,20 @@
     </row>
     <row r="74">
       <c r="X74" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -11554,20 +12220,20 @@
     </row>
     <row r="75">
       <c r="X75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -11582,11 +12248,11 @@
     </row>
     <row r="76">
       <c r="X76" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -11595,7 +12261,7 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
@@ -11610,11 +12276,11 @@
     </row>
     <row r="77">
       <c r="X77" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -11623,7 +12289,7 @@
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -11642,7 +12308,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -11651,7 +12317,7 @@
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -11670,7 +12336,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
@@ -11694,11 +12360,11 @@
     </row>
     <row r="80">
       <c r="X80" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
@@ -11707,7 +12373,7 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -11722,11 +12388,11 @@
     </row>
     <row r="81">
       <c r="X81" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
@@ -11735,7 +12401,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -11750,11 +12416,11 @@
     </row>
     <row r="82">
       <c r="X82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
@@ -11778,11 +12444,11 @@
     </row>
     <row r="83">
       <c r="X83" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
@@ -11806,11 +12472,11 @@
     </row>
     <row r="84">
       <c r="X84" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
@@ -11834,11 +12500,11 @@
     </row>
     <row r="85">
       <c r="X85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
@@ -11862,11 +12528,11 @@
     </row>
     <row r="86">
       <c r="X86" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
@@ -11894,7 +12560,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
@@ -11918,11 +12584,11 @@
     </row>
     <row r="88">
       <c r="X88" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
@@ -11946,11 +12612,11 @@
     </row>
     <row r="89">
       <c r="X89" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
@@ -11974,11 +12640,11 @@
     </row>
     <row r="90">
       <c r="X90" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -12002,11 +12668,11 @@
     </row>
     <row r="91">
       <c r="X91" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
@@ -12030,7 +12696,7 @@
     </row>
     <row r="92">
       <c r="X92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -12039,11 +12705,11 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -12058,20 +12724,20 @@
     </row>
     <row r="93">
       <c r="X93" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -12086,20 +12752,20 @@
     </row>
     <row r="94">
       <c r="X94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
         <v>3</v>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
-      </c>
-      <c r="AB94" t="n">
-        <v>28</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -12114,20 +12780,20 @@
     </row>
     <row r="95">
       <c r="X95" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB95" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
@@ -12142,16 +12808,16 @@
     </row>
     <row r="96">
       <c r="X96" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB96" t="n">
@@ -12170,20 +12836,20 @@
     </row>
     <row r="97">
       <c r="X97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -12202,16 +12868,16 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB98" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
@@ -12226,16 +12892,16 @@
     </row>
     <row r="99">
       <c r="X99" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB99" t="n">
@@ -12254,20 +12920,20 @@
     </row>
     <row r="100">
       <c r="X100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB100" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
@@ -12282,16 +12948,16 @@
     </row>
     <row r="101">
       <c r="X101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.woowabros</t>
         </is>
       </c>
       <c r="AB101" t="n">
@@ -12310,11 +12976,11 @@
     </row>
     <row r="102">
       <c r="X102" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
@@ -12338,11 +13004,11 @@
     </row>
     <row r="103">
       <c r="X103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
@@ -12366,11 +13032,11 @@
     </row>
     <row r="104">
       <c r="X104" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
@@ -12394,11 +13060,11 @@
     </row>
     <row r="105">
       <c r="X105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
@@ -12426,12 +13092,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB106" t="n">
@@ -12454,12 +13120,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB107" t="n">
@@ -12478,16 +13144,16 @@
     </row>
     <row r="108">
       <c r="X108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB108" t="n">
@@ -12506,16 +13172,16 @@
     </row>
     <row r="109">
       <c r="X109" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB109" t="n">
@@ -12534,20 +13200,20 @@
     </row>
     <row r="110">
       <c r="X110" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
@@ -12562,20 +13228,20 @@
     </row>
     <row r="111">
       <c r="X111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foody</t>
+          <t>com.logistics.rider.efood</t>
         </is>
       </c>
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
@@ -12589,6 +13255,19 @@
       </c>
     </row>
     <row r="112">
+      <c r="X112" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB112" t="n">
         <v>39</v>
       </c>
@@ -12604,6 +13283,19 @@
       </c>
     </row>
     <row r="113">
+      <c r="X113" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB113" t="n">
         <v>24</v>
       </c>
@@ -12619,6 +13311,19 @@
       </c>
     </row>
     <row r="114">
+      <c r="X114" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB114" t="n">
         <v>1</v>
       </c>
@@ -12634,8 +13339,21 @@
       </c>
     </row>
     <row r="115">
+      <c r="X115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
@@ -12649,6 +13367,19 @@
       </c>
     </row>
     <row r="116">
+      <c r="X116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB116" t="n">
         <v>111</v>
       </c>
@@ -12664,8 +13395,21 @@
       </c>
     </row>
     <row r="117">
+      <c r="X117" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB117" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
@@ -12679,6 +13423,19 @@
       </c>
     </row>
     <row r="118">
+      <c r="X118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB118" t="n">
         <v>1</v>
       </c>
@@ -12694,6 +13451,19 @@
       </c>
     </row>
     <row r="119">
+      <c r="X119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB119" t="n">
         <v>7</v>
       </c>
@@ -12709,6 +13479,19 @@
       </c>
     </row>
     <row r="120">
+      <c r="X120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
       <c r="AB120" t="n">
         <v>3</v>
       </c>
@@ -12725,7 +13508,7 @@
     </row>
     <row r="121">
       <c r="AB121" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
@@ -12740,7 +13523,7 @@
     </row>
     <row r="122">
       <c r="AB122" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
@@ -12800,7 +13583,7 @@
     </row>
     <row r="126">
       <c r="AB126" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
@@ -12815,7 +13598,7 @@
     </row>
     <row r="127">
       <c r="AB127" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -12965,7 +13748,7 @@
     </row>
     <row r="137">
       <c r="AB137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
@@ -12980,7 +13763,7 @@
     </row>
     <row r="138">
       <c r="AB138" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
@@ -12995,7 +13778,7 @@
     </row>
     <row r="139">
       <c r="AB139" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
@@ -13010,7 +13793,7 @@
     </row>
     <row r="140">
       <c r="AB140" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
@@ -13025,7 +13808,7 @@
     </row>
     <row r="141">
       <c r="AB141" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
@@ -13040,7 +13823,7 @@
     </row>
     <row r="142">
       <c r="AB142" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
@@ -13055,7 +13838,7 @@
     </row>
     <row r="143">
       <c r="AB143" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
@@ -13220,7 +14003,7 @@
     </row>
     <row r="154">
       <c r="AB154" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
@@ -13235,7 +14018,7 @@
     </row>
     <row r="155">
       <c r="AB155" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
@@ -13250,7 +14033,7 @@
     </row>
     <row r="156">
       <c r="AB156" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
@@ -13265,7 +14048,7 @@
     </row>
     <row r="157">
       <c r="AB157" t="n">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
@@ -13325,7 +14108,7 @@
     </row>
     <row r="161">
       <c r="AB161" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
@@ -13340,7 +14123,7 @@
     </row>
     <row r="162">
       <c r="AB162" t="n">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
@@ -13370,7 +14153,7 @@
     </row>
     <row r="164">
       <c r="AB164" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
@@ -13400,7 +14183,7 @@
     </row>
     <row r="166">
       <c r="AB166" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
@@ -13490,7 +14273,7 @@
     </row>
     <row r="172">
       <c r="AB172" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
@@ -13505,7 +14288,7 @@
     </row>
     <row r="173">
       <c r="AB173" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
@@ -13558,6 +14341,171 @@
         </is>
       </c>
       <c r="AD176" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="AB177" t="n">
+        <v>193</v>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="AB178" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="AB179" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="AB180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="AB181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="AB182" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="AB183" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="AB184" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="AB185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="AB186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="AB187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>
@@ -14102,7 +15050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14621,16 +15569,16 @@
         <v/>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -14698,7 +15646,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -14759,11 +15707,11 @@
         <v/>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -14834,11 +15782,11 @@
         <v/>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -14899,16 +15847,16 @@
         <v/>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -14964,16 +15912,16 @@
         <v/>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -14996,12 +15944,44 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="D13">
+        <f>SUMIFS(V:V,U:U,"*"&amp;$B$10&amp;"*",T:T,C13)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(X:X,Z:Z,"*"&amp;$B$10&amp;"*",Y:Y,C13)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>ROUND(MAX(0,MIN(100,(1-E13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30))*100)),2)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>MIN(1,(G13-$B$3)/($B$4-$B$3))*$B$1</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>SUMIFS(AB:AB,AD:AD,"*"&amp;$B$10&amp;"*",AC:AC,C13)</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>ROUND(MAX(0,MIN(100,100*(1-K13/IF(D13&gt;0,D13,SUMIFS(Consolidation!$M:$M,Consolidation!$A:$A,"*"&amp;$B$10&amp;"*")/30)))),2)</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>MAX(0,(L13-$B$6)/($B$7-$B$6)*$B$8)</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>$B$2+H13+M13</f>
+        <v/>
+      </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -15030,11 +16010,11 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -15067,7 +16047,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -15096,16 +16076,16 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -15129,16 +16109,16 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -15162,16 +16142,16 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -15195,11 +16175,11 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -15228,16 +16208,16 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -15261,16 +16241,16 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -15294,16 +16274,16 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -15327,16 +16307,16 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -15360,11 +16340,11 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -15393,16 +16373,16 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -15426,16 +16406,16 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -15459,16 +16439,16 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -15492,16 +16472,16 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -15525,16 +16505,16 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -15558,16 +16538,16 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>com.logistics.rider.woowabros</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -15591,16 +16571,16 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -15639,7 +16619,7 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -15648,7 +16628,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -15667,7 +16647,7 @@
     </row>
     <row r="33">
       <c r="D33">
-        <f>AVERAGE(D2:D12)</f>
+        <f>AVERAGE(D2:D13)</f>
         <v/>
       </c>
       <c r="G33" s="37">
@@ -15675,7 +16655,7 @@
         <v/>
       </c>
       <c r="H33">
-        <f>AVERAGE(H2:H12)</f>
+        <f>AVERAGE(H2:H13)</f>
         <v/>
       </c>
       <c r="I33" s="38">
@@ -15695,7 +16675,7 @@
         <v/>
       </c>
       <c r="X33" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -15704,7 +16684,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -15723,7 +16703,7 @@
     </row>
     <row r="34">
       <c r="X34" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -15732,7 +16712,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -15750,6 +16730,19 @@
       </c>
     </row>
     <row r="35">
+      <c r="X35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
       <c r="AB35" t="n">
         <v>51</v>
       </c>
@@ -15765,6 +16758,19 @@
       </c>
     </row>
     <row r="36">
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
       <c r="AB36" t="n">
         <v>6</v>
       </c>
@@ -15780,6 +16786,19 @@
       </c>
     </row>
     <row r="37">
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
       <c r="AB37" t="n">
         <v>2</v>
       </c>
@@ -15789,6 +16808,206 @@
         </is>
       </c>
       <c r="AD37" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="X38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>141</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodpanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="X41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="X42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foody</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="AB43" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.woowabros</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="AB45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.efood</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="AB46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
         <is>
           <t>com.logistics.rider.foody</t>
         </is>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -734,7 +734,7 @@
         <v>4.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0.82</v>
@@ -770,7 +770,7 @@
         <v>4.2</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0.82</v>
@@ -806,7 +806,7 @@
         <v>4.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0.82</v>
@@ -842,7 +842,7 @@
         <v>4.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.82</v>
@@ -878,7 +878,7 @@
         <v>4.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.82</v>
@@ -914,7 +914,7 @@
         <v>4.2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.82</v>
@@ -950,7 +950,7 @@
         <v>4.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0.82</v>
@@ -986,7 +986,7 @@
         <v>4.2</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.82</v>
@@ -1022,7 +1022,7 @@
         <v>4.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0.82</v>
@@ -1058,7 +1058,7 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1.162</v>
+        <v>1.14</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.82</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="AB7" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC7" s="7" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="Y15" s="7" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>55</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>5519</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>5569</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>5621</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>5557</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>5687</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC23" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>5395</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>5472</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="AC25" s="7" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>5687</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="7" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="AB29" s="7" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AC29" s="7" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>15396</v>
       </c>
       <c r="X40" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>15713</v>
       </c>
       <c r="X41" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y41" s="7" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>14823</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y42" s="4" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>14680</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y43" s="7" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>86030</v>
       </c>
       <c r="X46" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>82667</v>
       </c>
       <c r="X47" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y47" s="7" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="AB47" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC47" s="7" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>717</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>753</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AB63" s="7" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="AC63" s="7" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="AB65" s="7" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="AC65" s="7" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="AB71" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC71" s="7" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>51004</v>
       </c>
       <c r="X79" s="7" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Y79" s="7" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>50744</v>
       </c>
       <c r="X80" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>49774</v>
       </c>
       <c r="X84" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>49626</v>
       </c>
       <c r="X85" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y85" s="7" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="X90" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Y90" s="4" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>11599</v>
       </c>
       <c r="X91" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y91" s="7" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>11522</v>
       </c>
       <c r="X92" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y92" s="4" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>11614</v>
       </c>
       <c r="X93" s="7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y93" s="7" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>11098</v>
       </c>
       <c r="X94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y94" s="4" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>11097</v>
       </c>
       <c r="X95" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y95" s="7" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>11482</v>
       </c>
       <c r="X97" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y97" s="7" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>11380</v>
       </c>
       <c r="X99" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y99" s="7" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>11075</v>
       </c>
       <c r="X102" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>11539</v>
       </c>
       <c r="X103" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y103" s="7" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>11799</v>
       </c>
       <c r="X104" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>26509</v>
       </c>
       <c r="X105" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y105" s="7" t="inlineStr">
         <is>
@@ -6518,20 +6518,20 @@
         <v>26876</v>
       </c>
       <c r="X106" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y106" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z106" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.pedidosya</t>
+        </is>
+      </c>
+      <c r="AB106" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Y106" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Z106" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.pedidosya</t>
-        </is>
-      </c>
-      <c r="AB106" s="4" t="n">
-        <v>22</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>27154</v>
       </c>
       <c r="X107" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y107" s="7" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="AB107" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC107" s="7" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>26655</v>
       </c>
       <c r="X108" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y108" s="4" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="AC108" s="4" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>25267</v>
       </c>
       <c r="X109" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="7" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>24712</v>
       </c>
       <c r="X110" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Y110" s="4" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AB111" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC111" s="7" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>25640</v>
       </c>
       <c r="X112" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y112" s="4" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>26277</v>
       </c>
       <c r="X113" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y113" s="7" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>27017</v>
       </c>
       <c r="X114" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y114" s="4" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>26315</v>
       </c>
       <c r="X115" s="7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y115" s="7" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="AB115" s="7" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="AC115" s="7" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>17825</v>
       </c>
       <c r="X125" s="7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="7" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>17897</v>
       </c>
       <c r="X126" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="AB127" s="7" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="AC127" s="7" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>17704</v>
       </c>
       <c r="X128" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>17380</v>
       </c>
       <c r="X129" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y129" s="7" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>17336</v>
       </c>
       <c r="X130" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>17584</v>
       </c>
       <c r="X131" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y131" s="7" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="AB131" s="7" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>17915</v>
       </c>
       <c r="X132" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y132" s="4" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>783</v>
       </c>
       <c r="X136" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Y136" s="4" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>763</v>
       </c>
       <c r="X137" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y137" s="7" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="AB137" s="7" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>735</v>
       </c>
       <c r="X138" s="4" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y138" s="4" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>841</v>
       </c>
       <c r="X139" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y139" s="7" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>767</v>
       </c>
       <c r="X140" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y140" s="4" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>748</v>
       </c>
       <c r="X141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y141" s="7" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>772</v>
       </c>
       <c r="X143" s="7" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="Y143" s="7" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>728</v>
       </c>
       <c r="X144" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y144" s="4" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>744</v>
       </c>
       <c r="X145" s="7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Y145" s="7" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>2141</v>
       </c>
       <c r="X149" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Y149" s="7" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>2082</v>
       </c>
       <c r="X150" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Y150" s="4" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>1990</v>
       </c>
       <c r="X151" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y151" s="7" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="AB151" s="7" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AC151" s="7" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>2043</v>
       </c>
       <c r="X152" s="4" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="Y152" s="4" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
@@ -8445,20 +8445,20 @@
         <v>2148</v>
       </c>
       <c r="X153" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y153" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z153" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB153" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="Y153" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z153" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB153" s="7" t="n">
-        <v>139</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>2096</v>
       </c>
       <c r="X154" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y154" s="4" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="AB155" s="7" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="AC155" s="7" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>2187</v>
       </c>
       <c r="X156" s="4" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="Y156" s="4" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>2127</v>
       </c>
       <c r="X157" s="7" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Y157" s="7" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>2022</v>
       </c>
       <c r="X158" s="4" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="Y158" s="4" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>2040</v>
       </c>
       <c r="X159" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y159" s="7" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>2157</v>
       </c>
       <c r="X160" s="4" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="Y160" s="4" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
       <c r="U161" s="7" t="n"/>
       <c r="V161" s="7" t="n"/>
       <c r="X161" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y161" s="7" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
       <c r="U162" s="4" t="n"/>
       <c r="V162" s="4" t="n"/>
       <c r="X162" s="4" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="Y162" s="4" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
       <c r="U163" s="7" t="n"/>
       <c r="V163" s="7" t="n"/>
       <c r="X163" s="7" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="Y163" s="7" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
       <c r="U165" s="7" t="n"/>
       <c r="V165" s="7" t="n"/>
       <c r="X165" s="7" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="Y165" s="7" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>2</v>
+        <v>291</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
       <c r="U169" s="7" t="n"/>
       <c r="V169" s="7" t="n"/>
       <c r="X169" s="7" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="Y169" s="7" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
       <c r="U170" s="4" t="n"/>
       <c r="V170" s="4" t="n"/>
       <c r="X170" s="4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="Y170" s="4" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>291</v>
+        <v>2</v>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
       <c r="U171" s="7" t="n"/>
       <c r="V171" s="7" t="n"/>
       <c r="X171" s="7" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Y171" s="7" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="AB171" s="7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AC171" s="7" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="AB173" s="7" t="n">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="AC173" s="7" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
       <c r="U176" s="4" t="n"/>
       <c r="V176" s="4" t="n"/>
       <c r="X176" s="4" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="Y176" s="4" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
       <c r="U177" s="7" t="n"/>
       <c r="V177" s="7" t="n"/>
       <c r="X177" s="7" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Y177" s="7" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="AB177" s="7" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="AC177" s="7" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="AB180" s="4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="AC180" s="4" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="AB183" s="7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AC183" s="7" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
       <c r="U192" s="4" t="n"/>
       <c r="V192" s="4" t="n"/>
       <c r="X192" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y192" s="4" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
       <c r="U193" s="7" t="n"/>
       <c r="V193" s="7" t="n"/>
       <c r="X193" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y193" s="7" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
       <c r="U194" s="4" t="n"/>
       <c r="V194" s="4" t="n"/>
       <c r="X194" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y194" s="4" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
       <c r="U195" s="7" t="n"/>
       <c r="V195" s="7" t="n"/>
       <c r="X195" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y195" s="7" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="AC196" s="4" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="AB197" s="7" t="n">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="AC197" s="7" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="AB199" s="7" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="AC199" s="7" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
       <c r="U200" s="4" t="n"/>
       <c r="V200" s="4" t="n"/>
       <c r="X200" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y200" s="4" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
       <c r="U201" s="7" t="n"/>
       <c r="V201" s="7" t="n"/>
       <c r="X201" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y201" s="7" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="AB201" s="7" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AC201" s="7" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       <c r="U202" s="4" t="n"/>
       <c r="V202" s="4" t="n"/>
       <c r="X202" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y202" s="4" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AC202" s="4" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
       <c r="U203" s="7" t="n"/>
       <c r="V203" s="7" t="n"/>
       <c r="X203" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y203" s="7" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="AB203" s="7" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AC203" s="7" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="AB205" s="7" t="n">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="AC205" s="7" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="AB206" s="4" t="n">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="AC206" s="4" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
       <c r="Y213" s="7" t="n"/>
       <c r="Z213" s="7" t="n"/>
       <c r="AB213" s="7" t="n">
-        <v>216</v>
+        <v>87</v>
       </c>
       <c r="AC213" s="7" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
       <c r="Y215" s="7" t="n"/>
       <c r="Z215" s="7" t="n"/>
       <c r="AB215" s="7" t="n">
-        <v>87</v>
+        <v>216</v>
       </c>
       <c r="AC215" s="7" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
       <c r="Y218" s="4" t="n"/>
       <c r="Z218" s="4" t="n"/>
       <c r="AB218" s="4" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="AC218" s="4" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
       <c r="Y220" s="4" t="n"/>
       <c r="Z220" s="4" t="n"/>
       <c r="AB220" s="4" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AC220" s="4" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
       <c r="Y221" s="7" t="n"/>
       <c r="Z221" s="7" t="n"/>
       <c r="AB221" s="7" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="AC221" s="7" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       <c r="Y222" s="4" t="n"/>
       <c r="Z222" s="4" t="n"/>
       <c r="AB222" s="4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="AC222" s="4" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
       <c r="Y224" s="4" t="n"/>
       <c r="Z224" s="4" t="n"/>
       <c r="AB224" s="4" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="AC224" s="4" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
       <c r="Y225" s="7" t="n"/>
       <c r="Z225" s="7" t="n"/>
       <c r="AB225" s="7" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="AC225" s="7" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
       <c r="Y226" s="4" t="n"/>
       <c r="Z226" s="4" t="n"/>
       <c r="AB226" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC226" s="4" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
       <c r="Y227" s="7" t="n"/>
       <c r="Z227" s="7" t="n"/>
       <c r="AB227" s="7" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AC227" s="7" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
       <c r="Y228" s="4" t="n"/>
       <c r="Z228" s="4" t="n"/>
       <c r="AB228" s="4" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="AC228" s="4" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
       <c r="Y229" s="7" t="n"/>
       <c r="Z229" s="7" t="n"/>
       <c r="AB229" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AC229" s="7" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       <c r="Y234" s="4" t="n"/>
       <c r="Z234" s="4" t="n"/>
       <c r="AB234" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC234" s="4" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
       <c r="Y235" s="7" t="n"/>
       <c r="Z235" s="7" t="n"/>
       <c r="AB235" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC235" s="7" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
       <c r="Y240" s="4" t="n"/>
       <c r="Z240" s="4" t="n"/>
       <c r="AB240" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC240" s="4" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
       <c r="Y241" s="7" t="n"/>
       <c r="Z241" s="7" t="n"/>
       <c r="AB241" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC241" s="7" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
       <c r="Y242" s="4" t="n"/>
       <c r="Z242" s="4" t="n"/>
       <c r="AB242" s="4" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="AC242" s="4" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
       <c r="Y243" s="7" t="n"/>
       <c r="Z243" s="7" t="n"/>
       <c r="AB243" s="7" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AC243" s="7" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
       <c r="Y246" s="4" t="n"/>
       <c r="Z246" s="4" t="n"/>
       <c r="AB246" s="4" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="AC246" s="4" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
       <c r="Y247" s="7" t="n"/>
       <c r="Z247" s="7" t="n"/>
       <c r="AB247" s="7" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="AC247" s="7" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
       <c r="Y248" s="4" t="n"/>
       <c r="Z248" s="4" t="n"/>
       <c r="AB248" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AC248" s="4" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
       <c r="Y249" s="7" t="n"/>
       <c r="Z249" s="7" t="n"/>
       <c r="AB249" s="7" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AC249" s="7" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
       <c r="Y263" s="7" t="n"/>
       <c r="Z263" s="7" t="n"/>
       <c r="AB263" s="7" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="AC263" s="7" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
       <c r="Y264" s="4" t="n"/>
       <c r="Z264" s="4" t="n"/>
       <c r="AB264" s="4" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="AC264" s="4" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
       <c r="Y265" s="7" t="n"/>
       <c r="Z265" s="7" t="n"/>
       <c r="AB265" s="7" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AC265" s="7" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
       <c r="Y267" s="7" t="n"/>
       <c r="Z267" s="7" t="n"/>
       <c r="AB267" s="7" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AC267" s="7" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
       <c r="Y278" s="4" t="n"/>
       <c r="Z278" s="4" t="n"/>
       <c r="AB278" s="4" t="n">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="AC278" s="4" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
       <c r="Y279" s="7" t="n"/>
       <c r="Z279" s="7" t="n"/>
       <c r="AB279" s="7" t="n">
-        <v>228</v>
+        <v>134</v>
       </c>
       <c r="AC279" s="7" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
       <c r="Y280" s="4" t="n"/>
       <c r="Z280" s="4" t="n"/>
       <c r="AB280" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AC280" s="4" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
       <c r="Y281" s="7" t="n"/>
       <c r="Z281" s="7" t="n"/>
       <c r="AB281" s="7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AC281" s="7" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
       <c r="Y282" s="4" t="n"/>
       <c r="Z282" s="4" t="n"/>
       <c r="AB282" s="4" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="AC282" s="4" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
       <c r="Y283" s="7" t="n"/>
       <c r="Z283" s="7" t="n"/>
       <c r="AB283" s="7" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="AC283" s="7" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
       <c r="Y285" s="7" t="n"/>
       <c r="Z285" s="7" t="n"/>
       <c r="AB285" s="7" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="AC285" s="7" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="Y286" s="4" t="n"/>
       <c r="Z286" s="4" t="n"/>
       <c r="AB286" s="4" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="AC286" s="4" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
       <c r="Y287" s="7" t="n"/>
       <c r="Z287" s="7" t="n"/>
       <c r="AB287" s="7" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AC287" s="7" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
       <c r="Y288" s="4" t="n"/>
       <c r="Z288" s="4" t="n"/>
       <c r="AB288" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AC288" s="4" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
       <c r="Y294" s="4" t="n"/>
       <c r="Z294" s="4" t="n"/>
       <c r="AB294" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC294" s="4" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
       <c r="Y295" s="7" t="n"/>
       <c r="Z295" s="7" t="n"/>
       <c r="AB295" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC295" s="7" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>7963</v>
       </c>
       <c r="X35" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -14399,20 +14399,20 @@
         <v>11169</v>
       </c>
       <c r="X36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.talabat</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
         <v>1</v>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.talabat</t>
-        </is>
-      </c>
-      <c r="AB36" t="n">
-        <v>3</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>11593</v>
       </c>
       <c r="X39" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>10855</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>3533</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>4891</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>20742</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>19079</v>
       </c>
       <c r="X54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>2882</v>
       </c>
       <c r="X60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>3280</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>3951</v>
       </c>
       <c r="X62" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>5096</v>
       </c>
       <c r="X63" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>5937</v>
       </c>
       <c r="X67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>5525</v>
       </c>
       <c r="X68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>975</v>
       </c>
       <c r="X84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>622</v>
       </c>
       <c r="X85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         </is>
       </c>
       <c r="AB85" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         </is>
       </c>
       <c r="AB86" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="AB87" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         </is>
       </c>
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>13894</v>
       </c>
       <c r="X89" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>17235</v>
       </c>
       <c r="X90" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>23145</v>
       </c>
       <c r="X91" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="AB91" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>32675</v>
       </c>
       <c r="X92" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>33649</v>
       </c>
       <c r="X95" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>30739</v>
       </c>
       <c r="X96" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>27294</v>
       </c>
       <c r="X97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>21596</v>
       </c>
       <c r="X98" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>13483</v>
       </c>
       <c r="X99" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         </is>
       </c>
       <c r="AB102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>354</v>
       </c>
       <c r="X106" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>347</v>
       </c>
       <c r="X107" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>176</v>
       </c>
       <c r="X113" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>603</v>
       </c>
       <c r="X114" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         </is>
       </c>
       <c r="AB124" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         </is>
       </c>
       <c r="AB125" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="AB137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>304</v>
       </c>
       <c r="AB139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
     </row>
     <row r="142">
       <c r="AB142" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
     </row>
     <row r="143">
       <c r="AB143" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
     </row>
     <row r="161">
       <c r="AB161" t="n">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
     </row>
     <row r="162">
       <c r="AB162" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
     </row>
     <row r="165">
       <c r="AB165" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
     </row>
     <row r="166">
       <c r="AB166" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AC166" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
     </row>
     <row r="170">
       <c r="AB170" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
     </row>
     <row r="171">
       <c r="AB171" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC171" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
     </row>
     <row r="179">
       <c r="AB179" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
     </row>
     <row r="180">
       <c r="AB180" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
     </row>
     <row r="200">
       <c r="AB200" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
     </row>
     <row r="201">
       <c r="AB201" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>4.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0.58</v>
@@ -19808,7 +19808,7 @@
         <v>4.2</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0.58</v>
@@ -19844,7 +19844,7 @@
         <v>4.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0.58</v>
@@ -19880,7 +19880,7 @@
         <v>4.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.58</v>
@@ -19916,7 +19916,7 @@
         <v>4.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.58</v>
@@ -19952,7 +19952,7 @@
         <v>4.2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.58</v>
@@ -19988,7 +19988,7 @@
         <v>4.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0.58</v>
@@ -20024,7 +20024,7 @@
         <v>4.2</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.58</v>
@@ -20060,7 +20060,7 @@
         <v>4.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0.58</v>
@@ -20096,7 +20096,7 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.58</v>
@@ -23986,7 +23986,7 @@
         <v>4.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0.58</v>
@@ -24022,7 +24022,7 @@
         <v>4.2</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0.58</v>
@@ -24058,7 +24058,7 @@
         <v>4.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0.58</v>
@@ -24094,7 +24094,7 @@
         <v>4.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.58</v>
@@ -24130,7 +24130,7 @@
         <v>4.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.58</v>
@@ -24166,7 +24166,7 @@
         <v>4.2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.58</v>
@@ -24202,7 +24202,7 @@
         <v>4.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0.58</v>
@@ -24238,7 +24238,7 @@
         <v>4.2</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.58</v>
@@ -24274,7 +24274,7 @@
         <v>4.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0.58</v>
@@ -24310,7 +24310,7 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.58</v>

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="AC3" s="7" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="Y7" s="7" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="Y11" s="7" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="X13" s="7" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="AC15" s="7" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y17" s="7" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="Y19" s="7" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="AC21" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y23" s="7" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>55</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="Y25" s="7" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>5519</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>5196</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>5203</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="7" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>5472</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="Y34" s="4" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>5687</v>
       </c>
       <c r="X35" s="7" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="Y35" s="7" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AB35" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="7" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="AB37" s="7" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="AC37" s="7" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>5547</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>5822</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="Y39" s="7" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="AB43" s="7" t="n">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="AC43" s="7" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>5476</v>
       </c>
       <c r="X44" s="4" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="Y44" s="4" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="AC44" s="4" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>5446</v>
       </c>
       <c r="X45" s="7" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="Y45" s="7" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AC52" s="4" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>14553</v>
       </c>
       <c r="X53" s="7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="7" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="AB53" s="7" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="AC53" s="7" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>14491</v>
       </c>
       <c r="X54" s="4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>15132</v>
       </c>
       <c r="X55" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y55" s="7" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="AB55" s="7" t="n">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="AC55" s="7" t="inlineStr">
         <is>
@@ -4650,20 +4650,20 @@
         <v>15616</v>
       </c>
       <c r="X56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z56" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.foodora</t>
+        </is>
+      </c>
+      <c r="AB56" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="Y56" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.foodora</t>
-        </is>
-      </c>
-      <c r="AB56" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>15857</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="7" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="AB57" s="7" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="AC57" s="7" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>15396</v>
       </c>
       <c r="X58" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y58" s="4" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>14680</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y61" s="7" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="AB61" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC61" s="7" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>15388</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y62" s="4" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>15462</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y65" s="7" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>15905</v>
       </c>
       <c r="X66" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y66" s="4" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="AB67" s="7" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="7" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="AB73" s="7" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AC73" s="7" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>82796</v>
       </c>
       <c r="X75" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="7" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="AB75" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="AC75" s="7" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>80792</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y76" s="4" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="AB77" s="7" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="AC77" s="7" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>3</v>
+        <v>327</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="AB83" s="7" t="n">
-        <v>327</v>
+        <v>3</v>
       </c>
       <c r="AC83" s="7" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="AB85" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="7" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="AB87" s="7" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="AC87" s="7" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="AB91" s="7" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AC91" s="7" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="AB93" s="7" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AC93" s="7" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="AB95" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC95" s="7" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>717</v>
       </c>
       <c r="X97" s="7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Y97" s="7" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="AB97" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC97" s="7" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>753</v>
       </c>
       <c r="X98" s="4" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="Y98" s="4" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="AB99" s="7" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="AC99" s="7" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>743</v>
       </c>
       <c r="X101" s="7" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="Y101" s="7" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>714</v>
       </c>
       <c r="X102" s="4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Y102" s="4" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>733</v>
       </c>
       <c r="X103" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y103" s="7" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>737</v>
       </c>
       <c r="X104" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y104" s="4" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>736</v>
       </c>
       <c r="X105" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y105" s="7" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>701</v>
       </c>
       <c r="X107" s="7" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Y107" s="7" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>736</v>
       </c>
       <c r="X108" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Y108" s="4" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>731</v>
       </c>
       <c r="X109" s="7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Y109" s="7" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="AB109" s="7" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="AC109" s="7" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>712</v>
       </c>
       <c r="X112" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Y112" s="4" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="7" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>701</v>
       </c>
       <c r="X114" s="4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Y114" s="4" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="AB117" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AC117" s="7" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>51501</v>
       </c>
       <c r="X119" s="7" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="Y119" s="7" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>51715</v>
       </c>
       <c r="X120" s="4" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="4" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>50744</v>
       </c>
       <c r="X125" s="7" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="7" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>50396</v>
       </c>
       <c r="X126" s="4" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>51782</v>
       </c>
       <c r="X127" s="7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="Y127" s="7" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>50710</v>
       </c>
       <c r="X128" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>49774</v>
       </c>
       <c r="X129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y129" s="7" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="AB129" s="7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AC129" s="7" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>49626</v>
       </c>
       <c r="X130" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>51869</v>
       </c>
       <c r="X131" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y131" s="7" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="AB131" s="7" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="AC131" s="7" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>51059</v>
       </c>
       <c r="X133" s="7" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Y133" s="7" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="AB133" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC133" s="7" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>51562</v>
       </c>
       <c r="X135" s="7" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="Y135" s="7" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="AB135" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC135" s="7" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>50612</v>
       </c>
       <c r="X136" s="4" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="Y136" s="4" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="AB137" s="7" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AC137" s="7" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="AB139" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC139" s="7" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AB141" s="7" t="n">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="AC141" s="7" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="AB143" s="7" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="AC143" s="7" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="X144" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y144" s="4" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="X145" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y145" s="7" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="AB145" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC145" s="7" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>1</v>
       </c>
       <c r="X146" s="4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Y146" s="4" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="X147" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Y147" s="7" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="X150" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y150" s="4" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="X151" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y151" s="7" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>1</v>
       </c>
       <c r="X153" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y153" s="7" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="AB153" s="7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AC153" s="7" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="X154" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y154" s="4" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="X155" s="7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y155" s="7" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="X156" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y156" s="4" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="X157" s="7" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y157" s="7" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="X158" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y158" s="4" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>11599</v>
       </c>
       <c r="X159" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y159" s="7" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="AB161" s="7" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="AC161" s="7" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>11098</v>
       </c>
       <c r="X162" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y162" s="4" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>11097</v>
       </c>
       <c r="X163" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y163" s="7" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="AB163" s="7" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="AC163" s="7" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>11410</v>
       </c>
       <c r="X164" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y164" s="4" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>11482</v>
       </c>
       <c r="X165" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y165" s="7" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="AB165" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC165" s="7" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>11322</v>
       </c>
       <c r="X166" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Y166" s="4" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="AC168" s="4" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="AB169" s="7" t="n">
-        <v>55</v>
+        <v>291</v>
       </c>
       <c r="AC169" s="7" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>11075</v>
       </c>
       <c r="X170" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y170" s="4" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>11539</v>
       </c>
       <c r="X171" s="7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Y171" s="7" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="AB171" s="7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AC171" s="7" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>11799</v>
       </c>
       <c r="X172" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y172" s="4" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>11712</v>
       </c>
       <c r="X173" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y173" s="7" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>11683</v>
       </c>
       <c r="X174" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Y174" s="4" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>11729</v>
       </c>
       <c r="X175" s="7" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y175" s="7" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="AB179" s="7" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="AC179" s="7" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="AB180" s="4" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AC180" s="4" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="AB181" s="7" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="AC181" s="7" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="AB183" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC183" s="7" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>26876</v>
       </c>
       <c r="X184" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y184" s="4" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="AB184" s="4" t="n">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="AC184" s="4" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>27154</v>
       </c>
       <c r="X185" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y185" s="7" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>26655</v>
       </c>
       <c r="X186" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y186" s="4" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="AC186" s="4" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>25267</v>
       </c>
       <c r="X187" s="7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y187" s="7" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="AB189" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC189" s="7" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="AB190" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AC190" s="4" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>26277</v>
       </c>
       <c r="X191" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y191" s="7" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>27017</v>
       </c>
       <c r="X192" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y192" s="4" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="AB192" s="4" t="n">
-        <v>268</v>
+        <v>72</v>
       </c>
       <c r="AC192" s="4" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AB193" s="7" t="n">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="AC193" s="7" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>26408</v>
       </c>
       <c r="X195" s="7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y195" s="7" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>26352</v>
       </c>
       <c r="X196" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y196" s="4" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="AB197" s="7" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="AC197" s="7" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AB198" s="4" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="AC198" s="4" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="AB199" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AC199" s="7" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="AB201" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC201" s="7" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>24680</v>
       </c>
       <c r="X202" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y202" s="4" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AC202" s="4" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>25365</v>
       </c>
       <c r="X204" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y204" s="4" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="AB204" s="4" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AC204" s="4" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>17949</v>
       </c>
       <c r="X206" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y206" s="4" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>17549</v>
       </c>
       <c r="X207" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y207" s="7" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>17646</v>
       </c>
       <c r="X208" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y208" s="4" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>17131</v>
       </c>
       <c r="X209" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Y209" s="7" t="inlineStr">
         <is>
@@ -10964,20 +10964,20 @@
         <v>17470</v>
       </c>
       <c r="X210" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y210" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z210" s="4" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.hungerstation</t>
+        </is>
+      </c>
+      <c r="AB210" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="Y210" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="Z210" s="4" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.hungerstation</t>
-        </is>
-      </c>
-      <c r="AB210" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC210" s="4" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>17485</v>
       </c>
       <c r="X211" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y211" s="7" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="AB211" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC211" s="7" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="AB213" s="7" t="n">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="AC213" s="7" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         </is>
       </c>
       <c r="AB215" s="7" t="n">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="AC215" s="7" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>18111</v>
       </c>
       <c r="X220" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y220" s="4" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>17792</v>
       </c>
       <c r="X221" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y221" s="7" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>17777</v>
       </c>
       <c r="X222" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Y222" s="4" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>17292</v>
       </c>
       <c r="X223" s="7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="Y223" s="7" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="AB223" s="7" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="AC223" s="7" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="AC224" s="4" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="AB226" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AC226" s="4" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="AB227" s="7" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AC227" s="7" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>17803</v>
       </c>
       <c r="X228" s="4" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y228" s="4" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>745</v>
       </c>
       <c r="X229" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y229" s="7" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="AB229" s="7" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AC229" s="7" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>763</v>
       </c>
       <c r="X230" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Y230" s="4" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>740</v>
       </c>
       <c r="X231" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y231" s="7" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="AB231" s="7" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="AC231" s="7" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>783</v>
       </c>
       <c r="X232" s="4" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y232" s="4" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         </is>
       </c>
       <c r="AB232" s="4" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="AC232" s="4" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>763</v>
       </c>
       <c r="X233" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y233" s="7" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>841</v>
       </c>
       <c r="X235" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y235" s="7" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="AC238" s="4" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>772</v>
       </c>
       <c r="X239" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="Y239" s="7" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="AB239" s="7" t="n">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="AC239" s="7" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>728</v>
       </c>
       <c r="X240" s="4" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Y240" s="4" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>744</v>
       </c>
       <c r="X241" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y241" s="7" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>786</v>
       </c>
       <c r="X242" s="4" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="Y242" s="4" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>769</v>
       </c>
       <c r="X243" s="7" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="Y243" s="7" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="AB245" s="7" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="AC245" s="7" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="AC246" s="4" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>728</v>
       </c>
       <c r="X247" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y247" s="7" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="AB247" s="7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AC247" s="7" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>709</v>
       </c>
       <c r="X248" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y248" s="4" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>735</v>
       </c>
       <c r="X250" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y250" s="4" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>773</v>
       </c>
       <c r="X251" s="7" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="Y251" s="7" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>2142</v>
       </c>
       <c r="X252" s="4" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="Y252" s="4" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>2408</v>
       </c>
       <c r="X253" s="7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y253" s="7" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>2141</v>
       </c>
       <c r="X254" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y254" s="4" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="AB254" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC254" s="4" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="AB255" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC255" s="7" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="AC258" s="4" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         </is>
       </c>
       <c r="AB259" s="7" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="AC259" s="7" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>2265</v>
       </c>
       <c r="X260" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Y260" s="4" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>2187</v>
       </c>
       <c r="X261" s="7" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Y261" s="7" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>2127</v>
       </c>
       <c r="X262" s="4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Y262" s="4" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>2022</v>
       </c>
       <c r="X263" s="7" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="Y263" s="7" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>2040</v>
       </c>
       <c r="X264" s="4" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="Y264" s="4" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="AB265" s="7" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="AC265" s="7" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>2187</v>
       </c>
       <c r="X266" s="4" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Y266" s="4" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="AB266" s="4" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AC266" s="4" t="inlineStr">
         <is>
@@ -13301,20 +13301,20 @@
         <v>2290</v>
       </c>
       <c r="X267" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y267" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z267" s="7" t="inlineStr">
+        <is>
+          <t>com.logistics.rider.glovo</t>
+        </is>
+      </c>
+      <c r="AB267" s="7" t="n">
         <v>27</v>
-      </c>
-      <c r="Y267" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z267" s="7" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
-      <c r="AB267" s="7" t="n">
-        <v>59</v>
       </c>
       <c r="AC267" s="7" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="AB268" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AC268" s="4" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         </is>
       </c>
       <c r="AB269" s="7" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="AC269" s="7" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="AB271" s="7" t="n">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="AC271" s="7" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="AB272" s="4" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="AC272" s="4" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>2160</v>
       </c>
       <c r="X273" s="7" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="Y273" s="7" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>2276</v>
       </c>
       <c r="X274" s="4" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="Y274" s="4" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="AB275" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC275" s="7" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
       <c r="U276" s="4" t="n"/>
       <c r="V276" s="4" t="n"/>
       <c r="X276" s="4" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="Y276" s="4" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="AB276" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC276" s="4" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       <c r="U277" s="7" t="n"/>
       <c r="V277" s="7" t="n"/>
       <c r="X277" s="7" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="Y277" s="7" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
       <c r="U278" s="4" t="n"/>
       <c r="V278" s="4" t="n"/>
       <c r="X278" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y278" s="4" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       <c r="U279" s="7" t="n"/>
       <c r="V279" s="7" t="n"/>
       <c r="X279" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Y279" s="7" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
       <c r="U280" s="4" t="n"/>
       <c r="V280" s="4" t="n"/>
       <c r="X280" s="4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="Y280" s="4" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
       <c r="U281" s="7" t="n"/>
       <c r="V281" s="7" t="n"/>
       <c r="X281" s="7" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="Y281" s="7" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
       <c r="U282" s="4" t="n"/>
       <c r="V282" s="4" t="n"/>
       <c r="X282" s="4" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="Y282" s="4" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         </is>
       </c>
       <c r="AB285" s="7" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="AC285" s="7" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       <c r="U286" s="4" t="n"/>
       <c r="V286" s="4" t="n"/>
       <c r="X286" s="4" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="Y286" s="4" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="AC286" s="4" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
       <c r="U287" s="7" t="n"/>
       <c r="V287" s="7" t="n"/>
       <c r="X287" s="7" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="Y287" s="7" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="AB287" s="7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AC287" s="7" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
       <c r="U288" s="4" t="n"/>
       <c r="V288" s="4" t="n"/>
       <c r="X288" s="4" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y288" s="4" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AC288" s="4" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
       <c r="U289" s="7" t="n"/>
       <c r="V289" s="7" t="n"/>
       <c r="X289" s="7" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y289" s="7" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         </is>
       </c>
       <c r="AB294" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC294" s="4" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AB295" s="7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC295" s="7" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
       <c r="U297" s="7" t="n"/>
       <c r="V297" s="7" t="n"/>
       <c r="X297" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y297" s="7" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
       <c r="U298" s="4" t="n"/>
       <c r="V298" s="4" t="n"/>
       <c r="X298" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y298" s="4" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="AB298" s="4" t="n">
-        <v>258</v>
+        <v>90</v>
       </c>
       <c r="AC298" s="4" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="AB299" s="7" t="n">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="AC299" s="7" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="AB302" s="4" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="AC302" s="4" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
       <c r="U303" s="7" t="n"/>
       <c r="V303" s="7" t="n"/>
       <c r="X303" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y303" s="7" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="AB303" s="7" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="AC303" s="7" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
       <c r="U304" s="4" t="n"/>
       <c r="V304" s="4" t="n"/>
       <c r="X304" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y304" s="4" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         </is>
       </c>
       <c r="AB305" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC305" s="7" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="AB306" s="4" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="AC306" s="4" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         </is>
       </c>
       <c r="AB307" s="7" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="AC307" s="7" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
       <c r="U308" s="4" t="n"/>
       <c r="V308" s="4" t="n"/>
       <c r="X308" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y308" s="4" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
       <c r="U309" s="7" t="n"/>
       <c r="V309" s="7" t="n"/>
       <c r="X309" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y309" s="7" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
       <c r="U310" s="4" t="n"/>
       <c r="V310" s="4" t="n"/>
       <c r="X310" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y310" s="4" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
       <c r="U311" s="7" t="n"/>
       <c r="V311" s="7" t="n"/>
       <c r="X311" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y311" s="7" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
       <c r="U316" s="4" t="n"/>
       <c r="V316" s="4" t="n"/>
       <c r="X316" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y316" s="4" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
       <c r="U317" s="7" t="n"/>
       <c r="V317" s="7" t="n"/>
       <c r="X317" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y317" s="7" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="AB318" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AC318" s="4" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
       <c r="U319" s="7" t="n"/>
       <c r="V319" s="7" t="n"/>
       <c r="X319" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y319" s="7" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="AB319" s="7" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AC319" s="7" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
       <c r="U320" s="4" t="n"/>
       <c r="V320" s="4" t="n"/>
       <c r="X320" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y320" s="4" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
       <c r="U323" s="7" t="n"/>
       <c r="V323" s="7" t="n"/>
       <c r="X323" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y323" s="7" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
       <c r="U324" s="4" t="n"/>
       <c r="V324" s="4" t="n"/>
       <c r="X324" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y324" s="4" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         </is>
       </c>
       <c r="AB324" s="4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="AC324" s="4" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="AB325" s="7" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AC325" s="7" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         </is>
       </c>
       <c r="AB327" s="7" t="n">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="AC327" s="7" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         </is>
       </c>
       <c r="AB328" s="4" t="n">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="AC328" s="4" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="AB334" s="4" t="n">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="AC334" s="4" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         </is>
       </c>
       <c r="AB335" s="7" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AC335" s="7" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="AB338" s="4" t="n">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="AC338" s="4" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
       <c r="U340" s="4" t="n"/>
       <c r="V340" s="4" t="n"/>
       <c r="X340" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y340" s="4" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="AB340" s="4" t="n">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="AC340" s="4" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
       <c r="U341" s="7" t="n"/>
       <c r="V341" s="7" t="n"/>
       <c r="X341" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y341" s="7" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="AB341" s="7" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="AC341" s="7" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="AC342" s="4" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
       <c r="U343" s="7" t="n"/>
       <c r="V343" s="7" t="n"/>
       <c r="X343" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y343" s="7" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
       <c r="U344" s="4" t="n"/>
       <c r="V344" s="4" t="n"/>
       <c r="X344" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y344" s="4" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
       <c r="Y348" s="4" t="n"/>
       <c r="Z348" s="4" t="n"/>
       <c r="AB348" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC348" s="4" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
       <c r="Y349" s="7" t="n"/>
       <c r="Z349" s="7" t="n"/>
       <c r="AB349" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC349" s="7" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
       <c r="Y357" s="7" t="n"/>
       <c r="Z357" s="7" t="n"/>
       <c r="AB357" s="7" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AC357" s="7" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
       <c r="Y358" s="4" t="n"/>
       <c r="Z358" s="4" t="n"/>
       <c r="AB358" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC358" s="4" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
       <c r="Y359" s="7" t="n"/>
       <c r="Z359" s="7" t="n"/>
       <c r="AB359" s="7" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="AC359" s="7" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
       <c r="Y360" s="4" t="n"/>
       <c r="Z360" s="4" t="n"/>
       <c r="AB360" s="4" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="AC360" s="4" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
       <c r="Y369" s="7" t="n"/>
       <c r="Z369" s="7" t="n"/>
       <c r="AB369" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC369" s="7" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
       <c r="Y370" s="4" t="n"/>
       <c r="Z370" s="4" t="n"/>
       <c r="AB370" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC370" s="4" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
       <c r="Y375" s="7" t="n"/>
       <c r="Z375" s="7" t="n"/>
       <c r="AB375" s="7" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="AC375" s="7" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
       <c r="Y376" s="4" t="n"/>
       <c r="Z376" s="4" t="n"/>
       <c r="AB376" s="4" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="AC376" s="4" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
       <c r="Y381" s="7" t="n"/>
       <c r="Z381" s="7" t="n"/>
       <c r="AB381" s="7" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="AC381" s="7" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
       <c r="Y382" s="4" t="n"/>
       <c r="Z382" s="4" t="n"/>
       <c r="AB382" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="AC382" s="4" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
       <c r="Y384" s="4" t="n"/>
       <c r="Z384" s="4" t="n"/>
       <c r="AB384" s="4" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="AC384" s="4" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
       <c r="Y385" s="7" t="n"/>
       <c r="Z385" s="7" t="n"/>
       <c r="AB385" s="7" t="n">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="AC385" s="7" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
       <c r="Y392" s="4" t="n"/>
       <c r="Z392" s="4" t="n"/>
       <c r="AB392" s="4" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AC392" s="4" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
       <c r="Y393" s="7" t="n"/>
       <c r="Z393" s="7" t="n"/>
       <c r="AB393" s="7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AC393" s="7" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
       <c r="Y396" s="4" t="n"/>
       <c r="Z396" s="4" t="n"/>
       <c r="AB396" s="4" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="AC396" s="4" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
       <c r="Y397" s="7" t="n"/>
       <c r="Z397" s="7" t="n"/>
       <c r="AB397" s="7" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="AC397" s="7" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
       <c r="Y415" s="7" t="n"/>
       <c r="Z415" s="7" t="n"/>
       <c r="AB415" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AC415" s="7" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
       <c r="Y416" s="4" t="n"/>
       <c r="Z416" s="4" t="n"/>
       <c r="AB416" s="4" t="n">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="AC416" s="4" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
       <c r="Y417" s="7" t="n"/>
       <c r="Z417" s="7" t="n"/>
       <c r="AB417" s="7" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="AC417" s="7" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
       <c r="Y419" s="7" t="n"/>
       <c r="Z419" s="7" t="n"/>
       <c r="AB419" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC419" s="7" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
       <c r="Y420" s="4" t="n"/>
       <c r="Z420" s="4" t="n"/>
       <c r="AB420" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC420" s="4" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
       <c r="Y423" s="7" t="n"/>
       <c r="Z423" s="7" t="n"/>
       <c r="AB423" s="7" t="n">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="AC423" s="7" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
       <c r="Y424" s="4" t="n"/>
       <c r="Z424" s="4" t="n"/>
       <c r="AB424" s="4" t="n">
-        <v>289</v>
+        <v>49</v>
       </c>
       <c r="AC424" s="4" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
       <c r="Y425" s="7" t="n"/>
       <c r="Z425" s="7" t="n"/>
       <c r="AB425" s="7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="AC425" s="7" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
       <c r="Y426" s="4" t="n"/>
       <c r="Z426" s="4" t="n"/>
       <c r="AB426" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AC426" s="4" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
       <c r="Y427" s="7" t="n"/>
       <c r="Z427" s="7" t="n"/>
       <c r="AB427" s="7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AC427" s="7" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
       <c r="Y428" s="4" t="n"/>
       <c r="Z428" s="4" t="n"/>
       <c r="AB428" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC428" s="4" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
       <c r="Y429" s="7" t="n"/>
       <c r="Z429" s="7" t="n"/>
       <c r="AB429" s="7" t="n">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="AC429" s="7" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
       <c r="Y430" s="4" t="n"/>
       <c r="Z430" s="4" t="n"/>
       <c r="AB430" s="4" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="AC430" s="4" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
       <c r="Y431" s="7" t="n"/>
       <c r="Z431" s="7" t="n"/>
       <c r="AB431" s="7" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AC431" s="7" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       <c r="Y432" s="4" t="n"/>
       <c r="Z432" s="4" t="n"/>
       <c r="AB432" s="4" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="AC432" s="4" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
       <c r="Y439" s="7" t="n"/>
       <c r="Z439" s="7" t="n"/>
       <c r="AB439" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC439" s="7" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
       <c r="Y440" s="4" t="n"/>
       <c r="Z440" s="4" t="n"/>
       <c r="AB440" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC440" s="4" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
       <c r="Y441" s="7" t="n"/>
       <c r="Z441" s="7" t="n"/>
       <c r="AB441" s="7" t="n">
-        <v>332</v>
+        <v>53</v>
       </c>
       <c r="AC441" s="7" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
       <c r="Y442" s="4" t="n"/>
       <c r="Z442" s="4" t="n"/>
       <c r="AB442" s="4" t="n">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="AC442" s="4" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
       <c r="Y443" s="7" t="n"/>
       <c r="Z443" s="7" t="n"/>
       <c r="AB443" s="7" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AC443" s="7" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
       <c r="Y444" s="4" t="n"/>
       <c r="Z444" s="4" t="n"/>
       <c r="AB444" s="4" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="AC444" s="4" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
       <c r="Y447" s="7" t="n"/>
       <c r="Z447" s="7" t="n"/>
       <c r="AB447" s="7" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="AC447" s="7" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
       <c r="Y448" s="4" t="n"/>
       <c r="Z448" s="4" t="n"/>
       <c r="AB448" s="4" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="AC448" s="4" t="inlineStr">
         <is>
@@ -31825,16 +31825,16 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>com.logistics.rider.efood</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -31903,7 +31903,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -31991,7 +31991,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -32225,7 +32225,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -32303,16 +32303,16 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>com.logistics.rider.glovo</t>
+          <t>com.logistics.rider.foodpanda</t>
         </is>
       </c>
     </row>
@@ -32381,7 +32381,7 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodpanda</t>
+          <t>com.logistics.rider.foodora</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>com.logistics.rider.foodora</t>
+          <t>com.logistics.rider.talabat</t>
         </is>
       </c>
     </row>
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>com.logistics.rider.talabat</t>
+          <t>com.logistics.rider.pedidosya</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32615,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>com.logistics.rider.pedidosya</t>
+          <t>com.logistics.rider.hungerstation</t>
         </is>
       </c>
     </row>
@@ -32680,7 +32680,7 @@
         <v>1607</v>
       </c>
       <c r="AB19" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>com.logistics.rider.hungerstation</t>
+          <t>com.logistics.rider.glovo</t>
         </is>
       </c>
     </row>
@@ -32744,19 +32744,6 @@
       <c r="V20" t="n">
         <v>2003</v>
       </c>
-      <c r="AB20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.glovo</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -32808,19 +32795,6 @@
       </c>
       <c r="V21" t="n">
         <v>1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>com.logistics.rider.efood</t>
-        </is>
       </c>
     </row>
     <row r="22">

--- a/consolidation_report/sentry_data.xlsx
+++ b/consolidation_report/sentry_data.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -97,8 +101,13 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -134,11 +143,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -161,6 +214,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,6 +327,34 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Script</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Older values, not recently updated.
+Update manually for accurate AQS score.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Older values, not recently updated.
+Update manually for accurate AQS score.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Older values, not recently updated.
+Update manually for accurate AQS score.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1076,8 +1162,26 @@
         <v/>
       </c>
     </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>⚠  App size, ASTI and STTI